--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="980">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">1.74400758743286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71406757831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167271137238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67215156555176</t>
+    <t xml:space="preserve">1.71406745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6616724729538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67215144634247</t>
   </si>
   <si>
     <t xml:space="preserve">1.64969646930695</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">1.63921761512756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5733494758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49625360965729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48053514957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48203229904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637382984161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460725784302</t>
+    <t xml:space="preserve">1.57334971427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49625384807587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48053526878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48203241825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460713863373</t>
   </si>
   <si>
     <t xml:space="preserve">1.42215216159821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41990673542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41466701030731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41915810108185</t>
+    <t xml:space="preserve">1.41990661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41466724872589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41915833950043</t>
   </si>
   <si>
     <t xml:space="preserve">1.40718221664429</t>
@@ -98,46 +98,46 @@
     <t xml:space="preserve">1.38248157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38472712039948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3982001543045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35703253746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33607459068298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34730219841003</t>
+    <t xml:space="preserve">1.38472723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39820003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35703265666962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607447147369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34730207920074</t>
   </si>
   <si>
     <t xml:space="preserve">1.3428111076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3839784860611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478699207306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38098478317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36975693702698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873935699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4311341047287</t>
+    <t xml:space="preserve">1.38397860527039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478723049164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38098454475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36975717544556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873899936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43113422393799</t>
   </si>
   <si>
     <t xml:space="preserve">1.41017615795135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44535565376282</t>
+    <t xml:space="preserve">1.44535577297211</t>
   </si>
   <si>
     <t xml:space="preserve">1.46257126331329</t>
@@ -146,37 +146,37 @@
     <t xml:space="preserve">1.51197230815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52544558048248</t>
+    <t xml:space="preserve">1.52544546127319</t>
   </si>
   <si>
     <t xml:space="preserve">1.52245128154755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54490637779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191255569458</t>
+    <t xml:space="preserve">1.54490625858307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191243648529</t>
   </si>
   <si>
     <t xml:space="preserve">1.5493973493576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56287050247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60029566287994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60927736759186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173246383667</t>
+    <t xml:space="preserve">1.56287038326263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60029530525208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60927760601044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173270225525</t>
   </si>
   <si>
     <t xml:space="preserve">1.62424755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63023543357849</t>
+    <t xml:space="preserve">1.63023567199707</t>
   </si>
   <si>
     <t xml:space="preserve">1.61676251888275</t>
@@ -191,118 +191,118 @@
     <t xml:space="preserve">1.58682250976562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58831942081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472664356232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66017544269562</t>
+    <t xml:space="preserve">1.58831930160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472652435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017532348633</t>
   </si>
   <si>
     <t xml:space="preserve">1.66915762424469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68712162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69161248207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69310963153839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155261039734</t>
+    <t xml:space="preserve">1.68712151050568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69161260128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69310939311981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155249118805</t>
   </si>
   <si>
     <t xml:space="preserve">1.73502576351166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70358848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.706582903862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909739494324</t>
+    <t xml:space="preserve">1.70358884334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658266544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6990978717804</t>
   </si>
   <si>
     <t xml:space="preserve">1.67664265632629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68412744998932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66766035556793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263065814972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221143722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64670252799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514550685883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69964504241943</t>
+    <t xml:space="preserve">1.68412756919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6676607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263041973114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221167564392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64670264720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514526844025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69964480400085</t>
   </si>
   <si>
     <t xml:space="preserve">1.68433284759521</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69198870658875</t>
+    <t xml:space="preserve">1.69198894500732</t>
   </si>
   <si>
     <t xml:space="preserve">1.72108173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70576977729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6950511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495711803436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72261321544647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65370857715607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208325862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66902077198029</t>
+    <t xml:space="preserve">1.70577001571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69505143165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495699882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72261309623718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65370869636536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208313941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66902089118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.65217733383179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60624086856842</t>
+    <t xml:space="preserve">1.606241106987</t>
   </si>
   <si>
     <t xml:space="preserve">1.56183588504791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5541797876358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202427387238</t>
+    <t xml:space="preserve">1.55417990684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202451229095</t>
   </si>
   <si>
     <t xml:space="preserve">1.53121173381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59092879295349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5289146900177</t>
+    <t xml:space="preserve">1.59092891216278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52891480922699</t>
   </si>
   <si>
     <t xml:space="preserve">1.55111742019653</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">1.4929313659668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47608816623688</t>
+    <t xml:space="preserve">1.4760879278183</t>
   </si>
   <si>
     <t xml:space="preserve">1.52279007434845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46996307373047</t>
+    <t xml:space="preserve">1.46996319293976</t>
   </si>
   <si>
     <t xml:space="preserve">1.47761917114258</t>
@@ -341,16 +341,16 @@
     <t xml:space="preserve">1.56949186325073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62308418750763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66748940944672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136479377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67667675018311</t>
+    <t xml:space="preserve">1.62308442592621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66748976707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136467456818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6766768693924</t>
   </si>
   <si>
     <t xml:space="preserve">1.61542820930481</t>
@@ -359,16 +359,16 @@
     <t xml:space="preserve">1.57714796066284</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58480417728424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63839650154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6338027715683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57561683654785</t>
+    <t xml:space="preserve">1.58480393886566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63839638233185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63380289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57561671733856</t>
   </si>
   <si>
     <t xml:space="preserve">1.54652369022369</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">1.56796085834503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54499244689941</t>
+    <t xml:space="preserve">1.5449925661087</t>
   </si>
   <si>
     <t xml:space="preserve">1.52355563640594</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">1.55877351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58021032810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55264854431152</t>
+    <t xml:space="preserve">1.58021020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55264866352081</t>
   </si>
   <si>
     <t xml:space="preserve">1.53044605255127</t>
@@ -404,40 +404,40 @@
     <t xml:space="preserve">1.51972758769989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50594675540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671231746674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427410125732</t>
+    <t xml:space="preserve">1.50594651699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671219825745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427386283875</t>
   </si>
   <si>
     <t xml:space="preserve">1.56642949581146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57408571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58327305316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59246015548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50211870670319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47532248497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49675965309143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50747764110565</t>
+    <t xml:space="preserve">1.57408547401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58327281475067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59246003627777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5021185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824344158173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47532260417938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49675953388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50747787952423</t>
   </si>
   <si>
     <t xml:space="preserve">1.52968049049377</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">1.60011625289917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58786654472351</t>
+    <t xml:space="preserve">1.58786642551422</t>
   </si>
   <si>
     <t xml:space="preserve">1.56489825248718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56336724758148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255434989929</t>
+    <t xml:space="preserve">1.56336712837219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255446910858</t>
   </si>
   <si>
     <t xml:space="preserve">1.59858500957489</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">1.59399139881134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60470962524414</t>
+    <t xml:space="preserve">1.60470986366272</t>
   </si>
   <si>
     <t xml:space="preserve">1.64758372306824</t>
@@ -473,154 +473,154 @@
     <t xml:space="preserve">1.64605259895325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68280148506165</t>
+    <t xml:space="preserve">1.68280136585236</t>
   </si>
   <si>
     <t xml:space="preserve">1.63074052333832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686537742615</t>
+    <t xml:space="preserve">1.63686513900757</t>
   </si>
   <si>
     <t xml:space="preserve">1.64452147483826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6322717666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66289567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595828533173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026919364929</t>
+    <t xml:space="preserve">1.63227152824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66289591789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595840454102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333156108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026907444</t>
   </si>
   <si>
     <t xml:space="preserve">1.74558138847351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75017488002777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730066299438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423865318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73792517185211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75936257839203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089358329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7838613986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76854956150055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323712825775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486268520355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79151749610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223608016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061052322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754839420319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682969093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520413398743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.858891248703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87726557254791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85429716110229</t>
+    <t xml:space="preserve">1.75017499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730090141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423853397369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7379252910614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75936245918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089334487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78386151790619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76854944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323724746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486304283142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639380931854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7915176153183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223631858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061088085175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8175482749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682981014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520437240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448578834534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889089107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87726533412933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85429739952087</t>
   </si>
   <si>
     <t xml:space="preserve">1.85582864284515</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85123491287231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86654722690582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84970366954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348485946655</t>
+    <t xml:space="preserve">1.85123467445374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86654710769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84970378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348474025726</t>
   </si>
   <si>
     <t xml:space="preserve">1.8527660369873</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83745408058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511005878448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367300987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051644802094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817254543304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923257827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788984298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92167067527771</t>
+    <t xml:space="preserve">1.83745396137238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84511017799377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367289066315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051656723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817218780518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8680784702301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923269748688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788972377777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92167055606842</t>
   </si>
   <si>
     <t xml:space="preserve">1.92932665348053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9247328042984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607601642609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904383182526</t>
+    <t xml:space="preserve">1.92473292350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9660758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904371261597</t>
   </si>
   <si>
     <t xml:space="preserve">1.99823093414307</t>
@@ -629,19 +629,19 @@
     <t xml:space="preserve">2.00894975662231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0074188709259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01201224327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99057531356812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00282454490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00588703155518</t>
+    <t xml:space="preserve">2.00741863250732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01201200485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99057507514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0028247833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0058867931366</t>
   </si>
   <si>
     <t xml:space="preserve">2.09207773208618</t>
@@ -650,403 +650,406 @@
     <t xml:space="preserve">2.09051036834717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11401700973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424258232117</t>
+    <t xml:space="preserve">2.11401724815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424234390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17043280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14692640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15006065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655448913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259717941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1516273021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13909077644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16103029251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04663157463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0528998374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03722929954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04819893836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04506468772888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06543707847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073594093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10774874687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11715078353882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12342000007629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125538825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19393920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647597312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2033417224884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19237232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20804333686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16416430473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13595676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677910804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386995315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02625942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827721595764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805152416229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07640671730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05446743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10461473464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700396537781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566193580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797384262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2409520149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211177110672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2331166267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930708885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31460571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3271427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557582855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38669276237488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467520713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601723670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48541951179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49012088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5214626789093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53870129585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53086590766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168825149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52302980422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53243255615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206016540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5089259147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51362752914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49795651435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638938903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616429328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55123805999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53713417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55437207221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60608625411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70794796943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541096687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70324683189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67347145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406893730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705613136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5872814655304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5982506275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58571410179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57004308700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56220769882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54183554649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5198962688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52929830551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52459692955017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034598350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228526115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43370532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39609527587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975775718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27699589729309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28796529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34908175468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36475300788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064888000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848474502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333293914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43683958053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62489151954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63272666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46818161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36631989479065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.381991147995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251059532166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40549755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42116856575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878764152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363631248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2566237449646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27229428291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28012990951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445889472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558413505554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17043256759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14692640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15006041526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655377388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259741783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15162777900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13909077644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16103005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0466320514679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05290007591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03722906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04819893836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04506468772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06543684005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073594093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10774874687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11715126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12341976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125514984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19393920898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2033417224884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19237208366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20804309844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416454315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946316719055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13595652580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0638701915741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640695571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05446743965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700396537781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566217422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857132911682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24095225334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371411323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117734909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23311638832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930708885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31460571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3271427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38669228553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44467520713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601723670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48541951179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49012088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52146291732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735926628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5387008190155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53086566925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168825149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952340126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52302980422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53243279457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50892615318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51362752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795627593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638938903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5512375831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53713393211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55437207221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60608649253845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70794796943665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108222007751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205138206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541120529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70324635505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67347192764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406869888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981799125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58728122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59825086593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58571410179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57004308700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56220722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54183530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51989579200745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52929854393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52459716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131609916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228526115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43370532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39609527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206894874573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975728034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27699542045593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28796529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34908223152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36475300788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064911842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848474502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333341598511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43683958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62489128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6327269077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.468181848526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36632037162781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38199090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40549778938293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42116832733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363655090332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25662302970886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27229428291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28012990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445889472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528123855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12359809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09955716133118</t>
+    <t xml:space="preserve">2.1235978603363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0995569229126</t>
   </si>
   <si>
     <t xml:space="preserve">2.08352994918823</t>
@@ -1055,58 +1058,58 @@
     <t xml:space="preserve">2.09154319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339436531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750297546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18770670890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29188299179077</t>
+    <t xml:space="preserve">2.01942133903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339460372925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750249862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1877064704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29188275337219</t>
   </si>
   <si>
     <t xml:space="preserve">2.13962483406067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1636655330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14763855934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20373368263245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13161158561707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17167901992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19571995735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17969298362732</t>
+    <t xml:space="preserve">2.16366577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14763879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20373344421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13161134719849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17167949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19572019577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17969274520874</t>
   </si>
   <si>
     <t xml:space="preserve">2.10757088661194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05948901176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07551646232605</t>
+    <t xml:space="preserve">2.05948948860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07551622390747</t>
   </si>
   <si>
     <t xml:space="preserve">2.0354483127594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05147528648376</t>
+    <t xml:space="preserve">2.05147576332092</t>
   </si>
   <si>
     <t xml:space="preserve">2.27585554122925</t>
@@ -1115,7 +1118,7 @@
     <t xml:space="preserve">2.26784205436707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21976041793823</t>
+    <t xml:space="preserve">2.21976065635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.21174716949463</t>
@@ -1124,16 +1127,16 @@
     <t xml:space="preserve">2.24380135536194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23578810691833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22777462005615</t>
+    <t xml:space="preserve">2.23578786849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22777438163757</t>
   </si>
   <si>
     <t xml:space="preserve">2.15565204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30791020393372</t>
+    <t xml:space="preserve">2.30791044235229</t>
   </si>
   <si>
     <t xml:space="preserve">2.0274350643158</t>
@@ -1142,7 +1145,7 @@
     <t xml:space="preserve">2.04346179962158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99538064002991</t>
+    <t xml:space="preserve">1.99538052082062</t>
   </si>
   <si>
     <t xml:space="preserve">1.91524493694305</t>
@@ -1151,7 +1154,7 @@
     <t xml:space="preserve">1.92325830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96332633495331</t>
+    <t xml:space="preserve">1.96332621574402</t>
   </si>
   <si>
     <t xml:space="preserve">1.97133982181549</t>
@@ -1166,19 +1169,19 @@
     <t xml:space="preserve">1.8110682964325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81908178329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8431224822998</t>
+    <t xml:space="preserve">1.81908202171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84312260150909</t>
   </si>
   <si>
     <t xml:space="preserve">1.79504120349884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77901422977448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709562778473</t>
+    <t xml:space="preserve">1.77901387214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709550857544</t>
   </si>
   <si>
     <t xml:space="preserve">1.771000623703</t>
@@ -1190,112 +1193,109 @@
     <t xml:space="preserve">1.69887828826904</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71490550041199</t>
+    <t xml:space="preserve">1.7149053812027</t>
   </si>
   <si>
     <t xml:space="preserve">1.74695980548859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72291886806488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7389463186264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298677921295</t>
+    <t xml:space="preserve">1.72291898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73894619941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298689842224</t>
   </si>
   <si>
     <t xml:space="preserve">1.75497329235077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80305480957031</t>
+    <t xml:space="preserve">1.80305469036102</t>
   </si>
   <si>
     <t xml:space="preserve">1.85914969444275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86716341972351</t>
+    <t xml:space="preserve">1.86716330051422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83510887622833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87517666816711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723145008087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935354709625</t>
+    <t xml:space="preserve">1.87517690658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723121166229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935342788696</t>
   </si>
   <si>
     <t xml:space="preserve">1.93928551673889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02082967758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258134841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97134006023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9878363609314</t>
+    <t xml:space="preserve">2.02082943916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98783648014069</t>
   </si>
   <si>
     <t xml:space="preserve">1.99608469009399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96309173107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9795880317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03732633590698</t>
+    <t xml:space="preserve">1.9630913734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93834662437439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97958827018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0373260974884</t>
   </si>
   <si>
     <t xml:space="preserve">2.0620710849762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0538227558136</t>
+    <t xml:space="preserve">2.05382251739502</t>
   </si>
   <si>
     <t xml:space="preserve">2.09506392478943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16929864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16105008125305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11156010627747</t>
+    <t xml:space="preserve">2.16929888725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16105031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11156058311462</t>
   </si>
   <si>
     <t xml:space="preserve">2.10331201553345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12805724143982</t>
+    <t xml:space="preserve">2.12805700302124</t>
   </si>
   <si>
     <t xml:space="preserve">2.13630533218384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11980867385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14455366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07856774330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22703647613525</t>
+    <t xml:space="preserve">2.1198091506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14455389976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07856726646423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22703671455383</t>
   </si>
   <si>
     <t xml:space="preserve">2.21878814697266</t>
@@ -1304,37 +1304,37 @@
     <t xml:space="preserve">2.25178170204163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24353313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21054005622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26002979278564</t>
+    <t xml:space="preserve">2.24353289604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21054029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26003003120422</t>
   </si>
   <si>
     <t xml:space="preserve">2.26827788352966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33426427841187</t>
+    <t xml:space="preserve">2.33426403999329</t>
   </si>
   <si>
     <t xml:space="preserve">2.30951952934265</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30127143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31776785850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38375425338745</t>
+    <t xml:space="preserve">2.30127120018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31776762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38375401496887</t>
   </si>
   <si>
     <t xml:space="preserve">2.37550568580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32601571083069</t>
+    <t xml:space="preserve">2.32601618766785</t>
   </si>
   <si>
     <t xml:space="preserve">2.27652621269226</t>
@@ -1343,31 +1343,31 @@
     <t xml:space="preserve">2.28477454185486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29302310943604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23528480529785</t>
+    <t xml:space="preserve">2.29302287101746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23528504371643</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200258255005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4497401714325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4332435131073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849876403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42499566078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45798826217651</t>
+    <t xml:space="preserve">2.44974040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4167468547821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43324375152588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849900245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42499542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45798850059509</t>
   </si>
   <si>
     <t xml:space="preserve">2.4992299079895</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">2.47448492050171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5157265663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58996081352234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54871940612793</t>
+    <t xml:space="preserve">2.51572632789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58996105194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54871964454651</t>
   </si>
   <si>
     <t xml:space="preserve">2.4909815788269</t>
@@ -1391,31 +1391,31 @@
     <t xml:space="preserve">2.5074782371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4414918422699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35076069831848</t>
+    <t xml:space="preserve">2.44149208068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35076117515564</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025067329407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19404363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.185795545578</t>
+    <t xml:space="preserve">2.19404315948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18579530715942</t>
   </si>
   <si>
     <t xml:space="preserve">2.045574426651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87236022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264985084534</t>
+    <t xml:space="preserve">1.87236046791077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264973163605</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089806079865</t>
@@ -1430,10 +1430,10 @@
     <t xml:space="preserve">1.64553272724152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64140856266022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62491190433502</t>
+    <t xml:space="preserve">1.64140844345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62491178512573</t>
   </si>
   <si>
     <t xml:space="preserve">1.77338099479675</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">1.78162944316864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74863612651825</t>
+    <t xml:space="preserve">1.74863624572754</t>
   </si>
   <si>
     <t xml:space="preserve">1.80637419223785</t>
@@ -1454,19 +1454,19 @@
     <t xml:space="preserve">2.00433301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81462228298187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812598228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287096977234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84761548042297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111929893494</t>
+    <t xml:space="preserve">1.81462240219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812586307526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84761559963226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111882209778</t>
   </si>
   <si>
     <t xml:space="preserve">1.78987765312195</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">1.91360175609589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8971049785614</t>
+    <t xml:space="preserve">1.89710533618927</t>
   </si>
   <si>
     <t xml:space="preserve">1.90535342693329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95484340190887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907776832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08681583404541</t>
+    <t xml:space="preserve">1.9548431634903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907800674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08681607246399</t>
   </si>
   <si>
     <t xml:space="preserve">2.17754697799683</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">2.07031917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07786917686462</t>
+    <t xml:space="preserve">2.07786893844604</t>
   </si>
   <si>
     <t xml:space="preserve">2.06938791275024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03546380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9845769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609579563141</t>
+    <t xml:space="preserve">2.03546357154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98457682132721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9760959148407</t>
   </si>
   <si>
     <t xml:space="preserve">1.95065248012543</t>
@@ -1520,7 +1520,7 @@
     <t xml:space="preserve">1.99305784702301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06090712547302</t>
+    <t xml:space="preserve">2.06090688705444</t>
   </si>
   <si>
     <t xml:space="preserve">2.02698254585266</t>
@@ -1529,25 +1529,25 @@
     <t xml:space="preserve">2.05242586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04394459724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01002025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0015389919281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89976572990417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88280391693115</t>
+    <t xml:space="preserve">2.04394483566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0100200176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00153923034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89976608753204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88280355930328</t>
   </si>
   <si>
     <t xml:space="preserve">1.89128482341766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01850152015686</t>
+    <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
     <t xml:space="preserve">1.95913350582123</t>
@@ -1556,16 +1556,16 @@
     <t xml:space="preserve">2.08635020256042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875533103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12027454376221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16267991065979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20508527755737</t>
+    <t xml:space="preserve">2.12875556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12027478218079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16267967224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20508551597595</t>
   </si>
   <si>
     <t xml:space="preserve">2.23052906990051</t>
@@ -1583,55 +1583,55 @@
     <t xml:space="preserve">2.35774540901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559409141541</t>
+    <t xml:space="preserve">2.42559385299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.44255638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47648048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46799945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49344277381897</t>
+    <t xml:space="preserve">2.47648072242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46799969673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49344301223755</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43407511711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41711282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888585090637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58673501014709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977248191833</t>
+    <t xml:space="preserve">2.43407487869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4171130657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888632774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58673477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977272033691</t>
   </si>
   <si>
     <t xml:space="preserve">2.54432940483093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57825398445129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56129169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55281066894531</t>
+    <t xml:space="preserve">2.57825374603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56129145622253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55281043052673</t>
   </si>
   <si>
     <t xml:space="preserve">2.53584837913513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52736735343933</t>
+    <t xml:space="preserve">2.52736711502075</t>
   </si>
   <si>
     <t xml:space="preserve">2.64610242843628</t>
@@ -1643,79 +1643,79 @@
     <t xml:space="preserve">2.66306471824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547032356262</t>
+    <t xml:space="preserve">2.70547008514404</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698929786682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62914061546326</t>
+    <t xml:space="preserve">2.62914037704468</t>
   </si>
   <si>
     <t xml:space="preserve">2.71395134925842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73091340065002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77331924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78180003166199</t>
+    <t xml:space="preserve">2.7309136390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77331900596619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78180027008057</t>
   </si>
   <si>
     <t xml:space="preserve">2.84116792678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86661124229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88357305526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90901684761047</t>
+    <t xml:space="preserve">2.86661148071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88357329368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90901660919189</t>
   </si>
   <si>
     <t xml:space="preserve">2.85812973976135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80724334716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75635695457458</t>
+    <t xml:space="preserve">2.80724358558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75635671615601</t>
   </si>
   <si>
     <t xml:space="preserve">2.7393946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74787569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79876255989075</t>
+    <t xml:space="preserve">2.74787592887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79876208305359</t>
   </si>
   <si>
     <t xml:space="preserve">2.79028129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84964871406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268642425537</t>
+    <t xml:space="preserve">2.84964895248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268666267395</t>
   </si>
   <si>
     <t xml:space="preserve">2.82420563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91749787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01078963279724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03623294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95990324020386</t>
+    <t xml:space="preserve">2.9174976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01078987121582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0362331867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95990347862244</t>
   </si>
   <si>
     <t xml:space="preserve">3.07863879203796</t>
@@ -1724,31 +1724,31 @@
     <t xml:space="preserve">3.08711981773376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12104415893555</t>
+    <t xml:space="preserve">3.12104439735413</t>
   </si>
   <si>
     <t xml:space="preserve">3.18041181564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14648747444153</t>
+    <t xml:space="preserve">3.14648723602295</t>
   </si>
   <si>
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281742095947</t>
+    <t xml:space="preserve">3.22281718254089</t>
   </si>
   <si>
     <t xml:space="preserve">3.23129820823669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24826049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433591842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28218507766724</t>
+    <t xml:space="preserve">3.2482602596283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28218483924866</t>
   </si>
   <si>
     <t xml:space="preserve">3.40092039108276</t>
@@ -1766,19 +1766,19 @@
     <t xml:space="preserve">3.29066610336304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27370357513428</t>
+    <t xml:space="preserve">3.27370381355286</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31657671928406</t>
+    <t xml:space="preserve">3.31657695770264</t>
   </si>
   <si>
     <t xml:space="preserve">3.27339220046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35112452507019</t>
+    <t xml:space="preserve">3.35112500190735</t>
   </si>
   <si>
     <t xml:space="preserve">3.34248757362366</t>
@@ -1787,70 +1787,70 @@
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430928230286</t>
+    <t xml:space="preserve">3.39430904388428</t>
   </si>
   <si>
     <t xml:space="preserve">3.44613075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45476770401001</t>
+    <t xml:space="preserve">3.45476746559143</t>
   </si>
   <si>
     <t xml:space="preserve">3.4720413684845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54113674163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60159516334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5929582118988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65341687202454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61023187637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71387529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7829704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80888104438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6966016292572</t>
+    <t xml:space="preserve">3.54113698005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60159540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59295845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65341663360596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61023211479187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71387505531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069029808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78297066688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80888080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69660115242004</t>
   </si>
   <si>
     <t xml:space="preserve">3.62750577926636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.644779920578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73978590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7570595741272</t>
+    <t xml:space="preserve">3.64477968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73978543281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75705933570862</t>
   </si>
   <si>
     <t xml:space="preserve">3.55841064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67932772636414</t>
+    <t xml:space="preserve">3.67932748794556</t>
   </si>
   <si>
     <t xml:space="preserve">3.57568430900574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58432126045227</t>
+    <t xml:space="preserve">3.58432149887085</t>
   </si>
   <si>
     <t xml:space="preserve">3.70523810386658</t>
@@ -1859,16 +1859,16 @@
     <t xml:space="preserve">3.5238630771637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5497739315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48931550979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41158318519592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51522612571716</t>
+    <t xml:space="preserve">3.54977369308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48931527137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41158294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51522636413574</t>
   </si>
   <si>
     <t xml:space="preserve">3.68796420097351</t>
@@ -1877,34 +1877,34 @@
     <t xml:space="preserve">3.74842309951782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66205358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6188690662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86933994293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82615494728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86070275306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91252446174622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99889373779297</t>
+    <t xml:space="preserve">3.66205310821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61886930465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86933970451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8261547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8607029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91252493858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99889397621155</t>
   </si>
   <si>
     <t xml:space="preserve">3.9557089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9902560710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342861175537</t>
+    <t xml:space="preserve">3.99025678634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342837333679</t>
   </si>
   <si>
     <t xml:space="preserve">3.77433323860168</t>
@@ -1913,16 +1913,16 @@
     <t xml:space="preserve">3.76569676399231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92979836463928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661360740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9038872718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8779764175415</t>
+    <t xml:space="preserve">3.92979860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661336898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90388751029968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87797665596008</t>
   </si>
   <si>
     <t xml:space="preserve">3.81751847267151</t>
@@ -1931,10 +1931,10 @@
     <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89525032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93843507766724</t>
+    <t xml:space="preserve">3.89525079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93843483924866</t>
   </si>
   <si>
     <t xml:space="preserve">3.63614320755005</t>
@@ -1943,16 +1943,16 @@
     <t xml:space="preserve">3.4979522228241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885661125183</t>
+    <t xml:space="preserve">3.42885684967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.42021989822388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28202891349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25611877441406</t>
+    <t xml:space="preserve">3.28202939033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2561182975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.24748134613037</t>
@@ -1961,19 +1961,19 @@
     <t xml:space="preserve">3.29930305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26475524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33385062217712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43749380111694</t>
+    <t xml:space="preserve">3.26475548744202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3338508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43749356269836</t>
   </si>
   <si>
     <t xml:space="preserve">3.37703537940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40294623374939</t>
+    <t xml:space="preserve">3.40294599533081</t>
   </si>
   <si>
     <t xml:space="preserve">3.35976147651672</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">3.21293377876282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23020768165588</t>
+    <t xml:space="preserve">3.2302074432373</t>
   </si>
   <si>
     <t xml:space="preserve">3.15247559547424</t>
@@ -1994,7 +1994,7 @@
     <t xml:space="preserve">3.19565987586975</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14383840560913</t>
+    <t xml:space="preserve">3.14383864402771</t>
   </si>
   <si>
     <t xml:space="preserve">2.97973704338074</t>
@@ -2015,16 +2015,16 @@
     <t xml:space="preserve">3.38567209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54223012924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57765245437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56879711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5245189666748</t>
+    <t xml:space="preserve">3.54222989082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57765221595764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56879687309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52451872825623</t>
   </si>
   <si>
     <t xml:space="preserve">3.6130747795105</t>
@@ -2042,16 +2042,16 @@
     <t xml:space="preserve">3.35626292228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33855199813843</t>
+    <t xml:space="preserve">3.33855175971985</t>
   </si>
   <si>
     <t xml:space="preserve">3.34740734100342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26770734786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30312967300415</t>
+    <t xml:space="preserve">3.26770710945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30312943458557</t>
   </si>
   <si>
     <t xml:space="preserve">3.2322850227356</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">3.27656269073486</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3296959400177</t>
+    <t xml:space="preserve">3.32969617843628</t>
   </si>
   <si>
     <t xml:space="preserve">3.32084059715271</t>
@@ -2078,28 +2078,31 @@
     <t xml:space="preserve">3.55108571052551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40939617156982</t>
+    <t xml:space="preserve">3.4093964099884</t>
   </si>
   <si>
     <t xml:space="preserve">3.48909664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53337454795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59536337852478</t>
+    <t xml:space="preserve">3.53337430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59536361694336</t>
   </si>
   <si>
     <t xml:space="preserve">3.5599410533905</t>
   </si>
   <si>
+    <t xml:space="preserve">3.49795198440552</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.46252989768982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36511826515198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41825175285339</t>
+    <t xml:space="preserve">3.36511850357056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41825199127197</t>
   </si>
   <si>
     <t xml:space="preserve">3.3828296661377</t>
@@ -2117,22 +2120,22 @@
     <t xml:space="preserve">3.39168524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24999618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08174014091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14372897148132</t>
+    <t xml:space="preserve">3.24999594688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08173990249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1437292098999</t>
   </si>
   <si>
     <t xml:space="preserve">3.11716246604919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09059572219849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88691759109497</t>
+    <t xml:space="preserve">3.09059548377991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88691735267639</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890642166138</t>
@@ -2141,16 +2144,16 @@
     <t xml:space="preserve">2.84263968467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86920619010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74522829055786</t>
+    <t xml:space="preserve">2.86920642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74522805213928</t>
   </si>
   <si>
     <t xml:space="preserve">2.65667247772217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56811690330505</t>
+    <t xml:space="preserve">2.56811666488647</t>
   </si>
   <si>
     <t xml:space="preserve">2.78950619697571</t>
@@ -2162,7 +2165,7 @@
     <t xml:space="preserve">2.72751688957214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6832389831543</t>
+    <t xml:space="preserve">2.68323922157288</t>
   </si>
   <si>
     <t xml:space="preserve">2.82492852210999</t>
@@ -2180,28 +2183,28 @@
     <t xml:space="preserve">2.97547316551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99318432807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06402897834778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07288455963135</t>
+    <t xml:space="preserve">2.9931845664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0640287399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07288432121277</t>
   </si>
   <si>
     <t xml:space="preserve">3.01975131034851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09945106506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03746247291565</t>
+    <t xml:space="preserve">3.09945130348206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03746223449707</t>
   </si>
   <si>
     <t xml:space="preserve">2.94005084037781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01089549064636</t>
+    <t xml:space="preserve">3.01089572906494</t>
   </si>
   <si>
     <t xml:space="preserve">3.04631781578064</t>
@@ -2210,7 +2213,7 @@
     <t xml:space="preserve">2.98432874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96661782264709</t>
+    <t xml:space="preserve">2.96661758422852</t>
   </si>
   <si>
     <t xml:space="preserve">2.90462851524353</t>
@@ -2219,7 +2222,7 @@
     <t xml:space="preserve">3.00204014778137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93119549751282</t>
+    <t xml:space="preserve">2.93119525909424</t>
   </si>
   <si>
     <t xml:space="preserve">2.78065061569214</t>
@@ -2234,22 +2237,22 @@
     <t xml:space="preserve">2.81607294082642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8780620098114</t>
+    <t xml:space="preserve">2.87806177139282</t>
   </si>
   <si>
     <t xml:space="preserve">3.0286066532135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05517339706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17029571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19686269760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24114036560059</t>
+    <t xml:space="preserve">3.05517315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17029595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19686245918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24114060401917</t>
   </si>
   <si>
     <t xml:space="preserve">3.25885152816772</t>
@@ -2261,22 +2264,22 @@
     <t xml:space="preserve">3.37397408485413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40054059028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47138524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50680780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60421919822693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078570365906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62193036079407</t>
+    <t xml:space="preserve">3.40054082870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47138547897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50680756568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60421943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63078594207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62193059921265</t>
   </si>
   <si>
     <t xml:space="preserve">3.63964152336121</t>
@@ -2291,13 +2294,13 @@
     <t xml:space="preserve">3.72270464897156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77785587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69512867927551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70432114601135</t>
+    <t xml:space="preserve">3.77785563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69512891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70432090759277</t>
   </si>
   <si>
     <t xml:space="preserve">3.78704738616943</t>
@@ -2309,7 +2312,7 @@
     <t xml:space="preserve">3.8146231174469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76866364479065</t>
+    <t xml:space="preserve">3.76866388320923</t>
   </si>
   <si>
     <t xml:space="preserve">3.75028014183044</t>
@@ -2318,19 +2321,16 @@
     <t xml:space="preserve">3.63997769355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64916944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66755342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62159419059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53886699676514</t>
+    <t xml:space="preserve">3.64916968345642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66755318641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62159395217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53886723518372</t>
   </si>
   <si>
     <t xml:space="preserve">3.5572509765625</t>
@@ -2345,10 +2345,10 @@
     <t xml:space="preserve">3.52048349380493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4561402797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49290776252747</t>
+    <t xml:space="preserve">3.45614051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49290800094604</t>
   </si>
   <si>
     <t xml:space="preserve">3.56644296646118</t>
@@ -2360,19 +2360,19 @@
     <t xml:space="preserve">3.60321021080017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51129174232483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85139060020447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84219837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90654182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86058211326599</t>
+    <t xml:space="preserve">3.51129150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85139083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84219861030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90654158592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86058235168457</t>
   </si>
   <si>
     <t xml:space="preserve">3.68593716621399</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">3.74108839035034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58482670783997</t>
+    <t xml:space="preserve">3.58482646942139</t>
   </si>
   <si>
     <t xml:space="preserve">3.65836143493652</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">3.47452425956726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46533250808716</t>
+    <t xml:space="preserve">3.46533226966858</t>
   </si>
   <si>
     <t xml:space="preserve">3.50209975242615</t>
@@ -2402,7 +2402,7 @@
     <t xml:space="preserve">3.94330906867981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9157338142395</t>
+    <t xml:space="preserve">3.91573357582092</t>
   </si>
   <si>
     <t xml:space="preserve">3.95250105857849</t>
@@ -2411,25 +2411,25 @@
     <t xml:space="preserve">3.92492532730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98926877975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83300685882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96169257164001</t>
+    <t xml:space="preserve">3.98926854133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83300709724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96169281005859</t>
   </si>
   <si>
     <t xml:space="preserve">3.87896609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93411755561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97088503837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98007678985596</t>
+    <t xml:space="preserve">3.93411731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97088479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98007655143738</t>
   </si>
   <si>
     <t xml:space="preserve">3.823814868927</t>
@@ -2438,13 +2438,13 @@
     <t xml:space="preserve">3.79623937606812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88815808296204</t>
+    <t xml:space="preserve">3.88815784454346</t>
   </si>
   <si>
     <t xml:space="preserve">3.86977458000183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89734983444214</t>
+    <t xml:space="preserve">3.89734935760498</t>
   </si>
   <si>
     <t xml:space="preserve">4.13633823394775</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">4.20068168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42128562927246</t>
+    <t xml:space="preserve">4.42128610610962</t>
   </si>
   <si>
     <t xml:space="preserve">4.66946649551392</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">4.81653594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9636058807373</t>
+    <t xml:space="preserve">4.96360635757446</t>
   </si>
   <si>
     <t xml:space="preserve">4.85330390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76138496398926</t>
+    <t xml:space="preserve">4.7613844871521</t>
   </si>
   <si>
     <t xml:space="preserve">4.5867395401001</t>
@@ -2516,7 +2516,7 @@
     <t xml:space="preserve">4.90845489501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89007091522217</t>
+    <t xml:space="preserve">4.89007139205933</t>
   </si>
   <si>
     <t xml:space="preserve">5.16600561141968</t>
@@ -2949,6 +2949,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.77999973297119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69999980926514</t>
   </si>
 </sst>
 </file>
@@ -19087,7 +19090,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G608" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19113,7 +19116,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19139,7 +19142,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G610" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19165,7 +19168,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G611" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19191,7 +19194,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G612" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19217,7 +19220,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19243,7 +19246,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G614" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19269,7 +19272,7 @@
         <v>2.5</v>
       </c>
       <c r="G615" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19295,7 +19298,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G616" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19321,7 +19324,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19347,7 +19350,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G618" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19373,7 +19376,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G619" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19399,7 +19402,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G620" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19425,7 +19428,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G621" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19451,7 +19454,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G622" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19477,7 +19480,7 @@
         <v>2.75</v>
       </c>
       <c r="G623" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19503,7 +19506,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G624" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19529,7 +19532,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19555,7 +19558,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G626" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19581,7 +19584,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G627" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19607,7 +19610,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G628" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19633,7 +19636,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19659,7 +19662,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19685,7 +19688,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G631" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19711,7 +19714,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G632" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19737,7 +19740,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19763,7 +19766,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G634" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19789,7 +19792,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G635" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19815,7 +19818,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19841,7 +19844,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G637" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19867,7 +19870,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G638" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19893,7 +19896,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G639" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19919,7 +19922,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G640" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19945,7 +19948,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G641" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -19971,7 +19974,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -19997,7 +20000,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G643" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20023,7 +20026,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20049,7 +20052,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G645" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20075,7 +20078,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G646" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20101,7 +20104,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G647" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20127,7 +20130,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G648" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20153,7 +20156,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G649" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20179,7 +20182,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G650" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20205,7 +20208,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G651" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20231,7 +20234,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20257,7 +20260,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G653" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20283,7 +20286,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20309,7 +20312,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20335,7 +20338,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20361,7 +20364,7 @@
         <v>2.5</v>
       </c>
       <c r="G657" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20387,7 +20390,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G658" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20413,7 +20416,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G659" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20439,7 +20442,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G660" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20465,7 +20468,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G661" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20491,7 +20494,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G662" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20517,7 +20520,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20543,7 +20546,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G664" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20569,7 +20572,7 @@
         <v>2.75</v>
       </c>
       <c r="G665" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20595,7 +20598,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20621,7 +20624,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20647,7 +20650,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G668" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20673,7 +20676,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20699,7 +20702,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20725,7 +20728,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20751,7 +20754,7 @@
         <v>2.75</v>
       </c>
       <c r="G672" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20777,7 +20780,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20803,7 +20806,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20829,7 +20832,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G675" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20855,7 +20858,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G676" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20881,7 +20884,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G677" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20907,7 +20910,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G678" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20933,7 +20936,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G679" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -20959,7 +20962,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G680" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -20985,7 +20988,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21011,7 +21014,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21037,7 +21040,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G683" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21063,7 +21066,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G684" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21089,7 +21092,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G685" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21115,7 +21118,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G686" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21141,7 +21144,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21167,7 +21170,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G688" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21193,7 +21196,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21219,7 +21222,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G690" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21245,7 +21248,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G691" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21271,7 +21274,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G692" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21297,7 +21300,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21323,7 +21326,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G694" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21349,7 +21352,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G695" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21375,7 +21378,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21401,7 +21404,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21427,7 +21430,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G698" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21453,7 +21456,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G699" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21479,7 +21482,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G700" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21505,7 +21508,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G701" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21531,7 +21534,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G702" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21557,7 +21560,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G703" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21583,7 +21586,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G704" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21609,7 +21612,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21635,7 +21638,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21661,7 +21664,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G707" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21687,7 +21690,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G708" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21713,7 +21716,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21739,7 +21742,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G710" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21765,7 +21768,7 @@
         <v>2.5</v>
       </c>
       <c r="G711" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21791,7 +21794,7 @@
         <v>2.5</v>
       </c>
       <c r="G712" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21817,7 +21820,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G713" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21843,7 +21846,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21869,7 +21872,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G715" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21895,7 +21898,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21921,7 +21924,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G717" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21947,7 +21950,7 @@
         <v>2.5</v>
       </c>
       <c r="G718" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -21973,7 +21976,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G719" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -21999,7 +22002,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G720" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22025,7 +22028,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G721" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22051,7 +22054,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G722" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22077,7 +22080,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22103,7 +22106,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G724" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22129,7 +22132,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G725" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22155,7 +22158,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G726" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22181,7 +22184,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G727" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22207,7 +22210,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G728" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22233,7 +22236,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G729" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22259,7 +22262,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G730" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22285,7 +22288,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22311,7 +22314,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G732" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22337,7 +22340,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22363,7 +22366,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22389,7 +22392,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G735" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22415,7 +22418,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G736" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22441,7 +22444,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G737" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22467,7 +22470,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G738" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22493,7 +22496,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G739" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22519,7 +22522,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G740" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22545,7 +22548,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G741" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22571,7 +22574,7 @@
         <v>2.5</v>
       </c>
       <c r="G742" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22597,7 +22600,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G743" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22623,7 +22626,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G744" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22649,7 +22652,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G745" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22675,7 +22678,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G746" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22701,7 +22704,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G747" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22727,7 +22730,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22753,7 +22756,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G749" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22779,7 +22782,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22805,7 +22808,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G751" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22831,7 +22834,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G752" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22857,7 +22860,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22883,7 +22886,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22909,7 +22912,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G755" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22935,7 +22938,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G756" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -22961,7 +22964,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G757" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -22987,7 +22990,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G758" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23013,7 +23016,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G759" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23039,7 +23042,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23065,7 +23068,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G761" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23091,7 +23094,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G762" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23117,7 +23120,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G763" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23143,7 +23146,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G764" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23169,7 +23172,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G765" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23195,7 +23198,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G766" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23221,7 +23224,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G767" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23247,7 +23250,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G768" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23273,7 +23276,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23299,7 +23302,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G770" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23325,7 +23328,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G771" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23351,7 +23354,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G772" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23377,7 +23380,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G773" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23403,7 +23406,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G774" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23429,7 +23432,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G775" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23455,7 +23458,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G776" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23481,7 +23484,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23507,7 +23510,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G778" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23533,7 +23536,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G779" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23559,7 +23562,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G780" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23585,7 +23588,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23611,7 +23614,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23637,7 +23640,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G783" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23663,7 +23666,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G784" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23689,7 +23692,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G785" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23715,7 +23718,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G786" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23741,7 +23744,7 @@
         <v>2.25</v>
       </c>
       <c r="G787" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23767,7 +23770,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G788" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23793,7 +23796,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G789" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23819,7 +23822,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23845,7 +23848,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23871,7 +23874,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G792" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23897,7 +23900,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G793" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23923,7 +23926,7 @@
         <v>2.5</v>
       </c>
       <c r="G794" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23949,7 +23952,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G795" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -23975,7 +23978,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24001,7 +24004,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24027,7 +24030,7 @@
         <v>2.5</v>
       </c>
       <c r="G798" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24053,7 +24056,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G799" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24079,7 +24082,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G800" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24105,7 +24108,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G801" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24131,7 +24134,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G802" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24157,7 +24160,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G803" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24183,7 +24186,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24209,7 +24212,7 @@
         <v>2.5</v>
       </c>
       <c r="G805" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24235,7 +24238,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G806" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24261,7 +24264,7 @@
         <v>2.5</v>
       </c>
       <c r="G807" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24287,7 +24290,7 @@
         <v>2.5</v>
       </c>
       <c r="G808" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24313,7 +24316,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G809" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24339,7 +24342,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G810" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24365,7 +24368,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G811" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24391,7 +24394,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G812" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24417,7 +24420,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G813" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24443,7 +24446,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24469,7 +24472,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G815" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24495,7 +24498,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24521,7 +24524,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G817" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24547,7 +24550,7 @@
         <v>2.5</v>
       </c>
       <c r="G818" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24573,7 +24576,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24599,7 +24602,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G820" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24625,7 +24628,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24651,7 +24654,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G822" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24677,7 +24680,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G823" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24703,7 +24706,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G824" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24729,7 +24732,7 @@
         <v>2.5</v>
       </c>
       <c r="G825" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24755,7 +24758,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24781,7 +24784,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G827" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24807,7 +24810,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G828" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24833,7 +24836,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G829" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24859,7 +24862,7 @@
         <v>2.5</v>
       </c>
       <c r="G830" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24885,7 +24888,7 @@
         <v>2.5</v>
       </c>
       <c r="G831" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24911,7 +24914,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24937,7 +24940,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G833" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -24963,7 +24966,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G834" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -24989,7 +24992,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G835" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25015,7 +25018,7 @@
         <v>2.5</v>
       </c>
       <c r="G836" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25041,7 +25044,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G837" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25067,7 +25070,7 @@
         <v>2.5</v>
       </c>
       <c r="G838" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25093,7 +25096,7 @@
         <v>2.5</v>
       </c>
       <c r="G839" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25119,7 +25122,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25145,7 +25148,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G841" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25171,7 +25174,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G842" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25197,7 +25200,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G843" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25223,7 +25226,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G844" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25249,7 +25252,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25275,7 +25278,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G846" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25301,7 +25304,7 @@
         <v>2.5</v>
       </c>
       <c r="G847" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25327,7 +25330,7 @@
         <v>2.5</v>
       </c>
       <c r="G848" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25353,7 +25356,7 @@
         <v>2.5</v>
       </c>
       <c r="G849" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25379,7 +25382,7 @@
         <v>2.5</v>
       </c>
       <c r="G850" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25405,7 +25408,7 @@
         <v>2.5</v>
       </c>
       <c r="G851" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25431,7 +25434,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25457,7 +25460,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25483,7 +25486,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G854" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25509,7 +25512,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G855" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25535,7 +25538,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G856" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25561,7 +25564,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G857" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25587,7 +25590,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25613,7 +25616,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G859" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25639,7 +25642,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25665,7 +25668,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G861" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25691,7 +25694,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G862" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25769,7 +25772,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G865" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25951,7 +25954,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G872" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26133,7 +26136,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G879" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26159,7 +26162,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G880" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26185,7 +26188,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G881" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -31489,7 +31492,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1085" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32477,7 +32480,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32503,7 +32506,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32581,7 +32584,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1127" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32685,7 +32688,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1131" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32815,7 +32818,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1136" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32945,7 +32948,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1141" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33205,7 +33208,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1151" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33257,7 +33260,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1153" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33283,7 +33286,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1154" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33335,7 +33338,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1156" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34115,7 +34118,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1186" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34193,7 +34196,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1189" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -46881,7 +46884,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1677" t="s">
-        <v>642</v>
+        <v>693</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46907,7 +46910,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1678" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46959,7 +46962,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1680" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46985,7 +46988,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1681" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47115,7 +47118,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1686" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47141,7 +47144,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1687" t="s">
-        <v>642</v>
+        <v>693</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47167,7 +47170,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1688" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47193,7 +47196,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1689" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47271,7 +47274,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1692" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47297,7 +47300,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1693" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47323,7 +47326,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1694" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47401,7 +47404,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1697" t="s">
-        <v>642</v>
+        <v>693</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47427,7 +47430,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1698" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47453,7 +47456,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47479,7 +47482,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1700" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47531,7 +47534,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1702" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47557,7 +47560,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1703" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47583,7 +47586,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1704" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47609,7 +47612,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1705" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47739,7 +47742,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47791,7 +47794,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47817,7 +47820,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1713" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47843,7 +47846,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47869,7 +47872,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1715" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47895,7 +47898,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47921,7 +47924,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1717" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47947,7 +47950,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47973,7 +47976,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -47999,7 +48002,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48025,7 +48028,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48051,7 +48054,7 @@
         <v>3</v>
       </c>
       <c r="G1722" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48077,7 +48080,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1723" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48103,7 +48106,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48129,7 +48132,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1725" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48155,7 +48158,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1726" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48181,7 +48184,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1727" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48207,7 +48210,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48233,7 +48236,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48259,7 +48262,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1730" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48285,7 +48288,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1731" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48311,7 +48314,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48337,7 +48340,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1733" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48363,7 +48366,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1734" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48389,7 +48392,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1735" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48415,7 +48418,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1736" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48441,7 +48444,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1737" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48467,7 +48470,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1738" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48493,7 +48496,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1739" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48519,7 +48522,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1740" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48545,7 +48548,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1741" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48571,7 +48574,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1742" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48597,7 +48600,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48623,7 +48626,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1744" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48649,7 +48652,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1745" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48675,7 +48678,7 @@
         <v>3.5</v>
       </c>
       <c r="G1746" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48701,7 +48704,7 @@
         <v>3.5</v>
       </c>
       <c r="G1747" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48727,7 +48730,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1748" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48753,7 +48756,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1749" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48779,7 +48782,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1750" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48805,7 +48808,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48831,7 +48834,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1752" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48857,7 +48860,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1753" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48883,7 +48886,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1754" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48909,7 +48912,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1755" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48935,7 +48938,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1756" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48961,7 +48964,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1757" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48987,7 +48990,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49013,7 +49016,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1759" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49039,7 +49042,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49065,7 +49068,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1761" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49091,7 +49094,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1762" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49117,7 +49120,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1763" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49143,7 +49146,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1764" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49169,7 +49172,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1765" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49195,7 +49198,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1766" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49221,7 +49224,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1767" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49247,7 +49250,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1768" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49273,7 +49276,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1769" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49299,7 +49302,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1770" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49325,7 +49328,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1771" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49351,7 +49354,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1772" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49377,7 +49380,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1773" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49403,7 +49406,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1774" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49429,7 +49432,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1775" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49455,7 +49458,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1776" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49481,7 +49484,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49507,7 +49510,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1778" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49533,7 +49536,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1779" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49559,7 +49562,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49585,7 +49588,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1781" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49611,7 +49614,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1782" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49637,7 +49640,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49663,7 +49666,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1784" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49689,7 +49692,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1785" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49715,7 +49718,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1786" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49741,7 +49744,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1787" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49767,7 +49770,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49793,7 +49796,7 @@
         <v>3.25</v>
       </c>
       <c r="G1789" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49819,7 +49822,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1790" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49845,7 +49848,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1791" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49871,7 +49874,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1792" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49897,7 +49900,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1793" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49923,7 +49926,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49949,7 +49952,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49975,7 +49978,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1796" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50001,7 +50004,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1797" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50027,7 +50030,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1798" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50053,7 +50056,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1799" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50079,7 +50082,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1800" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50105,7 +50108,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1801" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50131,7 +50134,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50183,7 +50186,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1804" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50209,7 +50212,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1805" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50235,7 +50238,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1806" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50261,7 +50264,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1807" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50287,7 +50290,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1808" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50365,7 +50368,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1811" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50573,7 +50576,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1819" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50755,7 +50758,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1826" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50781,7 +50784,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1827" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50807,7 +50810,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1828" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50859,7 +50862,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1830" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50885,7 +50888,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50911,7 +50914,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1832" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50937,7 +50940,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1833" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50963,7 +50966,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50989,7 +50992,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1835" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51067,7 +51070,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1838" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51223,7 +51226,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1844" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51301,7 +51304,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1847" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51483,7 +51486,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1854" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51509,7 +51512,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51535,7 +51538,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1856" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51587,7 +51590,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1858" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51613,7 +51616,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1859" t="s">
-        <v>642</v>
+        <v>693</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51639,7 +51642,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1860" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51691,7 +51694,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51795,7 +51798,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1866" t="s">
-        <v>642</v>
+        <v>693</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51821,7 +51824,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1867" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51951,7 +51954,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1872" t="s">
-        <v>642</v>
+        <v>693</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52081,7 +52084,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1877" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52133,7 +52136,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1879" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52159,7 +52162,7 @@
         <v>4</v>
       </c>
       <c r="G1880" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52185,7 +52188,7 @@
         <v>4</v>
       </c>
       <c r="G1881" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52211,7 +52214,7 @@
         <v>4</v>
       </c>
       <c r="G1882" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52237,7 +52240,7 @@
         <v>4</v>
       </c>
       <c r="G1883" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52263,7 +52266,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52289,7 +52292,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1885" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52315,7 +52318,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1886" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52341,7 +52344,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52367,7 +52370,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1888" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52393,7 +52396,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1889" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52419,7 +52422,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52445,7 +52448,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1891" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52471,7 +52474,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1892" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52497,7 +52500,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1893" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52523,7 +52526,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1894" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52549,7 +52552,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52575,7 +52578,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1896" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52601,7 +52604,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1897" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52627,7 +52630,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1898" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52653,7 +52656,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1899" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52679,7 +52682,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1900" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52705,7 +52708,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52731,7 +52734,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52757,7 +52760,7 @@
         <v>4</v>
       </c>
       <c r="G1903" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52783,7 +52786,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1904" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52809,7 +52812,7 @@
         <v>4</v>
       </c>
       <c r="G1905" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52835,7 +52838,7 @@
         <v>4</v>
       </c>
       <c r="G1906" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52861,7 +52864,7 @@
         <v>4</v>
       </c>
       <c r="G1907" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52887,7 +52890,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1908" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52913,7 +52916,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1909" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52965,7 +52968,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1911" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53433,7 +53436,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1929" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53537,7 +53540,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1933" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53641,7 +53644,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53667,7 +53670,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1938" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53693,7 +53696,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53719,7 +53722,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1940" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53745,7 +53748,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1941" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53771,7 +53774,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1942" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53823,7 +53826,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1944" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53901,7 +53904,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1947" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53927,7 +53930,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1948" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53953,7 +53956,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1949" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53979,7 +53982,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1950" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54005,7 +54008,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54031,7 +54034,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1952" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54057,7 +54060,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1953" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54083,7 +54086,7 @@
         <v>4</v>
       </c>
       <c r="G1954" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54109,7 +54112,7 @@
         <v>4</v>
       </c>
       <c r="G1955" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54135,7 +54138,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54161,7 +54164,7 @@
         <v>4</v>
       </c>
       <c r="G1957" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54187,7 +54190,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1958" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54811,7 +54814,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1982" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54915,7 +54918,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1986" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55097,7 +55100,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55123,7 +55126,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55201,7 +55204,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1997" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55279,7 +55282,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2000" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55305,7 +55308,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55331,7 +55334,7 @@
         <v>4</v>
       </c>
       <c r="G2002" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55357,7 +55360,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2003" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55409,7 +55412,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2005" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55435,7 +55438,7 @@
         <v>4</v>
       </c>
       <c r="G2006" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55461,7 +55464,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2007" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55487,7 +55490,7 @@
         <v>4</v>
       </c>
       <c r="G2008" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55513,7 +55516,7 @@
         <v>4</v>
       </c>
       <c r="G2009" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55591,7 +55594,7 @@
         <v>4</v>
       </c>
       <c r="G2012" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55617,7 +55620,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2013" t="s">
-        <v>770</v>
+        <v>754</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55643,7 +55646,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2014" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55669,7 +55672,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55695,7 +55698,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55721,7 +55724,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55747,7 +55750,7 @@
         <v>4</v>
       </c>
       <c r="G2018" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55773,7 +55776,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2019" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55799,7 +55802,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2020" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55825,7 +55828,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2021" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55851,7 +55854,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2022" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55877,7 +55880,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2023" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55929,7 +55932,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55955,7 +55958,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55981,7 +55984,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56033,7 +56036,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2029" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56059,7 +56062,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2030" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56085,7 +56088,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2031" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56137,7 +56140,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2033" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56423,7 +56426,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2044" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57073,7 +57076,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2069" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57151,7 +57154,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2072" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57177,7 +57180,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2073" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57255,7 +57258,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2076" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57281,7 +57284,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2077" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -67949,7 +67952,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6495138889</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>113055</v>
@@ -67970,6 +67973,32 @@
         <v>978</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6494097222</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>41717</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>979</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652267456055</t>
+    <t xml:space="preserve">1.73652255535126</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400758743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71406745910645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6616724729538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67215144634247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64969646930695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921761512756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57334971427917</t>
+    <t xml:space="preserve">1.74400794506073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71406757831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167271137238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67215156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64969670772552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57334923744202</t>
   </si>
   <si>
     <t xml:space="preserve">1.49625384807587</t>
@@ -71,43 +71,43 @@
     <t xml:space="preserve">1.48053526878357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48203241825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460713863373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42215216159821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990661621094</t>
+    <t xml:space="preserve">1.48203229904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637382984161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460725784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42215204238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990673542023</t>
   </si>
   <si>
     <t xml:space="preserve">1.41466724872589</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41915833950043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40718221664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38248157501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38472723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39820003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35703265666962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33607447147369</t>
+    <t xml:space="preserve">1.41915810108185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.407182097435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3824816942215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38472712039948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3982001543045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35703241825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607470989227</t>
   </si>
   <si>
     <t xml:space="preserve">1.34730207920074</t>
@@ -116,28 +116,28 @@
     <t xml:space="preserve">1.3428111076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38397860527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478723049164</t>
+    <t xml:space="preserve">1.38397872447968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478711128235</t>
   </si>
   <si>
     <t xml:space="preserve">1.38098454475403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36975717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873899936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113422393799</t>
+    <t xml:space="preserve">1.36975729465485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873911857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4311341047287</t>
   </si>
   <si>
     <t xml:space="preserve">1.41017615795135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44535577297211</t>
+    <t xml:space="preserve">1.44535565376282</t>
   </si>
   <si>
     <t xml:space="preserve">1.46257126331329</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">1.51197230815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52544546127319</t>
+    <t xml:space="preserve">1.5254453420639</t>
   </si>
   <si>
     <t xml:space="preserve">1.52245128154755</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">1.54490625858307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54191243648529</t>
+    <t xml:space="preserve">1.541912317276</t>
   </si>
   <si>
     <t xml:space="preserve">1.5493973493576</t>
@@ -164,94 +164,94 @@
     <t xml:space="preserve">1.56287038326263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60029530525208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60927760601044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173270225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63023567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676251888275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418767929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64370882511139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682250976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58831930160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472652435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66017532348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915762424469</t>
+    <t xml:space="preserve">1.60029554367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60927748680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173258304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424743175507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63023555278778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676239967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418756008148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370858669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682239055634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5883195400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472676277161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017556190491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691575050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68712151050568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69161260128021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69310939311981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155249118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502576351166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358884334564</t>
+    <t xml:space="preserve">1.6916127204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69310963153839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155261039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502588272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358836650848</t>
   </si>
   <si>
     <t xml:space="preserve">1.70658266544342</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6990978717804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664265632629</t>
+    <t xml:space="preserve">1.69909763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67664241790771</t>
   </si>
   <si>
     <t xml:space="preserve">1.68412756919861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6676607131958</t>
+    <t xml:space="preserve">1.66766047477722</t>
   </si>
   <si>
     <t xml:space="preserve">1.68263041973114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64221167564392</t>
+    <t xml:space="preserve">1.64221155643463</t>
   </si>
   <si>
     <t xml:space="preserve">1.64670264720917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67514526844025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69964480400085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68433284759521</t>
+    <t xml:space="preserve">1.67514538764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69964516162872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6843329668045</t>
   </si>
   <si>
     <t xml:space="preserve">1.69198894500732</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">1.72108173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70577001571655</t>
+    <t xml:space="preserve">1.70576977729797</t>
   </si>
   <si>
     <t xml:space="preserve">1.69505143165588</t>
@@ -272,43 +272,43 @@
     <t xml:space="preserve">1.72261309623718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65370869636536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208313941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66902089118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65217733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.606241106987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56183588504791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55417990684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202451229095</t>
+    <t xml:space="preserve">1.65370857715607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66902077198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65217757225037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60624122619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56183576583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5541797876358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202439308167</t>
   </si>
   <si>
     <t xml:space="preserve">1.53121173381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59092891216278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52891480922699</t>
+    <t xml:space="preserve">1.59092915058136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52891492843628</t>
   </si>
   <si>
     <t xml:space="preserve">1.55111742019653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53886783123016</t>
+    <t xml:space="preserve">1.53886771202087</t>
   </si>
   <si>
     <t xml:space="preserve">1.4929313659668</t>
@@ -317,67 +317,67 @@
     <t xml:space="preserve">1.4760879278183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52279007434845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996319293976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589953899384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50058746337891</t>
+    <t xml:space="preserve">1.52278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996295452118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761929035187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058734416962</t>
   </si>
   <si>
     <t xml:space="preserve">1.60777223110199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59705364704132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56949186325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308442592621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66748976707458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136467456818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6766768693924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61542820930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714796066284</t>
+    <t xml:space="preserve">1.5970538854599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56949198246002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308430671692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66748952865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136455535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67667663097382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6154283285141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714807987213</t>
   </si>
   <si>
     <t xml:space="preserve">1.58480393886566</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63839638233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63380289077759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57561671733856</t>
+    <t xml:space="preserve">1.63839650154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63380300998688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
     <t xml:space="preserve">1.54652369022369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56796085834503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5449925661087</t>
+    <t xml:space="preserve">1.56796073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54499232769012</t>
   </si>
   <si>
     <t xml:space="preserve">1.52355563640594</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">1.54193007946014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58174169063568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55877351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58021020889282</t>
+    <t xml:space="preserve">1.58174157142639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55877339839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58021032810211</t>
   </si>
   <si>
     <t xml:space="preserve">1.55264866352081</t>
@@ -401,46 +401,46 @@
     <t xml:space="preserve">1.53044605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51972758769989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50594651699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671219825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427386283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56642949581146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57408547401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58327281475067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59246003627777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5021185874939</t>
+    <t xml:space="preserve">1.5197274684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50594663619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671207904816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427398204803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56642937660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57408559322357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58327293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59246015548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50211882591248</t>
   </si>
   <si>
     <t xml:space="preserve">1.50824344158173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47532260417938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49675953388214</t>
+    <t xml:space="preserve">1.47532248497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49675941467285</t>
   </si>
   <si>
     <t xml:space="preserve">1.50747787952423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52968049049377</t>
+    <t xml:space="preserve">1.52968060970306</t>
   </si>
   <si>
     <t xml:space="preserve">1.60011625289917</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">1.58786642551422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56489825248718</t>
+    <t xml:space="preserve">1.5648980140686</t>
   </si>
   <si>
     <t xml:space="preserve">1.56336712837219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57255446910858</t>
+    <t xml:space="preserve">1.57255423069</t>
   </si>
   <si>
     <t xml:space="preserve">1.59858500957489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59399139881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60470986366272</t>
+    <t xml:space="preserve">1.59399127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60470974445343</t>
   </si>
   <si>
     <t xml:space="preserve">1.64758372306824</t>
@@ -473,58 +473,58 @@
     <t xml:space="preserve">1.64605259895325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68280136585236</t>
+    <t xml:space="preserve">1.68280160427094</t>
   </si>
   <si>
     <t xml:space="preserve">1.63074052333832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452147483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227152824402</t>
+    <t xml:space="preserve">1.63686525821686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452159404755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227164745331</t>
   </si>
   <si>
     <t xml:space="preserve">1.66289591789246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333156108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026907444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558138847351</t>
+    <t xml:space="preserve">1.66595828533173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333191871643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026931285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558126926422</t>
   </si>
   <si>
     <t xml:space="preserve">1.75017499923706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70730090141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423853397369</t>
+    <t xml:space="preserve">1.70730102062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423865318298</t>
   </si>
   <si>
     <t xml:space="preserve">1.7379252910614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75936245918274</t>
+    <t xml:space="preserve">1.75936210155487</t>
   </si>
   <si>
     <t xml:space="preserve">1.76089334487915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78386151790619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76854944229126</t>
+    <t xml:space="preserve">1.78386175632477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76854968070984</t>
   </si>
   <si>
     <t xml:space="preserve">1.75323724746704</t>
@@ -533,535 +533,535 @@
     <t xml:space="preserve">1.73486304283142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73639380931854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7915176153183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223631858826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061088085175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8175482749939</t>
+    <t xml:space="preserve">1.73639404773712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79151737689972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223608016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061052322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81754863262177</t>
   </si>
   <si>
     <t xml:space="preserve">1.80682981014252</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82520437240601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448578834534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889089107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87726533412933</t>
+    <t xml:space="preserve">1.8252044916153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448590755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889065265656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87726545333862</t>
   </si>
   <si>
     <t xml:space="preserve">1.85429739952087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85582864284515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85123467445374</t>
+    <t xml:space="preserve">1.85582888126373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85123491287231</t>
   </si>
   <si>
     <t xml:space="preserve">1.86654710769653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84970378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348474025726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8527660369873</t>
+    <t xml:space="preserve">1.84970366954803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348462104797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85276615619659</t>
   </si>
   <si>
     <t xml:space="preserve">1.83745396137238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84511017799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367289066315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8680784702301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923269748688</t>
+    <t xml:space="preserve">1.84511041641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367312908173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051632881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817254543304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807811260223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923257827759</t>
   </si>
   <si>
     <t xml:space="preserve">1.90788972377777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92167055606842</t>
+    <t xml:space="preserve">1.92167091369629</t>
   </si>
   <si>
     <t xml:space="preserve">1.92932665348053</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92473292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9660758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904371261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894975662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00741863250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01201200485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99057507514954</t>
+    <t xml:space="preserve">1.9247328042984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607577800751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904395103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823129177094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894999504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00741815567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01201224327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99057483673096</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0058867931366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09207773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051036834717</t>
+    <t xml:space="preserve">2.00588703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09207797050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051060676575</t>
   </si>
   <si>
     <t xml:space="preserve">2.11401724815369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08424234390259</t>
+    <t xml:space="preserve">2.08424210548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558413505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17043280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14692616462708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15006041526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655401229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259717941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1516273021698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16103029251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0466320514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290007591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03722882270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04819917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04506492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06543684005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073546409607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10774850845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11715126037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12341952323914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125538825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1939389705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647573471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20334196090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19237208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20804309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16416430473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13595652580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677910804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386995315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02625942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805176258087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07640647888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05446720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10461449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566217422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797384262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2409520149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211177110672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23311686515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781800270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3146059513092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3271427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982653617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3866925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467520713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601723670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48541975021362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49012112617493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52146315574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735878944397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53870105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53086566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168801307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952340126038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52303028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53243279457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206040382385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50892639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51362776756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4979567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638962745667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616453170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653668403625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55123782157898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53713417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55437231063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60608649253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70794796943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541120529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70324683189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67347168922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406941413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705613136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728122711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5982506275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58571410179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57004308700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56220769882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54183506965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51989579200745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52929854393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52459692955017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034598350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4337055683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39609551429749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206894874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27699565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2879650592804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34908199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36475324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064935684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848474502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333317756653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43683981895447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62489151954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6327269077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46818137168884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36632013320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.381991147995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766240119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251059532166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40549778938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42116856575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900395393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878787994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363607406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25662326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27229428291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2801296710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445865631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558437347412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17043280601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14692640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15006065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655448913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259717941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1516273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13909077644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16103029251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04663157463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0528998374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03722929954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04819893836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04506468772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06543707847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073594093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10774874687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11715078353882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12342000007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125538825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19393920898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647597312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2033417224884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19237232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20804333686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416430473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13595676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677910804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06386995315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827721595764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805152416229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640671730042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05446743965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10461473464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700396537781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566193580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2409520149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.211177110672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2331166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930708885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31460571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3271427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557582855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38669276237488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44467520713806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601723670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48541951179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49012088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5214626789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735902786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53870129585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53086590766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168825149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52302980422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53243255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5089259147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51362752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795651435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638938903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55123805999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53713417053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55437207221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60608625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70794796943665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541096687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70324683189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67347145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406893730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705613136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981822967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5872814655304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5982506275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58571410179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57004308700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56220769882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54183554649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5198962688446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52929830551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52459692955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034598350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131609916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228526115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43370532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39609527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975775718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27699589729309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28796529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34908175468445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36475300788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064888000488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848474502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43683958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62489151954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63272666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46818161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36631989479065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.381991147995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251059532166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40549755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42116856575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363631248474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2566237449646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27229428291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28012990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445889472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11558413505554</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.1235978603363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0995569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08352994918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09154319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01942133903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339460372925</t>
+    <t xml:space="preserve">2.09955716133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08352971076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09154343605042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01942157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339388847351</t>
   </si>
   <si>
     <t xml:space="preserve">2.06750249862671</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.16366577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14763879776001</t>
+    <t xml:space="preserve">2.14763832092285</t>
   </si>
   <si>
     <t xml:space="preserve">2.20373344421387</t>
@@ -1088,34 +1088,34 @@
     <t xml:space="preserve">2.13161134719849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17167949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19572019577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17969274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10757088661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05948948860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07551622390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0354483127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05147576332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27585554122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784205436707</t>
+    <t xml:space="preserve">2.17167901992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19571995735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17969298362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10757040977478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05948925018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07551646232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03544855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05147552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27585530281067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784229278564</t>
   </si>
   <si>
     <t xml:space="preserve">2.21976065635681</t>
@@ -1136,55 +1136,55 @@
     <t xml:space="preserve">2.15565204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30791044235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0274350643158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04346179962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99538052082062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524493694305</t>
+    <t xml:space="preserve">2.30791020393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02743482589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04346203804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524469852448</t>
   </si>
   <si>
     <t xml:space="preserve">1.92325830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96332621574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97133982181549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736691474915</t>
+    <t xml:space="preserve">1.96332633495331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736715316772</t>
   </si>
   <si>
     <t xml:space="preserve">2.01140761375427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8110682964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81908202171326</t>
+    <t xml:space="preserve">1.81106841564178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81908190250397</t>
   </si>
   <si>
     <t xml:space="preserve">1.84312260150909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79504120349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901387214661</t>
+    <t xml:space="preserve">1.79504108428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77901411056519</t>
   </si>
   <si>
     <t xml:space="preserve">1.82709550857544</t>
   </si>
   <si>
-    <t xml:space="preserve">1.771000623703</t>
+    <t xml:space="preserve">1.77100026607513</t>
   </si>
   <si>
     <t xml:space="preserve">1.73093259334564</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">1.74695980548859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72291898727417</t>
+    <t xml:space="preserve">1.72291910648346</t>
   </si>
   <si>
     <t xml:space="preserve">1.73894619941711</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76298689842224</t>
+    <t xml:space="preserve">1.76298701763153</t>
   </si>
   <si>
     <t xml:space="preserve">1.75497329235077</t>
@@ -1220,19 +1220,19 @@
     <t xml:space="preserve">1.86716330051422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83510887622833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723121166229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928551673889</t>
+    <t xml:space="preserve">1.83510911464691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8751767873764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723156929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935330867767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9392853975296</t>
   </si>
   <si>
     <t xml:space="preserve">2.02082943916321</t>
@@ -1244,25 +1244,25 @@
     <t xml:space="preserve">1.98783648014069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99608469009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9630913734436</t>
+    <t xml:space="preserve">1.99608480930328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96309149265289</t>
   </si>
   <si>
     <t xml:space="preserve">1.93834662437439</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97958827018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0373260974884</t>
+    <t xml:space="preserve">1.9795880317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03732633590698</t>
   </si>
   <si>
     <t xml:space="preserve">2.0620710849762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05382251739502</t>
+    <t xml:space="preserve">2.0538227558136</t>
   </si>
   <si>
     <t xml:space="preserve">2.09506392478943</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">2.16929888725281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16105031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11156058311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10331201553345</t>
+    <t xml:space="preserve">2.16105008125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11156034469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10331225395203</t>
   </si>
   <si>
     <t xml:space="preserve">2.12805700302124</t>
@@ -1286,37 +1286,37 @@
     <t xml:space="preserve">2.13630533218384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1198091506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14455389976501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07856726646423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22703671455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21878814697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25178170204163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24353289604187</t>
+    <t xml:space="preserve">2.11980867385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14455366134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07856750488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22703647613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21878838539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25178146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24353313446045</t>
   </si>
   <si>
     <t xml:space="preserve">2.21054029464722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26003003120422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26827788352966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33426403999329</t>
+    <t xml:space="preserve">2.26002979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26827812194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33426427841187</t>
   </si>
   <si>
     <t xml:space="preserve">2.30951952934265</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">2.38375401496887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550568580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601618766785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27652621269226</t>
+    <t xml:space="preserve">2.3755054473877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601594924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27652645111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.28477454185486</t>
@@ -1346,22 +1346,22 @@
     <t xml:space="preserve">2.29302287101746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23528504371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200258255005</t>
+    <t xml:space="preserve">2.23528480529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200234413147</t>
   </si>
   <si>
     <t xml:space="preserve">2.44974040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4167468547821</t>
+    <t xml:space="preserve">2.41674709320068</t>
   </si>
   <si>
     <t xml:space="preserve">2.43324375152588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40849900245667</t>
+    <t xml:space="preserve">2.40849876403809</t>
   </si>
   <si>
     <t xml:space="preserve">2.42499542236328</t>
@@ -1373,76 +1373,76 @@
     <t xml:space="preserve">2.4992299079895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47448492050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51572632789612</t>
+    <t xml:space="preserve">2.47448515892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5157265663147</t>
   </si>
   <si>
     <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871964454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4909815788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5074782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44149208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35076117515564</t>
+    <t xml:space="preserve">2.54871940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49098181724548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50747799873352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4414918422699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35076093673706</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025067329407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19404315948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18579530715942</t>
+    <t xml:space="preserve">2.19404363632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18579506874084</t>
   </si>
   <si>
     <t xml:space="preserve">2.045574426651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87236046791077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264973163605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089806079865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56717383861542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71564292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64553272724152</t>
+    <t xml:space="preserve">1.8723601102829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8806084394455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264985084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089818000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56717395782471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71564280986786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64553248882294</t>
   </si>
   <si>
     <t xml:space="preserve">1.64140844345093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62491178512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77338099479675</t>
+    <t xml:space="preserve">1.62491190433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77338111400604</t>
   </si>
   <si>
     <t xml:space="preserve">1.78162944316864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74863624572754</t>
+    <t xml:space="preserve">1.74863588809967</t>
   </si>
   <si>
     <t xml:space="preserve">1.80637419223785</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">1.86411201953888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00433301925659</t>
+    <t xml:space="preserve">2.00433278083801</t>
   </si>
   <si>
     <t xml:space="preserve">1.81462240219116</t>
@@ -1463,43 +1463,43 @@
     <t xml:space="preserve">1.82287073135376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84761559963226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111882209778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78987765312195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360175609589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710533618927</t>
+    <t xml:space="preserve">1.84761536121368</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111894130707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78987777233124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885676860809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8971049785614</t>
   </si>
   <si>
     <t xml:space="preserve">1.90535342693329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548431634903</t>
+    <t xml:space="preserve">1.95484340190887</t>
   </si>
   <si>
     <t xml:space="preserve">2.02907800674438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08681607246399</t>
+    <t xml:space="preserve">2.08681559562683</t>
   </si>
   <si>
     <t xml:space="preserve">2.17754697799683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07031917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07786893844604</t>
+    <t xml:space="preserve">2.07031941413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07786870002747</t>
   </si>
   <si>
     <t xml:space="preserve">2.06938791275024</t>
@@ -1508,16 +1508,16 @@
     <t xml:space="preserve">2.03546357154846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98457682132721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9760959148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065248012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99305784702301</t>
+    <t xml:space="preserve">1.98457705974579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609603404999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065236091614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9930579662323</t>
   </si>
   <si>
     <t xml:space="preserve">2.06090688705444</t>
@@ -1532,25 +1532,25 @@
     <t xml:space="preserve">2.04394483566284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0100200176239</t>
+    <t xml:space="preserve">2.01002025604248</t>
   </si>
   <si>
     <t xml:space="preserve">2.00153923034668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89976608753204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88280355930328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128482341766</t>
+    <t xml:space="preserve">1.89976584911346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88280379772186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128494262695</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95913350582123</t>
+    <t xml:space="preserve">1.95913338661194</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
@@ -1559,37 +1559,37 @@
     <t xml:space="preserve">2.12875556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12027478218079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16267967224121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20508551597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23052906990051</t>
+    <t xml:space="preserve">2.12027454376221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16268014907837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20508575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23052883148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.3068585395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33230185508728</t>
+    <t xml:space="preserve">2.33230209350586</t>
   </si>
   <si>
     <t xml:space="preserve">2.34926414489746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35774540901184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42559385299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47648072242737</t>
+    <t xml:space="preserve">2.35774517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42559409141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255661964417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47648048400879</t>
   </si>
   <si>
     <t xml:space="preserve">2.46799969673157</t>
@@ -1601,19 +1601,19 @@
     <t xml:space="preserve">2.51040506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43407487869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4171130657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888632774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58673477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977272033691</t>
+    <t xml:space="preserve">2.43407535552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41711258888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888608932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58673453330994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977248191833</t>
   </si>
   <si>
     <t xml:space="preserve">2.54432940483093</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">2.56129145622253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55281043052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53584837913513</t>
+    <t xml:space="preserve">2.55281066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53584814071655</t>
   </si>
   <si>
     <t xml:space="preserve">2.52736711502075</t>
@@ -1637,19 +1637,19 @@
     <t xml:space="preserve">2.64610242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63762164115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66306471824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70547008514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69698929786682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62914037704468</t>
+    <t xml:space="preserve">2.63762140274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66306519508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70547032356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69698905944824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6291401386261</t>
   </si>
   <si>
     <t xml:space="preserve">2.71395134925842</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">2.7309136390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77331900596619</t>
+    <t xml:space="preserve">2.77331924438477</t>
   </si>
   <si>
     <t xml:space="preserve">2.78180027008057</t>
@@ -1667,40 +1667,40 @@
     <t xml:space="preserve">2.84116792678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86661148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88357329368591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90901660919189</t>
+    <t xml:space="preserve">2.86661100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88357353210449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90901684761047</t>
   </si>
   <si>
     <t xml:space="preserve">2.85812973976135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80724358558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75635671615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7393946647644</t>
+    <t xml:space="preserve">2.80724334716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75635695457458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939442634583</t>
   </si>
   <si>
     <t xml:space="preserve">2.74787592887878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79876208305359</t>
+    <t xml:space="preserve">2.79876232147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.79028129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84964895248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268666267395</t>
+    <t xml:space="preserve">2.84964871406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268690109253</t>
   </si>
   <si>
     <t xml:space="preserve">2.82420563697815</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">3.01078987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0362331867218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95990347862244</t>
+    <t xml:space="preserve">3.03623294830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95990324020386</t>
   </si>
   <si>
     <t xml:space="preserve">3.07863879203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08711981773376</t>
+    <t xml:space="preserve">3.08711957931519</t>
   </si>
   <si>
     <t xml:space="preserve">3.12104439735413</t>
@@ -1736,31 +1736,31 @@
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281718254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23129820823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2482602596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28218483924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40092039108276</t>
+    <t xml:space="preserve">3.22281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23129844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24826049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433615684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28218507766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40092062950134</t>
   </si>
   <si>
     <t xml:space="preserve">3.42636346817017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36699604988098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31610941886902</t>
+    <t xml:space="preserve">3.3669958114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31610918045044</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066610336304</t>
@@ -1769,19 +1769,19 @@
     <t xml:space="preserve">3.27370381355286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3079400062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31657695770264</t>
+    <t xml:space="preserve">3.30794024467468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31657671928406</t>
   </si>
   <si>
     <t xml:space="preserve">3.27339220046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35112500190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34248757362366</t>
+    <t xml:space="preserve">3.35112476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34248733520508</t>
   </si>
   <si>
     <t xml:space="preserve">3.36839842796326</t>
@@ -1796,88 +1796,88 @@
     <t xml:space="preserve">3.45476746559143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4720413684845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54113698005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60159540176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59295845031738</t>
+    <t xml:space="preserve">3.47204160690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54113674163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60159516334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5929582118988</t>
   </si>
   <si>
     <t xml:space="preserve">3.65341663360596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61023211479187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71387505531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069029808044</t>
+    <t xml:space="preserve">3.61023187637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71387553215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6706907749176</t>
   </si>
   <si>
     <t xml:space="preserve">3.78297066688538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80888080596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69660115242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62750577926636</t>
+    <t xml:space="preserve">3.8088812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6966016292572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62750601768494</t>
   </si>
   <si>
     <t xml:space="preserve">3.64477968215942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73978543281555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75705933570862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55841064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67932748794556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57568430900574</t>
+    <t xml:space="preserve">3.73978567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7570595741272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55841016769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67932772636414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57568454742432</t>
   </si>
   <si>
     <t xml:space="preserve">3.58432149887085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70523810386658</t>
+    <t xml:space="preserve">3.705237865448</t>
   </si>
   <si>
     <t xml:space="preserve">3.5238630771637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54977369308472</t>
+    <t xml:space="preserve">3.5497739315033</t>
   </si>
   <si>
     <t xml:space="preserve">3.48931527137756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41158294677734</t>
+    <t xml:space="preserve">3.41158318519592</t>
   </si>
   <si>
     <t xml:space="preserve">3.51522636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68796420097351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74842309951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66205310821533</t>
+    <t xml:space="preserve">3.68796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74842286109924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66205334663391</t>
   </si>
   <si>
     <t xml:space="preserve">3.61886930465698</t>
@@ -1886,34 +1886,34 @@
     <t xml:space="preserve">3.86933970451355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8261547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8607029914856</t>
+    <t xml:space="preserve">3.82615494728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86070275306702</t>
   </si>
   <si>
     <t xml:space="preserve">3.91252493858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99889397621155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9557089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99025678634644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342837333679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77433323860168</t>
+    <t xml:space="preserve">3.99889373779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95570874214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99025630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77433347702026</t>
   </si>
   <si>
     <t xml:space="preserve">3.76569676399231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92979860305786</t>
+    <t xml:space="preserve">3.9297981262207</t>
   </si>
   <si>
     <t xml:space="preserve">3.88661336898804</t>
@@ -1922,7 +1922,7 @@
     <t xml:space="preserve">3.90388751029968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87797665596008</t>
+    <t xml:space="preserve">3.8779764175415</t>
   </si>
   <si>
     <t xml:space="preserve">3.81751847267151</t>
@@ -1931,187 +1931,187 @@
     <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89525079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93843483924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63614320755005</t>
+    <t xml:space="preserve">3.89525032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93843507766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63614273071289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49795246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42885684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021989822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28202939033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2561182975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24748158454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29930281639099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26475524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3338508605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43749380111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37703537940979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40294599533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3597617149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2129340171814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23020768165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15247559547424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11792778968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19566011428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14383864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97973728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06610584259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53249979019165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56704759597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46340465545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3856725692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54223012924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57765245437622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56879687309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5245189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6130747795105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58650803565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.294273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31198501586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35626292228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33855175971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34740734100342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26770710945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30312943458557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2322850227356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27656269073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32969617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32084059715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28541827201843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42710757255554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51566338539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55108571052551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4093964099884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48909664154053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53337430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59536361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55994129180908</t>
   </si>
   <si>
     <t xml:space="preserve">3.4979522228241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885684967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021989822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28202939033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2561182975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24748134613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29930305480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26475548744202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3338508605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43749356269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37703537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40294599533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35976147651672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21293377876282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2302074432373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15247559547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11792778968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19565987586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14383864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97973704338074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06610608100891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53250002861023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56704759597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46340465545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38567209243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54222989082336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57765221595764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56879687309265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52451872825623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6130747795105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58650803565979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.294273853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31198501586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35626292228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33855175971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34740734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26770710945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30312943458557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2322850227356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27656269073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32969617843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32084059715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28541827201843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42710757255554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51566314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55108571052551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4093964099884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48909664154053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53337430953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59536361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5599410533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49795198440552</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.46252989768982</t>
   </si>
   <si>
     <t xml:space="preserve">3.36511850357056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41825199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3828296661377</t>
+    <t xml:space="preserve">3.41825175285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38282942771912</t>
   </si>
   <si>
     <t xml:space="preserve">3.44481873512268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45367431640625</t>
+    <t xml:space="preserve">3.45367407798767</t>
   </si>
   <si>
     <t xml:space="preserve">3.48024106025696</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">3.1437292098999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11716246604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09059548377991</t>
+    <t xml:space="preserve">3.11716222763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09059572219849</t>
   </si>
   <si>
     <t xml:space="preserve">2.88691735267639</t>
@@ -2144,7 +2144,7 @@
     <t xml:space="preserve">2.84263968467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86920642852783</t>
+    <t xml:space="preserve">2.86920619010925</t>
   </si>
   <si>
     <t xml:space="preserve">2.74522805213928</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">2.65667247772217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56811666488647</t>
+    <t xml:space="preserve">2.56811690330505</t>
   </si>
   <si>
     <t xml:space="preserve">2.78950619697571</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">2.75408363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72751688957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68323922157288</t>
+    <t xml:space="preserve">2.72751712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6832389831543</t>
   </si>
   <si>
     <t xml:space="preserve">2.82492852210999</t>
@@ -2189,16 +2189,16 @@
     <t xml:space="preserve">3.0640287399292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07288432121277</t>
+    <t xml:space="preserve">3.07288455963135</t>
   </si>
   <si>
     <t xml:space="preserve">3.01975131034851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09945130348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03746223449707</t>
+    <t xml:space="preserve">3.09945106506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03746247291565</t>
   </si>
   <si>
     <t xml:space="preserve">2.94005084037781</t>
@@ -2237,19 +2237,19 @@
     <t xml:space="preserve">2.81607294082642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87806177139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0286066532135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05517315864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17029595375061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19686245918274</t>
+    <t xml:space="preserve">2.8780620098114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02860689163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05517339706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17029571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19686269760132</t>
   </si>
   <si>
     <t xml:space="preserve">3.24114060401917</t>
@@ -2264,25 +2264,25 @@
     <t xml:space="preserve">3.37397408485413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40054082870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47138547897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50680756568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60421943664551</t>
+    <t xml:space="preserve">3.40054059028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47138524055481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50680780410767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60421919822693</t>
   </si>
   <si>
     <t xml:space="preserve">3.63078594207764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62193059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63964152336121</t>
+    <t xml:space="preserve">3.62193036079407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63964128494263</t>
   </si>
   <si>
     <t xml:space="preserve">3.67674517631531</t>
@@ -67978,7 +67978,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6494097222</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>41717</v>
@@ -67999,6 +67999,32 @@
         <v>979</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6503125</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>107762</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>976</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="981" uniqueCount="981">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="982">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652243614197</t>
+    <t xml:space="preserve">1.73652279376984</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400770664215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71406769752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167271137238</t>
+    <t xml:space="preserve">1.74400782585144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71406757831573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6616724729538</t>
   </si>
   <si>
     <t xml:space="preserve">1.67215144634247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969658851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921749591827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5733494758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49625396728516</t>
+    <t xml:space="preserve">1.64969646930695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921761512756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57334935665131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49625372886658</t>
   </si>
   <si>
     <t xml:space="preserve">1.48053526878357</t>
@@ -74,7 +74,7 @@
     <t xml:space="preserve">1.48203229904175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43637371063232</t>
+    <t xml:space="preserve">1.4363739490509</t>
   </si>
   <si>
     <t xml:space="preserve">1.44460713863373</t>
@@ -83,55 +83,55 @@
     <t xml:space="preserve">1.42215216159821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41990673542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41466724872589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41915810108185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40718221664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38248157501221</t>
+    <t xml:space="preserve">1.41990685462952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41466736793518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41915833950043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40718197822571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38248181343079</t>
   </si>
   <si>
     <t xml:space="preserve">1.38472723960876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39820027351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35703277587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33607447147369</t>
+    <t xml:space="preserve">1.3982001543045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35703253746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607459068298</t>
   </si>
   <si>
     <t xml:space="preserve">1.34730207920074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34281122684479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397872447968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478711128235</t>
+    <t xml:space="preserve">1.3428111076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3839784860611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478699207306</t>
   </si>
   <si>
     <t xml:space="preserve">1.38098454475403</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36975717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113422393799</t>
+    <t xml:space="preserve">1.36975705623627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873935699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4311341047287</t>
   </si>
   <si>
     <t xml:space="preserve">1.41017615795135</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">1.44535577297211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46257138252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51197218894958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52544546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52245116233826</t>
+    <t xml:space="preserve">1.46257126331329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51197230815887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5254453420639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52245128154755</t>
   </si>
   <si>
     <t xml:space="preserve">1.54490637779236</t>
@@ -170,100 +170,100 @@
     <t xml:space="preserve">1.60927748680115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63173258304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424767017365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63023555278778</t>
+    <t xml:space="preserve">1.63173246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424743175507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63023543357849</t>
   </si>
   <si>
     <t xml:space="preserve">1.61676263809204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65418744087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64370858669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682239055634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58831942081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472676277161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66017532348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915738582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6916127204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6931095123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155284881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502552509308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358860492706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909775257111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68412744998932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66766059398651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263041973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221143722534</t>
+    <t xml:space="preserve">1.65418779850006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370846748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682227134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58831930160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472664356232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017544269562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691575050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712151050568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69161283969879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69310963153839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155261039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502576351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358848571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658266544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67664229869843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68412756919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66766047477722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263030052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221155643463</t>
   </si>
   <si>
     <t xml:space="preserve">1.64670252799988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6751457452774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69964504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6843329668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69198882579803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7210818529129</t>
+    <t xml:space="preserve">1.67514562606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69964492321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68433272838593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69198894500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72108173370361</t>
   </si>
   <si>
     <t xml:space="preserve">1.70576977729797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69505143165588</t>
+    <t xml:space="preserve">1.6950511932373</t>
   </si>
   <si>
     <t xml:space="preserve">1.71495699882507</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">1.72261309623718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65370881557465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208349704742</t>
+    <t xml:space="preserve">1.65370857715607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208325862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.66902077198029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65217757225037</t>
+    <t xml:space="preserve">1.65217745304108</t>
   </si>
   <si>
     <t xml:space="preserve">1.606241106987</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">1.5541797876358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52202427387238</t>
+    <t xml:space="preserve">1.52202439308167</t>
   </si>
   <si>
     <t xml:space="preserve">1.53121161460876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59092903137207</t>
+    <t xml:space="preserve">1.59092915058136</t>
   </si>
   <si>
     <t xml:space="preserve">1.52891480922699</t>
@@ -308,37 +308,37 @@
     <t xml:space="preserve">1.55111742019653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53886759281158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4929313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47608780860901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52278983592987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996331214905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50058734416962</t>
+    <t xml:space="preserve">1.53886771202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49293148517609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608816623688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52279007434845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761929035187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589941978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058746337891</t>
   </si>
   <si>
     <t xml:space="preserve">1.60777223110199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59705376625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56949174404144</t>
+    <t xml:space="preserve">1.5970538854599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56949186325073</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308430671692</t>
@@ -347,13 +347,13 @@
     <t xml:space="preserve">1.66748952865601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66136479377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67667663097382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61542844772339</t>
+    <t xml:space="preserve">1.66136467456818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67667698860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6154283285141</t>
   </si>
   <si>
     <t xml:space="preserve">1.57714796066284</t>
@@ -362,31 +362,31 @@
     <t xml:space="preserve">1.58480405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63839638233185</t>
+    <t xml:space="preserve">1.63839650154114</t>
   </si>
   <si>
     <t xml:space="preserve">1.63380289077759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57561683654785</t>
+    <t xml:space="preserve">1.57561695575714</t>
   </si>
   <si>
     <t xml:space="preserve">1.54652380943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56796073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54499220848083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355563640594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54192996025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58174157142639</t>
+    <t xml:space="preserve">1.56796085834503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54499232769012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355575561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54193007946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174169063568</t>
   </si>
   <si>
     <t xml:space="preserve">1.55877351760864</t>
@@ -401,25 +401,25 @@
     <t xml:space="preserve">1.53044605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51972734928131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50594675540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671219825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427398204803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56642937660217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57408547401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58327269554138</t>
+    <t xml:space="preserve">1.51972770690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50594663619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671231746674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56642949581146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57408571243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58327281475067</t>
   </si>
   <si>
     <t xml:space="preserve">1.59246015548706</t>
@@ -428,16 +428,16 @@
     <t xml:space="preserve">1.50211870670319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50824344158173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4753223657608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49675929546356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50747787952423</t>
+    <t xml:space="preserve">1.50824356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47532260417938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49675941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50747776031494</t>
   </si>
   <si>
     <t xml:space="preserve">1.52968049049377</t>
@@ -446,28 +446,28 @@
     <t xml:space="preserve">1.60011625289917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58786654472351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489837169647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56336724758148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255411148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59858500957489</t>
+    <t xml:space="preserve">1.58786642551422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489825248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5633670091629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255423069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5985848903656</t>
   </si>
   <si>
     <t xml:space="preserve">1.59399139881134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60470974445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64758372306824</t>
+    <t xml:space="preserve">1.60470962524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64758384227753</t>
   </si>
   <si>
     <t xml:space="preserve">1.64605247974396</t>
@@ -476,19 +476,19 @@
     <t xml:space="preserve">1.68280160427094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63074040412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63686537742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452147483826</t>
+    <t xml:space="preserve">1.63074052333832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63686513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452135562897</t>
   </si>
   <si>
     <t xml:space="preserve">1.63227164745331</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66289579868317</t>
+    <t xml:space="preserve">1.66289591789246</t>
   </si>
   <si>
     <t xml:space="preserve">1.66595828533173</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">1.73333168029785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73026919364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558138847351</t>
+    <t xml:space="preserve">1.73026931285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558126926422</t>
   </si>
   <si>
     <t xml:space="preserve">1.75017488002777</t>
@@ -509,133 +509,133 @@
     <t xml:space="preserve">1.70730090141296</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70423877239227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73792541027069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75936222076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089346408844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78386163711548</t>
+    <t xml:space="preserve">1.70423865318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73792517185211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75936245918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089358329773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78386151790619</t>
   </si>
   <si>
     <t xml:space="preserve">1.76854956150055</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75323736667633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486292362213</t>
+    <t xml:space="preserve">1.75323748588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486280441284</t>
   </si>
   <si>
     <t xml:space="preserve">1.73639392852783</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7915176153183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223608016968</t>
+    <t xml:space="preserve">1.79151737689972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223643779755</t>
   </si>
   <si>
     <t xml:space="preserve">1.82061076164246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8175482749939</t>
+    <t xml:space="preserve">1.81754863262177</t>
   </si>
   <si>
     <t xml:space="preserve">1.80682969093323</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82520461082458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448566913605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889077186584</t>
+    <t xml:space="preserve">1.8252044916153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448590755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889101028442</t>
   </si>
   <si>
     <t xml:space="preserve">1.87726557254791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85429739952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582864284515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8512350320816</t>
+    <t xml:space="preserve">1.85429716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582852363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85123491287231</t>
   </si>
   <si>
     <t xml:space="preserve">1.86654722690582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84970378875732</t>
+    <t xml:space="preserve">1.84970331192017</t>
   </si>
   <si>
     <t xml:space="preserve">1.86348450183868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85276591777802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745396137238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511005878448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367289066315</t>
+    <t xml:space="preserve">1.8527660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745408058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84511017799377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367312908173</t>
   </si>
   <si>
     <t xml:space="preserve">1.84051656723022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84817230701447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807823181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9492324590683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788960456848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92167067527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932665348053</t>
+    <t xml:space="preserve">1.84817242622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807835102081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923233985901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90789020061493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92167043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932677268982</t>
   </si>
   <si>
     <t xml:space="preserve">1.92473292350769</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96607565879822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904418945312</t>
+    <t xml:space="preserve">1.96607601642609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904359340668</t>
   </si>
   <si>
     <t xml:space="preserve">1.99823141098022</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894951820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00741863250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01201200485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99057495594025</t>
+    <t xml:space="preserve">2.00894999504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0074188709259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01201224327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99057483673096</t>
   </si>
   <si>
     <t xml:space="preserve">2.00282454490662</t>
@@ -647,58 +647,58 @@
     <t xml:space="preserve">2.0920774936676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09051036834717</t>
+    <t xml:space="preserve">2.09051060676575</t>
   </si>
   <si>
     <t xml:space="preserve">2.11401700973511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08424234390259</t>
+    <t xml:space="preserve">2.08424258232117</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558437347412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17043280601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14692616462708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15006065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655401229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259694099426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15162777900696</t>
+    <t xml:space="preserve">2.17043256759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14692640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15006017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655377388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259741783142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15162754058838</t>
   </si>
   <si>
     <t xml:space="preserve">2.1390905380249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16103005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04663157463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05290007591248</t>
+    <t xml:space="preserve">2.16102981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0466320514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290031433105</t>
   </si>
   <si>
     <t xml:space="preserve">2.03722906112671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04819893836975</t>
+    <t xml:space="preserve">2.04819869995117</t>
   </si>
   <si>
     <t xml:space="preserve">2.04506492614746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06543707847595</t>
+    <t xml:space="preserve">2.06543684005737</t>
   </si>
   <si>
     <t xml:space="preserve">2.06073570251465</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">2.10774850845337</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1171510219574</t>
+    <t xml:space="preserve">2.11715126037598</t>
   </si>
   <si>
     <t xml:space="preserve">2.12341952323914</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">2.18296957015991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19393920898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647573471069</t>
+    <t xml:space="preserve">2.1939389705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647597312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.20334196090698</t>
@@ -731,13 +731,13 @@
     <t xml:space="preserve">2.19237232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20804309844971</t>
+    <t xml:space="preserve">2.20804286003113</t>
   </si>
   <si>
     <t xml:space="preserve">2.16416430473328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15946269035339</t>
+    <t xml:space="preserve">2.15946316719055</t>
   </si>
   <si>
     <t xml:space="preserve">2.13595652580261</t>
@@ -746,58 +746,58 @@
     <t xml:space="preserve">2.09677910804749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06386971473694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02625942230225</t>
+    <t xml:space="preserve">2.06386995315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0262598991394</t>
   </si>
   <si>
     <t xml:space="preserve">1.96827697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99805176258087</t>
+    <t xml:space="preserve">1.99805188179016</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640671730042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05446743965149</t>
+    <t xml:space="preserve">2.05446720123291</t>
   </si>
   <si>
     <t xml:space="preserve">2.10461497306824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06700396537781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566241264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954120635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2409520149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117734909058</t>
+    <t xml:space="preserve">2.06700420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566217422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857132911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797408103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24095225334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371435165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211177110672</t>
   </si>
   <si>
     <t xml:space="preserve">2.23311686515808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23781800270081</t>
+    <t xml:space="preserve">2.23781776428223</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930732727051</t>
@@ -809,19 +809,19 @@
     <t xml:space="preserve">2.32714247703552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32557559013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38669276237488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44467496871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601747512817</t>
+    <t xml:space="preserve">2.32557535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982701301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38669228553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467520713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601723670959</t>
   </si>
   <si>
     <t xml:space="preserve">2.48541975021362</t>
@@ -830,52 +830,52 @@
     <t xml:space="preserve">2.49012088775635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52146291732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735878944397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53870129585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53086566925049</t>
+    <t xml:space="preserve">2.52146315574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53870105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53086543083191</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168825149536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50422501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52303004264832</t>
+    <t xml:space="preserve">2.50422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952340126038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52302980422974</t>
   </si>
   <si>
     <t xml:space="preserve">2.53243279457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51206040382385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50892639160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51362776756287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4979567527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638962745667</t>
+    <t xml:space="preserve">2.51206064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50892615318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51362729072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49795651435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638938903809</t>
   </si>
   <si>
     <t xml:space="preserve">2.52616453170776</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5465362071991</t>
+    <t xml:space="preserve">2.54653644561768</t>
   </si>
   <si>
     <t xml:space="preserve">2.5512375831604</t>
@@ -884,43 +884,43 @@
     <t xml:space="preserve">2.53713417053223</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55437231063843</t>
+    <t xml:space="preserve">2.55437183380127</t>
   </si>
   <si>
     <t xml:space="preserve">2.60608649253845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70794796943665</t>
+    <t xml:space="preserve">2.70794773101807</t>
   </si>
   <si>
     <t xml:space="preserve">2.71108198165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541120529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70324635505676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67347145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705613136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981846809387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58728098869324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59825086593628</t>
+    <t xml:space="preserve">2.72205185890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541096687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70324659347534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67347168922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728122711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5982506275177</t>
   </si>
   <si>
     <t xml:space="preserve">2.5857138633728</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">2.54183530807495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51989603042603</t>
+    <t xml:space="preserve">2.51989579200745</t>
   </si>
   <si>
     <t xml:space="preserve">2.52929830551147</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">2.48228526115417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4337055683136</t>
+    <t xml:space="preserve">2.43370532989502</t>
   </si>
   <si>
     <t xml:space="preserve">2.39609527587891</t>
@@ -965,19 +965,19 @@
     <t xml:space="preserve">2.30206918716431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25975728034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27699542045593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28796482086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34908175468445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36475300788879</t>
+    <t xml:space="preserve">2.25975751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27699565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28796529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34908223152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36475276947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.35064911842346</t>
@@ -989,82 +989,82 @@
     <t xml:space="preserve">2.41333317756653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43683958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62489151954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63272666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46818161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36631989479065</t>
+    <t xml:space="preserve">2.43683981895447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62489175796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6327269077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.468181848526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36632013320923</t>
   </si>
   <si>
     <t xml:space="preserve">2.381991147995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766240119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40549778938293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42116856575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363607406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25662350654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27229428291321</t>
+    <t xml:space="preserve">2.39766216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251059532166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40549802780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4211688041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900395393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878787994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25662326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27229452133179</t>
   </si>
   <si>
     <t xml:space="preserve">2.28012943267822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26445841789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1235978603363</t>
+    <t xml:space="preserve">2.26445865631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528123855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12359762191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.0995569229126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08352971076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09154367446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01942157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339388847351</t>
+    <t xml:space="preserve">2.08353018760681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09154391288757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01942133903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339412689209</t>
   </si>
   <si>
     <t xml:space="preserve">2.06750273704529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18770623207092</t>
+    <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188275337219</t>
@@ -1079,49 +1079,49 @@
     <t xml:space="preserve">2.14763832092285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20373344421387</t>
+    <t xml:space="preserve">2.20373368263245</t>
   </si>
   <si>
     <t xml:space="preserve">2.13161134719849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17167901992798</t>
+    <t xml:space="preserve">2.17167925834656</t>
   </si>
   <si>
     <t xml:space="preserve">2.19571995735168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17969298362732</t>
+    <t xml:space="preserve">2.1796932220459</t>
   </si>
   <si>
     <t xml:space="preserve">2.10757064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05948925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07551622390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0354483127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05147552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27585554122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784205436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21976065635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21174693107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24380135536194</t>
+    <t xml:space="preserve">2.05948901176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07551670074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03544855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05147528648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27585577964783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784229278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21976089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21174716949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24380111694336</t>
   </si>
   <si>
     <t xml:space="preserve">2.23578786849976</t>
@@ -1133,16 +1133,16 @@
     <t xml:space="preserve">2.15565204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30790996551514</t>
+    <t xml:space="preserve">2.30791020393372</t>
   </si>
   <si>
     <t xml:space="preserve">2.02743482589722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04346227645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99538052082062</t>
+    <t xml:space="preserve">2.04346203804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99538064002991</t>
   </si>
   <si>
     <t xml:space="preserve">1.91524481773376</t>
@@ -1151,40 +1151,40 @@
     <t xml:space="preserve">1.92325830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96332621574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97134006023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736715316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140761375427</t>
+    <t xml:space="preserve">1.96332609653473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133982181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736703395844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140785217285</t>
   </si>
   <si>
     <t xml:space="preserve">1.81106841564178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81908190250397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84312260150909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79504108428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901422977448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709550857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100038528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73093259334564</t>
+    <t xml:space="preserve">1.81908202171326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84312272071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79504132270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7790139913559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709538936615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77100026607513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73093247413635</t>
   </si>
   <si>
     <t xml:space="preserve">1.69887828826904</t>
@@ -1193,16 +1193,16 @@
     <t xml:space="preserve">1.7149053812027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695980548859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72291910648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73894619941711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298701763153</t>
+    <t xml:space="preserve">1.74695992469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72291898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7389463186264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298689842224</t>
   </si>
   <si>
     <t xml:space="preserve">1.75497317314148</t>
@@ -1211,40 +1211,40 @@
     <t xml:space="preserve">1.80305469036102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85914957523346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86716330051422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510911464691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723156929016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935318946838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928551673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082943916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258111000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98783648014069</t>
+    <t xml:space="preserve">1.85914969444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8671635389328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510899543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8751767873764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723145008087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935330867767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93928563594818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258134841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98783659934998</t>
   </si>
   <si>
     <t xml:space="preserve">1.99608469009399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96309161186218</t>
+    <t xml:space="preserve">1.96309149265289</t>
   </si>
   <si>
     <t xml:space="preserve">1.93834662437439</t>
@@ -1253,52 +1253,52 @@
     <t xml:space="preserve">1.9795880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0373260974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06207132339478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0538227558136</t>
+    <t xml:space="preserve">2.03732585906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06207084655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05382251739502</t>
   </si>
   <si>
     <t xml:space="preserve">2.09506392478943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16929888725281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16105008125305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11156058311462</t>
+    <t xml:space="preserve">2.16929841041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16105031967163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11156034469604</t>
   </si>
   <si>
     <t xml:space="preserve">2.10331225395203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12805700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13630509376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11980867385864</t>
+    <t xml:space="preserve">2.12805724143982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13630557060242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11980891227722</t>
   </si>
   <si>
     <t xml:space="preserve">2.14455366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07856750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22703671455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21878838539124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25178146362305</t>
+    <t xml:space="preserve">2.07856774330139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22703647613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21878814697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25178170204163</t>
   </si>
   <si>
     <t xml:space="preserve">2.24353313446045</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.21054029464722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26002979278564</t>
+    <t xml:space="preserve">2.26002955436707</t>
   </si>
   <si>
     <t xml:space="preserve">2.26827812194824</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">2.33426427841187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30951952934265</t>
+    <t xml:space="preserve">2.30951929092407</t>
   </si>
   <si>
     <t xml:space="preserve">2.30127120018005</t>
@@ -1331,10 +1331,10 @@
     <t xml:space="preserve">2.3755054473877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32601594924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27652645111084</t>
+    <t xml:space="preserve">2.32601618766785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27652621269226</t>
   </si>
   <si>
     <t xml:space="preserve">2.28477454185486</t>
@@ -1343,37 +1343,37 @@
     <t xml:space="preserve">2.29302287101746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23528480529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200234413147</t>
+    <t xml:space="preserve">2.23528504371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200258255005</t>
   </si>
   <si>
     <t xml:space="preserve">2.4497401714325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43324375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849900245667</t>
+    <t xml:space="preserve">2.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4332435131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849876403809</t>
   </si>
   <si>
     <t xml:space="preserve">2.42499542236328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798850059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4992299079895</t>
+    <t xml:space="preserve">2.45798873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49923014640808</t>
   </si>
   <si>
     <t xml:space="preserve">2.47448515892029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5157265663147</t>
+    <t xml:space="preserve">2.51572632789612</t>
   </si>
   <si>
     <t xml:space="preserve">2.58996105194092</t>
@@ -1382,16 +1382,16 @@
     <t xml:space="preserve">2.54871964454651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49098181724548</t>
+    <t xml:space="preserve">2.4909815788269</t>
   </si>
   <si>
     <t xml:space="preserve">2.5074782371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4414918422699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35076093673706</t>
+    <t xml:space="preserve">2.44149231910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35076069831848</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025067329407</t>
@@ -1400,16 +1400,16 @@
     <t xml:space="preserve">2.19404363632202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18579530715942</t>
+    <t xml:space="preserve">2.185795545578</t>
   </si>
   <si>
     <t xml:space="preserve">2.045574426651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87236022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8806084394455</t>
+    <t xml:space="preserve">1.8723601102829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060879707336</t>
   </si>
   <si>
     <t xml:space="preserve">1.68264973163605</t>
@@ -1424,34 +1424,34 @@
     <t xml:space="preserve">1.71564280986786</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64553248882294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64140844345093</t>
+    <t xml:space="preserve">1.64553260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64140856266022</t>
   </si>
   <si>
     <t xml:space="preserve">1.62491190433502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77338099479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162944316864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74863600730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80637407302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411201953888</t>
+    <t xml:space="preserve">1.77338123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162920475006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74863612651825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80637419223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411213874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.00433301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81462240219116</t>
+    <t xml:space="preserve">1.81462252140045</t>
   </si>
   <si>
     <t xml:space="preserve">1.79812586307526</t>
@@ -1466,22 +1466,22 @@
     <t xml:space="preserve">1.83111894130707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78987777233124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885676860809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710485935211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90535342693329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95484328269958</t>
+    <t xml:space="preserve">1.78987765312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885700702667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360175609589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710509777069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90535354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95484340190887</t>
   </si>
   <si>
     <t xml:space="preserve">2.02907800674438</t>
@@ -1490,25 +1490,25 @@
     <t xml:space="preserve">2.08681559562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17754673957825</t>
+    <t xml:space="preserve">2.17754697799683</t>
   </si>
   <si>
     <t xml:space="preserve">2.07031917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07786870002747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06938791275024</t>
+    <t xml:space="preserve">2.07786917686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06938767433167</t>
   </si>
   <si>
     <t xml:space="preserve">2.03546357154846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9845769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9760959148407</t>
+    <t xml:space="preserve">1.98457670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609579563141</t>
   </si>
   <si>
     <t xml:space="preserve">1.95065248012543</t>
@@ -1523,34 +1523,34 @@
     <t xml:space="preserve">2.02698254585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05242586135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04394483566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01002025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00153923034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89976584911346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88280367851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128482341766</t>
+    <t xml:space="preserve">2.05242562294006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04394459724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0100200176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0015389919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89976596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88280391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128494262695</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95913326740265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08635020256042</t>
+    <t xml:space="preserve">1.95913374423981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08634996414185</t>
   </si>
   <si>
     <t xml:space="preserve">2.12875556945801</t>
@@ -1562,7 +1562,7 @@
     <t xml:space="preserve">2.16267991065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20508551597595</t>
+    <t xml:space="preserve">2.20508527755737</t>
   </si>
   <si>
     <t xml:space="preserve">2.23052906990051</t>
@@ -1574,16 +1574,16 @@
     <t xml:space="preserve">2.33230209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34926414489746</t>
+    <t xml:space="preserve">2.34926438331604</t>
   </si>
   <si>
     <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559385299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255638122559</t>
+    <t xml:space="preserve">2.42559409141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255661964417</t>
   </si>
   <si>
     <t xml:space="preserve">2.47648048400879</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">2.46799969673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49344325065613</t>
+    <t xml:space="preserve">2.49344277381897</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040506362915</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">2.43407535552979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41711258888245</t>
+    <t xml:space="preserve">2.4171130657196</t>
   </si>
   <si>
     <t xml:space="preserve">2.51888608932495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58673477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977248191833</t>
+    <t xml:space="preserve">2.58673501014709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977272033691</t>
   </si>
   <si>
     <t xml:space="preserve">2.54432940483093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57825374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56129145622253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55281066894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53584837913513</t>
+    <t xml:space="preserve">2.57825398445129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56129169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55281043052673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53584814071655</t>
   </si>
   <si>
     <t xml:space="preserve">2.52736711502075</t>
@@ -1640,13 +1640,13 @@
     <t xml:space="preserve">2.66306495666504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547008514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69698905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62914037704468</t>
+    <t xml:space="preserve">2.70547032356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69698929786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6291401386261</t>
   </si>
   <si>
     <t xml:space="preserve">2.71395134925842</t>
@@ -1655,46 +1655,46 @@
     <t xml:space="preserve">2.7309136390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77331924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78180027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84116768836975</t>
+    <t xml:space="preserve">2.77331900596619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78180003166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84116792678833</t>
   </si>
   <si>
     <t xml:space="preserve">2.86661124229431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88357329368591</t>
+    <t xml:space="preserve">2.88357353210449</t>
   </si>
   <si>
     <t xml:space="preserve">2.90901684761047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85812973976135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80724358558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75635671615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939442634583</t>
+    <t xml:space="preserve">2.85812997817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80724334716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75635695457458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939490318298</t>
   </si>
   <si>
     <t xml:space="preserve">2.74787592887878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79876208305359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79028129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84964895248413</t>
+    <t xml:space="preserve">2.79876232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79028105735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84964871406555</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268690109253</t>
@@ -1703,7 +1703,7 @@
     <t xml:space="preserve">2.82420563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9174976348877</t>
+    <t xml:space="preserve">2.91749787330627</t>
   </si>
   <si>
     <t xml:space="preserve">3.01078987121582</t>
@@ -1721,19 +1721,19 @@
     <t xml:space="preserve">3.08711981773376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12104439735413</t>
+    <t xml:space="preserve">3.12104415893555</t>
   </si>
   <si>
     <t xml:space="preserve">3.18041181564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14648723602295</t>
+    <t xml:space="preserve">3.14648771286011</t>
   </si>
   <si>
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281742095947</t>
+    <t xml:space="preserve">3.22281718254089</t>
   </si>
   <si>
     <t xml:space="preserve">3.23129844665527</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">3.21433615684509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28218483924866</t>
+    <t xml:space="preserve">3.28218507766724</t>
   </si>
   <si>
     <t xml:space="preserve">3.40092062950134</t>
@@ -1754,40 +1754,40 @@
     <t xml:space="preserve">3.42636346817017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3669958114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31610941886902</t>
+    <t xml:space="preserve">3.36699604988098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3161096572876</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066610336304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27370381355286</t>
+    <t xml:space="preserve">3.27370357513428</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31657695770264</t>
+    <t xml:space="preserve">3.31657671928406</t>
   </si>
   <si>
     <t xml:space="preserve">3.27339220046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35112500190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34248733520508</t>
+    <t xml:space="preserve">3.35112452507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34248757362366</t>
   </si>
   <si>
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44613099098206</t>
+    <t xml:space="preserve">3.39430952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44613075256348</t>
   </si>
   <si>
     <t xml:space="preserve">3.45476746559143</t>
@@ -1802,61 +1802,61 @@
     <t xml:space="preserve">3.60159516334534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5929582118988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65341663360596</t>
+    <t xml:space="preserve">3.59295773506165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65341687202454</t>
   </si>
   <si>
     <t xml:space="preserve">3.61023187637329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71387553215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6706907749176</t>
+    <t xml:space="preserve">3.71387529373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069053649902</t>
   </si>
   <si>
     <t xml:space="preserve">3.78297066688538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8088812828064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6966016292572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62750577926636</t>
+    <t xml:space="preserve">3.80888104438782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69660139083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62750554084778</t>
   </si>
   <si>
     <t xml:space="preserve">3.64477968215942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73978567123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7570595741272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55841040611267</t>
+    <t xml:space="preserve">3.73978543281555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75705981254578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55841064453125</t>
   </si>
   <si>
     <t xml:space="preserve">3.67932772636414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57568454742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58432173728943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.705237865448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5238630771637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54977369308472</t>
+    <t xml:space="preserve">3.57568430900574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58432126045227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70523834228516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52386283874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5497739315033</t>
   </si>
   <si>
     <t xml:space="preserve">3.48931527137756</t>
@@ -1868,13 +1868,13 @@
     <t xml:space="preserve">3.51522612571716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68796443939209</t>
+    <t xml:space="preserve">3.68796467781067</t>
   </si>
   <si>
     <t xml:space="preserve">3.74842286109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66205334663391</t>
+    <t xml:space="preserve">3.66205310821533</t>
   </si>
   <si>
     <t xml:space="preserve">3.61886930465698</t>
@@ -1883,55 +1883,55 @@
     <t xml:space="preserve">3.86933970451355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8261547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86070251464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91252493858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99889397621155</t>
+    <t xml:space="preserve">3.82615518569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86070275306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91252446174622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99889373779297</t>
   </si>
   <si>
     <t xml:space="preserve">3.9557089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99025630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342885017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77433347702026</t>
+    <t xml:space="preserve">3.99025654792786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77433323860168</t>
   </si>
   <si>
     <t xml:space="preserve">3.76569676399231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9297981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661336898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90388751029968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87797665596008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81751847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434569358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89525032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93843483924866</t>
+    <t xml:space="preserve">3.92979836463928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661360740662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90388679504395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87797617912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81751823425293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89525079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93843460083008</t>
   </si>
   <si>
     <t xml:space="preserve">3.63614296913147</t>
@@ -1940,16 +1940,16 @@
     <t xml:space="preserve">3.4979522228241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885708808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021989822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2820291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2561182975769</t>
+    <t xml:space="preserve">3.42885684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4202196598053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28202891349792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25611853599548</t>
   </si>
   <si>
     <t xml:space="preserve">3.24748158454895</t>
@@ -1958,25 +1958,25 @@
     <t xml:space="preserve">3.29930281639099</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26475524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3338508605957</t>
+    <t xml:space="preserve">3.26475501060486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33385062217712</t>
   </si>
   <si>
     <t xml:space="preserve">3.43749356269836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37703537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40294599533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35976147651672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2129340171814</t>
+    <t xml:space="preserve">3.37703561782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40294623374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3597617149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21293377876282</t>
   </si>
   <si>
     <t xml:space="preserve">3.23020768165588</t>
@@ -1985,22 +1985,22 @@
     <t xml:space="preserve">3.15247559547424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11792778968811</t>
+    <t xml:space="preserve">3.11792755126953</t>
   </si>
   <si>
     <t xml:space="preserve">3.19566011428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14383840560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97973728179932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06610584259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53249979019165</t>
+    <t xml:space="preserve">3.14383864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97973704338074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06610631942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53250002861023</t>
   </si>
   <si>
     <t xml:space="preserve">3.56704759597778</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">3.52451872825623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6130747795105</t>
+    <t xml:space="preserve">3.61307454109192</t>
   </si>
   <si>
     <t xml:space="preserve">3.58650803565979</t>
@@ -2042,34 +2042,34 @@
     <t xml:space="preserve">3.33855175971985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34740734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26770710945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30312943458557</t>
+    <t xml:space="preserve">3.34740710258484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26770734786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30312967300415</t>
   </si>
   <si>
     <t xml:space="preserve">3.2322850227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27656269073486</t>
+    <t xml:space="preserve">3.27656292915344</t>
   </si>
   <si>
     <t xml:space="preserve">3.32969617843628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32084059715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28541827201843</t>
+    <t xml:space="preserve">3.32084083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28541851043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.42710757255554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51566314697266</t>
+    <t xml:space="preserve">3.51566338539124</t>
   </si>
   <si>
     <t xml:space="preserve">3.55108571052551</t>
@@ -2081,46 +2081,43 @@
     <t xml:space="preserve">3.48909664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53337430953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59536361694336</t>
+    <t xml:space="preserve">3.53337454795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59536337852478</t>
   </si>
   <si>
     <t xml:space="preserve">3.5599410533905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49795198440552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46252989768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36511850357056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41825199127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3828296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44481873512268</t>
+    <t xml:space="preserve">3.4625301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36511826515198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41825175285339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38282942771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">3.45367431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48024106025696</t>
+    <t xml:space="preserve">3.48024129867554</t>
   </si>
   <si>
     <t xml:space="preserve">3.39168524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24999594688416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08173990249634</t>
+    <t xml:space="preserve">3.24999618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08174014091492</t>
   </si>
   <si>
     <t xml:space="preserve">3.1437292098999</t>
@@ -2129,7 +2126,7 @@
     <t xml:space="preserve">3.11716246604919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09059548377991</t>
+    <t xml:space="preserve">3.09059572219849</t>
   </si>
   <si>
     <t xml:space="preserve">2.88691735267639</t>
@@ -2183,10 +2180,10 @@
     <t xml:space="preserve">2.9931845664978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0640287399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07288432121277</t>
+    <t xml:space="preserve">3.06402897834778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07288455963135</t>
   </si>
   <si>
     <t xml:space="preserve">3.01975131034851</t>
@@ -2240,7 +2237,7 @@
     <t xml:space="preserve">3.0286066532135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05517315864563</t>
+    <t xml:space="preserve">3.05517339706421</t>
   </si>
   <si>
     <t xml:space="preserve">3.17029595375061</t>
@@ -2252,7 +2249,7 @@
     <t xml:space="preserve">3.24114060401917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25885152816772</t>
+    <t xml:space="preserve">3.2588517665863</t>
   </si>
   <si>
     <t xml:space="preserve">3.16144037246704</t>
@@ -2261,7 +2258,7 @@
     <t xml:space="preserve">3.37397408485413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40054082870483</t>
+    <t xml:space="preserve">3.40054059028625</t>
   </si>
   <si>
     <t xml:space="preserve">3.47138547897339</t>
@@ -2270,60 +2267,63 @@
     <t xml:space="preserve">3.50680756568909</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60421943664551</t>
+    <t xml:space="preserve">3.60421919822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63078570365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62193036079407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63964152336121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67674517631531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71351265907288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72270464897156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77785563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69512891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70432090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78704738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75947213172913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8146231174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76866388320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75028014183044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63997769355774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64916968345642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66755318641663</t>
   </si>
   <si>
     <t xml:space="preserve">3.63078594207764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62193059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63964152336121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67674517631531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71351265907288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72270464897156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77785563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69512891769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70432090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78704738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75947213172913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8146231174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76866388320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75028014183044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63997769355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64916968345642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66755318641663</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.62159395217896</t>
   </si>
   <si>
@@ -2955,6 +2955,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.64000034332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89999961853027</t>
   </si>
 </sst>
 </file>
@@ -46887,7 +46890,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1677" t="s">
-        <v>692</v>
+        <v>641</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46913,7 +46916,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1678" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46965,7 +46968,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1680" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -46991,7 +46994,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1681" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47121,7 +47124,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1686" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47147,7 +47150,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1687" t="s">
-        <v>692</v>
+        <v>641</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47173,7 +47176,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1688" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47199,7 +47202,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1689" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47277,7 +47280,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1692" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47303,7 +47306,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1693" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47329,7 +47332,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1694" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47407,7 +47410,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1697" t="s">
-        <v>692</v>
+        <v>641</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47433,7 +47436,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1698" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47459,7 +47462,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47485,7 +47488,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1700" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47537,7 +47540,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1702" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47563,7 +47566,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1703" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47589,7 +47592,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1704" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47615,7 +47618,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1705" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47745,7 +47748,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47797,7 +47800,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47823,7 +47826,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1713" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47849,7 +47852,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47875,7 +47878,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1715" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47901,7 +47904,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47927,7 +47930,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1717" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47953,7 +47956,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -47979,7 +47982,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48005,7 +48008,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48031,7 +48034,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48057,7 +48060,7 @@
         <v>3</v>
       </c>
       <c r="G1722" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48083,7 +48086,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1723" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48109,7 +48112,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48135,7 +48138,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1725" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48161,7 +48164,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1726" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48187,7 +48190,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1727" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48213,7 +48216,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48239,7 +48242,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48265,7 +48268,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1730" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48291,7 +48294,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1731" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48317,7 +48320,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48343,7 +48346,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1733" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48369,7 +48372,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1734" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48395,7 +48398,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1735" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48421,7 +48424,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1736" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48447,7 +48450,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1737" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48473,7 +48476,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1738" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48499,7 +48502,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1739" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48525,7 +48528,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1740" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48551,7 +48554,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1741" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48577,7 +48580,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1742" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48603,7 +48606,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48629,7 +48632,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1744" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48655,7 +48658,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1745" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48681,7 +48684,7 @@
         <v>3.5</v>
       </c>
       <c r="G1746" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48707,7 +48710,7 @@
         <v>3.5</v>
       </c>
       <c r="G1747" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48733,7 +48736,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1748" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48759,7 +48762,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1749" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48785,7 +48788,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1750" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48811,7 +48814,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48837,7 +48840,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1752" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48863,7 +48866,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1753" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48889,7 +48892,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1754" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48915,7 +48918,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1755" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48941,7 +48944,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1756" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48967,7 +48970,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1757" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -48993,7 +48996,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49019,7 +49022,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1759" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49045,7 +49048,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49071,7 +49074,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1761" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49097,7 +49100,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1762" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49123,7 +49126,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1763" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49149,7 +49152,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1764" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49175,7 +49178,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1765" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49201,7 +49204,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1766" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49227,7 +49230,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1767" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49253,7 +49256,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1768" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49279,7 +49282,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1769" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49305,7 +49308,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1770" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49331,7 +49334,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1771" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49357,7 +49360,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1772" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49383,7 +49386,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1773" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49409,7 +49412,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1774" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49435,7 +49438,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1775" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49461,7 +49464,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1776" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49487,7 +49490,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49513,7 +49516,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1778" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49539,7 +49542,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1779" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49565,7 +49568,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49591,7 +49594,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1781" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49617,7 +49620,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1782" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49643,7 +49646,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49669,7 +49672,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1784" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49695,7 +49698,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1785" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49721,7 +49724,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1786" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49747,7 +49750,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1787" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49773,7 +49776,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49799,7 +49802,7 @@
         <v>3.25</v>
       </c>
       <c r="G1789" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49825,7 +49828,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1790" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49851,7 +49854,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1791" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49877,7 +49880,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1792" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49903,7 +49906,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1793" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49929,7 +49932,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49955,7 +49958,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -49981,7 +49984,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1796" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50007,7 +50010,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1797" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50033,7 +50036,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1798" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50059,7 +50062,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1799" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50085,7 +50088,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1800" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50111,7 +50114,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1801" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50137,7 +50140,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50189,7 +50192,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1804" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50215,7 +50218,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1805" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50241,7 +50244,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1806" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50267,7 +50270,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1807" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50293,7 +50296,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1808" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50371,7 +50374,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1811" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50579,7 +50582,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1819" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50761,7 +50764,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1826" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50787,7 +50790,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1827" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50813,7 +50816,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1828" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50865,7 +50868,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1830" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50891,7 +50894,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50917,7 +50920,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1832" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50943,7 +50946,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1833" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50969,7 +50972,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -50995,7 +50998,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1835" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51073,7 +51076,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1838" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51229,7 +51232,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1844" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51307,7 +51310,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1847" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51489,7 +51492,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1854" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51515,7 +51518,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51541,7 +51544,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1856" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51593,7 +51596,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1858" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51619,7 +51622,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1859" t="s">
-        <v>692</v>
+        <v>641</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51645,7 +51648,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1860" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51697,7 +51700,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51801,7 +51804,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1866" t="s">
-        <v>692</v>
+        <v>641</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51827,7 +51830,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1867" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51957,7 +51960,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1872" t="s">
-        <v>692</v>
+        <v>641</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52087,7 +52090,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1877" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52139,7 +52142,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1879" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52165,7 +52168,7 @@
         <v>4</v>
       </c>
       <c r="G1880" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52191,7 +52194,7 @@
         <v>4</v>
       </c>
       <c r="G1881" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52217,7 +52220,7 @@
         <v>4</v>
       </c>
       <c r="G1882" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52243,7 +52246,7 @@
         <v>4</v>
       </c>
       <c r="G1883" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52269,7 +52272,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52295,7 +52298,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1885" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52321,7 +52324,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1886" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52347,7 +52350,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52373,7 +52376,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1888" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52399,7 +52402,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1889" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52425,7 +52428,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52451,7 +52454,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1891" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52477,7 +52480,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1892" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52503,7 +52506,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1893" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52529,7 +52532,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1894" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52555,7 +52558,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52581,7 +52584,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1896" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52607,7 +52610,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1897" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52633,7 +52636,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1898" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52659,7 +52662,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1899" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52685,7 +52688,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1900" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52711,7 +52714,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52737,7 +52740,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52763,7 +52766,7 @@
         <v>4</v>
       </c>
       <c r="G1903" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52789,7 +52792,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1904" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52815,7 +52818,7 @@
         <v>4</v>
       </c>
       <c r="G1905" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52841,7 +52844,7 @@
         <v>4</v>
       </c>
       <c r="G1906" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52867,7 +52870,7 @@
         <v>4</v>
       </c>
       <c r="G1907" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52893,7 +52896,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1908" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52919,7 +52922,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1909" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52971,7 +52974,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1911" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53439,7 +53442,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1929" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53543,7 +53546,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1933" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53647,7 +53650,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53673,7 +53676,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1938" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53699,7 +53702,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53725,7 +53728,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1940" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53751,7 +53754,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1941" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53777,7 +53780,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1942" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53829,7 +53832,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1944" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53907,7 +53910,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1947" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53933,7 +53936,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1948" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53959,7 +53962,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1949" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -53985,7 +53988,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1950" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54011,7 +54014,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54037,7 +54040,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1952" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54063,7 +54066,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1953" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54089,7 +54092,7 @@
         <v>4</v>
       </c>
       <c r="G1954" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54115,7 +54118,7 @@
         <v>4</v>
       </c>
       <c r="G1955" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54141,7 +54144,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54167,7 +54170,7 @@
         <v>4</v>
       </c>
       <c r="G1957" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54193,7 +54196,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1958" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54817,7 +54820,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1982" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54921,7 +54924,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1986" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55103,7 +55106,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55129,7 +55132,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55207,7 +55210,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1997" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55285,7 +55288,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2000" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55311,7 +55314,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55337,7 +55340,7 @@
         <v>4</v>
       </c>
       <c r="G2002" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55363,7 +55366,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2003" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55415,7 +55418,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2005" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55441,7 +55444,7 @@
         <v>4</v>
       </c>
       <c r="G2006" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55467,7 +55470,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2007" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55493,7 +55496,7 @@
         <v>4</v>
       </c>
       <c r="G2008" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55519,7 +55522,7 @@
         <v>4</v>
       </c>
       <c r="G2009" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55597,7 +55600,7 @@
         <v>4</v>
       </c>
       <c r="G2012" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55623,7 +55626,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2013" t="s">
-        <v>753</v>
+        <v>769</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55649,7 +55652,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2014" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55675,7 +55678,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55701,7 +55704,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55727,7 +55730,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55753,7 +55756,7 @@
         <v>4</v>
       </c>
       <c r="G2018" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55779,7 +55782,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2019" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55805,7 +55808,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2020" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55831,7 +55834,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2021" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55857,7 +55860,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2022" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55883,7 +55886,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2023" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55935,7 +55938,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55961,7 +55964,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -55987,7 +55990,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56039,7 +56042,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2029" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56065,7 +56068,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2030" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56091,7 +56094,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2031" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56143,7 +56146,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2033" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56429,7 +56432,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2044" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57079,7 +57082,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2069" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57157,7 +57160,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2072" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57183,7 +57186,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2073" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57261,7 +57264,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2076" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57287,7 +57290,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2077" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -68059,7 +68062,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.649375</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>26896</v>
@@ -68080,6 +68083,32 @@
         <v>980</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.649537037</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>19295</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>8.72000026702881</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>981</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="988" uniqueCount="988">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="987" uniqueCount="987">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652267456055</t>
+    <t xml:space="preserve">1.73652255535126</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400770664215</t>
+    <t xml:space="preserve">1.74400746822357</t>
   </si>
   <si>
     <t xml:space="preserve">1.71406745910645</t>
@@ -53,85 +53,85 @@
     <t xml:space="preserve">1.66167259216309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67215144634247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64969658851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921749591827</t>
+    <t xml:space="preserve">1.67215156555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64969646930695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921737670898</t>
   </si>
   <si>
     <t xml:space="preserve">1.57334935665131</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49625384807587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48053526878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48203241825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637382984161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460725784302</t>
+    <t xml:space="preserve">1.49625360965729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48053538799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48203217983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460713863373</t>
   </si>
   <si>
     <t xml:space="preserve">1.42215216159821</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41990685462952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41466701030731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41915822029114</t>
+    <t xml:space="preserve">1.41990649700165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4146671295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41915833950043</t>
   </si>
   <si>
     <t xml:space="preserve">1.40718221664429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3824816942215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38472723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39820027351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35703253746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33607470989227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34730207920074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3428111076355</t>
+    <t xml:space="preserve">1.38248157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38472712039948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3982001543045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35703277587891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607447147369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34730195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34281098842621</t>
   </si>
   <si>
     <t xml:space="preserve">1.38397872447968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35478699207306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38098442554474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36975717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113422393799</t>
+    <t xml:space="preserve">1.35478711128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38098466396332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36975729465485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873923778534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4311341047287</t>
   </si>
   <si>
     <t xml:space="preserve">1.41017615795135</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">1.44535577297211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.462571144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51197242736816</t>
+    <t xml:space="preserve">1.46257126331329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51197218894958</t>
   </si>
   <si>
     <t xml:space="preserve">1.5254453420639</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">1.52245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54490649700165</t>
+    <t xml:space="preserve">1.54490637779236</t>
   </si>
   <si>
     <t xml:space="preserve">1.541912317276</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5493973493576</t>
+    <t xml:space="preserve">1.54939723014832</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287038326263</t>
@@ -167,61 +167,61 @@
     <t xml:space="preserve">1.60029554367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60927748680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173258304596</t>
+    <t xml:space="preserve">1.60927760601044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173246383667</t>
   </si>
   <si>
     <t xml:space="preserve">1.62424755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63023555278778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676228046417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418744087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64370822906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682250976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58831930160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472676277161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6601756811142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915738582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712151050568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6916127204895</t>
+    <t xml:space="preserve">1.63023543357849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676251888275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418779850006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370858669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682227134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58831942081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472640514374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017532348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66915774345398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712162971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69161260128021</t>
   </si>
   <si>
     <t xml:space="preserve">1.6931095123291</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72155272960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502564430237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358824729919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.706582903862</t>
+    <t xml:space="preserve">1.72155249118805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502576351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358872413635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658266544342</t>
   </si>
   <si>
     <t xml:space="preserve">1.69909751415253</t>
@@ -236,133 +236,133 @@
     <t xml:space="preserve">1.66766047477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68263041973114</t>
+    <t xml:space="preserve">1.68263065814972</t>
   </si>
   <si>
     <t xml:space="preserve">1.64221155643463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64670288562775</t>
+    <t xml:space="preserve">1.64670252799988</t>
   </si>
   <si>
     <t xml:space="preserve">1.67514562606812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69964516162872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6843329668045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69198870658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72108173370361</t>
+    <t xml:space="preserve">1.69964504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68433284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6919891834259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72108197212219</t>
   </si>
   <si>
     <t xml:space="preserve">1.70576977729797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69505131244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495699882507</t>
+    <t xml:space="preserve">1.69505143165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495711803436</t>
   </si>
   <si>
     <t xml:space="preserve">1.72261297702789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65370857715607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208349704742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66902077198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65217745304108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.606241106987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56183576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5541797876358</t>
+    <t xml:space="preserve">1.65370869636536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208313941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.669020652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65217733383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60624122619629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56183588504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417990684509</t>
   </si>
   <si>
     <t xml:space="preserve">1.52202439308167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121161460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59092891216278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52891480922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55111742019653</t>
+    <t xml:space="preserve">1.53121173381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59092915058136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52891492843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55111730098724</t>
   </si>
   <si>
     <t xml:space="preserve">1.53886771202087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4929313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4760879278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52279007434845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996295452118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761929035187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5005875825882</t>
+    <t xml:space="preserve">1.49293148517609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996319293976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761905193329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589941978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058734416962</t>
   </si>
   <si>
     <t xml:space="preserve">1.6077721118927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59705376625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56949198246002</t>
+    <t xml:space="preserve">1.5970538854599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56949186325073</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308442592621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6674896478653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136455535889</t>
+    <t xml:space="preserve">1.66748940944672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136479377747</t>
   </si>
   <si>
     <t xml:space="preserve">1.67667675018311</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61542844772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714796066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58480429649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63839650154114</t>
+    <t xml:space="preserve">1.61542820930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714807987213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58480405807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63839662075043</t>
   </si>
   <si>
     <t xml:space="preserve">1.6338027715683</t>
@@ -374,139 +374,139 @@
     <t xml:space="preserve">1.54652380943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56796061992645</t>
+    <t xml:space="preserve">1.56796073913574</t>
   </si>
   <si>
     <t xml:space="preserve">1.54499244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355563640594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54193007946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58174157142639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55877351760864</t>
+    <t xml:space="preserve">1.52355551719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54192996025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174169063568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55877339839935</t>
   </si>
   <si>
     <t xml:space="preserve">1.5802104473114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55264866352081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53044605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5197274684906</t>
+    <t xml:space="preserve">1.5526487827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53044593334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51972734928131</t>
   </si>
   <si>
     <t xml:space="preserve">1.50594663619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50671219825745</t>
+    <t xml:space="preserve">1.50671243667603</t>
   </si>
   <si>
     <t xml:space="preserve">1.53427410125732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56642961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57408559322357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58327293395996</t>
+    <t xml:space="preserve">1.56642937660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57408571243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58327281475067</t>
   </si>
   <si>
     <t xml:space="preserve">1.59246003627777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50211870670319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824368000031</t>
+    <t xml:space="preserve">1.5021185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824356079102</t>
   </si>
   <si>
     <t xml:space="preserve">1.47532248497009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49675953388214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50747799873352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52968049049377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60011625289917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58786630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489825248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56336724758148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255411148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59858500957489</t>
+    <t xml:space="preserve">1.49675941467285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50747787952423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52968037128448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60011613368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58786642551422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489813327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56336712837219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255434989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59858512878418</t>
   </si>
   <si>
     <t xml:space="preserve">1.59399139881134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60470962524414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64758360385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64605247974396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68280160427094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63074040412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63686537742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452135562897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227152824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66289579868317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595828533173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333168029785</t>
+    <t xml:space="preserve">1.60470986366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64758372306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64605259895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68280172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63074064254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63686525821686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452147483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6322717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66289567947388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595852375031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333156108856</t>
   </si>
   <si>
     <t xml:space="preserve">1.73026931285858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7455815076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730090141296</t>
+    <t xml:space="preserve">1.74558115005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017488002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730102062225</t>
   </si>
   <si>
     <t xml:space="preserve">1.70423865318298</t>
@@ -515,43 +515,43 @@
     <t xml:space="preserve">1.73792517185211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75936233997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089370250702</t>
+    <t xml:space="preserve">1.75936222076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089310646057</t>
   </si>
   <si>
     <t xml:space="preserve">1.78386151790619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76854944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323724746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486304283142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639380931854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7915176153183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223619937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061076164246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754851341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682957172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520425319672</t>
+    <t xml:space="preserve">1.76854920387268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323712825775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486268520355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639392852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79151749610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223608016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061064243317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81754815578461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682969093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520413398743</t>
   </si>
   <si>
     <t xml:space="preserve">1.81448578834534</t>
@@ -566,97 +566,97 @@
     <t xml:space="preserve">1.85429716110229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85582864284515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8512350320816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86654710769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84970378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8634842634201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276591777802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511017799377</t>
+    <t xml:space="preserve">1.85582876205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85123455524445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86654686927795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84970343112946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348462104797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85276615619659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745408058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84511005878448</t>
   </si>
   <si>
     <t xml:space="preserve">1.82367289066315</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84051656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817254543304</t>
+    <t xml:space="preserve">1.84051668643951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817266464233</t>
   </si>
   <si>
     <t xml:space="preserve">1.86807823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94923257827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788984298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.921670794487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932665348053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9660758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904407024384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823129177094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894975662231</t>
+    <t xml:space="preserve">1.9492324590683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90789008140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92167031764984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932641506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9247328042984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607577800751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904371261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823117256165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894999504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.00741839408875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01201176643372</t>
+    <t xml:space="preserve">2.01201200485229</t>
   </si>
   <si>
     <t xml:space="preserve">1.99057519435883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0028247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00588726997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09207797050476</t>
+    <t xml:space="preserve">2.00282502174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00588703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0920774936676</t>
   </si>
   <si>
     <t xml:space="preserve">2.09051060676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11401748657227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11558437347412</t>
+    <t xml:space="preserve">2.11401677131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424210548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558389663696</t>
   </si>
   <si>
     <t xml:space="preserve">2.17043280601501</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">2.14692616462708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15006065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655401229858</t>
+    <t xml:space="preserve">2.15006017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655377388</t>
   </si>
   <si>
     <t xml:space="preserve">2.16259717941284</t>
@@ -680,58 +680,58 @@
     <t xml:space="preserve">2.1390905380249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16103005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04663157463074</t>
+    <t xml:space="preserve">2.16102981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04663181304932</t>
   </si>
   <si>
     <t xml:space="preserve">2.05290007591248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03722882270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04819869995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04506492614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06543684005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10774922370911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1171510219574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12341952323914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125538825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296980857849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19393944740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647597312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2033417224884</t>
+    <t xml:space="preserve">2.03722929954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04819917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0450644493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06543707847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073594093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10774874687195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11715149879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12341976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125514984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296933174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1939389705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647573471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20334196090698</t>
   </si>
   <si>
     <t xml:space="preserve">2.19237208366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20804333686829</t>
+    <t xml:space="preserve">2.20804309844971</t>
   </si>
   <si>
     <t xml:space="preserve">2.16416430473328</t>
@@ -740,22 +740,22 @@
     <t xml:space="preserve">2.15946316719055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13595676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677934646606</t>
+    <t xml:space="preserve">2.13595652580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677910804749</t>
   </si>
   <si>
     <t xml:space="preserve">2.06386995315552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827709674835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805176258087</t>
+    <t xml:space="preserve">2.02625966072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827673912048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805152416229</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640671730042</t>
@@ -764,43 +764,43 @@
     <t xml:space="preserve">2.05446720123291</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10461449623108</t>
+    <t xml:space="preserve">2.1046142578125</t>
   </si>
   <si>
     <t xml:space="preserve">2.06700420379639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03566217422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954120635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857132911682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797408103943</t>
+    <t xml:space="preserve">2.03566193580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797360420227</t>
   </si>
   <si>
     <t xml:space="preserve">2.2409520149231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22371435165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117734909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2331166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781800270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930708885193</t>
+    <t xml:space="preserve">2.22371411323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211177110672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23311638832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930685043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.3146059513092</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">2.3271427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32557559013367</t>
+    <t xml:space="preserve">2.32557535171509</t>
   </si>
   <si>
     <t xml:space="preserve">2.38982653617859</t>
@@ -827,136 +827,136 @@
     <t xml:space="preserve">2.48541975021362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49012112617493</t>
+    <t xml:space="preserve">2.49012088775635</t>
   </si>
   <si>
     <t xml:space="preserve">2.52146315574646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50735902786255</t>
+    <t xml:space="preserve">2.50735926628113</t>
   </si>
   <si>
     <t xml:space="preserve">2.53870105743408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53086543083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4916877746582</t>
+    <t xml:space="preserve">2.53086566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168825149536</t>
   </si>
   <si>
     <t xml:space="preserve">2.50422477722168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49952340126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52303004264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5324330329895</t>
+    <t xml:space="preserve">2.49952387809753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52303028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53243279457092</t>
   </si>
   <si>
     <t xml:space="preserve">2.51206040382385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5089259147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51362729072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795627593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638938903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5512375831604</t>
+    <t xml:space="preserve">2.50892615318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51362752914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4979567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638962745667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616453170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653692245483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55123805999756</t>
   </si>
   <si>
     <t xml:space="preserve">2.53713393211365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55437207221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60608649253845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70794749259949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541120529175</t>
+    <t xml:space="preserve">2.55437231063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60608625411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70794773101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108222007751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541144371033</t>
   </si>
   <si>
     <t xml:space="preserve">2.70324659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67347192764282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406917572021</t>
+    <t xml:space="preserve">2.67347145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406941413879</t>
   </si>
   <si>
     <t xml:space="preserve">2.61705613136292</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59981799125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5872814655304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59825086593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58571410179138</t>
+    <t xml:space="preserve">2.59981822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728122711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59825110435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58571434020996</t>
   </si>
   <si>
     <t xml:space="preserve">2.57004308700562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56220769882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54183506965637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51989579200745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52929854393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52459669113159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4822850227356</t>
+    <t xml:space="preserve">2.56220746040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54183530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5198962688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52929830551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52459740638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034598350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131562232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228549957275</t>
   </si>
   <si>
     <t xml:space="preserve">2.43370532989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39609527587891</t>
+    <t xml:space="preserve">2.39609479904175</t>
   </si>
   <si>
     <t xml:space="preserve">2.32087421417236</t>
@@ -974,25 +974,25 @@
     <t xml:space="preserve">2.2879650592804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34908199310303</t>
+    <t xml:space="preserve">2.34908175468445</t>
   </si>
   <si>
     <t xml:space="preserve">2.36475276947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35064935684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848498344421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333341598511</t>
+    <t xml:space="preserve">2.35064888000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848450660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333293914795</t>
   </si>
   <si>
     <t xml:space="preserve">2.43683958053589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62489151954651</t>
+    <t xml:space="preserve">2.62489175796509</t>
   </si>
   <si>
     <t xml:space="preserve">2.6327269077301</t>
@@ -1004,10 +1004,10 @@
     <t xml:space="preserve">2.36632013320923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38199090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766240119934</t>
+    <t xml:space="preserve">2.381991147995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766192436218</t>
   </si>
   <si>
     <t xml:space="preserve">2.45251059532166</t>
@@ -1016,67 +1016,67 @@
     <t xml:space="preserve">2.40549755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4211688041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900395393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363631248474</t>
+    <t xml:space="preserve">2.42116832733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878740310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363607406616</t>
   </si>
   <si>
     <t xml:space="preserve">2.25662302970886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27229428291321</t>
+    <t xml:space="preserve">2.27229404449463</t>
   </si>
   <si>
     <t xml:space="preserve">2.28012943267822</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26445841789246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1235978603363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0995569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08352947235107</t>
+    <t xml:space="preserve">2.26445865631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528123855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12359762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09955716133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08352994918823</t>
   </si>
   <si>
     <t xml:space="preserve">2.09154367446899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942133903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339388847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750273704529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18770623207092</t>
+    <t xml:space="preserve">2.01942157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339436531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750297546387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188275337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13962507247925</t>
+    <t xml:space="preserve">2.13962483406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.16366577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14763832092285</t>
+    <t xml:space="preserve">2.14763855934143</t>
   </si>
   <si>
     <t xml:space="preserve">2.20373368263245</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">2.13161134719849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17167901992798</t>
+    <t xml:space="preserve">2.17167925834656</t>
   </si>
   <si>
     <t xml:space="preserve">2.19571995735168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17969298362732</t>
+    <t xml:space="preserve">2.17969250679016</t>
   </si>
   <si>
     <t xml:space="preserve">2.10757064819336</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">2.05948901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07551646232605</t>
+    <t xml:space="preserve">2.07551622390747</t>
   </si>
   <si>
     <t xml:space="preserve">2.03544855117798</t>
@@ -1109,31 +1109,31 @@
     <t xml:space="preserve">2.05147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27585554122925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784229278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21976065635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21174716949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2438018321991</t>
+    <t xml:space="preserve">2.27585577964783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784205436707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21976089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21174693107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24380135536194</t>
   </si>
   <si>
     <t xml:space="preserve">2.23578786849976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22777414321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15565252304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30790996551514</t>
+    <t xml:space="preserve">2.22777438163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15565228462219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30791020393372</t>
   </si>
   <si>
     <t xml:space="preserve">2.02743482589722</t>
@@ -1142,25 +1142,25 @@
     <t xml:space="preserve">2.04346203804016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99538052082062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524469852448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325818538666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96332621574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9713397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736703395844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140785217285</t>
+    <t xml:space="preserve">1.9953807592392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524493694305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325842380524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96332633495331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736715316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140761375427</t>
   </si>
   <si>
     <t xml:space="preserve">1.81106841564178</t>
@@ -1169,46 +1169,46 @@
     <t xml:space="preserve">1.81908178329468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84312295913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79504120349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901411056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709562778473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100026607513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73093259334564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69887828826904</t>
+    <t xml:space="preserve">1.84312260150909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79504108428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77901422977448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709550857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77100074291229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73093271255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69887804985046</t>
   </si>
   <si>
     <t xml:space="preserve">1.7149053812027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7469596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72291898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73894608020782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298689842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75497341156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305457115173</t>
+    <t xml:space="preserve">1.74695992469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72291874885559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7389463186264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298677921295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75497317314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305469036102</t>
   </si>
   <si>
     <t xml:space="preserve">1.85914981365204</t>
@@ -1217,49 +1217,49 @@
     <t xml:space="preserve">1.8671635389328</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83510899543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517666816711</t>
+    <t xml:space="preserve">1.83510911464691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517714500427</t>
   </si>
   <si>
     <t xml:space="preserve">1.90723145008087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97935342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9392853975296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082967758179</t>
+    <t xml:space="preserve">1.97935354709625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93928587436676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082920074463</t>
   </si>
   <si>
     <t xml:space="preserve">2.01258134841919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98783624172211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99608480930328</t>
+    <t xml:space="preserve">1.98783659934998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99608469009399</t>
   </si>
   <si>
     <t xml:space="preserve">1.96309161186218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9383465051651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9795880317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03732585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0620710849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05382251739502</t>
+    <t xml:space="preserve">1.93834638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97958815097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0373260974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06207084655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0538227558136</t>
   </si>
   <si>
     <t xml:space="preserve">2.09506392478943</t>
@@ -1271,10 +1271,10 @@
     <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11156034469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10331249237061</t>
+    <t xml:space="preserve">2.1115608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10331225395203</t>
   </si>
   <si>
     <t xml:space="preserve">2.12805724143982</t>
@@ -1295,16 +1295,16 @@
     <t xml:space="preserve">2.22703647613525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21878838539124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25178170204163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24353289604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21054005622864</t>
+    <t xml:space="preserve">2.21878814697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25178146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24353337287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21054029464722</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002979278564</t>
@@ -1316,34 +1316,34 @@
     <t xml:space="preserve">2.33426427841187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30951929092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30127120018005</t>
+    <t xml:space="preserve">2.30951952934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30127096176147</t>
   </si>
   <si>
     <t xml:space="preserve">2.31776785850525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38375425338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3755054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601594924927</t>
+    <t xml:space="preserve">2.38375401496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37550568580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601571083069</t>
   </si>
   <si>
     <t xml:space="preserve">2.27652645111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28477430343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29302263259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23528504371643</t>
+    <t xml:space="preserve">2.28477454185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29302287101746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23528480529785</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200234413147</t>
@@ -1355,67 +1355,67 @@
     <t xml:space="preserve">2.41674709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43324375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849900245667</t>
+    <t xml:space="preserve">2.43324398994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849876403809</t>
   </si>
   <si>
     <t xml:space="preserve">2.42499566078186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798873901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4992299079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47448539733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5157265663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5899612903595</t>
+    <t xml:space="preserve">2.45798850059509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49922966957092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47448515892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51572632789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
     <t xml:space="preserve">2.54871940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4909815788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5074782371521</t>
+    <t xml:space="preserve">2.49098181724548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50747847557068</t>
   </si>
   <si>
     <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35076069831848</t>
+    <t xml:space="preserve">2.35076117515564</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025067329407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1940438747406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.185795545578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04557418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87236022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264985084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089818000793</t>
+    <t xml:space="preserve">2.19404339790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18579530715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.045574426651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87236034870148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060867786407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264973163605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089806079865</t>
   </si>
   <si>
     <t xml:space="preserve">1.56717395782471</t>
@@ -1439,64 +1439,64 @@
     <t xml:space="preserve">1.78162944316864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74863600730896</t>
+    <t xml:space="preserve">1.74863612651825</t>
   </si>
   <si>
     <t xml:space="preserve">1.80637407302856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86411237716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00433278083801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81462240219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287085056305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84761524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111882209778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78987741470337</t>
+    <t xml:space="preserve">1.86411225795746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00433301925659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81462252140045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84761559963226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111917972565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78987765312195</t>
   </si>
   <si>
     <t xml:space="preserve">1.88885700702667</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9136016368866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710533618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90535366535187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9548431634903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907776832581</t>
+    <t xml:space="preserve">1.91360175609589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8971049785614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90535354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95484340190887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907800674438</t>
   </si>
   <si>
     <t xml:space="preserve">2.08681559562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17754673957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07031941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07786917686462</t>
+    <t xml:space="preserve">2.17754697799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07031917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07786893844604</t>
   </si>
   <si>
     <t xml:space="preserve">2.06938791275024</t>
@@ -1505,31 +1505,31 @@
     <t xml:space="preserve">2.03546357154846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9845769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609567642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065248012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9930579662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06090712547302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02698230743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05242586135864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04394435882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01002049446106</t>
+    <t xml:space="preserve">1.98457670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609579563141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065224170685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99305784702301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06090688705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02698254585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05242562294006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04394483566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01002025604248</t>
   </si>
   <si>
     <t xml:space="preserve">2.0015389919281</t>
@@ -1538,22 +1538,22 @@
     <t xml:space="preserve">1.89976596832275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88280379772186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128506183624</t>
+    <t xml:space="preserve">1.88280391693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128482341766</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850152015686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95913350582123</t>
+    <t xml:space="preserve">1.95913362503052</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875556945801</t>
+    <t xml:space="preserve">2.12875533103943</t>
   </si>
   <si>
     <t xml:space="preserve">2.12027454376221</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">2.20508527755737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23052859306335</t>
+    <t xml:space="preserve">2.23052906990051</t>
   </si>
   <si>
     <t xml:space="preserve">2.30685877799988</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559432983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255638122559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47648072242737</t>
+    <t xml:space="preserve">2.42559409141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255614280701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47648048400879</t>
   </si>
   <si>
     <t xml:space="preserve">2.46799969673157</t>
@@ -1595,31 +1595,31 @@
     <t xml:space="preserve">2.49344301223755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51040530204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43407511711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41711258888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888632774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58673501014709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54432940483093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57825374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56129193305969</t>
+    <t xml:space="preserve">2.51040506362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43407487869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4171130657196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888608932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58673477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977248191833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54432964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57825398445129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56129169464111</t>
   </si>
   <si>
     <t xml:space="preserve">2.55281043052673</t>
@@ -1631,16 +1631,16 @@
     <t xml:space="preserve">2.52736711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6461021900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63762140274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66306495666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70547032356262</t>
+    <t xml:space="preserve">2.64610242843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63762164115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66306471824646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70547008514404</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698905944824</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">2.62914037704468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71395134925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7309136390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77331876754761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78179979324341</t>
+    <t xml:space="preserve">2.71395182609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73091387748718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77331900596619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78180003166199</t>
   </si>
   <si>
     <t xml:space="preserve">2.84116792678833</t>
@@ -1676,55 +1676,55 @@
     <t xml:space="preserve">2.85812997817993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80724334716797</t>
+    <t xml:space="preserve">2.80724382400513</t>
   </si>
   <si>
     <t xml:space="preserve">2.75635695457458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73939490318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74787592887878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79876232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79028129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84964919090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268666267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82420539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91749787330627</t>
+    <t xml:space="preserve">2.7393946647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74787569046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79876255989075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79028105735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84964895248413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268642425537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82420563697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9174976348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.01078963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03623294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95990300178528</t>
+    <t xml:space="preserve">3.0362331867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95990324020386</t>
   </si>
   <si>
     <t xml:space="preserve">3.07863879203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08711981773376</t>
+    <t xml:space="preserve">3.08711957931519</t>
   </si>
   <si>
     <t xml:space="preserve">3.12104415893555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18041205406189</t>
+    <t xml:space="preserve">3.18041181564331</t>
   </si>
   <si>
     <t xml:space="preserve">3.14648723602295</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281742095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23129844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24826049804688</t>
+    <t xml:space="preserve">3.22281718254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23129820823669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24826073646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.21433615684509</t>
@@ -1751,31 +1751,31 @@
     <t xml:space="preserve">3.40092039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42636346817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36699604988098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3161096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29066634178162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27370357513428</t>
+    <t xml:space="preserve">3.42636394500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3669958114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31610941886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29066610336304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27370381355286</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31657671928406</t>
+    <t xml:space="preserve">3.31657695770264</t>
   </si>
   <si>
     <t xml:space="preserve">3.27339220046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35112500190735</t>
+    <t xml:space="preserve">3.35112452507019</t>
   </si>
   <si>
     <t xml:space="preserve">3.34248757362366</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430904388428</t>
+    <t xml:space="preserve">3.39430928230286</t>
   </si>
   <si>
     <t xml:space="preserve">3.44613075256348</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">3.45476770401001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47204160690308</t>
+    <t xml:space="preserve">3.4720413684845</t>
   </si>
   <si>
     <t xml:space="preserve">3.54113674163818</t>
@@ -1802,19 +1802,19 @@
     <t xml:space="preserve">3.60159516334534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5929582118988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65341663360596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61023187637329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71387553215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6706907749176</t>
+    <t xml:space="preserve">3.59295797348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65341687202454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61023163795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71387529373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069053649902</t>
   </si>
   <si>
     <t xml:space="preserve">3.7829704284668</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">3.62750577926636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64477968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73978590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75705933570862</t>
+    <t xml:space="preserve">3.644779920578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73978567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75705981254578</t>
   </si>
   <si>
     <t xml:space="preserve">3.55841040611267</t>
@@ -1844,13 +1844,13 @@
     <t xml:space="preserve">3.67932772636414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57568454742432</t>
+    <t xml:space="preserve">3.57568430900574</t>
   </si>
   <si>
     <t xml:space="preserve">3.58432149887085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.705237865448</t>
+    <t xml:space="preserve">3.70523810386658</t>
   </si>
   <si>
     <t xml:space="preserve">3.52386283874512</t>
@@ -1859,22 +1859,22 @@
     <t xml:space="preserve">3.5497739315033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48931503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41158294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51522612571716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68796443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74842286109924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66205334663391</t>
+    <t xml:space="preserve">3.48931550979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41158318519592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51522588729858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68796420097351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74842309951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66205358505249</t>
   </si>
   <si>
     <t xml:space="preserve">3.61886930465698</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">3.86933970451355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82615518569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8607029914856</t>
+    <t xml:space="preserve">3.8261547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86070275306702</t>
   </si>
   <si>
     <t xml:space="preserve">3.91252446174622</t>
@@ -1898,10 +1898,10 @@
     <t xml:space="preserve">3.9557089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99025630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342861175537</t>
+    <t xml:space="preserve">3.99025654792786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342885017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.77433347702026</t>
@@ -1910,52 +1910,52 @@
     <t xml:space="preserve">3.76569700241089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92979788780212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661360740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9038872718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87797617912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81751847267151</t>
+    <t xml:space="preserve">3.92979836463928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661336898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90388774871826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8779764175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81751823425293</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89525032043457</t>
+    <t xml:space="preserve">3.89525055885315</t>
   </si>
   <si>
     <t xml:space="preserve">3.93843507766724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63614296913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49795246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42885708808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42022013664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28202939033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2561182975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29066610336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24748134613037</t>
+    <t xml:space="preserve">3.63614320755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4979522228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42885661125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021989822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2820291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25611853599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29066586494446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24748158454895</t>
   </si>
   <si>
     <t xml:space="preserve">3.29930305480957</t>
@@ -1967,49 +1967,49 @@
     <t xml:space="preserve">3.33385062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43749356269836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37703561782837</t>
+    <t xml:space="preserve">3.43749380111694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37703537940979</t>
   </si>
   <si>
     <t xml:space="preserve">3.40294623374939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35976147651672</t>
+    <t xml:space="preserve">3.3597617149353</t>
   </si>
   <si>
     <t xml:space="preserve">3.2129340171814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23020768165588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15247535705566</t>
+    <t xml:space="preserve">3.23020792007446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15247559547424</t>
   </si>
   <si>
     <t xml:space="preserve">3.11792778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19565987586975</t>
+    <t xml:space="preserve">3.19566011428833</t>
   </si>
   <si>
     <t xml:space="preserve">3.14383840560913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97973728179932</t>
+    <t xml:space="preserve">2.97973704338074</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610608100891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53250002861023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5670473575592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46340441703796</t>
+    <t xml:space="preserve">3.53250026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56704759597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46340465545654</t>
   </si>
   <si>
     <t xml:space="preserve">3.38567209243774</t>
@@ -2091,9 +2091,6 @@
   </si>
   <si>
     <t xml:space="preserve">3.5599410533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4979522228241</t>
   </si>
   <si>
     <t xml:space="preserve">3.46252989768982</t>
@@ -46908,7 +46905,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1677" t="s">
-        <v>693</v>
+        <v>641</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46934,7 +46931,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1678" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -46986,7 +46983,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1680" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47012,7 +47009,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1681" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47142,7 +47139,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1686" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47168,7 +47165,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1687" t="s">
-        <v>693</v>
+        <v>641</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47194,7 +47191,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1688" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47220,7 +47217,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1689" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47298,7 +47295,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1692" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47324,7 +47321,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1693" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47350,7 +47347,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1694" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47428,7 +47425,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1697" t="s">
-        <v>693</v>
+        <v>641</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47454,7 +47451,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1698" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47480,7 +47477,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47506,7 +47503,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1700" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47558,7 +47555,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1702" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47584,7 +47581,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1703" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47610,7 +47607,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1704" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47636,7 +47633,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1705" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47766,7 +47763,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47818,7 +47815,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47844,7 +47841,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1713" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47870,7 +47867,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47896,7 +47893,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1715" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47922,7 +47919,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47948,7 +47945,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1717" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47974,7 +47971,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48000,7 +47997,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48026,7 +48023,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48052,7 +48049,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48078,7 +48075,7 @@
         <v>3</v>
       </c>
       <c r="G1722" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48104,7 +48101,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1723" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48130,7 +48127,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48156,7 +48153,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1725" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48182,7 +48179,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1726" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48208,7 +48205,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1727" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48234,7 +48231,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48260,7 +48257,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48286,7 +48283,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1730" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48312,7 +48309,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1731" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48338,7 +48335,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48364,7 +48361,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1733" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48390,7 +48387,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1734" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48416,7 +48413,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1735" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48442,7 +48439,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1736" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48468,7 +48465,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1737" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48494,7 +48491,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1738" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48520,7 +48517,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1739" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48546,7 +48543,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1740" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48572,7 +48569,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1741" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48598,7 +48595,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1742" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48624,7 +48621,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48650,7 +48647,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1744" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48676,7 +48673,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1745" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48702,7 +48699,7 @@
         <v>3.5</v>
       </c>
       <c r="G1746" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48728,7 +48725,7 @@
         <v>3.5</v>
       </c>
       <c r="G1747" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48754,7 +48751,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1748" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48780,7 +48777,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1749" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48806,7 +48803,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1750" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48832,7 +48829,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48858,7 +48855,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1752" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48884,7 +48881,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1753" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48910,7 +48907,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1754" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48936,7 +48933,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1755" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48962,7 +48959,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1756" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -48988,7 +48985,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1757" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49014,7 +49011,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49040,7 +49037,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1759" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49066,7 +49063,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49092,7 +49089,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1761" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49118,7 +49115,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1762" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49144,7 +49141,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1763" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49170,7 +49167,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1764" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49196,7 +49193,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1765" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49222,7 +49219,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1766" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49248,7 +49245,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1767" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49274,7 +49271,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1768" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49300,7 +49297,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1769" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49326,7 +49323,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1770" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49352,7 +49349,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1771" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49378,7 +49375,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1772" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49404,7 +49401,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1773" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49430,7 +49427,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1774" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49456,7 +49453,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1775" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49482,7 +49479,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1776" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49508,7 +49505,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49534,7 +49531,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1778" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49560,7 +49557,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1779" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49586,7 +49583,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49612,7 +49609,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1781" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49638,7 +49635,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1782" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49664,7 +49661,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49690,7 +49687,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1784" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49716,7 +49713,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1785" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49742,7 +49739,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1786" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49768,7 +49765,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1787" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49794,7 +49791,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49820,7 +49817,7 @@
         <v>3.25</v>
       </c>
       <c r="G1789" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49846,7 +49843,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1790" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49872,7 +49869,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1791" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49898,7 +49895,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1792" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49924,7 +49921,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1793" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49950,7 +49947,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49976,7 +49973,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50002,7 +49999,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1796" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50028,7 +50025,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1797" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50054,7 +50051,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1798" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50080,7 +50077,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1799" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50106,7 +50103,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1800" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50132,7 +50129,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1801" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50158,7 +50155,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50210,7 +50207,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1804" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50236,7 +50233,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1805" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50262,7 +50259,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1806" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50288,7 +50285,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1807" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50314,7 +50311,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1808" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50392,7 +50389,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1811" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50600,7 +50597,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1819" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50782,7 +50779,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1826" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50808,7 +50805,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1827" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50834,7 +50831,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1828" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50886,7 +50883,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1830" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50912,7 +50909,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50938,7 +50935,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1832" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50964,7 +50961,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1833" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -50990,7 +50987,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51016,7 +51013,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1835" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51094,7 +51091,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1838" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51250,7 +51247,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1844" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51328,7 +51325,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1847" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51510,7 +51507,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1854" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51536,7 +51533,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51562,7 +51559,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1856" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51614,7 +51611,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1858" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51640,7 +51637,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1859" t="s">
-        <v>693</v>
+        <v>641</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51666,7 +51663,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1860" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51718,7 +51715,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51822,7 +51819,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1866" t="s">
-        <v>693</v>
+        <v>641</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51848,7 +51845,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1867" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51978,7 +51975,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1872" t="s">
-        <v>693</v>
+        <v>641</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52108,7 +52105,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1877" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52160,7 +52157,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1879" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52186,7 +52183,7 @@
         <v>4</v>
       </c>
       <c r="G1880" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52212,7 +52209,7 @@
         <v>4</v>
       </c>
       <c r="G1881" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52238,7 +52235,7 @@
         <v>4</v>
       </c>
       <c r="G1882" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52264,7 +52261,7 @@
         <v>4</v>
       </c>
       <c r="G1883" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52290,7 +52287,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52316,7 +52313,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1885" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52342,7 +52339,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1886" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52368,7 +52365,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52394,7 +52391,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1888" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52420,7 +52417,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1889" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52446,7 +52443,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52472,7 +52469,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1891" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52498,7 +52495,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1892" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52524,7 +52521,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1893" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52550,7 +52547,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1894" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52576,7 +52573,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52602,7 +52599,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1896" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52628,7 +52625,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1897" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52654,7 +52651,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1898" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52680,7 +52677,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1899" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52706,7 +52703,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1900" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52732,7 +52729,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52758,7 +52755,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52784,7 +52781,7 @@
         <v>4</v>
       </c>
       <c r="G1903" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52810,7 +52807,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1904" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52836,7 +52833,7 @@
         <v>4</v>
       </c>
       <c r="G1905" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52862,7 +52859,7 @@
         <v>4</v>
       </c>
       <c r="G1906" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52888,7 +52885,7 @@
         <v>4</v>
       </c>
       <c r="G1907" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52914,7 +52911,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1908" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52940,7 +52937,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1909" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52966,7 +52963,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1910" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -52992,7 +52989,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1911" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53018,7 +53015,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1912" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53044,7 +53041,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1913" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53070,7 +53067,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1914" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53096,7 +53093,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1915" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53122,7 +53119,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1916" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53148,7 +53145,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1917" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53174,7 +53171,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1918" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53200,7 +53197,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1919" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53226,7 +53223,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1920" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53252,7 +53249,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1921" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53278,7 +53275,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1922" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53304,7 +53301,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1923" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53330,7 +53327,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1924" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53356,7 +53353,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1925" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53382,7 +53379,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1926" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53408,7 +53405,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1927" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53434,7 +53431,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1928" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53460,7 +53457,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1929" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53486,7 +53483,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1930" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53512,7 +53509,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1931" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53538,7 +53535,7 @@
         <v>4.25</v>
       </c>
       <c r="G1932" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53564,7 +53561,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1933" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53590,7 +53587,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1934" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53616,7 +53613,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1935" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53642,7 +53639,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1936" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53668,7 +53665,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53694,7 +53691,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1938" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53720,7 +53717,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53746,7 +53743,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1940" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53772,7 +53769,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1941" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53798,7 +53795,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1942" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53824,7 +53821,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1943" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53850,7 +53847,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1944" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53876,7 +53873,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1945" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53902,7 +53899,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1946" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -53928,7 +53925,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1947" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53954,7 +53951,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1948" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -53980,7 +53977,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1949" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54006,7 +54003,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1950" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54032,7 +54029,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54058,7 +54055,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1952" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54084,7 +54081,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1953" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54110,7 +54107,7 @@
         <v>4</v>
       </c>
       <c r="G1954" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54136,7 +54133,7 @@
         <v>4</v>
       </c>
       <c r="G1955" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54162,7 +54159,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54188,7 +54185,7 @@
         <v>4</v>
       </c>
       <c r="G1957" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54214,7 +54211,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1958" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54240,7 +54237,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1959" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54266,7 +54263,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1960" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54292,7 +54289,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1961" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54318,7 +54315,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1962" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54344,7 +54341,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1963" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54370,7 +54367,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1964" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54396,7 +54393,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1965" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54422,7 +54419,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1966" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54448,7 +54445,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1967" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54474,7 +54471,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1968" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54500,7 +54497,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54526,7 +54523,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1970" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54552,7 +54549,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1971" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54578,7 +54575,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1972" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54604,7 +54601,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1973" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54630,7 +54627,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1974" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54656,7 +54653,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1975" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54682,7 +54679,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54708,7 +54705,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1977" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54734,7 +54731,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1978" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54760,7 +54757,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1979" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54786,7 +54783,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54812,7 +54809,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1981" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54838,7 +54835,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1982" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54864,7 +54861,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1983" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54890,7 +54887,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1984" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54916,7 +54913,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1985" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54942,7 +54939,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1986" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -54968,7 +54965,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1987" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -54994,7 +54991,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55020,7 +55017,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1989" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55046,7 +55043,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1990" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55072,7 +55069,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1991" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55098,7 +55095,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1992" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55124,7 +55121,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55150,7 +55147,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55176,7 +55173,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55202,7 +55199,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1996" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55228,7 +55225,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1997" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55254,7 +55251,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55280,7 +55277,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1999" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55306,7 +55303,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2000" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55332,7 +55329,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55358,7 +55355,7 @@
         <v>4</v>
       </c>
       <c r="G2002" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55384,7 +55381,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2003" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55410,7 +55407,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2004" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55436,7 +55433,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2005" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55462,7 +55459,7 @@
         <v>4</v>
       </c>
       <c r="G2006" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55488,7 +55485,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2007" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55514,7 +55511,7 @@
         <v>4</v>
       </c>
       <c r="G2008" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55540,7 +55537,7 @@
         <v>4</v>
       </c>
       <c r="G2009" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55566,7 +55563,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G2010" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55592,7 +55589,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2011" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55618,7 +55615,7 @@
         <v>4</v>
       </c>
       <c r="G2012" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55644,7 +55641,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2013" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55670,7 +55667,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2014" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55696,7 +55693,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55722,7 +55719,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55748,7 +55745,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55774,7 +55771,7 @@
         <v>4</v>
       </c>
       <c r="G2018" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55800,7 +55797,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2019" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55826,7 +55823,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2020" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55852,7 +55849,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2021" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55878,7 +55875,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2022" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55904,7 +55901,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2023" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55930,7 +55927,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2024" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -55956,7 +55953,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -55982,7 +55979,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56008,7 +56005,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56034,7 +56031,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2028" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56060,7 +56057,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2029" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56086,7 +56083,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2030" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56112,7 +56109,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2031" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56138,7 +56135,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2032" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56164,7 +56161,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2033" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56190,7 +56187,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2034" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56216,7 +56213,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2035" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56242,7 +56239,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2036" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56268,7 +56265,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2037" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56294,7 +56291,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2038" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56320,7 +56317,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2039" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56346,7 +56343,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2040" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56372,7 +56369,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2041" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56398,7 +56395,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2042" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56424,7 +56421,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2043" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56450,7 +56447,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2044" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -56476,7 +56473,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2045" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56502,7 +56499,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2046" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56528,7 +56525,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2047" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56554,7 +56551,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2048" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56580,7 +56577,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2049" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56606,7 +56603,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2050" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56632,7 +56629,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2051" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56658,7 +56655,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2052" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56684,7 +56681,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2053" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56710,7 +56707,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2054" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56736,7 +56733,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2055" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56762,7 +56759,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56788,7 +56785,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G2057" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56814,7 +56811,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2058" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56840,7 +56837,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2059" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56866,7 +56863,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2060" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56892,7 +56889,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2061" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56918,7 +56915,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2062" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56944,7 +56941,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2063" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -56970,7 +56967,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2064" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -56996,7 +56993,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2065" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57022,7 +57019,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2066" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57048,7 +57045,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2067" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57074,7 +57071,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2068" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57100,7 +57097,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2069" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57126,7 +57123,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2070" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57152,7 +57149,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2071" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57178,7 +57175,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2072" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57204,7 +57201,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2073" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57230,7 +57227,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2074" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57256,7 +57253,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2075" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57282,7 +57279,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2076" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57308,7 +57305,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2077" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -57334,7 +57331,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2078" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57360,7 +57357,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57386,7 +57383,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2080" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57412,7 +57409,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2081" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57438,7 +57435,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2082" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57464,7 +57461,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2083" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57490,7 +57487,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2084" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57516,7 +57513,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2085" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57542,7 +57539,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2086" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57568,7 +57565,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2087" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57594,7 +57591,7 @@
         <v>4.5</v>
       </c>
       <c r="G2088" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57620,7 +57617,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2089" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57646,7 +57643,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G2090" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57672,7 +57669,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2091" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57698,7 +57695,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2092" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57724,7 +57721,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2093" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57750,7 +57747,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G2094" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57776,7 +57773,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2095" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57802,7 +57799,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2096" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57828,7 +57825,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57854,7 +57851,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2098" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57880,7 +57877,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2099" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57906,7 +57903,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2100" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57932,7 +57929,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2101" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57958,7 +57955,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2102" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -57984,7 +57981,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2103" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58010,7 +58007,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2104" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58036,7 +58033,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2105" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58062,7 +58059,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2106" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58088,7 +58085,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2107" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58114,7 +58111,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2108" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58140,7 +58137,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2109" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58166,7 +58163,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G2110" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58192,7 +58189,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2111" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58218,7 +58215,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G2112" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58244,7 +58241,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2113" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58270,7 +58267,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G2114" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58296,7 +58293,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2115" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58322,7 +58319,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58348,7 +58345,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2117" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58374,7 +58371,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2118" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58400,7 +58397,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2119" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58426,7 +58423,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2120" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58452,7 +58449,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2121" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58478,7 +58475,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2122" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58504,7 +58501,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2123" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58530,7 +58527,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2124" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58556,7 +58553,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2125" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58582,7 +58579,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2126" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58608,7 +58605,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2127" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58634,7 +58631,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2128" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58660,7 +58657,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2129" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58686,7 +58683,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2130" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58712,7 +58709,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2131" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58738,7 +58735,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2132" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58764,7 +58761,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2133" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58790,7 +58787,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2134" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58816,7 +58813,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2135" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58842,7 +58839,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2136" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58868,7 +58865,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2137" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58894,7 +58891,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2138" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58920,7 +58917,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2139" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58946,7 +58943,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2140" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -58972,7 +58969,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2141" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -58998,7 +58995,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2142" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59024,7 +59021,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2143" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59050,7 +59047,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2144" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59076,7 +59073,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2145" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59102,7 +59099,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2146" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59128,7 +59125,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2147" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59154,7 +59151,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G2148" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59180,7 +59177,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2149" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59206,7 +59203,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2150" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59232,7 +59229,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2151" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59258,7 +59255,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2152" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59284,7 +59281,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2153" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59310,7 +59307,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2154" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59336,7 +59333,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2155" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59362,7 +59359,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2156" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59388,7 +59385,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2157" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59414,7 +59411,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2158" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59440,7 +59437,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2159" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59466,7 +59463,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2160" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59492,7 +59489,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2161" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59518,7 +59515,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2162" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59544,7 +59541,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2163" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59570,7 +59567,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2164" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59596,7 +59593,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2165" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59622,7 +59619,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2166" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59648,7 +59645,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2167" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59674,7 +59671,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2168" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59700,7 +59697,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2169" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59726,7 +59723,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2170" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59752,7 +59749,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2171" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59778,7 +59775,7 @@
         <v>5.5</v>
       </c>
       <c r="G2172" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59804,7 +59801,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59830,7 +59827,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2174" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59856,7 +59853,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2175" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59882,7 +59879,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2176" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59908,7 +59905,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2177" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59934,7 +59931,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2178" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59960,7 +59957,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2179" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -59986,7 +59983,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2180" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60012,7 +60009,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2181" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60038,7 +60035,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2182" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60064,7 +60061,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2183" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60090,7 +60087,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2184" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60116,7 +60113,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2185" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60142,7 +60139,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2186" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60168,7 +60165,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2187" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60194,7 +60191,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60220,7 +60217,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2189" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60246,7 +60243,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2190" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60272,7 +60269,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2191" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60298,7 +60295,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2192" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60324,7 +60321,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2193" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60350,7 +60347,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2194" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60376,7 +60373,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2195" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60402,7 +60399,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2196" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60428,7 +60425,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2197" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60454,7 +60451,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2198" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60480,7 +60477,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2199" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60506,7 +60503,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2200" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60532,7 +60529,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2201" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60558,7 +60555,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2202" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60584,7 +60581,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2203" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60610,7 +60607,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2204" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60636,7 +60633,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60662,7 +60659,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2206" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60688,7 +60685,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2207" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60714,7 +60711,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2208" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60740,7 +60737,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2209" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60766,7 +60763,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2210" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60792,7 +60789,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2211" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60818,7 +60815,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2212" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60844,7 +60841,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2213" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60870,7 +60867,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2214" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60896,7 +60893,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2215" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60922,7 +60919,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2216" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60948,7 +60945,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2217" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -60974,7 +60971,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2218" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61000,7 +60997,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2219" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61026,7 +61023,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2220" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61052,7 +61049,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2221" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61078,7 +61075,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2222" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61104,7 +61101,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2223" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61130,7 +61127,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2224" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61156,7 +61153,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2225" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61182,7 +61179,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61208,7 +61205,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61234,7 +61231,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61260,7 +61257,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61286,7 +61283,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2230" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61312,7 +61309,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2231" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61338,7 +61335,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2232" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61364,7 +61361,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2233" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61390,7 +61387,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2234" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61416,7 +61413,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2235" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61442,7 +61439,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2236" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61468,7 +61465,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2237" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61494,7 +61491,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2238" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61520,7 +61517,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2239" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61546,7 +61543,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2240" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61572,7 +61569,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2241" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61598,7 +61595,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2242" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61624,7 +61621,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2243" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61650,7 +61647,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2244" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61676,7 +61673,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2245" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61702,7 +61699,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2246" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61728,7 +61725,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61754,7 +61751,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2248" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61780,7 +61777,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61806,7 +61803,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2250" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61832,7 +61829,7 @@
         <v>6</v>
       </c>
       <c r="G2251" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61858,7 +61855,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G2252" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61884,7 +61881,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2253" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61910,7 +61907,7 @@
         <v>6</v>
       </c>
       <c r="G2254" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61936,7 +61933,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2255" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61962,7 +61959,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G2256" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -61988,7 +61985,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2257" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62014,7 +62011,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2258" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62040,7 +62037,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2259" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62066,7 +62063,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G2260" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62092,7 +62089,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2261" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62118,7 +62115,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2262" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62144,7 +62141,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2263" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62170,7 +62167,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2264" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62196,7 +62193,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2265" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62222,7 +62219,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2266" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62248,7 +62245,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2267" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62274,7 +62271,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2268" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62300,7 +62297,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2269" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62326,7 +62323,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2270" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62352,7 +62349,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2271" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62378,7 +62375,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2272" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62404,7 +62401,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2273" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62430,7 +62427,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2274" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62456,7 +62453,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2275" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62482,7 +62479,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2276" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62508,7 +62505,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G2277" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62534,7 +62531,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G2278" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62560,7 +62557,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G2279" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62586,7 +62583,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2280" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62612,7 +62609,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G2281" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62638,7 +62635,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2282" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62664,7 +62661,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2283" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62690,7 +62687,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G2284" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62716,7 +62713,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2285" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62742,7 +62739,7 @@
         <v>6.5</v>
       </c>
       <c r="G2286" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62768,7 +62765,7 @@
         <v>6.5</v>
       </c>
       <c r="G2287" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62794,7 +62791,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2288" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62820,7 +62817,7 @@
         <v>6.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62846,7 +62843,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G2290" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62872,7 +62869,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2291" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62898,7 +62895,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2292" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62924,7 +62921,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2293" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62950,7 +62947,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -62976,7 +62973,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G2295" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63002,7 +62999,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2296" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63028,7 +63025,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G2297" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63054,7 +63051,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G2298" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63080,7 +63077,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2299" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63106,7 +63103,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G2300" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63132,7 +63129,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G2301" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63158,7 +63155,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2302" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63184,7 +63181,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2303" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63210,7 +63207,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63236,7 +63233,7 @@
         <v>7</v>
       </c>
       <c r="G2305" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63262,7 +63259,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63288,7 +63285,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2307" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63314,7 +63311,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2308" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63340,7 +63337,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2309" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63366,7 +63363,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2310" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63392,7 +63389,7 @@
         <v>7</v>
       </c>
       <c r="G2311" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63418,7 +63415,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2312" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63444,7 +63441,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2313" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63470,7 +63467,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2314" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63496,7 +63493,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63522,7 +63519,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2316" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63548,7 +63545,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63574,7 +63571,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2318" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63600,7 +63597,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2319" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63626,7 +63623,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2320" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63652,7 +63649,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2321" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63678,7 +63675,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2322" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63704,7 +63701,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2323" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63730,7 +63727,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2324" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63756,7 +63753,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2325" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63782,7 +63779,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2326" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63808,7 +63805,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2327" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63834,7 +63831,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2328" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63860,7 +63857,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G2329" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63886,7 +63883,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2330" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63912,7 +63909,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2331" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63938,7 +63935,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2332" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63964,7 +63961,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2333" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -63990,7 +63987,7 @@
         <v>7.5</v>
       </c>
       <c r="G2334" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64016,7 +64013,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2335" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64042,7 +64039,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2336" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64068,7 +64065,7 @@
         <v>7.5</v>
       </c>
       <c r="G2337" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64094,7 +64091,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2338" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64120,7 +64117,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2339" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64146,7 +64143,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2340" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64172,7 +64169,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2341" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64198,7 +64195,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2342" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64224,7 +64221,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G2343" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64250,7 +64247,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2344" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64276,7 +64273,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G2345" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64302,7 +64299,7 @@
         <v>7.5</v>
       </c>
       <c r="G2346" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64328,7 +64325,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64354,7 +64351,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64380,7 +64377,7 @@
         <v>7.5</v>
       </c>
       <c r="G2349" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64406,7 +64403,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G2350" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64432,7 +64429,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2351" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64458,7 +64455,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2352" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64484,7 +64481,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2353" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64510,7 +64507,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2354" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64536,7 +64533,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2355" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64562,7 +64559,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2356" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64588,7 +64585,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2357" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64614,7 +64611,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2358" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64640,7 +64637,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G2359" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64666,7 +64663,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2360" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64692,7 +64689,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G2361" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64718,7 +64715,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2362" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64744,7 +64741,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2363" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64770,7 +64767,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G2364" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64796,7 +64793,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G2365" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64822,7 +64819,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G2366" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64848,7 +64845,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2367" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64874,7 +64871,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2368" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64900,7 +64897,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2369" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64926,7 +64923,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2370" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64952,7 +64949,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2371" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -64978,7 +64975,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2372" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65004,7 +65001,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2373" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65030,7 +65027,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2374" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65056,7 +65053,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2375" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65082,7 +65079,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2376" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65108,7 +65105,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G2377" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65134,7 +65131,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2378" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65160,7 +65157,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2379" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65186,7 +65183,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2380" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65212,7 +65209,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G2381" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65238,7 +65235,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2382" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65264,7 +65261,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65290,7 +65287,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2384" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65316,7 +65313,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2385" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65342,7 +65339,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2386" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65368,7 +65365,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2387" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65394,7 +65391,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2388" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65420,7 +65417,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2389" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65446,7 +65443,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2390" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65472,7 +65469,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2391" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65498,7 +65495,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2392" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65524,7 +65521,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2393" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65550,7 +65547,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2394" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65576,7 +65573,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2395" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65602,7 +65599,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2396" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65628,7 +65625,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2397" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65654,7 +65651,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2398" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65680,7 +65677,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2399" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65706,7 +65703,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2400" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65732,7 +65729,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2401" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65758,7 +65755,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2402" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65784,7 +65781,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2403" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65810,7 +65807,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2404" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65836,7 +65833,7 @@
         <v>7</v>
       </c>
       <c r="G2405" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65862,7 +65859,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2406" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65888,7 +65885,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2407" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65914,7 +65911,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2408" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65940,7 +65937,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2409" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65966,7 +65963,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2410" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -65992,7 +65989,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2411" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66018,7 +66015,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2412" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66044,7 +66041,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2413" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66070,7 +66067,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2414" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66096,7 +66093,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2415" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66122,7 +66119,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2416" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66148,7 +66145,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2417" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66174,7 +66171,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2418" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66200,7 +66197,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2419" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66226,7 +66223,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2420" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66252,7 +66249,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2421" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66278,7 +66275,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2422" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66304,7 +66301,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66330,7 +66327,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2424" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66356,7 +66353,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2425" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66382,7 +66379,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2426" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66408,7 +66405,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2427" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66434,7 +66431,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2428" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66460,7 +66457,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2429" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66486,7 +66483,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66512,7 +66509,7 @@
         <v>7</v>
       </c>
       <c r="G2431" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66538,7 +66535,7 @@
         <v>7</v>
       </c>
       <c r="G2432" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66564,7 +66561,7 @@
         <v>7</v>
       </c>
       <c r="G2433" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66590,7 +66587,7 @@
         <v>7</v>
       </c>
       <c r="G2434" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66616,7 +66613,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66642,7 +66639,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2436" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66668,7 +66665,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2437" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66694,7 +66691,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2438" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66720,7 +66717,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2439" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66746,7 +66743,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2440" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66772,7 +66769,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2441" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66798,7 +66795,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2442" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66824,7 +66821,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2443" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66850,7 +66847,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2444" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66876,7 +66873,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2445" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66902,7 +66899,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2446" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66928,7 +66925,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2447" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66954,7 +66951,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2448" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -66980,7 +66977,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2449" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67006,7 +67003,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2450" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67032,7 +67029,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2451" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67058,7 +67055,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2452" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67084,7 +67081,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2453" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67110,7 +67107,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2454" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67136,7 +67133,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2455" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67162,7 +67159,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2456" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67188,7 +67185,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2457" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67214,7 +67211,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G2458" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67240,7 +67237,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67266,7 +67263,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2460" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67292,7 +67289,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2461" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67318,7 +67315,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2462" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67344,7 +67341,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2463" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67370,7 +67367,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2464" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67396,7 +67393,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2465" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67422,7 +67419,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67448,7 +67445,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2467" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67474,7 +67471,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2468" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67500,7 +67497,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2469" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67526,7 +67523,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2470" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67552,7 +67549,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2471" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67578,7 +67575,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2472" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67604,7 +67601,7 @@
         <v>8.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67630,7 +67627,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G2474" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67656,7 +67653,7 @@
         <v>8.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67682,7 +67679,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2476" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67708,7 +67705,7 @@
         <v>8.5</v>
       </c>
       <c r="G2477" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67734,7 +67731,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67760,7 +67757,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2479" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67786,7 +67783,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67812,7 +67809,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2481" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67838,7 +67835,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G2482" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67864,7 +67861,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67890,7 +67887,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2484" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67916,7 +67913,7 @@
         <v>8.5</v>
       </c>
       <c r="G2485" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67942,7 +67939,7 @@
         <v>9</v>
       </c>
       <c r="G2486" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -67968,7 +67965,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -67994,7 +67991,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2488" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68020,7 +68017,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2489" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68046,7 +68043,7 @@
         <v>9</v>
       </c>
       <c r="G2490" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68072,7 +68069,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2491" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68098,7 +68095,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G2492" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68124,7 +68121,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G2493" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68150,7 +68147,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2494" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68176,7 +68173,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68202,7 +68199,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2496" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68228,7 +68225,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G2497" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68254,7 +68251,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2498" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68262,7 +68259,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6911342593</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>18331</v>
@@ -68280,9 +68277,35 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2499" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6911805556</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>21976</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>9.11999988555908</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>976</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,76 +38,76 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652267456055</t>
+    <t xml:space="preserve">1.73652255535126</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400770664215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71406769752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167259216309</t>
+    <t xml:space="preserve">1.74400758743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7140679359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6616724729538</t>
   </si>
   <si>
     <t xml:space="preserve">1.67215156555176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969658851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921785354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5733494758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49625372886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48053526878357</t>
+    <t xml:space="preserve">1.64969646930695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921761512756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57334935665131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49625384807587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48053514957428</t>
   </si>
   <si>
     <t xml:space="preserve">1.48203229904175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43637359142303</t>
+    <t xml:space="preserve">1.43637371063232</t>
   </si>
   <si>
     <t xml:space="preserve">1.44460713863373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4221522808075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990661621094</t>
+    <t xml:space="preserve">1.42215216159821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990649700165</t>
   </si>
   <si>
     <t xml:space="preserve">1.4146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41915822029114</t>
+    <t xml:space="preserve">1.41915810108185</t>
   </si>
   <si>
     <t xml:space="preserve">1.40718221664429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3824816942215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38472735881805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39820027351379</t>
+    <t xml:space="preserve">1.38248157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38472712039948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3982001543045</t>
   </si>
   <si>
     <t xml:space="preserve">1.35703265666962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33607459068298</t>
+    <t xml:space="preserve">1.33607447147369</t>
   </si>
   <si>
     <t xml:space="preserve">1.34730207920074</t>
@@ -119,22 +119,22 @@
     <t xml:space="preserve">1.38397872447968</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35478687286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38098454475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36975717544556</t>
+    <t xml:space="preserve">1.35478711128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38098466396332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36975705623627</t>
   </si>
   <si>
     <t xml:space="preserve">1.37873911857605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4311341047287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41017603874207</t>
+    <t xml:space="preserve">1.43113422393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41017627716064</t>
   </si>
   <si>
     <t xml:space="preserve">1.44535577297211</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">1.51197242736816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52544546127319</t>
+    <t xml:space="preserve">1.5254453420639</t>
   </si>
   <si>
     <t xml:space="preserve">1.52245128154755</t>
@@ -155,58 +155,58 @@
     <t xml:space="preserve">1.54490625858307</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54191255569458</t>
+    <t xml:space="preserve">1.54191219806671</t>
   </si>
   <si>
     <t xml:space="preserve">1.5493973493576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56287038326263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60029542446136</t>
+    <t xml:space="preserve">1.56287026405334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60029530525208</t>
   </si>
   <si>
     <t xml:space="preserve">1.60927748680115</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63173270225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63023567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676251888275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418756008148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64370882511139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682239055634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58831942081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472664356232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66017544269562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915738582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69161260128021</t>
+    <t xml:space="preserve">1.63173282146454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424743175507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63023555278778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676263809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418744087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370858669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682227134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58831930160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472652435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017556190491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66915762424469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712151050568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6916127204895</t>
   </si>
   <si>
     <t xml:space="preserve">1.69310963153839</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">1.72155272960663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73502552509308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358884334564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658254623413</t>
+    <t xml:space="preserve">1.73502576351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358860492706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658278465271</t>
   </si>
   <si>
     <t xml:space="preserve">1.69909775257111</t>
@@ -230,58 +230,58 @@
     <t xml:space="preserve">1.67664265632629</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6841276884079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66766047477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263041973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221155643463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64670240879059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514538764954</t>
+    <t xml:space="preserve">1.68412744998932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66766035556793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263065814972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64670264720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514562606812</t>
   </si>
   <si>
     <t xml:space="preserve">1.69964492321014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68433308601379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69198882579803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72108161449432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70576989650726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69505131244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495699882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72261321544647</t>
+    <t xml:space="preserve">1.6843329668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69198870658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7210818529129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70576977729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6950511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495711803436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72261297702789</t>
   </si>
   <si>
     <t xml:space="preserve">1.65370881557465</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67208325862885</t>
+    <t xml:space="preserve">1.67208302021027</t>
   </si>
   <si>
     <t xml:space="preserve">1.66902077198029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65217757225037</t>
+    <t xml:space="preserve">1.65217745304108</t>
   </si>
   <si>
     <t xml:space="preserve">1.606241106987</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">1.56183588504791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55417990684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121185302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59092891216278</t>
+    <t xml:space="preserve">1.5541797876358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202415466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121173381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59092903137207</t>
   </si>
   <si>
     <t xml:space="preserve">1.52891480922699</t>
@@ -311,22 +311,22 @@
     <t xml:space="preserve">1.53886771202087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49293148517609</t>
+    <t xml:space="preserve">1.4929313659668</t>
   </si>
   <si>
     <t xml:space="preserve">1.4760879278183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52278995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996331214905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761929035187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589965820312</t>
+    <t xml:space="preserve">1.52279007434845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589953899384</t>
   </si>
   <si>
     <t xml:space="preserve">1.50058746337891</t>
@@ -341,46 +341,46 @@
     <t xml:space="preserve">1.56949186325073</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62308418750763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66748940944672</t>
+    <t xml:space="preserve">1.62308406829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66748952865601</t>
   </si>
   <si>
     <t xml:space="preserve">1.66136467456818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6766768693924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61542820930481</t>
+    <t xml:space="preserve">1.67667675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6154283285141</t>
   </si>
   <si>
     <t xml:space="preserve">1.57714784145355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58480393886566</t>
+    <t xml:space="preserve">1.58480417728424</t>
   </si>
   <si>
     <t xml:space="preserve">1.63839650154114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6338027715683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57561683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54652392864227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56796073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54499244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355563640594</t>
+    <t xml:space="preserve">1.63380289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57561671733856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54652380943298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56796061992645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54499232769012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355551719666</t>
   </si>
   <si>
     <t xml:space="preserve">1.54193019866943</t>
@@ -392,10 +392,10 @@
     <t xml:space="preserve">1.55877351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58021056652069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55264854431152</t>
+    <t xml:space="preserve">1.58021032810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55264866352081</t>
   </si>
   <si>
     <t xml:space="preserve">1.53044617176056</t>
@@ -407,25 +407,25 @@
     <t xml:space="preserve">1.50594663619995</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50671207904816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427410125732</t>
+    <t xml:space="preserve">1.50671243667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427422046661</t>
   </si>
   <si>
     <t xml:space="preserve">1.56642949581146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57408547401428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58327305316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59246003627777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5021185874939</t>
+    <t xml:space="preserve">1.57408535480499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58327293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59246015548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50211870670319</t>
   </si>
   <si>
     <t xml:space="preserve">1.50824344158173</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">1.47532248497009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49675941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50747787952423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52968037128448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60011601448059</t>
+    <t xml:space="preserve">1.49675929546356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50747799873352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52968049049377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60011625289917</t>
   </si>
   <si>
     <t xml:space="preserve">1.58786654472351</t>
@@ -455,61 +455,61 @@
     <t xml:space="preserve">1.56336712837219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57255434989929</t>
+    <t xml:space="preserve">1.57255423069</t>
   </si>
   <si>
     <t xml:space="preserve">1.5985848903656</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59399151802063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60470974445343</t>
+    <t xml:space="preserve">1.59399127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60470962524414</t>
   </si>
   <si>
     <t xml:space="preserve">1.64758372306824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64605247974396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68280184268951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63074028491974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63686513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452111721039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227164745331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66289567947388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595816612244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333156108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026931285858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7455815076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017499923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730113983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423865318298</t>
+    <t xml:space="preserve">1.64605259895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68280160427094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63074052333832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63686525821686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452147483826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6322717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66289591789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595828533173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026919364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558162689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730102062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423877239227</t>
   </si>
   <si>
     <t xml:space="preserve">1.7379252910614</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">1.76089346408844</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78386151790619</t>
+    <t xml:space="preserve">1.78386163711548</t>
   </si>
   <si>
     <t xml:space="preserve">1.76854944229126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75323748588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486304283142</t>
+    <t xml:space="preserve">1.75323760509491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486280441284</t>
   </si>
   <si>
     <t xml:space="preserve">1.73639380931854</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">1.7915176153183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80223596096039</t>
+    <t xml:space="preserve">1.80223608016968</t>
   </si>
   <si>
     <t xml:space="preserve">1.82061076164246</t>
@@ -548,25 +548,25 @@
     <t xml:space="preserve">1.81754839420319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80682957172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520425319672</t>
+    <t xml:space="preserve">1.80682981014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8252044916153</t>
   </si>
   <si>
     <t xml:space="preserve">1.81448578834534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85889065265656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87726533412933</t>
+    <t xml:space="preserve">1.85889101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87726545333862</t>
   </si>
   <si>
     <t xml:space="preserve">1.85429716110229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85582852363586</t>
+    <t xml:space="preserve">1.85582876205444</t>
   </si>
   <si>
     <t xml:space="preserve">1.85123467445374</t>
@@ -575,94 +575,94 @@
     <t xml:space="preserve">1.86654698848724</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84970366954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348474025726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276615619659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745408058167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511017799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367312908173</t>
+    <t xml:space="preserve">1.84970343112946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348462104797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85276639461517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84511005878448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367300987244</t>
   </si>
   <si>
     <t xml:space="preserve">1.84051656723022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84817254543304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807835102081</t>
+    <t xml:space="preserve">1.84817278385162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8680784702301</t>
   </si>
   <si>
     <t xml:space="preserve">1.9492324590683</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90788984298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92167067527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932665348053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473304271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607613563538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904418945312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894951820374</t>
+    <t xml:space="preserve">1.90789008140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.921670794487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932689189911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473316192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607565879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904383182526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823117256165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894999504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.00741863250732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01201224327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99057519435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00282454490662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00588726997375</t>
+    <t xml:space="preserve">2.01201200485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99057507514954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00282502174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00588750839233</t>
   </si>
   <si>
     <t xml:space="preserve">2.09207773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09051084518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401677131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424210548401</t>
+    <t xml:space="preserve">2.09051036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401700973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424258232117</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558413505554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17043304443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14692640304565</t>
+    <t xml:space="preserve">2.17043280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14692616462708</t>
   </si>
   <si>
     <t xml:space="preserve">2.15006041526794</t>
@@ -671,16 +671,16 @@
     <t xml:space="preserve">2.12655401229858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16259717941284</t>
+    <t xml:space="preserve">2.16259741783142</t>
   </si>
   <si>
     <t xml:space="preserve">2.15162777900696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1390905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16102981567383</t>
+    <t xml:space="preserve">2.13909077644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16103005409241</t>
   </si>
   <si>
     <t xml:space="preserve">2.0466320514679</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">2.03722929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04819893836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0450644493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06543707847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073570251465</t>
+    <t xml:space="preserve">2.04819917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04506468772888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06543684005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073594093323</t>
   </si>
   <si>
     <t xml:space="preserve">2.10774874687195</t>
@@ -713,49 +713,49 @@
     <t xml:space="preserve">2.12341976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13125514984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296957015991</t>
+    <t xml:space="preserve">2.13125538825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296933174133</t>
   </si>
   <si>
     <t xml:space="preserve">2.19393920898438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20647621154785</t>
+    <t xml:space="preserve">2.20647597312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.20334196090698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19237184524536</t>
+    <t xml:space="preserve">2.19237208366394</t>
   </si>
   <si>
     <t xml:space="preserve">2.20804309844971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16416478157043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946340560913</t>
+    <t xml:space="preserve">2.16416430473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946316719055</t>
   </si>
   <si>
     <t xml:space="preserve">2.13595652580261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09677910804749</t>
+    <t xml:space="preserve">2.09677934646606</t>
   </si>
   <si>
     <t xml:space="preserve">2.0638701915741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02625966072083</t>
+    <t xml:space="preserve">2.02625942230225</t>
   </si>
   <si>
     <t xml:space="preserve">1.96827697753906</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99805164337158</t>
+    <t xml:space="preserve">1.99805200099945</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640671730042</t>
@@ -764,61 +764,61 @@
     <t xml:space="preserve">2.05446743965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10461473464966</t>
+    <t xml:space="preserve">2.10461497306824</t>
   </si>
   <si>
     <t xml:space="preserve">2.06700420379639</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03566241264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976582527161</t>
+    <t xml:space="preserve">2.03566217422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976606369019</t>
   </si>
   <si>
     <t xml:space="preserve">2.07954096794128</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0685715675354</t>
+    <t xml:space="preserve">2.06857132911682</t>
   </si>
   <si>
     <t xml:space="preserve">2.07797384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24095225334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371435165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.211177110672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2331166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781776428223</t>
+    <t xml:space="preserve">2.2409520149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371411323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21117758750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23311686515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781800270081</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930756568909</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3146059513092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3271427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557535171509</t>
+    <t xml:space="preserve">2.31460571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32714247703552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557559013367</t>
   </si>
   <si>
     <t xml:space="preserve">2.38982677459717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38669228553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44467520713806</t>
+    <t xml:space="preserve">2.3866925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4446747303009</t>
   </si>
   <si>
     <t xml:space="preserve">2.47601723670959</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">2.49012112617493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5214626789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735926628113</t>
+    <t xml:space="preserve">2.52146291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735878944397</t>
   </si>
   <si>
     <t xml:space="preserve">2.53870105743408</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">2.53086543083191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49168825149536</t>
+    <t xml:space="preserve">2.49168801307678</t>
   </si>
   <si>
     <t xml:space="preserve">2.50422477722168</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">2.52303004264832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53243279457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50892615318298</t>
+    <t xml:space="preserve">2.5324330329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206088066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5089259147644</t>
   </si>
   <si>
     <t xml:space="preserve">2.51362729072571</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">2.52616429328918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54653644561768</t>
+    <t xml:space="preserve">2.5465362071991</t>
   </si>
   <si>
     <t xml:space="preserve">2.55123782157898</t>
@@ -887,13 +887,13 @@
     <t xml:space="preserve">2.55437207221985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60608601570129</t>
+    <t xml:space="preserve">2.60608649253845</t>
   </si>
   <si>
     <t xml:space="preserve">2.70794796943665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71108174324036</t>
+    <t xml:space="preserve">2.71108198165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220516204834</t>
@@ -902,7 +902,7 @@
     <t xml:space="preserve">2.69541096687317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70324635505676</t>
+    <t xml:space="preserve">2.70324659347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.67347168922424</t>
@@ -923,49 +923,49 @@
     <t xml:space="preserve">2.59825086593628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5857138633728</t>
+    <t xml:space="preserve">2.58571410179138</t>
   </si>
   <si>
     <t xml:space="preserve">2.57004308700562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56220722198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54183483123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51989579200745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52929854393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52459740638733</t>
+    <t xml:space="preserve">2.56220746040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54183530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5198962688446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52929830551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52459716796875</t>
   </si>
   <si>
     <t xml:space="preserve">2.46034622192383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47131609916687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228526115417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43370532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39609527587891</t>
+    <t xml:space="preserve">2.47131586074829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4337055683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39609503746033</t>
   </si>
   <si>
     <t xml:space="preserve">2.32087397575378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30206871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975751876831</t>
+    <t xml:space="preserve">2.30206894874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975775718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.27699565887451</t>
@@ -977,46 +977,46 @@
     <t xml:space="preserve">2.34908199310303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36475276947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064935684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848450660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333317756653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43683981895447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62489151954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63272714614868</t>
+    <t xml:space="preserve">2.36475324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064888000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848498344421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333293914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43683934211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62489175796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6327269077301</t>
   </si>
   <si>
     <t xml:space="preserve">2.46818161010742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36631989479065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38199090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766192436218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251083374023</t>
+    <t xml:space="preserve">2.36632013320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.381991147995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251059532166</t>
   </si>
   <si>
     <t xml:space="preserve">2.40549755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42116856575012</t>
+    <t xml:space="preserve">2.42116832733154</t>
   </si>
   <si>
     <t xml:space="preserve">2.42900395393372</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">2.24878764152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30363655090332</t>
+    <t xml:space="preserve">2.30363631248474</t>
   </si>
   <si>
     <t xml:space="preserve">2.25662350654602</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">2.27229428291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2801296710968</t>
+    <t xml:space="preserve">2.28012990951538</t>
   </si>
   <si>
     <t xml:space="preserve">2.26445865631104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22528123855591</t>
+    <t xml:space="preserve">2.22528100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558437347412</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">2.09154343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942110061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339436531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750273704529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18770670890808</t>
+    <t xml:space="preserve">2.01942157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750249862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188275337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13962507247925</t>
+    <t xml:space="preserve">2.13962483406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.16366577148438</t>
@@ -1085,40 +1085,40 @@
     <t xml:space="preserve">2.20373368263245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13161134719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17167925834656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19572019577026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17969298362732</t>
+    <t xml:space="preserve">2.13161158561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17167901992798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19571995735168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17969274520874</t>
   </si>
   <si>
     <t xml:space="preserve">2.10757064819336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05948901176453</t>
+    <t xml:space="preserve">2.05948948860168</t>
   </si>
   <si>
     <t xml:space="preserve">2.07551622390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03544855117798</t>
+    <t xml:space="preserve">2.03544807434082</t>
   </si>
   <si>
     <t xml:space="preserve">2.05147552490234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27585601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784205436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21976089477539</t>
+    <t xml:space="preserve">2.27585554122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784253120422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21976065635681</t>
   </si>
   <si>
     <t xml:space="preserve">2.21174716949463</t>
@@ -1127,64 +1127,64 @@
     <t xml:space="preserve">2.24380111694336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23578763008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22777414321899</t>
+    <t xml:space="preserve">2.23578786849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22777438163757</t>
   </si>
   <si>
     <t xml:space="preserve">2.15565204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30790996551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02743482589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04346203804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99538064002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524493694305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325842380524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96332633495331</t>
+    <t xml:space="preserve">2.30791020393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0274350643158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04346227645874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99538028240204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524481773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325806617737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96332597732544</t>
   </si>
   <si>
     <t xml:space="preserve">1.97133982181549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98736703395844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140761375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81106841564178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81908214092255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84312272071838</t>
+    <t xml:space="preserve">1.98736715316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140785217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8110682964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81908190250397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84312260150909</t>
   </si>
   <si>
     <t xml:space="preserve">1.79504120349884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77901387214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709527015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100026607513</t>
+    <t xml:space="preserve">1.7790139913559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709562778473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77100038528442</t>
   </si>
   <si>
     <t xml:space="preserve">1.73093271255493</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">1.7149053812027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7469596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72291874885559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7389463186264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298701763153</t>
+    <t xml:space="preserve">1.74695980548859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72291898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73894608020782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298689842224</t>
   </si>
   <si>
     <t xml:space="preserve">1.75497317314148</t>
@@ -1214,49 +1214,49 @@
     <t xml:space="preserve">1.80305469036102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85914981365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8671635389328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510887622833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517654895782</t>
+    <t xml:space="preserve">1.85914969444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86716330051422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510935306549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517690658569</t>
   </si>
   <si>
     <t xml:space="preserve">1.90723121166229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97935354709625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928563594818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082943916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258134841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9878363609314</t>
+    <t xml:space="preserve">1.97935318946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93928575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98783624172211</t>
   </si>
   <si>
     <t xml:space="preserve">1.99608469009399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96309149265289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834626674652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97958815097809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03732633590698</t>
+    <t xml:space="preserve">1.9630913734436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93834638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97958827018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0373260974884</t>
   </si>
   <si>
     <t xml:space="preserve">2.0620710849762</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11156034469604</t>
+    <t xml:space="preserve">2.11156058311462</t>
   </si>
   <si>
     <t xml:space="preserve">2.10331225395203</t>
@@ -1283,10 +1283,10 @@
     <t xml:space="preserve">2.12805700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13630533218384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11980867385864</t>
+    <t xml:space="preserve">2.13630509376526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11980891227722</t>
   </si>
   <si>
     <t xml:space="preserve">2.14455389976501</t>
@@ -1298,22 +1298,22 @@
     <t xml:space="preserve">2.22703647613525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21878814697266</t>
+    <t xml:space="preserve">2.21878838539124</t>
   </si>
   <si>
     <t xml:space="preserve">2.25178146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24353313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21054005622864</t>
+    <t xml:space="preserve">2.24353337287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21054029464722</t>
   </si>
   <si>
     <t xml:space="preserve">2.26003003120422</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26827812194824</t>
+    <t xml:space="preserve">2.26827836036682</t>
   </si>
   <si>
     <t xml:space="preserve">2.33426403999329</t>
@@ -1325,7 +1325,7 @@
     <t xml:space="preserve">2.30127096176147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31776762008667</t>
+    <t xml:space="preserve">2.31776738166809</t>
   </si>
   <si>
     <t xml:space="preserve">2.38375401496887</t>
@@ -1334,22 +1334,22 @@
     <t xml:space="preserve">2.37550568580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32601571083069</t>
+    <t xml:space="preserve">2.32601594924927</t>
   </si>
   <si>
     <t xml:space="preserve">2.27652621269226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28477501869202</t>
+    <t xml:space="preserve">2.28477478027344</t>
   </si>
   <si>
     <t xml:space="preserve">2.29302287101746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23528480529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200258255005</t>
+    <t xml:space="preserve">2.23528504371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200234413147</t>
   </si>
   <si>
     <t xml:space="preserve">2.44974040985107</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">2.41674709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4332435131073</t>
+    <t xml:space="preserve">2.43324398994446</t>
   </si>
   <si>
     <t xml:space="preserve">2.40849900245667</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">2.42499566078186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798850059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4992299079895</t>
+    <t xml:space="preserve">2.45798873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49922966957092</t>
   </si>
   <si>
     <t xml:space="preserve">2.47448492050171</t>
@@ -1379,7 +1379,7 @@
     <t xml:space="preserve">2.51572632789612</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5899612903595</t>
+    <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
     <t xml:space="preserve">2.54871964454651</t>
@@ -1388,19 +1388,19 @@
     <t xml:space="preserve">2.4909815788269</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5074782371521</t>
+    <t xml:space="preserve">2.50747799873352</t>
   </si>
   <si>
     <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35076069831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40025091171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19404363632202</t>
+    <t xml:space="preserve">2.35076093673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40025067329407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19404339790344</t>
   </si>
   <si>
     <t xml:space="preserve">2.18579530715942</t>
@@ -1409,31 +1409,31 @@
     <t xml:space="preserve">2.045574426651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87236058712006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060855865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264997005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089818000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56717395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71564280986786</t>
+    <t xml:space="preserve">1.87236046791077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060879707336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264973163605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089829921722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56717383861542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71564292907715</t>
   </si>
   <si>
     <t xml:space="preserve">1.64553248882294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64140856266022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62491190433502</t>
+    <t xml:space="preserve">1.64140844345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62491178512573</t>
   </si>
   <si>
     <t xml:space="preserve">1.77338087558746</t>
@@ -1451,16 +1451,16 @@
     <t xml:space="preserve">1.86411225795746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00433301925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81462252140045</t>
+    <t xml:space="preserve">2.00433325767517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81462240219116</t>
   </si>
   <si>
     <t xml:space="preserve">1.79812586307526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287061214447</t>
+    <t xml:space="preserve">1.82287073135376</t>
   </si>
   <si>
     <t xml:space="preserve">1.84761548042297</t>
@@ -1469,25 +1469,25 @@
     <t xml:space="preserve">1.83111894130707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78987765312195</t>
+    <t xml:space="preserve">1.78987753391266</t>
   </si>
   <si>
     <t xml:space="preserve">1.88885688781738</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91360187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90535354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95484340190887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907776832581</t>
+    <t xml:space="preserve">1.91360175609589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710533618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90535366535187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9548431634903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907800674438</t>
   </si>
   <si>
     <t xml:space="preserve">2.08681583404541</t>
@@ -1499,37 +1499,37 @@
     <t xml:space="preserve">2.07031917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07786917686462</t>
+    <t xml:space="preserve">2.07786893844604</t>
   </si>
   <si>
     <t xml:space="preserve">2.06938791275024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9845769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609579563141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065259933472</t>
+    <t xml:space="preserve">2.03546380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98457658290863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9760959148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065248012543</t>
   </si>
   <si>
     <t xml:space="preserve">1.99305784702301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06090688705444</t>
+    <t xml:space="preserve">2.06090712547302</t>
   </si>
   <si>
     <t xml:space="preserve">2.02698254585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05242562294006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04394459724426</t>
+    <t xml:space="preserve">2.05242586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04394483566284</t>
   </si>
   <si>
     <t xml:space="preserve">2.0100200176239</t>
@@ -1541,16 +1541,16 @@
     <t xml:space="preserve">1.89976608753204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88280367851257</t>
+    <t xml:space="preserve">1.88280379772186</t>
   </si>
   <si>
     <t xml:space="preserve">1.89128482341766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01850128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913374423981</t>
+    <t xml:space="preserve">2.01850152015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913350582123</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
@@ -1559,7 +1559,7 @@
     <t xml:space="preserve">2.12875556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12027478218079</t>
+    <t xml:space="preserve">2.12027454376221</t>
   </si>
   <si>
     <t xml:space="preserve">2.16267991065979</t>
@@ -1577,7 +1577,7 @@
     <t xml:space="preserve">2.33230209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34926438331604</t>
+    <t xml:space="preserve">2.34926414489746</t>
   </si>
   <si>
     <t xml:space="preserve">2.35774517059326</t>
@@ -1586,28 +1586,28 @@
     <t xml:space="preserve">2.42559385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44255661964417</t>
+    <t xml:space="preserve">2.44255614280701</t>
   </si>
   <si>
     <t xml:space="preserve">2.47648072242737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46799969673157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49344301223755</t>
+    <t xml:space="preserve">2.46799945831299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49344277381897</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040530204773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43407511711121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4171130657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888608932495</t>
+    <t xml:space="preserve">2.43407487869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41711282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888632774353</t>
   </si>
   <si>
     <t xml:space="preserve">2.58673477172852</t>
@@ -1622,10 +1622,10 @@
     <t xml:space="preserve">2.57825374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56129169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55281019210815</t>
+    <t xml:space="preserve">2.56129145622253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55281043052673</t>
   </si>
   <si>
     <t xml:space="preserve">2.53584837913513</t>
@@ -1640,10 +1640,10 @@
     <t xml:space="preserve">2.63762140274048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66306471824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7054705619812</t>
+    <t xml:space="preserve">2.66306495666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70547008514404</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698929786682</t>
@@ -1664,10 +1664,10 @@
     <t xml:space="preserve">2.78180027008057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84116792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86661148071289</t>
+    <t xml:space="preserve">2.84116768836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86661124229431</t>
   </si>
   <si>
     <t xml:space="preserve">2.88357353210449</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">2.85812997817993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80724334716797</t>
+    <t xml:space="preserve">2.80724358558655</t>
   </si>
   <si>
     <t xml:space="preserve">2.75635695457458</t>
@@ -1691,43 +1691,43 @@
     <t xml:space="preserve">2.74787569046021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79876232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79028105735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84964871406555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268690109253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82420539855957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91749787330627</t>
+    <t xml:space="preserve">2.79876208305359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79028129577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84964919090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268666267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82420563697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9174976348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.01078987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03623294830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95990324020386</t>
+    <t xml:space="preserve">3.0362331867218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95990300178528</t>
   </si>
   <si>
     <t xml:space="preserve">3.07863879203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08711981773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12104392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18041157722473</t>
+    <t xml:space="preserve">3.08712005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12104415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18041181564331</t>
   </si>
   <si>
     <t xml:space="preserve">3.14648723602295</t>
@@ -1745,16 +1745,16 @@
     <t xml:space="preserve">3.24826049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21433615684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28218507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40092062950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42636370658875</t>
+    <t xml:space="preserve">3.21433639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28218483924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40092039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42636346817017</t>
   </si>
   <si>
     <t xml:space="preserve">3.36699604988098</t>
@@ -1766,7 +1766,7 @@
     <t xml:space="preserve">3.29066634178162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27370357513428</t>
+    <t xml:space="preserve">3.27370405197144</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079400062561</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.27339220046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35112476348877</t>
+    <t xml:space="preserve">3.35112500190735</t>
   </si>
   <si>
     <t xml:space="preserve">3.34248757362366</t>
@@ -1787,10 +1787,10 @@
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430928230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4461305141449</t>
+    <t xml:space="preserve">3.39430904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44613075256348</t>
   </si>
   <si>
     <t xml:space="preserve">3.45476746559143</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">3.60159540176392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5929582118988</t>
+    <t xml:space="preserve">3.59295845031738</t>
   </si>
   <si>
     <t xml:space="preserve">3.65341663360596</t>
@@ -1823,16 +1823,16 @@
     <t xml:space="preserve">3.78297066688538</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80888104438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69660139083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62750601768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.644779920578</t>
+    <t xml:space="preserve">3.80888080596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69660115242004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62750577926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64477968215942</t>
   </si>
   <si>
     <t xml:space="preserve">3.73978543281555</t>
@@ -1850,7 +1850,7 @@
     <t xml:space="preserve">3.57568430900574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58432126045227</t>
+    <t xml:space="preserve">3.58432149887085</t>
   </si>
   <si>
     <t xml:space="preserve">3.70523810386658</t>
@@ -1859,7 +1859,7 @@
     <t xml:space="preserve">3.5238630771637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5497739315033</t>
+    <t xml:space="preserve">3.54977369308472</t>
   </si>
   <si>
     <t xml:space="preserve">3.48931527137756</t>
@@ -1874,7 +1874,7 @@
     <t xml:space="preserve">3.68796420097351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74842286109924</t>
+    <t xml:space="preserve">3.74842309951782</t>
   </si>
   <si>
     <t xml:space="preserve">3.66205310821533</t>
@@ -1889,22 +1889,22 @@
     <t xml:space="preserve">3.8261547088623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86070275306702</t>
+    <t xml:space="preserve">3.8607029914856</t>
   </si>
   <si>
     <t xml:space="preserve">3.91252493858337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99889373779297</t>
+    <t xml:space="preserve">3.99889397621155</t>
   </si>
   <si>
     <t xml:space="preserve">3.9557089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99025654792786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342861175537</t>
+    <t xml:space="preserve">3.99025678634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342837333679</t>
   </si>
   <si>
     <t xml:space="preserve">3.77433323860168</t>
@@ -1913,19 +1913,19 @@
     <t xml:space="preserve">3.76569676399231</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92979836463928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661360740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9038872718811</t>
+    <t xml:space="preserve">3.92979860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661336898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90388751029968</t>
   </si>
   <si>
     <t xml:space="preserve">3.87797665596008</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81751823425293</t>
+    <t xml:space="preserve">3.81751847267151</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434617042542</t>
@@ -1934,7 +1934,7 @@
     <t xml:space="preserve">3.89525079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93843507766724</t>
+    <t xml:space="preserve">3.93843483924866</t>
   </si>
   <si>
     <t xml:space="preserve">3.63614320755005</t>
@@ -1943,28 +1943,28 @@
     <t xml:space="preserve">3.4979522228241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885661125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4202196598053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2820291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25611853599548</t>
+    <t xml:space="preserve">3.42885684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021989822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28202939033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2561182975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066610336304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24748158454895</t>
+    <t xml:space="preserve">3.24748134613037</t>
   </si>
   <si>
     <t xml:space="preserve">3.29930305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26475524902344</t>
+    <t xml:space="preserve">3.26475548744202</t>
   </si>
   <si>
     <t xml:space="preserve">3.3338508605957</t>
@@ -1976,7 +1976,7 @@
     <t xml:space="preserve">3.37703537940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40294623374939</t>
+    <t xml:space="preserve">3.40294599533081</t>
   </si>
   <si>
     <t xml:space="preserve">3.35976147651672</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">3.21293377876282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23020768165588</t>
+    <t xml:space="preserve">3.2302074432373</t>
   </si>
   <si>
     <t xml:space="preserve">3.15247559547424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11792755126953</t>
+    <t xml:space="preserve">3.11792778968811</t>
   </si>
   <si>
     <t xml:space="preserve">3.19565987586975</t>
@@ -2000,13 +2000,13 @@
     <t xml:space="preserve">3.14383864402771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97973680496216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06610631942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53250026702881</t>
+    <t xml:space="preserve">2.97973704338074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06610608100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53250002861023</t>
   </si>
   <si>
     <t xml:space="preserve">3.56704759597778</t>
@@ -2015,7 +2015,7 @@
     <t xml:space="preserve">3.46340465545654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38567233085632</t>
+    <t xml:space="preserve">3.38567209243774</t>
   </si>
   <si>
     <t xml:space="preserve">3.54222989082336</t>
@@ -68317,7 +68317,7 @@
     </row>
     <row r="2501">
       <c r="A2501" s="1" t="n">
-        <v>45960.6912384259</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2501" t="n">
         <v>29095</v>
@@ -68338,6 +68338,32 @@
         <v>988</v>
       </c>
       <c r="H2501" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2502">
+      <c r="A2502" s="1" t="n">
+        <v>45961.69125</v>
+      </c>
+      <c r="B2502" t="n">
+        <v>48555</v>
+      </c>
+      <c r="C2502" t="n">
+        <v>9.07999992370605</v>
+      </c>
+      <c r="D2502" t="n">
+        <v>8.72000026702881</v>
+      </c>
+      <c r="E2502" t="n">
+        <v>8.94999980926514</v>
+      </c>
+      <c r="F2502" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2502" t="s">
+        <v>977</v>
+      </c>
+      <c r="H2502" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652255535126</t>
+    <t xml:space="preserve">1.73652291297913</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400758743286</t>
+    <t xml:space="preserve">1.74400770664215</t>
   </si>
   <si>
     <t xml:space="preserve">1.71406769752502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6616724729538</t>
+    <t xml:space="preserve">1.66167259216309</t>
   </si>
   <si>
     <t xml:space="preserve">1.67215156555176</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">1.64969646930695</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63921749591827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57334923744202</t>
+    <t xml:space="preserve">1.63921761512756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57334935665131</t>
   </si>
   <si>
     <t xml:space="preserve">1.49625372886658</t>
@@ -71,61 +71,61 @@
     <t xml:space="preserve">1.48053526878357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48203241825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637382984161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460725784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42215216159821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990661621094</t>
+    <t xml:space="preserve">1.48203229904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460701942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4221522808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990673542023</t>
   </si>
   <si>
     <t xml:space="preserve">1.4146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41915810108185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.407182097435</t>
+    <t xml:space="preserve">1.41915822029114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40718197822571</t>
   </si>
   <si>
     <t xml:space="preserve">1.3824816942215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38472723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3982001543045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35703229904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33607447147369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34730219841003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34281098842621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397860527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478723049164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38098454475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36975705623627</t>
+    <t xml:space="preserve">1.38472712039948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39820003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35703253746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607470989227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34730207920074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34281122684479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397872447968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478711128235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38098466396332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36975729465485</t>
   </si>
   <si>
     <t xml:space="preserve">1.37873911857605</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">1.41017615795135</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4453558921814</t>
+    <t xml:space="preserve">1.44535577297211</t>
   </si>
   <si>
     <t xml:space="preserve">1.46257138252258</t>
@@ -146,19 +146,19 @@
     <t xml:space="preserve">1.51197230815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5254453420639</t>
+    <t xml:space="preserve">1.52544546127319</t>
   </si>
   <si>
     <t xml:space="preserve">1.52245116233826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54490625858307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.541912317276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5493973493576</t>
+    <t xml:space="preserve">1.54490637779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191219806671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54939723014832</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287038326263</t>
@@ -167,88 +167,88 @@
     <t xml:space="preserve">1.60029542446136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60927748680115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173258304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63023567199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676263809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418779850006</t>
+    <t xml:space="preserve">1.60927772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424767017365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63023543357849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676251888275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418767929077</t>
   </si>
   <si>
     <t xml:space="preserve">1.64370858669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58682239055634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58831930160522</t>
+    <t xml:space="preserve">1.58682227134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58831942081451</t>
   </si>
   <si>
     <t xml:space="preserve">1.63472652435303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66017532348633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6691575050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712151050568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6916127204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69310975074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155261039734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502552509308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658266544342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909799098969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664265632629</t>
+    <t xml:space="preserve">1.66017544269562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66915738582611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712162971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69161260128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69310963153839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155272960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502576351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358872413635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909751415253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.676642537117</t>
   </si>
   <si>
     <t xml:space="preserve">1.68412756919861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66766047477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263041973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221143722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64670264720917</t>
+    <t xml:space="preserve">1.66766023635864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263030052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221155643463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64670252799988</t>
   </si>
   <si>
     <t xml:space="preserve">1.67514562606812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69964492321014</t>
+    <t xml:space="preserve">1.69964504241943</t>
   </si>
   <si>
     <t xml:space="preserve">1.68433284759521</t>
@@ -260,37 +260,37 @@
     <t xml:space="preserve">1.72108173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70576965808868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6950511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495711803436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72261309623718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65370869636536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208313941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.669020652771</t>
+    <t xml:space="preserve">1.70576977729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69505131244659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495699882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72261321544647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65370857715607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208337783813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66902077198029</t>
   </si>
   <si>
     <t xml:space="preserve">1.65217733383179</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60624122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56183576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55417990684509</t>
+    <t xml:space="preserve">1.60624098777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5618360042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417966842651</t>
   </si>
   <si>
     <t xml:space="preserve">1.52202439308167</t>
@@ -299,70 +299,70 @@
     <t xml:space="preserve">1.53121173381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59092879295349</t>
+    <t xml:space="preserve">1.59092891216278</t>
   </si>
   <si>
     <t xml:space="preserve">1.52891480922699</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55111742019653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53886771202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49293160438538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4760879278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52278995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996319293976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761929035187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5005875825882</t>
+    <t xml:space="preserve">1.55111753940582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53886783123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4929313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608828544617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52279007434845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996295452118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589953899384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058746337891</t>
   </si>
   <si>
     <t xml:space="preserve">1.60777223110199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59705376625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56949186325073</t>
+    <t xml:space="preserve">1.59705364704132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56949198246002</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308430671692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6674896478653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136455535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67667663097382</t>
+    <t xml:space="preserve">1.66748929023743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136491298676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67667675018311</t>
   </si>
   <si>
     <t xml:space="preserve">1.61542820930481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57714807987213</t>
+    <t xml:space="preserve">1.57714796066284</t>
   </si>
   <si>
     <t xml:space="preserve">1.58480405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63839650154114</t>
+    <t xml:space="preserve">1.63839638233185</t>
   </si>
   <si>
     <t xml:space="preserve">1.6338027715683</t>
@@ -371,43 +371,43 @@
     <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54652369022369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56796085834503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54499244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355563640594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54193007946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58174169063568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55877351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58021032810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5526487827301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53044605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51972758769989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50594675540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671243667603</t>
+    <t xml:space="preserve">1.54652380943298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56796073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5449925661087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355551719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54193019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174157142639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55877339839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5802104473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55264866352081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53044593334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51972782611847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50594651699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671231746674</t>
   </si>
   <si>
     <t xml:space="preserve">1.53427410125732</t>
@@ -419,43 +419,43 @@
     <t xml:space="preserve">1.57408571243286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58327281475067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59246015548706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50211882591248</t>
+    <t xml:space="preserve">1.58327293395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59245979785919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50211870670319</t>
   </si>
   <si>
     <t xml:space="preserve">1.50824344158173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4753223657608</t>
+    <t xml:space="preserve">1.47532248497009</t>
   </si>
   <si>
     <t xml:space="preserve">1.49675941467285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50747787952423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52968072891235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60011625289917</t>
+    <t xml:space="preserve">1.50747776031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52968037128448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60011637210846</t>
   </si>
   <si>
     <t xml:space="preserve">1.58786642551422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56489825248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56336712837219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255423069</t>
+    <t xml:space="preserve">1.56489813327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56336724758148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255434989929</t>
   </si>
   <si>
     <t xml:space="preserve">1.59858500957489</t>
@@ -470,64 +470,64 @@
     <t xml:space="preserve">1.64758360385895</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64605259895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68280160427094</t>
+    <t xml:space="preserve">1.64605283737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68280172348022</t>
   </si>
   <si>
     <t xml:space="preserve">1.63074064254761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686549663544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452147483826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227152824402</t>
+    <t xml:space="preserve">1.63686525821686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452135562897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227188587189</t>
   </si>
   <si>
     <t xml:space="preserve">1.66289579868317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595852375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333156108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026943206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558115005493</t>
+    <t xml:space="preserve">1.66595828533173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026919364929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558162689209</t>
   </si>
   <si>
     <t xml:space="preserve">1.75017488002777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70730102062225</t>
+    <t xml:space="preserve">1.70730090141296</t>
   </si>
   <si>
     <t xml:space="preserve">1.70423877239227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73792541027069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75936222076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089334487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78386163711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76854932308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323748588562</t>
+    <t xml:space="preserve">1.73792505264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75936245918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089322566986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78386151790619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76854944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323736667633</t>
   </si>
   <si>
     <t xml:space="preserve">1.73486280441284</t>
@@ -536,16 +536,16 @@
     <t xml:space="preserve">1.73639380931854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79151749610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8022358417511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061052322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754815578461</t>
+    <t xml:space="preserve">1.7915176153183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223619937897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061076164246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81754839420319</t>
   </si>
   <si>
     <t xml:space="preserve">1.80682992935181</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">1.82520425319672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81448566913605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889101028442</t>
+    <t xml:space="preserve">1.81448590755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889077186584</t>
   </si>
   <si>
     <t xml:space="preserve">1.87726557254791</t>
@@ -566,22 +566,22 @@
     <t xml:space="preserve">1.85429728031158</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85582852363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8512350320816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86654686927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8497040271759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348450183868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276639461517</t>
+    <t xml:space="preserve">1.85582864284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85123479366302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86654698848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84970366954803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348462104797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85276627540588</t>
   </si>
   <si>
     <t xml:space="preserve">1.83745419979095</t>
@@ -590,16 +590,16 @@
     <t xml:space="preserve">1.84511005878448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82367324829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051644802094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817230701447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807811260223</t>
+    <t xml:space="preserve">1.82367277145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051620960236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817254543304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807835102081</t>
   </si>
   <si>
     <t xml:space="preserve">1.9492324590683</t>
@@ -608,61 +608,61 @@
     <t xml:space="preserve">1.90788996219635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92167055606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932653427124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473304271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9660758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904383182526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823093414307</t>
+    <t xml:space="preserve">1.921670794487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932689189911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473292350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607601642609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904371261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823129177094</t>
   </si>
   <si>
     <t xml:space="preserve">2.00894975662231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00741839408875</t>
+    <t xml:space="preserve">2.00741863250732</t>
   </si>
   <si>
     <t xml:space="preserve">2.01201224327087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99057495594025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00282502174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00588750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09207797050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051060676575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401724815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424210548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1155846118927</t>
+    <t xml:space="preserve">1.99057519435883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0028247833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00588703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09207773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401700973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424234390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558437347412</t>
   </si>
   <si>
     <t xml:space="preserve">2.17043256759644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14692664146423</t>
+    <t xml:space="preserve">2.1469259262085</t>
   </si>
   <si>
     <t xml:space="preserve">2.15006041526794</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">2.12655377388</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16259670257568</t>
+    <t xml:space="preserve">2.16259717941284</t>
   </si>
   <si>
     <t xml:space="preserve">2.15162754058838</t>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">2.16103005409241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04663181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0528998374939</t>
+    <t xml:space="preserve">2.0466320514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290007591248</t>
   </si>
   <si>
     <t xml:space="preserve">2.03722906112671</t>
@@ -695,34 +695,34 @@
     <t xml:space="preserve">2.04819893836975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04506468772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06543707847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10774850845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11715126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12342000007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125538825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1939389705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647621154785</t>
+    <t xml:space="preserve">2.0450644493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06543684005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073594093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10774898529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1171510219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12341976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125514984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296933174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19393920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647597312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.20334196090698</t>
@@ -731,34 +731,34 @@
     <t xml:space="preserve">2.19237232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20804286003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416430473328</t>
+    <t xml:space="preserve">2.20804309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16416454315186</t>
   </si>
   <si>
     <t xml:space="preserve">2.15946292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13595652580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0638701915741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02625966072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827721595764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805188179016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640719413757</t>
+    <t xml:space="preserve">2.13595700263977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677910804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386971473694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0262598991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805176258087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07640671730042</t>
   </si>
   <si>
     <t xml:space="preserve">2.05446743965149</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">2.10461473464966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06700420379639</t>
+    <t xml:space="preserve">2.06700444221497</t>
   </si>
   <si>
     <t xml:space="preserve">2.03566217422485</t>
@@ -776,31 +776,31 @@
     <t xml:space="preserve">2.04976582527161</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07954096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24095225334167</t>
+    <t xml:space="preserve">2.07954120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857132911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797360420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2409520149231</t>
   </si>
   <si>
     <t xml:space="preserve">2.22371411323547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21117758750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23311638832092</t>
+    <t xml:space="preserve">2.211177110672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2331166267395</t>
   </si>
   <si>
     <t xml:space="preserve">2.23781800270081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31930685043335</t>
+    <t xml:space="preserve">2.31930756568909</t>
   </si>
   <si>
     <t xml:space="preserve">2.3146059513092</t>
@@ -809,10 +809,10 @@
     <t xml:space="preserve">2.3271427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982629776001</t>
+    <t xml:space="preserve">2.32557511329651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982653617859</t>
   </si>
   <si>
     <t xml:space="preserve">2.3866925239563</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.44467496871948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47601747512817</t>
+    <t xml:space="preserve">2.47601699829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.48541975021362</t>
@@ -830,19 +830,19 @@
     <t xml:space="preserve">2.49012088775635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52146291732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735926628113</t>
+    <t xml:space="preserve">2.5214626789093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735950469971</t>
   </si>
   <si>
     <t xml:space="preserve">2.53870105743408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53086566925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168801307678</t>
+    <t xml:space="preserve">2.53086543083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168825149536</t>
   </si>
   <si>
     <t xml:space="preserve">2.50422501564026</t>
@@ -851,16 +851,16 @@
     <t xml:space="preserve">2.49952363967896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52303004264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5324330329895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206040382385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5089259147644</t>
+    <t xml:space="preserve">2.52303028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53243279457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50892615318298</t>
   </si>
   <si>
     <t xml:space="preserve">2.51362752914429</t>
@@ -878,28 +878,28 @@
     <t xml:space="preserve">2.54653644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55123782157898</t>
+    <t xml:space="preserve">2.55123805999756</t>
   </si>
   <si>
     <t xml:space="preserve">2.53713393211365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55437231063843</t>
+    <t xml:space="preserve">2.55437207221985</t>
   </si>
   <si>
     <t xml:space="preserve">2.60608649253845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70794773101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541144371033</t>
+    <t xml:space="preserve">2.70794820785522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108174324036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205138206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541120529175</t>
   </si>
   <si>
     <t xml:space="preserve">2.70324659347534</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">2.66406917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61705589294434</t>
+    <t xml:space="preserve">2.61705613136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.59981799125671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58728122711182</t>
+    <t xml:space="preserve">2.58728098869324</t>
   </si>
   <si>
     <t xml:space="preserve">2.59825086593628</t>
@@ -926,13 +926,13 @@
     <t xml:space="preserve">2.58571410179138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57004308700562</t>
+    <t xml:space="preserve">2.57004284858704</t>
   </si>
   <si>
     <t xml:space="preserve">2.56220746040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54183530807495</t>
+    <t xml:space="preserve">2.54183506965637</t>
   </si>
   <si>
     <t xml:space="preserve">2.51989603042603</t>
@@ -944,10 +944,10 @@
     <t xml:space="preserve">2.52459716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46034598350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131586074829</t>
+    <t xml:space="preserve">2.46034622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131609916687</t>
   </si>
   <si>
     <t xml:space="preserve">2.48228549957275</t>
@@ -956,121 +956,121 @@
     <t xml:space="preserve">2.43370532989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39609527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087397575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27699542045593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2879650592804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34908223152161</t>
+    <t xml:space="preserve">2.39609503746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206894874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975728034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27699518203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28796529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34908199310303</t>
   </si>
   <si>
     <t xml:space="preserve">2.36475300788879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35064935684204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848474502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333293914795</t>
+    <t xml:space="preserve">2.35064911842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333341598511</t>
   </si>
   <si>
     <t xml:space="preserve">2.43683958053589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62489151954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6327269077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46818137168884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36632037162781</t>
+    <t xml:space="preserve">2.62489128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63272714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.468181848526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36632013320923</t>
   </si>
   <si>
     <t xml:space="preserve">2.381991147995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766192436218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251059532166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40549778938293</t>
+    <t xml:space="preserve">2.39766240119934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40549731254578</t>
   </si>
   <si>
     <t xml:space="preserve">2.42116856575012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42900419235229</t>
+    <t xml:space="preserve">2.42900395393372</t>
   </si>
   <si>
     <t xml:space="preserve">2.24878764152527</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30363607406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25662350654602</t>
+    <t xml:space="preserve">2.30363655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25662326812744</t>
   </si>
   <si>
     <t xml:space="preserve">2.27229428291321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28012990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445865631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528147697449</t>
+    <t xml:space="preserve">2.28012943267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445841789246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528123855591</t>
   </si>
   <si>
     <t xml:space="preserve">2.1235978603363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09955716133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08352994918823</t>
+    <t xml:space="preserve">2.0995569229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08352971076965</t>
   </si>
   <si>
     <t xml:space="preserve">2.09154319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339436531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750226020813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18770670890808</t>
+    <t xml:space="preserve">2.01942133903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750249862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188275337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13962507247925</t>
+    <t xml:space="preserve">2.13962483406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.16366577148438</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">2.14763855934143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20373344421387</t>
+    <t xml:space="preserve">2.20373368263245</t>
   </si>
   <si>
     <t xml:space="preserve">2.13161158561707</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">2.17969274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10757064819336</t>
+    <t xml:space="preserve">2.10757088661194</t>
   </si>
   <si>
     <t xml:space="preserve">2.05948901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07551622390747</t>
+    <t xml:space="preserve">2.07551598548889</t>
   </si>
   <si>
     <t xml:space="preserve">2.03544855117798</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">2.05147528648376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27585554122925</t>
+    <t xml:space="preserve">2.27585577964783</t>
   </si>
   <si>
     <t xml:space="preserve">2.26784229278564</t>
@@ -1121,10 +1121,10 @@
     <t xml:space="preserve">2.21174716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24380159378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23578763008118</t>
+    <t xml:space="preserve">2.24380135536194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23578786849976</t>
   </si>
   <si>
     <t xml:space="preserve">2.22777438163757</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">2.15565228462219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30790996551514</t>
+    <t xml:space="preserve">2.30791020393372</t>
   </si>
   <si>
     <t xml:space="preserve">2.02743482589722</t>
@@ -1142,19 +1142,19 @@
     <t xml:space="preserve">2.04346203804016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9953807592392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524469852448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325830459595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96332621574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97134006023407</t>
+    <t xml:space="preserve">1.99538087844849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524493694305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325842380524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9633264541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133982181549</t>
   </si>
   <si>
     <t xml:space="preserve">1.98736703395844</t>
@@ -1169,19 +1169,19 @@
     <t xml:space="preserve">1.81908178329468</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84312295913696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79504120349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901411056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709562778473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100050449371</t>
+    <t xml:space="preserve">1.84312272071838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79504108428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7790139913559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709550857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77100038528442</t>
   </si>
   <si>
     <t xml:space="preserve">1.73093247413635</t>
@@ -1193,34 +1193,34 @@
     <t xml:space="preserve">1.7149053812027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74695980548859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72291898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73894619941711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298689842224</t>
+    <t xml:space="preserve">1.7469596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72291886806488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73894608020782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298701763153</t>
   </si>
   <si>
     <t xml:space="preserve">1.75497329235077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80305469036102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85914993286133</t>
+    <t xml:space="preserve">1.80305457115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85914981365204</t>
   </si>
   <si>
     <t xml:space="preserve">1.86716341972351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83510887622833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517690658569</t>
+    <t xml:space="preserve">1.83510899543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517702579498</t>
   </si>
   <si>
     <t xml:space="preserve">1.90723121166229</t>
@@ -1229,49 +1229,49 @@
     <t xml:space="preserve">1.97935366630554</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93928527832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082943916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258111000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9713397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98783648014069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99608433246613</t>
+    <t xml:space="preserve">1.93928551673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258087158203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9878363609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9960845708847</t>
   </si>
   <si>
     <t xml:space="preserve">1.96309149265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93834662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9795880317688</t>
+    <t xml:space="preserve">1.9383465051651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97958815097809</t>
   </si>
   <si>
     <t xml:space="preserve">2.03732633590698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0620710849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0538227558136</t>
+    <t xml:space="preserve">2.06207084655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05382299423218</t>
   </si>
   <si>
     <t xml:space="preserve">2.09506416320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16929864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16105031967163</t>
+    <t xml:space="preserve">2.16929888725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
     <t xml:space="preserve">2.11156034469604</t>
@@ -1280,19 +1280,19 @@
     <t xml:space="preserve">2.10331225395203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12805676460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13630533218384</t>
+    <t xml:space="preserve">2.12805700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13630509376526</t>
   </si>
   <si>
     <t xml:space="preserve">2.11980867385864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14455366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07856774330139</t>
+    <t xml:space="preserve">2.14455342292786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07856750488281</t>
   </si>
   <si>
     <t xml:space="preserve">2.22703671455383</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.21878838539124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25178170204163</t>
+    <t xml:space="preserve">2.25178146362305</t>
   </si>
   <si>
     <t xml:space="preserve">2.24353313446045</t>
@@ -1313,28 +1313,28 @@
     <t xml:space="preserve">2.26002955436707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26827788352966</t>
+    <t xml:space="preserve">2.26827812194824</t>
   </si>
   <si>
     <t xml:space="preserve">2.33426427841187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30951952934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30127096176147</t>
+    <t xml:space="preserve">2.30951929092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30127120018005</t>
   </si>
   <si>
     <t xml:space="preserve">2.31776785850525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38375401496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37550568580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601571083069</t>
+    <t xml:space="preserve">2.38375377655029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37550592422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601594924927</t>
   </si>
   <si>
     <t xml:space="preserve">2.27652621269226</t>
@@ -1349,10 +1349,10 @@
     <t xml:space="preserve">2.23528480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200234413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44974064826965</t>
+    <t xml:space="preserve">2.39200258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44974040985107</t>
   </si>
   <si>
     <t xml:space="preserve">2.41674709320068</t>
@@ -1373,7 +1373,7 @@
     <t xml:space="preserve">2.49922966957092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47448492050171</t>
+    <t xml:space="preserve">2.47448515892029</t>
   </si>
   <si>
     <t xml:space="preserve">2.51572632789612</t>
@@ -1391,10 +1391,10 @@
     <t xml:space="preserve">2.5074782371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44149208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35076093673706</t>
+    <t xml:space="preserve">2.44149231910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35076069831848</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025043487549</t>
@@ -1412,31 +1412,31 @@
     <t xml:space="preserve">1.87236022949219</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88060879707336</t>
+    <t xml:space="preserve">1.88060867786407</t>
   </si>
   <si>
     <t xml:space="preserve">1.68264997005463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69089829921722</t>
+    <t xml:space="preserve">1.69089818000793</t>
   </si>
   <si>
     <t xml:space="preserve">1.56717395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71564280986786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64553248882294</t>
+    <t xml:space="preserve">1.71564292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64553260803223</t>
   </si>
   <si>
     <t xml:space="preserve">1.64140844345093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62491190433502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77338099479675</t>
+    <t xml:space="preserve">1.62491178512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77338087558746</t>
   </si>
   <si>
     <t xml:space="preserve">1.78162920475006</t>
@@ -1454,82 +1454,82 @@
     <t xml:space="preserve">2.00433301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81462240219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812598228455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84761559963226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111906051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78987765312195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885676860809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360199451447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710557460785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90535378456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95484292507172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907800674438</t>
+    <t xml:space="preserve">1.81462252140045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812586307526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287061214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84761548042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111894130707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78987753391266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710533618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90535354614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95484304428101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907776832581</t>
   </si>
   <si>
     <t xml:space="preserve">2.08681559562683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17754721641541</t>
+    <t xml:space="preserve">2.17754697799683</t>
   </si>
   <si>
     <t xml:space="preserve">2.07031941413879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07786893844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06938791275024</t>
+    <t xml:space="preserve">2.07786917686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06938767433167</t>
   </si>
   <si>
     <t xml:space="preserve">2.03546357154846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98457682132721</t>
+    <t xml:space="preserve">1.9845769405365</t>
   </si>
   <si>
     <t xml:space="preserve">1.97609603404999</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9506528377533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9930579662323</t>
+    <t xml:space="preserve">1.95065271854401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99305784702301</t>
   </si>
   <si>
     <t xml:space="preserve">2.06090688705444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02698230743408</t>
+    <t xml:space="preserve">2.02698254585266</t>
   </si>
   <si>
     <t xml:space="preserve">2.05242562294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04394483566284</t>
+    <t xml:space="preserve">2.04394459724426</t>
   </si>
   <si>
     <t xml:space="preserve">2.0100200176239</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9591338634491</t>
+    <t xml:space="preserve">1.95913374423981</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">2.16267991065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20508551597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23052883148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3068585395813</t>
+    <t xml:space="preserve">2.20508527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23052906990051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30685877799988</t>
   </si>
   <si>
     <t xml:space="preserve">2.33230209350586</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559409141541</t>
+    <t xml:space="preserve">2.42559385299683</t>
   </si>
   <si>
     <t xml:space="preserve">2.44255638122559</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">2.46799945831299</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49344325065613</t>
+    <t xml:space="preserve">2.49344301223755</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040530204773</t>
@@ -1625,10 +1625,10 @@
     <t xml:space="preserve">2.56129169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55281043052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53584837913513</t>
+    <t xml:space="preserve">2.55281019210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53584861755371</t>
   </si>
   <si>
     <t xml:space="preserve">2.52736735343933</t>
@@ -1637,7 +1637,7 @@
     <t xml:space="preserve">2.64610242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63762140274048</t>
+    <t xml:space="preserve">2.63762164115906</t>
   </si>
   <si>
     <t xml:space="preserve">2.66306495666504</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">2.69698929786682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62914037704468</t>
+    <t xml:space="preserve">2.6291401386261</t>
   </si>
   <si>
     <t xml:space="preserve">2.713951587677</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">2.77331900596619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180027008057</t>
+    <t xml:space="preserve">2.78180003166199</t>
   </si>
   <si>
     <t xml:space="preserve">2.84116768836975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86661124229431</t>
+    <t xml:space="preserve">2.86661148071289</t>
   </si>
   <si>
     <t xml:space="preserve">2.88357353210449</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">2.7393946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74787545204163</t>
+    <t xml:space="preserve">2.74787569046021</t>
   </si>
   <si>
     <t xml:space="preserve">2.79876232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79028105735779</t>
+    <t xml:space="preserve">2.79028129577637</t>
   </si>
   <si>
     <t xml:space="preserve">2.84964895248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268690109253</t>
+    <t xml:space="preserve">2.83268666267395</t>
   </si>
   <si>
     <t xml:space="preserve">2.82420563697815</t>
@@ -1709,10 +1709,10 @@
     <t xml:space="preserve">2.91749787330627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01078987121582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03623294830322</t>
+    <t xml:space="preserve">3.01078963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0362331867218</t>
   </si>
   <si>
     <t xml:space="preserve">2.95990324020386</t>
@@ -1742,7 +1742,7 @@
     <t xml:space="preserve">3.23129844665527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24826049804688</t>
+    <t xml:space="preserve">3.24826073646545</t>
   </si>
   <si>
     <t xml:space="preserve">3.21433615684509</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">3.40092039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42636346817017</t>
+    <t xml:space="preserve">3.42636370658875</t>
   </si>
   <si>
     <t xml:space="preserve">3.36699604988098</t>
@@ -68696,7 +68696,7 @@
     </row>
     <row r="2515">
       <c r="A2515" s="1" t="n">
-        <v>45980.6910648148</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2515" t="n">
         <v>30246</v>
@@ -68717,6 +68717,32 @@
         <v>993</v>
       </c>
       <c r="H2515" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2516">
+      <c r="A2516" s="1" t="n">
+        <v>45981.6912152778</v>
+      </c>
+      <c r="B2516" t="n">
+        <v>21997</v>
+      </c>
+      <c r="C2516" t="n">
+        <v>9.02000045776367</v>
+      </c>
+      <c r="D2516" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="E2516" t="n">
+        <v>8.77999973297119</v>
+      </c>
+      <c r="F2516" t="n">
+        <v>8.89999961853027</v>
+      </c>
+      <c r="G2516" t="s">
+        <v>982</v>
+      </c>
+      <c r="H2516" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="995">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652291297913</t>
+    <t xml:space="preserve">1.73652267456055</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">1.74400770664215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71406769752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167259216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67215156555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64969646930695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921761512756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57334935665131</t>
+    <t xml:space="preserve">1.71406745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167271137238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67215168476105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921749591827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5733494758606</t>
   </si>
   <si>
     <t xml:space="preserve">1.49625372886658</t>
@@ -71,28 +71,28 @@
     <t xml:space="preserve">1.48053526878357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48203229904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460701942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4221522808075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990673542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4146671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41915822029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40718197822571</t>
+    <t xml:space="preserve">1.48203241825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637347221375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460725784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42215204238892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990685462952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41466701030731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41915810108185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40718233585358</t>
   </si>
   <si>
     <t xml:space="preserve">1.3824816942215</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">1.38472712039948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39820003509521</t>
+    <t xml:space="preserve">1.3982001543045</t>
   </si>
   <si>
     <t xml:space="preserve">1.35703253746033</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">1.33607470989227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34730207920074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34281122684479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397872447968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478711128235</t>
+    <t xml:space="preserve">1.34730195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3428111076355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3839784860611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478699207306</t>
   </si>
   <si>
     <t xml:space="preserve">1.38098466396332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36975729465485</t>
+    <t xml:space="preserve">1.36975705623627</t>
   </si>
   <si>
     <t xml:space="preserve">1.37873911857605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43113422393799</t>
+    <t xml:space="preserve">1.4311341047287</t>
   </si>
   <si>
     <t xml:space="preserve">1.41017615795135</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">1.44535577297211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46257138252258</t>
+    <t xml:space="preserve">1.46257126331329</t>
   </si>
   <si>
     <t xml:space="preserve">1.51197230815887</t>
@@ -149,184 +149,184 @@
     <t xml:space="preserve">1.52544546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52245116233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54490637779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191219806671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54939723014832</t>
+    <t xml:space="preserve">1.52245128154755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54490613937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191243648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54939746856689</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287038326263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60029542446136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60927772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424767017365</t>
+    <t xml:space="preserve">1.60029554367065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60927748680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173258304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424778938293</t>
   </si>
   <si>
     <t xml:space="preserve">1.63023543357849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61676251888275</t>
+    <t xml:space="preserve">1.61676239967346</t>
   </si>
   <si>
     <t xml:space="preserve">1.65418767929077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64370858669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682227134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58831942081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472652435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66017544269562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915738582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69161260128021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69310963153839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155272960663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502576351166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358872413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658278465271</t>
+    <t xml:space="preserve">1.6437087059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682239055634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5883195400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472664356232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6601756811142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66915774345398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712139129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69161236286163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6931095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502588272095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358860492706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658254623413</t>
   </si>
   <si>
     <t xml:space="preserve">1.69909751415253</t>
   </si>
   <si>
-    <t xml:space="preserve">1.676642537117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68412756919861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66766023635864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263030052185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221155643463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64670252799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514562606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69964504241943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68433284759521</t>
+    <t xml:space="preserve">1.67664241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68412733078003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66766059398651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263065814972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221131801605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64670264720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514538764954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69964492321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68433272838593</t>
   </si>
   <si>
     <t xml:space="preserve">1.69198894500732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72108173370361</t>
+    <t xml:space="preserve">1.7210818529129</t>
   </si>
   <si>
     <t xml:space="preserve">1.70576977729797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69505131244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495699882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72261321544647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65370857715607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208337783813</t>
+    <t xml:space="preserve">1.6950511932373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495735645294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7226128578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65370869636536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208313941956</t>
   </si>
   <si>
     <t xml:space="preserve">1.66902077198029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65217733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60624098777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5618360042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55417966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121173381805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59092891216278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52891480922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55111753940582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53886783123016</t>
+    <t xml:space="preserve">1.65217745304108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.606241106987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56183576583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417954921722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202451229095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121161460876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59092915058136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5289146900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55111742019653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53886771202087</t>
   </si>
   <si>
     <t xml:space="preserve">1.4929313659668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47608828544617</t>
+    <t xml:space="preserve">1.47608804702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.52279007434845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46996295452118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589953899384</t>
+    <t xml:space="preserve">1.46996319293976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761905193329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589965820312</t>
   </si>
   <si>
     <t xml:space="preserve">1.50058746337891</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">1.60777223110199</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59705364704132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56949198246002</t>
+    <t xml:space="preserve">1.59705376625061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56949186325073</t>
   </si>
   <si>
     <t xml:space="preserve">1.62308430671692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66748929023743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136491298676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67667675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61542820930481</t>
+    <t xml:space="preserve">1.6674896478653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136455535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67667663097382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61542809009552</t>
   </si>
   <si>
     <t xml:space="preserve">1.57714796066284</t>
@@ -362,73 +362,73 @@
     <t xml:space="preserve">1.58480405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63839638233185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6338027715683</t>
+    <t xml:space="preserve">1.63839650154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63380300998688</t>
   </si>
   <si>
     <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54652380943298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56796073913574</t>
+    <t xml:space="preserve">1.54652369022369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56796085834503</t>
   </si>
   <si>
     <t xml:space="preserve">1.5449925661087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355551719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54193019866943</t>
+    <t xml:space="preserve">1.52355563640594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54193007946014</t>
   </si>
   <si>
     <t xml:space="preserve">1.58174157142639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55877339839935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5802104473114</t>
+    <t xml:space="preserve">1.55877351760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58021032810211</t>
   </si>
   <si>
     <t xml:space="preserve">1.55264866352081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53044593334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51972782611847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50594651699066</t>
+    <t xml:space="preserve">1.53044605255127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5197274684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50594663619995</t>
   </si>
   <si>
     <t xml:space="preserve">1.50671231746674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53427410125732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56642961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57408571243286</t>
+    <t xml:space="preserve">1.53427398204803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56642937660217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57408547401428</t>
   </si>
   <si>
     <t xml:space="preserve">1.58327293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59245979785919</t>
+    <t xml:space="preserve">1.59246003627777</t>
   </si>
   <si>
     <t xml:space="preserve">1.50211870670319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50824344158173</t>
+    <t xml:space="preserve">1.50824368000031</t>
   </si>
   <si>
     <t xml:space="preserve">1.47532248497009</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">1.49675941467285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50747776031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52968037128448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60011637210846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58786642551422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489813327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56336724758148</t>
+    <t xml:space="preserve">1.50747787952423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52968049049377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60011613368988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58786618709564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489825248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56336712837219</t>
   </si>
   <si>
     <t xml:space="preserve">1.57255434989929</t>
@@ -464,34 +464,34 @@
     <t xml:space="preserve">1.59399139881134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60470974445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64758360385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64605283737183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68280172348022</t>
+    <t xml:space="preserve">1.60470986366272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64758384227753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64605271816254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68280148506165</t>
   </si>
   <si>
     <t xml:space="preserve">1.63074064254761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686525821686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452135562897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227188587189</t>
+    <t xml:space="preserve">1.63686513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452159404755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63227164745331</t>
   </si>
   <si>
     <t xml:space="preserve">1.66289579868317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595828533173</t>
+    <t xml:space="preserve">1.66595852375031</t>
   </si>
   <si>
     <t xml:space="preserve">1.73333168029785</t>
@@ -500,79 +500,79 @@
     <t xml:space="preserve">1.73026919364929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74558162689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017488002777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730090141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423877239227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73792505264282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75936245918274</t>
+    <t xml:space="preserve">1.74558103084564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730102062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423853397369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7379252910614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75936210155487</t>
   </si>
   <si>
     <t xml:space="preserve">1.76089322566986</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78386151790619</t>
+    <t xml:space="preserve">1.78386175632477</t>
   </si>
   <si>
     <t xml:space="preserve">1.76854944229126</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75323736667633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639380931854</t>
+    <t xml:space="preserve">1.75323748588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486292362213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639392852783</t>
   </si>
   <si>
     <t xml:space="preserve">1.7915176153183</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80223619937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061076164246</t>
+    <t xml:space="preserve">1.80223631858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061088085175</t>
   </si>
   <si>
     <t xml:space="preserve">1.81754839420319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80682992935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520425319672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448590755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889077186584</t>
+    <t xml:space="preserve">1.80682969093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520461082458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889101028442</t>
   </si>
   <si>
     <t xml:space="preserve">1.87726557254791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85429728031158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582864284515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85123479366302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86654698848724</t>
+    <t xml:space="preserve">1.85429751873016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582876205444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8512350320816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86654686927795</t>
   </si>
   <si>
     <t xml:space="preserve">1.84970366954803</t>
@@ -581,49 +581,49 @@
     <t xml:space="preserve">1.86348462104797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85276627540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745419979095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511005878448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367277145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051620960236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817254543304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807835102081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9492324590683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788996219635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.921670794487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932689189911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607601642609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904371261597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823129177094</t>
+    <t xml:space="preserve">1.85276615619659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745431900024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84510982036591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367300987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051632881165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817230701447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8680784702301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923233985901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788984298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92167055606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932665348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473304271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607577800751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904395103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823093414307</t>
   </si>
   <si>
     <t xml:space="preserve">2.00894975662231</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">2.01201224327087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99057519435883</t>
+    <t xml:space="preserve">1.99057507514954</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">2.09207773208618</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09051036834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401700973511</t>
+    <t xml:space="preserve">2.09051084518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401724815369</t>
   </si>
   <si>
     <t xml:space="preserve">2.08424234390259</t>
@@ -662,37 +662,37 @@
     <t xml:space="preserve">2.17043256759644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1469259262085</t>
+    <t xml:space="preserve">2.14692640304565</t>
   </si>
   <si>
     <t xml:space="preserve">2.15006041526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12655377388</t>
+    <t xml:space="preserve">2.12655401229858</t>
   </si>
   <si>
     <t xml:space="preserve">2.16259717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15162754058838</t>
+    <t xml:space="preserve">2.1516273021698</t>
   </si>
   <si>
     <t xml:space="preserve">2.13909077644348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16103005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0466320514679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05290007591248</t>
+    <t xml:space="preserve">2.16103029251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04663181304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290031433105</t>
   </si>
   <si>
     <t xml:space="preserve">2.03722906112671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04819893836975</t>
+    <t xml:space="preserve">2.04819869995117</t>
   </si>
   <si>
     <t xml:space="preserve">2.0450644493103</t>
@@ -701,10 +701,10 @@
     <t xml:space="preserve">2.06543684005737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06073594093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10774898529053</t>
+    <t xml:space="preserve">2.06073570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10774874687195</t>
   </si>
   <si>
     <t xml:space="preserve">2.1171510219574</t>
@@ -716,43 +716,43 @@
     <t xml:space="preserve">2.13125514984131</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18296933174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19393920898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647597312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20334196090698</t>
+    <t xml:space="preserve">2.18296957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19393944740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2033417224884</t>
   </si>
   <si>
     <t xml:space="preserve">2.19237232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20804309844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416454315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13595700263977</t>
+    <t xml:space="preserve">2.20804333686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16416430473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946316719055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13595652580261</t>
   </si>
   <si>
     <t xml:space="preserve">2.09677910804749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06386971473694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0262598991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827697753906</t>
+    <t xml:space="preserve">2.06386995315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02625942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827721595764</t>
   </si>
   <si>
     <t xml:space="preserve">1.99805176258087</t>
@@ -764,34 +764,34 @@
     <t xml:space="preserve">2.05446743965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10461473464966</t>
+    <t xml:space="preserve">2.10461449623108</t>
   </si>
   <si>
     <t xml:space="preserve">2.06700444221497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03566217422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954120635986</t>
+    <t xml:space="preserve">2.03566241264343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954072952271</t>
   </si>
   <si>
     <t xml:space="preserve">2.06857132911682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07797360420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2409520149231</t>
+    <t xml:space="preserve">2.07797384262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24095225334167</t>
   </si>
   <si>
     <t xml:space="preserve">2.22371411323547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.211177110672</t>
+    <t xml:space="preserve">2.21117734909058</t>
   </si>
   <si>
     <t xml:space="preserve">2.2331166267395</t>
@@ -800,22 +800,22 @@
     <t xml:space="preserve">2.23781800270081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31930756568909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3146059513092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3271427154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557511329651</t>
+    <t xml:space="preserve">2.31930708885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31460571289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32714295387268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557535171509</t>
   </si>
   <si>
     <t xml:space="preserve">2.38982653617859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3866925239563</t>
+    <t xml:space="preserve">2.38669300079346</t>
   </si>
   <si>
     <t xml:space="preserve">2.44467496871948</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">2.47601699829102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48541975021362</t>
+    <t xml:space="preserve">2.48541951179504</t>
   </si>
   <si>
     <t xml:space="preserve">2.49012088775635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5214626789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735950469971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53870105743408</t>
+    <t xml:space="preserve">2.52146291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53870129585266</t>
   </si>
   <si>
     <t xml:space="preserve">2.53086543083191</t>
@@ -857,19 +857,19 @@
     <t xml:space="preserve">2.53243279457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51206064224243</t>
+    <t xml:space="preserve">2.51206040382385</t>
   </si>
   <si>
     <t xml:space="preserve">2.50892615318298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51362752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795651435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638962745667</t>
+    <t xml:space="preserve">2.51362729072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49795627593994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638915061951</t>
   </si>
   <si>
     <t xml:space="preserve">2.52616429328918</t>
@@ -887,43 +887,43 @@
     <t xml:space="preserve">2.55437207221985</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60608649253845</t>
+    <t xml:space="preserve">2.60608625411987</t>
   </si>
   <si>
     <t xml:space="preserve">2.70794820785522</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71108174324036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205138206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541120529175</t>
+    <t xml:space="preserve">2.71108198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205185890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541096687317</t>
   </si>
   <si>
     <t xml:space="preserve">2.70324659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67347168922424</t>
+    <t xml:space="preserve">2.67347121238708</t>
   </si>
   <si>
     <t xml:space="preserve">2.66406917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61705613136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981799125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58728098869324</t>
+    <t xml:space="preserve">2.61705589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728075027466</t>
   </si>
   <si>
     <t xml:space="preserve">2.59825086593628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58571410179138</t>
+    <t xml:space="preserve">2.5857138633728</t>
   </si>
   <si>
     <t xml:space="preserve">2.57004284858704</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">2.56220746040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54183506965637</t>
+    <t xml:space="preserve">2.54183530807495</t>
   </si>
   <si>
     <t xml:space="preserve">2.51989603042603</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">2.46034622192383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47131609916687</t>
+    <t xml:space="preserve">2.47131633758545</t>
   </si>
   <si>
     <t xml:space="preserve">2.48228549957275</t>
@@ -959,19 +959,19 @@
     <t xml:space="preserve">2.39609503746033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206894874573</t>
+    <t xml:space="preserve">2.32087397575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206918716431</t>
   </si>
   <si>
     <t xml:space="preserve">2.25975728034973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27699518203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28796529769897</t>
+    <t xml:space="preserve">2.27699565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2879650592804</t>
   </si>
   <si>
     <t xml:space="preserve">2.34908199310303</t>
@@ -983,22 +983,22 @@
     <t xml:space="preserve">2.35064911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35848426818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333341598511</t>
+    <t xml:space="preserve">2.35848474502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333293914795</t>
   </si>
   <si>
     <t xml:space="preserve">2.43683958053589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62489128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63272714614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.468181848526</t>
+    <t xml:space="preserve">2.62489175796509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6327269077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46818161010742</t>
   </si>
   <si>
     <t xml:space="preserve">2.36632013320923</t>
@@ -1007,10 +1007,10 @@
     <t xml:space="preserve">2.381991147995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39766240119934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251083374023</t>
+    <t xml:space="preserve">2.39766192436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251059532166</t>
   </si>
   <si>
     <t xml:space="preserve">2.40549731254578</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">2.42116856575012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42900395393372</t>
+    <t xml:space="preserve">2.42900371551514</t>
   </si>
   <si>
     <t xml:space="preserve">2.24878764152527</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">2.25662326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27229428291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28012943267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445841789246</t>
+    <t xml:space="preserve">2.27229452133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28012990951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.22528123855591</t>
@@ -1046,16 +1046,16 @@
     <t xml:space="preserve">2.1235978603363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0995569229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08352971076965</t>
+    <t xml:space="preserve">2.09955716133118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08352994918823</t>
   </si>
   <si>
     <t xml:space="preserve">2.09154319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942133903503</t>
+    <t xml:space="preserve">2.01942110061646</t>
   </si>
   <si>
     <t xml:space="preserve">2.00339412689209</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29188275337219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13962483406067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16366577148438</t>
+    <t xml:space="preserve">2.29188299179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13962507247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16366600990295</t>
   </si>
   <si>
     <t xml:space="preserve">2.14763855934143</t>
@@ -1082,37 +1082,37 @@
     <t xml:space="preserve">2.20373368263245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13161158561707</t>
+    <t xml:space="preserve">2.13161134719849</t>
   </si>
   <si>
     <t xml:space="preserve">2.17167925834656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19571971893311</t>
+    <t xml:space="preserve">2.19572019577026</t>
   </si>
   <si>
     <t xml:space="preserve">2.17969274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10757088661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05948901176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07551598548889</t>
+    <t xml:space="preserve">2.10757064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05948925018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07551622390747</t>
   </si>
   <si>
     <t xml:space="preserve">2.03544855117798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05147528648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27585577964783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784229278564</t>
+    <t xml:space="preserve">2.05147576332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27585554122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784205436707</t>
   </si>
   <si>
     <t xml:space="preserve">2.21976065635681</t>
@@ -1121,49 +1121,49 @@
     <t xml:space="preserve">2.21174716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24380135536194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23578786849976</t>
+    <t xml:space="preserve">2.24380159378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23578763008118</t>
   </si>
   <si>
     <t xml:space="preserve">2.22777438163757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15565228462219</t>
+    <t xml:space="preserve">2.15565204620361</t>
   </si>
   <si>
     <t xml:space="preserve">2.30791020393372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02743482589722</t>
+    <t xml:space="preserve">2.0274350643158</t>
   </si>
   <si>
     <t xml:space="preserve">2.04346203804016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99538087844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524493694305</t>
+    <t xml:space="preserve">1.99538064002991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524457931519</t>
   </si>
   <si>
     <t xml:space="preserve">1.92325842380524</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9633264541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97133982181549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736703395844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140785217285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8110682964325</t>
+    <t xml:space="preserve">1.96332633495331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97134017944336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736691474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140761375427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81106853485107</t>
   </si>
   <si>
     <t xml:space="preserve">1.81908178329468</t>
@@ -1172,46 +1172,46 @@
     <t xml:space="preserve">1.84312272071838</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79504108428955</t>
+    <t xml:space="preserve">1.79504132270813</t>
   </si>
   <si>
     <t xml:space="preserve">1.7790139913559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82709550857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100038528442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73093247413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69887804985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7149053812027</t>
+    <t xml:space="preserve">1.82709527015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77100050449371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73093259334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69887816905975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71490526199341</t>
   </si>
   <si>
     <t xml:space="preserve">1.7469596862793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72291886806488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73894608020782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298701763153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75497329235077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305457115173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85914981365204</t>
+    <t xml:space="preserve">1.72291910648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73894619941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298689842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75497341156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305469036102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85914945602417</t>
   </si>
   <si>
     <t xml:space="preserve">1.86716341972351</t>
@@ -1220,28 +1220,28 @@
     <t xml:space="preserve">1.83510899543762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87517702579498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723121166229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935366630554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928551673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082967758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258087158203</t>
+    <t xml:space="preserve">1.8751767873764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935330867767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93928563594818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082943916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258134841919</t>
   </si>
   <si>
     <t xml:space="preserve">1.97133994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9878363609314</t>
+    <t xml:space="preserve">1.98783648014069</t>
   </si>
   <si>
     <t xml:space="preserve">1.9960845708847</t>
@@ -1250,58 +1250,58 @@
     <t xml:space="preserve">1.96309149265289</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9383465051651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97958815097809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03732633590698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06207084655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05382299423218</t>
+    <t xml:space="preserve">1.93834638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9795880317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03732657432556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0620710849762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05382227897644</t>
   </si>
   <si>
     <t xml:space="preserve">2.09506416320801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16929888725281</t>
+    <t xml:space="preserve">2.16929864883423</t>
   </si>
   <si>
     <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11156034469604</t>
+    <t xml:space="preserve">2.11156058311462</t>
   </si>
   <si>
     <t xml:space="preserve">2.10331225395203</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12805700302124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13630509376526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11980867385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14455342292786</t>
+    <t xml:space="preserve">2.12805676460266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13630557060242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11980891227722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14455389976501</t>
   </si>
   <si>
     <t xml:space="preserve">2.07856750488281</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22703671455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21878838539124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25178146362305</t>
+    <t xml:space="preserve">2.22703647613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21878814697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25178170204163</t>
   </si>
   <si>
     <t xml:space="preserve">2.24353313446045</t>
@@ -1310,25 +1310,25 @@
     <t xml:space="preserve">2.21054005622864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26002955436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26827812194824</t>
+    <t xml:space="preserve">2.26002979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26827788352966</t>
   </si>
   <si>
     <t xml:space="preserve">2.33426427841187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30951929092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30127120018005</t>
+    <t xml:space="preserve">2.30951976776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30127096176147</t>
   </si>
   <si>
     <t xml:space="preserve">2.31776785850525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38375377655029</t>
+    <t xml:space="preserve">2.38375401496887</t>
   </si>
   <si>
     <t xml:space="preserve">2.37550592422485</t>
@@ -1352,7 +1352,7 @@
     <t xml:space="preserve">2.39200258255005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44974040985107</t>
+    <t xml:space="preserve">2.44974064826965</t>
   </si>
   <si>
     <t xml:space="preserve">2.41674709320068</t>
@@ -1364,19 +1364,19 @@
     <t xml:space="preserve">2.40849876403809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42499566078186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45798873901367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49922966957092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47448515892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51572632789612</t>
+    <t xml:space="preserve">2.42499542236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45798850059509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4992299079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47448492050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51572608947754</t>
   </si>
   <si>
     <t xml:space="preserve">2.5899612903595</t>
@@ -1385,97 +1385,97 @@
     <t xml:space="preserve">2.54871964454651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49098181724548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5074782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44149231910706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35076069831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40025043487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19404363632202</t>
+    <t xml:space="preserve">2.4909815788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50747847557068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4414918422699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35076093673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40025067329407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19404339790344</t>
   </si>
   <si>
     <t xml:space="preserve">2.18579530715942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.045574426651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87236022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060867786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264997005463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089818000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56717395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71564292907715</t>
+    <t xml:space="preserve">2.04557418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87236034870148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264985084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089806079865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56717383861542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71564280986786</t>
   </si>
   <si>
     <t xml:space="preserve">1.64553260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64140844345093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62491178512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77338087558746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162920475006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74863588809967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80637407302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411213874817</t>
+    <t xml:space="preserve">1.64140832424164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62491190433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77338111400604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162944316864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74863612651825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80637419223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411201953888</t>
   </si>
   <si>
     <t xml:space="preserve">2.00433301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81462252140045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287061214447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84761548042297</t>
+    <t xml:space="preserve">1.81462228298187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812610149384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84761571884155</t>
   </si>
   <si>
     <t xml:space="preserve">1.83111894130707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78987753391266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360187530518</t>
+    <t xml:space="preserve">1.78987765312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885700702667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360151767731</t>
   </si>
   <si>
     <t xml:space="preserve">1.89710533618927</t>
@@ -1484,40 +1484,40 @@
     <t xml:space="preserve">1.90535354614258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95484304428101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907776832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08681559562683</t>
+    <t xml:space="preserve">1.9548431634903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907800674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08681583404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.17754697799683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07031941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07786917686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06938767433167</t>
+    <t xml:space="preserve">2.07031917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07786893844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06938815116882</t>
   </si>
   <si>
     <t xml:space="preserve">2.03546357154846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9845769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609603404999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065271854401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99305784702301</t>
+    <t xml:space="preserve">1.98457682132721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609579563141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99305772781372</t>
   </si>
   <si>
     <t xml:space="preserve">2.06090688705444</t>
@@ -1526,37 +1526,37 @@
     <t xml:space="preserve">2.02698254585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05242562294006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04394459724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0100200176239</t>
+    <t xml:space="preserve">2.05242586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04394483566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01002025604248</t>
   </si>
   <si>
     <t xml:space="preserve">2.00153923034668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89976596832275</t>
+    <t xml:space="preserve">1.89976608753204</t>
   </si>
   <si>
     <t xml:space="preserve">1.88280379772186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89128482341766</t>
+    <t xml:space="preserve">1.89128494262695</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850128173828</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95913374423981</t>
+    <t xml:space="preserve">1.95913362503052</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875580787659</t>
+    <t xml:space="preserve">2.12875556945801</t>
   </si>
   <si>
     <t xml:space="preserve">2.12027454376221</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">2.16267991065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20508527755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23052906990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30685877799988</t>
+    <t xml:space="preserve">2.20508575439453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23052883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3068585395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.33230209350586</t>
@@ -1583,22 +1583,22 @@
     <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559385299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255638122559</t>
+    <t xml:space="preserve">2.42559409141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255661964417</t>
   </si>
   <si>
     <t xml:space="preserve">2.47648048400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46799945831299</t>
+    <t xml:space="preserve">2.46799969673157</t>
   </si>
   <si>
     <t xml:space="preserve">2.49344301223755</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51040530204773</t>
+    <t xml:space="preserve">2.51040506362915</t>
   </si>
   <si>
     <t xml:space="preserve">2.43407511711121</t>
@@ -1610,28 +1610,28 @@
     <t xml:space="preserve">2.51888632774353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58673477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977248191833</t>
+    <t xml:space="preserve">2.58673453330994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977272033691</t>
   </si>
   <si>
     <t xml:space="preserve">2.54432940483093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57825374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56129169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55281019210815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53584861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52736735343933</t>
+    <t xml:space="preserve">2.57825398445129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56129145622253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55281066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53584814071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52736711502075</t>
   </si>
   <si>
     <t xml:space="preserve">2.64610242843628</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">2.6291401386261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.713951587677</t>
+    <t xml:space="preserve">2.71395134925842</t>
   </si>
   <si>
     <t xml:space="preserve">2.7309136390686</t>
@@ -1664,16 +1664,16 @@
     <t xml:space="preserve">2.78180003166199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84116768836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86661148071289</t>
+    <t xml:space="preserve">2.84116792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86661124229431</t>
   </si>
   <si>
     <t xml:space="preserve">2.88357353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90901684761047</t>
+    <t xml:space="preserve">2.90901660919189</t>
   </si>
   <si>
     <t xml:space="preserve">2.85812973976135</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">2.7393946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74787569046021</t>
+    <t xml:space="preserve">2.74787592887878</t>
   </si>
   <si>
     <t xml:space="preserve">2.79876232147217</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">2.79028129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84964895248413</t>
+    <t xml:space="preserve">2.84964871406555</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268666267395</t>
@@ -1706,10 +1706,10 @@
     <t xml:space="preserve">2.82420563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91749787330627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01078963279724</t>
+    <t xml:space="preserve">2.9174976348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01078987121582</t>
   </si>
   <si>
     <t xml:space="preserve">3.0362331867218</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">2.95990324020386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07863879203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08711981773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12104415893555</t>
+    <t xml:space="preserve">3.07863855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08711957931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12104439735413</t>
   </si>
   <si>
     <t xml:space="preserve">3.18041181564331</t>
@@ -1733,34 +1733,34 @@
     <t xml:space="preserve">3.14648723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2397792339325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22281742095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23129844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24826073646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433615684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28218483924866</t>
+    <t xml:space="preserve">3.23977947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22281718254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23129820823669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24826049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28218507766724</t>
   </si>
   <si>
     <t xml:space="preserve">3.40092039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42636370658875</t>
+    <t xml:space="preserve">3.42636346817017</t>
   </si>
   <si>
     <t xml:space="preserve">3.36699604988098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31610941886902</t>
+    <t xml:space="preserve">3.31610918045044</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066610336304</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">3.27370381355286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3079400062561</t>
+    <t xml:space="preserve">3.30794024467468</t>
   </si>
   <si>
     <t xml:space="preserve">3.31657671928406</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.27339220046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35112452507019</t>
+    <t xml:space="preserve">3.35112476348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.34248757362366</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430928230286</t>
+    <t xml:space="preserve">3.39430904388428</t>
   </si>
   <si>
     <t xml:space="preserve">3.4461305141449</t>
@@ -1796,7 +1796,7 @@
     <t xml:space="preserve">3.45476746559143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4720413684845</t>
+    <t xml:space="preserve">3.47204160690308</t>
   </si>
   <si>
     <t xml:space="preserve">3.54113698005676</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">3.60159540176392</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5929582118988</t>
+    <t xml:space="preserve">3.59295845031738</t>
   </si>
   <si>
     <t xml:space="preserve">3.65341663360596</t>
@@ -1817,16 +1817,16 @@
     <t xml:space="preserve">3.71387505531311</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67069053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7829704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80888104438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69660139083862</t>
+    <t xml:space="preserve">3.67069029808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78297066688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8088812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69660115242004</t>
   </si>
   <si>
     <t xml:space="preserve">3.62750601768494</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">3.7570595741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55841040611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67932748794556</t>
+    <t xml:space="preserve">3.55841016769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67932772636414</t>
   </si>
   <si>
     <t xml:space="preserve">3.57568430900574</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">3.58432126045227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70523810386658</t>
+    <t xml:space="preserve">3.705237865448</t>
   </si>
   <si>
     <t xml:space="preserve">3.5238630771637</t>
@@ -1871,13 +1871,13 @@
     <t xml:space="preserve">3.51522636413574</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68796420097351</t>
+    <t xml:space="preserve">3.68796443939209</t>
   </si>
   <si>
     <t xml:space="preserve">3.74842286109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66205310821533</t>
+    <t xml:space="preserve">3.66205334663391</t>
   </si>
   <si>
     <t xml:space="preserve">3.61886930465698</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">3.86933970451355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82615518569946</t>
+    <t xml:space="preserve">3.82615494728088</t>
   </si>
   <si>
     <t xml:space="preserve">3.86070275306702</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91252446174622</t>
+    <t xml:space="preserve">3.91252493858337</t>
   </si>
   <si>
     <t xml:space="preserve">3.99889373779297</t>
@@ -1916,7 +1916,7 @@
     <t xml:space="preserve">3.9297981262207</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88661336898804</t>
+    <t xml:space="preserve">3.8866138458252</t>
   </si>
   <si>
     <t xml:space="preserve">3.90388751029968</t>
@@ -1928,22 +1928,22 @@
     <t xml:space="preserve">3.81751799583435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434569358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89525032043457</t>
+    <t xml:space="preserve">3.96434617042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89525079727173</t>
   </si>
   <si>
     <t xml:space="preserve">3.93843507766724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63614320755005</t>
+    <t xml:space="preserve">3.63614296913147</t>
   </si>
   <si>
     <t xml:space="preserve">3.49795246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885684967041</t>
+    <t xml:space="preserve">3.42885661125183</t>
   </si>
   <si>
     <t xml:space="preserve">3.42021989822388</t>
@@ -1952,25 +1952,25 @@
     <t xml:space="preserve">3.28202939033508</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25611853599548</t>
+    <t xml:space="preserve">3.2561182975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.24748158454895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29930281639099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26475548744202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33385062217712</t>
+    <t xml:space="preserve">3.29930305480957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26475524902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3338508605957</t>
   </si>
   <si>
     <t xml:space="preserve">3.43749380111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37703537940979</t>
+    <t xml:space="preserve">3.37703514099121</t>
   </si>
   <si>
     <t xml:space="preserve">3.40294599533081</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">3.21293377876282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23020792007446</t>
+    <t xml:space="preserve">3.23020768165588</t>
   </si>
   <si>
     <t xml:space="preserve">3.15247559547424</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">3.56704759597778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46340465545654</t>
+    <t xml:space="preserve">3.46340489387512</t>
   </si>
   <si>
     <t xml:space="preserve">3.38567233085632</t>
@@ -2994,6 +2994,9 @@
   </si>
   <si>
     <t xml:space="preserve">8.72000026702881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73999977111816</t>
   </si>
 </sst>
 </file>
@@ -68722,7 +68725,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6912152778</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>21997</v>
@@ -68743,6 +68746,32 @@
         <v>982</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6911226852</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>37928</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>8.5600004196167</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>8.73999977111816</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>994</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652267456055</t>
+    <t xml:space="preserve">1.73652255535126</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.74400770664215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71406745910645</t>
+    <t xml:space="preserve">1.71406757831573</t>
   </si>
   <si>
     <t xml:space="preserve">1.66167271137238</t>
@@ -56,52 +56,52 @@
     <t xml:space="preserve">1.67215168476105</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969635009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921749591827</t>
+    <t xml:space="preserve">1.64969646930695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921761512756</t>
   </si>
   <si>
     <t xml:space="preserve">1.5733494758606</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49625372886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48053526878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48203241825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637347221375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460725784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42215204238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990685462952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41466701030731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41915810108185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40718233585358</t>
+    <t xml:space="preserve">1.49625384807587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48053538799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48203217983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460713863373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4221522808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990673542023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41466736793518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41915822029114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.407182097435</t>
   </si>
   <si>
     <t xml:space="preserve">1.3824816942215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38472712039948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3982001543045</t>
+    <t xml:space="preserve">1.38472723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39820027351379</t>
   </si>
   <si>
     <t xml:space="preserve">1.35703253746033</t>
@@ -110,76 +110,76 @@
     <t xml:space="preserve">1.33607470989227</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34730195999146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3428111076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3839784860611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478699207306</t>
+    <t xml:space="preserve">1.34730219841003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34281098842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397860527039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478675365448</t>
   </si>
   <si>
     <t xml:space="preserve">1.38098466396332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36975705623627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873911857605</t>
+    <t xml:space="preserve">1.36975729465485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873899936676</t>
   </si>
   <si>
     <t xml:space="preserve">1.4311341047287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41017615795135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44535577297211</t>
+    <t xml:space="preserve">1.41017627716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44535565376282</t>
   </si>
   <si>
     <t xml:space="preserve">1.46257126331329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51197230815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52544546127319</t>
+    <t xml:space="preserve">1.51197254657745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5254453420639</t>
   </si>
   <si>
     <t xml:space="preserve">1.52245128154755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54490613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191243648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54939746856689</t>
+    <t xml:space="preserve">1.54490637779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.541912317276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54939758777618</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287038326263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60029554367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60927748680115</t>
+    <t xml:space="preserve">1.60029542446136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60927760601044</t>
   </si>
   <si>
     <t xml:space="preserve">1.63173258304596</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62424778938293</t>
+    <t xml:space="preserve">1.62424755096436</t>
   </si>
   <si>
     <t xml:space="preserve">1.63023543357849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61676239967346</t>
+    <t xml:space="preserve">1.61676251888275</t>
   </si>
   <si>
     <t xml:space="preserve">1.65418767929077</t>
@@ -188,121 +188,121 @@
     <t xml:space="preserve">1.6437087059021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58682239055634</t>
+    <t xml:space="preserve">1.58682250976562</t>
   </si>
   <si>
     <t xml:space="preserve">1.5883195400238</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63472664356232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6601756811142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915774345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712139129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69161236286163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6931095123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155284881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502588272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358860492706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909751415253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68412733078003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66766059398651</t>
+    <t xml:space="preserve">1.63472652435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017556190491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691575050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712151050568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6916127204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69310975074768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155237197876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502576351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358848571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658266544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6990978717804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67664265632629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68412756919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66766083240509</t>
   </si>
   <si>
     <t xml:space="preserve">1.68263065814972</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64221131801605</t>
+    <t xml:space="preserve">1.64221143722534</t>
   </si>
   <si>
     <t xml:space="preserve">1.64670264720917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67514538764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69964492321014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68433272838593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69198894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7210818529129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70576977729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6950511932373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495735645294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7226128578186</t>
+    <t xml:space="preserve">1.6751457452774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69964528083801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6843329668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69198882579803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72108173370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70576965808868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69505107402802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495699882507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72261333465576</t>
   </si>
   <si>
     <t xml:space="preserve">1.65370869636536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67208313941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66902077198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65217745304108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.606241106987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56183576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55417954921722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202451229095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121161460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59092915058136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5289146900177</t>
+    <t xml:space="preserve">1.67208302021027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.669020652771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65217733383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60624098777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56183588504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417966842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202427387238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121173381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59092879295349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52891480922699</t>
   </si>
   <si>
     <t xml:space="preserve">1.55111742019653</t>
@@ -311,97 +311,97 @@
     <t xml:space="preserve">1.53886771202087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4929313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47608804702759</t>
+    <t xml:space="preserve">1.49293148517609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4760879278183</t>
   </si>
   <si>
     <t xml:space="preserve">1.52279007434845</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46996319293976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761905193329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50058746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60777223110199</t>
+    <t xml:space="preserve">1.46996295452118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761929035187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589953899384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058734416962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60777199268341</t>
   </si>
   <si>
     <t xml:space="preserve">1.59705376625061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56949186325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308430671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6674896478653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136455535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67667663097382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61542809009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714796066284</t>
+    <t xml:space="preserve">1.56949198246002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308418750763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66748952865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136479377747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67667675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6154283285141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714784145355</t>
   </si>
   <si>
     <t xml:space="preserve">1.58480405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63839650154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63380300998688</t>
+    <t xml:space="preserve">1.63839662075043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6338027715683</t>
   </si>
   <si>
     <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54652369022369</t>
+    <t xml:space="preserve">1.54652380943298</t>
   </si>
   <si>
     <t xml:space="preserve">1.56796085834503</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5449925661087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355563640594</t>
+    <t xml:space="preserve">1.54499244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355551719666</t>
   </si>
   <si>
     <t xml:space="preserve">1.54193007946014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58174157142639</t>
+    <t xml:space="preserve">1.58174169063568</t>
   </si>
   <si>
     <t xml:space="preserve">1.55877351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58021032810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55264866352081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53044605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5197274684906</t>
+    <t xml:space="preserve">1.58021020889282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5526487827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53044593334198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51972770690918</t>
   </si>
   <si>
     <t xml:space="preserve">1.50594663619995</t>
@@ -410,31 +410,31 @@
     <t xml:space="preserve">1.50671231746674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53427398204803</t>
+    <t xml:space="preserve">1.53427410125732</t>
   </si>
   <si>
     <t xml:space="preserve">1.56642937660217</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57408547401428</t>
+    <t xml:space="preserve">1.57408571243286</t>
   </si>
   <si>
     <t xml:space="preserve">1.58327293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59246003627777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50211870670319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824368000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47532248497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49675941467285</t>
+    <t xml:space="preserve">1.59246015548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5021185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824344158173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4753223657608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49675953388214</t>
   </si>
   <si>
     <t xml:space="preserve">1.50747787952423</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">1.52968049049377</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60011613368988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58786618709564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489825248718</t>
+    <t xml:space="preserve">1.60011625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58786642551422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489813327789</t>
   </si>
   <si>
     <t xml:space="preserve">1.56336712837219</t>
@@ -458,19 +458,19 @@
     <t xml:space="preserve">1.57255434989929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59858500957489</t>
+    <t xml:space="preserve">1.59858512878418</t>
   </si>
   <si>
     <t xml:space="preserve">1.59399139881134</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60470986366272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64758384227753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64605271816254</t>
+    <t xml:space="preserve">1.60470962524414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64758360385895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64605259895325</t>
   </si>
   <si>
     <t xml:space="preserve">1.68280148506165</t>
@@ -479,34 +479,34 @@
     <t xml:space="preserve">1.63074064254761</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452159404755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227164745331</t>
+    <t xml:space="preserve">1.63686537742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452123641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6322717666626</t>
   </si>
   <si>
     <t xml:space="preserve">1.66289579868317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595852375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026919364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558103084564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730102062225</t>
+    <t xml:space="preserve">1.66595828533173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333144187927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026895523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558138847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017464160919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730066299438</t>
   </si>
   <si>
     <t xml:space="preserve">1.70423853397369</t>
@@ -515,127 +515,127 @@
     <t xml:space="preserve">1.7379252910614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75936210155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089322566986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78386175632477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76854944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323748588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486292362213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7915176153183</t>
+    <t xml:space="preserve">1.75936257839203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089358329773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78386151790619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76854968070984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323688983917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486280441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639404773712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79151773452759</t>
   </si>
   <si>
     <t xml:space="preserve">1.80223631858826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82061088085175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754839420319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682969093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520461082458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889101028442</t>
+    <t xml:space="preserve">1.82061100006104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81754863262177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682992935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520437240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448566913605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889089107513</t>
   </si>
   <si>
     <t xml:space="preserve">1.87726557254791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85429751873016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582876205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8512350320816</t>
+    <t xml:space="preserve">1.85429739952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582864284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85123455524445</t>
   </si>
   <si>
     <t xml:space="preserve">1.86654686927795</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84970366954803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348462104797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276615619659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84510982036591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367300987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051632881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817230701447</t>
+    <t xml:space="preserve">1.84970331192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348450183868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8527660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745384216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84511029720306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367277145386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051656723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817254543304</t>
   </si>
   <si>
     <t xml:space="preserve">1.8680784702301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94923233985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788984298706</t>
+    <t xml:space="preserve">1.9492324590683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788972377777</t>
   </si>
   <si>
     <t xml:space="preserve">1.92167055606842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92932665348053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473304271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607577800751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904395103455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823093414307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894975662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00741863250732</t>
+    <t xml:space="preserve">1.92932641506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473292350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9660758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904383182526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823117256165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894999504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00741839408875</t>
   </si>
   <si>
     <t xml:space="preserve">2.01201224327087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99057507514954</t>
+    <t xml:space="preserve">1.99057531356812</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
@@ -644,25 +644,25 @@
     <t xml:space="preserve">2.00588703155518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09207773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051084518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401724815369</t>
+    <t xml:space="preserve">2.0920774936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051036834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401677131653</t>
   </si>
   <si>
     <t xml:space="preserve">2.08424234390259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11558437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17043256759644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14692640304565</t>
+    <t xml:space="preserve">2.11558389663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17043280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1469259262085</t>
   </si>
   <si>
     <t xml:space="preserve">2.15006041526794</t>
@@ -674,34 +674,34 @@
     <t xml:space="preserve">2.16259717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1516273021698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13909077644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16103029251099</t>
+    <t xml:space="preserve">2.15162777900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16103005409241</t>
   </si>
   <si>
     <t xml:space="preserve">2.04663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05290031433105</t>
+    <t xml:space="preserve">2.05290007591248</t>
   </si>
   <si>
     <t xml:space="preserve">2.03722906112671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04819869995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0450644493103</t>
+    <t xml:space="preserve">2.04819893836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04506492614746</t>
   </si>
   <si>
     <t xml:space="preserve">2.06543684005737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06073570251465</t>
+    <t xml:space="preserve">2.06073594093323</t>
   </si>
   <si>
     <t xml:space="preserve">2.10774874687195</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">2.1171510219574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12341976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125514984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19393944740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647621154785</t>
+    <t xml:space="preserve">2.12341952323914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125538825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296933174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19393920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647597312927</t>
   </si>
   <si>
     <t xml:space="preserve">2.2033417224884</t>
@@ -731,67 +731,67 @@
     <t xml:space="preserve">2.19237232208252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20804333686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416430473328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946316719055</t>
+    <t xml:space="preserve">2.20804309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1641640663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946292877197</t>
   </si>
   <si>
     <t xml:space="preserve">2.13595652580261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09677910804749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06386995315552</t>
+    <t xml:space="preserve">2.09677886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0638701915741</t>
   </si>
   <si>
     <t xml:space="preserve">2.02625942230225</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96827721595764</t>
+    <t xml:space="preserve">1.96827697753906</t>
   </si>
   <si>
     <t xml:space="preserve">1.99805176258087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07640671730042</t>
+    <t xml:space="preserve">2.07640695571899</t>
   </si>
   <si>
     <t xml:space="preserve">2.05446743965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700444221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566241264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857132911682</t>
+    <t xml:space="preserve">2.10461473464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700396537781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566193580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857085227966</t>
   </si>
   <si>
     <t xml:space="preserve">2.07797384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24095225334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371411323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117734909058</t>
+    <t xml:space="preserve">2.2409520149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371387481689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211177110672</t>
   </si>
   <si>
     <t xml:space="preserve">2.2331166267395</t>
@@ -803,28 +803,28 @@
     <t xml:space="preserve">2.31930708885193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31460571289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32714295387268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982653617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38669300079346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44467496871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48541951179504</t>
+    <t xml:space="preserve">2.3146059513092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32714247703552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557559013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982701301575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3866925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467520713806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601723670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4854199886322</t>
   </si>
   <si>
     <t xml:space="preserve">2.49012088775635</t>
@@ -836,25 +836,25 @@
     <t xml:space="preserve">2.50735902786255</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53870129585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53086543083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168825149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422501564026</t>
+    <t xml:space="preserve">2.53870105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53086566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168801307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422525405884</t>
   </si>
   <si>
     <t xml:space="preserve">2.49952363967896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52303028106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53243279457092</t>
+    <t xml:space="preserve">2.52303004264832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5324330329895</t>
   </si>
   <si>
     <t xml:space="preserve">2.51206040382385</t>
@@ -863,16 +863,16 @@
     <t xml:space="preserve">2.50892615318298</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51362729072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795627593994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638915061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616429328918</t>
+    <t xml:space="preserve">2.51362776756287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4979567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638962745667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616453170776</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653644561768</t>
@@ -884,52 +884,52 @@
     <t xml:space="preserve">2.53713393211365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55437207221985</t>
+    <t xml:space="preserve">2.55437231063843</t>
   </si>
   <si>
     <t xml:space="preserve">2.60608625411987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70794820785522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205185890198</t>
+    <t xml:space="preserve">2.70794796943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108222007751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220516204834</t>
   </si>
   <si>
     <t xml:space="preserve">2.69541096687317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70324659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67347121238708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705589294434</t>
+    <t xml:space="preserve">2.70324635505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67347168922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406893730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705613136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.59981822967529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58728075027466</t>
+    <t xml:space="preserve">2.58728098869324</t>
   </si>
   <si>
     <t xml:space="preserve">2.59825086593628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5857138633728</t>
+    <t xml:space="preserve">2.58571410179138</t>
   </si>
   <si>
     <t xml:space="preserve">2.57004284858704</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56220746040344</t>
+    <t xml:space="preserve">2.5622079372406</t>
   </si>
   <si>
     <t xml:space="preserve">2.54183530807495</t>
@@ -944,16 +944,16 @@
     <t xml:space="preserve">2.52459716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46034622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131633758545</t>
+    <t xml:space="preserve">2.46034598350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131609916687</t>
   </si>
   <si>
     <t xml:space="preserve">2.48228549957275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43370532989502</t>
+    <t xml:space="preserve">2.4337055683136</t>
   </si>
   <si>
     <t xml:space="preserve">2.39609503746033</t>
@@ -968,7 +968,7 @@
     <t xml:space="preserve">2.25975728034973</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27699565887451</t>
+    <t xml:space="preserve">2.27699542045593</t>
   </si>
   <si>
     <t xml:space="preserve">2.2879650592804</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">2.34908199310303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36475300788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064911842346</t>
+    <t xml:space="preserve">2.36475324630737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064935684204</t>
   </si>
   <si>
     <t xml:space="preserve">2.35848474502563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41333293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43683958053589</t>
+    <t xml:space="preserve">2.41333317756653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43684005737305</t>
   </si>
   <si>
     <t xml:space="preserve">2.62489175796509</t>
@@ -998,103 +998,106 @@
     <t xml:space="preserve">2.6327269077301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46818161010742</t>
+    <t xml:space="preserve">2.468181848526</t>
   </si>
   <si>
     <t xml:space="preserve">2.36632013320923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.381991147995</t>
+    <t xml:space="preserve">2.38199138641357</t>
   </si>
   <si>
     <t xml:space="preserve">2.39766192436218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45251059532166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40549731254578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42116856575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900371551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363655090332</t>
+    <t xml:space="preserve">2.45251083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40549802780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4211688041687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878740310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363607406616</t>
   </si>
   <si>
     <t xml:space="preserve">2.25662326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27229452133179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28012990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445889472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528123855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1235978603363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09955716133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08352994918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09154319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01942110061646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750249862671</t>
+    <t xml:space="preserve">2.27229380607605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28012943267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445865631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528100013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558413505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12359833717346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0995569229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08352971076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09154367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01942133903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339436531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750273704529</t>
   </si>
   <si>
     <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29188299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13962507247925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16366600990295</t>
+    <t xml:space="preserve">2.29188251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13962483406067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16366577148438</t>
   </si>
   <si>
     <t xml:space="preserve">2.14763855934143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20373368263245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13161134719849</t>
+    <t xml:space="preserve">2.20373344421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13161158561707</t>
   </si>
   <si>
     <t xml:space="preserve">2.17167925834656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19572019577026</t>
+    <t xml:space="preserve">2.19571995735168</t>
   </si>
   <si>
     <t xml:space="preserve">2.17969274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10757064819336</t>
+    <t xml:space="preserve">2.10757088661194</t>
   </si>
   <si>
     <t xml:space="preserve">2.05948925018311</t>
@@ -1103,172 +1106,169 @@
     <t xml:space="preserve">2.07551622390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03544855117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05147576332092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27585554122925</t>
+    <t xml:space="preserve">2.0354483127594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05147552490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27585577964783</t>
   </si>
   <si>
     <t xml:space="preserve">2.26784205436707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21976065635681</t>
+    <t xml:space="preserve">2.21976041793823</t>
   </si>
   <si>
     <t xml:space="preserve">2.21174716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24380159378052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23578763008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22777438163757</t>
+    <t xml:space="preserve">2.24380135536194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23578786849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22777414321899</t>
   </si>
   <si>
     <t xml:space="preserve">2.15565204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30791020393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0274350643158</t>
+    <t xml:space="preserve">2.30790996551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02743482589722</t>
   </si>
   <si>
     <t xml:space="preserve">2.04346203804016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99538064002991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524457931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325842380524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96332633495331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97134017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736691474915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140761375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81106853485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81908178329468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84312272071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79504132270813</t>
+    <t xml:space="preserve">1.9953807592392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524481773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325830459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9633264541626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133982181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736667633057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140785217285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8110682964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81908190250397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8431224822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79504096508026</t>
   </si>
   <si>
     <t xml:space="preserve">1.7790139913559</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82709527015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100050449371</t>
+    <t xml:space="preserve">1.82709538936615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77100026607513</t>
   </si>
   <si>
     <t xml:space="preserve">1.73093259334564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69887816905975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71490526199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7469596862793</t>
+    <t xml:space="preserve">1.69887804985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7149053812027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695980548859</t>
   </si>
   <si>
     <t xml:space="preserve">1.72291910648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73894619941711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298689842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75497341156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305469036102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85914945602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86716341972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510899543762</t>
+    <t xml:space="preserve">1.7389463186264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298666000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75497329235077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305457115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85914957523346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86716330051422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510875701904</t>
   </si>
   <si>
     <t xml:space="preserve">1.8751767873764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90723133087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935330867767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928563594818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082943916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258134841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97133994102478</t>
+    <t xml:space="preserve">1.90723145008087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935354709625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93928575515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258087158203</t>
   </si>
   <si>
     <t xml:space="preserve">1.98783648014069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9960845708847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96309149265289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834638595581</t>
+    <t xml:space="preserve">1.99608469009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96309161186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93834662437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.9795880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03732657432556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0620710849762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05382227897644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09506416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16929864883423</t>
+    <t xml:space="preserve">2.0373260974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06207084655762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0538227558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09506392478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16929888725281</t>
   </si>
   <si>
     <t xml:space="preserve">2.16105008125305</t>
@@ -1277,19 +1277,19 @@
     <t xml:space="preserve">2.11156058311462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10331225395203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12805676460266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13630557060242</t>
+    <t xml:space="preserve">2.10331249237061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12805724143982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13630533218384</t>
   </si>
   <si>
     <t xml:space="preserve">2.11980891227722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14455389976501</t>
+    <t xml:space="preserve">2.14455366134644</t>
   </si>
   <si>
     <t xml:space="preserve">2.07856750488281</t>
@@ -1298,10 +1298,10 @@
     <t xml:space="preserve">2.22703647613525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21878814697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25178170204163</t>
+    <t xml:space="preserve">2.21878838539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25178146362305</t>
   </si>
   <si>
     <t xml:space="preserve">2.24353313446045</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">2.21054005622864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26002979278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26827788352966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33426427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30951976776123</t>
+    <t xml:space="preserve">2.26002955436707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26827812194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33426403999329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30951952934265</t>
   </si>
   <si>
     <t xml:space="preserve">2.30127096176147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31776785850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38375401496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37550592422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601594924927</t>
+    <t xml:space="preserve">2.31776762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38375425338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37550568580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601571083069</t>
   </si>
   <si>
     <t xml:space="preserve">2.27652621269226</t>
@@ -1349,19 +1349,19 @@
     <t xml:space="preserve">2.23528480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200258255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44974064826965</t>
+    <t xml:space="preserve">2.39200234413147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44974040985107</t>
   </si>
   <si>
     <t xml:space="preserve">2.41674709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43324375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849876403809</t>
+    <t xml:space="preserve">2.43324398994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849900245667</t>
   </si>
   <si>
     <t xml:space="preserve">2.42499542236328</t>
@@ -1370,16 +1370,16 @@
     <t xml:space="preserve">2.45798850059509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4992299079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47448492050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51572608947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5899612903595</t>
+    <t xml:space="preserve">2.49923014640808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47448515892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51572632789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
     <t xml:space="preserve">2.54871964454651</t>
@@ -1397,13 +1397,13 @@
     <t xml:space="preserve">2.35076093673706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40025067329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19404339790344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18579530715942</t>
+    <t xml:space="preserve">2.40025043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19404363632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.185795545578</t>
   </si>
   <si>
     <t xml:space="preserve">2.04557418823242</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">1.87236034870148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88060855865479</t>
+    <t xml:space="preserve">1.8806084394455</t>
   </si>
   <si>
     <t xml:space="preserve">1.68264985084534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69089806079865</t>
+    <t xml:space="preserve">1.69089818000793</t>
   </si>
   <si>
     <t xml:space="preserve">1.56717383861542</t>
@@ -1430,22 +1430,22 @@
     <t xml:space="preserve">1.64553260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64140832424164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62491190433502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77338111400604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162944316864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74863612651825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80637419223785</t>
+    <t xml:space="preserve">1.64140844345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62491178512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77338123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162932395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74863600730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80637407302856</t>
   </si>
   <si>
     <t xml:space="preserve">1.86411201953888</t>
@@ -1454,16 +1454,16 @@
     <t xml:space="preserve">2.00433301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81462228298187</t>
+    <t xml:space="preserve">1.81462216377258</t>
   </si>
   <si>
     <t xml:space="preserve">1.79812610149384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287073135376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84761571884155</t>
+    <t xml:space="preserve">1.82287061214447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84761524200439</t>
   </si>
   <si>
     <t xml:space="preserve">1.83111894130707</t>
@@ -1472,16 +1472,16 @@
     <t xml:space="preserve">1.78987765312195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88885700702667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360151767731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710533618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90535354614258</t>
+    <t xml:space="preserve">1.88885688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360175609589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710509777069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90535342693329</t>
   </si>
   <si>
     <t xml:space="preserve">1.9548431634903</t>
@@ -1493,31 +1493,31 @@
     <t xml:space="preserve">2.08681583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17754697799683</t>
+    <t xml:space="preserve">2.17754673957825</t>
   </si>
   <si>
     <t xml:space="preserve">2.07031917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07786893844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06938815116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03546357154846</t>
+    <t xml:space="preserve">2.07786917686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06938791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03546333312988</t>
   </si>
   <si>
     <t xml:space="preserve">1.98457682132721</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97609579563141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065259933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99305772781372</t>
+    <t xml:space="preserve">1.97609567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065248012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99305808544159</t>
   </si>
   <si>
     <t xml:space="preserve">2.06090688705444</t>
@@ -1532,25 +1532,25 @@
     <t xml:space="preserve">2.04394483566284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01002025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00153923034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89976608753204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88280379772186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128494262695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01850128173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913362503052</t>
+    <t xml:space="preserve">2.0100200176239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0015389919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89976584911346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88280367851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128482341766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01850152015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913350582123</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
@@ -1565,16 +1565,16 @@
     <t xml:space="preserve">2.16267991065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20508575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23052883148193</t>
+    <t xml:space="preserve">2.20508527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23052906990051</t>
   </si>
   <si>
     <t xml:space="preserve">2.3068585395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33230209350586</t>
+    <t xml:space="preserve">2.33230185508728</t>
   </si>
   <si>
     <t xml:space="preserve">2.34926414489746</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559409141541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255661964417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47648048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46799969673157</t>
+    <t xml:space="preserve">2.42559385299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255614280701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47648072242737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46799945831299</t>
   </si>
   <si>
     <t xml:space="preserve">2.49344301223755</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">2.51040506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43407511711121</t>
+    <t xml:space="preserve">2.43407487869263</t>
   </si>
   <si>
     <t xml:space="preserve">2.41711282730103</t>
@@ -1610,16 +1610,16 @@
     <t xml:space="preserve">2.51888632774353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58673453330994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977272033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54432940483093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57825398445129</t>
+    <t xml:space="preserve">2.58673501014709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977295875549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54432964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57825374603271</t>
   </si>
   <si>
     <t xml:space="preserve">2.56129145622253</t>
@@ -1628,19 +1628,19 @@
     <t xml:space="preserve">2.55281066894531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53584814071655</t>
+    <t xml:space="preserve">2.53584837913513</t>
   </si>
   <si>
     <t xml:space="preserve">2.52736711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64610242843628</t>
+    <t xml:space="preserve">2.64610266685486</t>
   </si>
   <si>
     <t xml:space="preserve">2.63762164115906</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66306495666504</t>
+    <t xml:space="preserve">2.66306471824646</t>
   </si>
   <si>
     <t xml:space="preserve">2.70547032356262</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">2.69698929786682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6291401386261</t>
+    <t xml:space="preserve">2.62914037704468</t>
   </si>
   <si>
     <t xml:space="preserve">2.71395134925842</t>
@@ -1658,46 +1658,46 @@
     <t xml:space="preserve">2.7309136390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77331900596619</t>
+    <t xml:space="preserve">2.77331924438477</t>
   </si>
   <si>
     <t xml:space="preserve">2.78180003166199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84116792678833</t>
+    <t xml:space="preserve">2.84116768836975</t>
   </si>
   <si>
     <t xml:space="preserve">2.86661124229431</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88357353210449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90901660919189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85812973976135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80724334716797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75635695457458</t>
+    <t xml:space="preserve">2.88357329368591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90901684761047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85812997817993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80724358558655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75635671615601</t>
   </si>
   <si>
     <t xml:space="preserve">2.7393946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74787592887878</t>
+    <t xml:space="preserve">2.74787569046021</t>
   </si>
   <si>
     <t xml:space="preserve">2.79876232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79028129577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84964871406555</t>
+    <t xml:space="preserve">2.79028105735779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84964895248413</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268666267395</t>
@@ -1715,52 +1715,52 @@
     <t xml:space="preserve">3.0362331867218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95990324020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07863855361938</t>
+    <t xml:space="preserve">2.95990347862244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07863879203796</t>
   </si>
   <si>
     <t xml:space="preserve">3.08711957931519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12104439735413</t>
+    <t xml:space="preserve">3.12104415893555</t>
   </si>
   <si>
     <t xml:space="preserve">3.18041181564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14648723602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23977947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22281718254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23129820823669</t>
+    <t xml:space="preserve">3.14648747444153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2397792339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23129844665527</t>
   </si>
   <si>
     <t xml:space="preserve">3.24826049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21433639526367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28218507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40092039108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42636346817017</t>
+    <t xml:space="preserve">3.21433615684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28218483924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40092062950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42636370658875</t>
   </si>
   <si>
     <t xml:space="preserve">3.36699604988098</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31610918045044</t>
+    <t xml:space="preserve">3.31610941886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066610336304</t>
@@ -1769,7 +1769,7 @@
     <t xml:space="preserve">3.27370381355286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30794024467468</t>
+    <t xml:space="preserve">3.3079400062561</t>
   </si>
   <si>
     <t xml:space="preserve">3.31657671928406</t>
@@ -1787,52 +1787,52 @@
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4461305141449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45476746559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47204160690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54113698005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60159540176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59295845031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65341663360596</t>
+    <t xml:space="preserve">3.39430952072144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44613075256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45476770401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4720413684845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54113674163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60159516334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5929582118988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65341711044312</t>
   </si>
   <si>
     <t xml:space="preserve">3.61023187637329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71387505531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069029808044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78297066688538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8088812828064</t>
+    <t xml:space="preserve">3.71387553215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069053649902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78297090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80888104438782</t>
   </si>
   <si>
     <t xml:space="preserve">3.69660115242004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62750601768494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.644779920578</t>
+    <t xml:space="preserve">3.62750554084778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64477944374084</t>
   </si>
   <si>
     <t xml:space="preserve">3.73978567123413</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">3.7570595741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55841016769409</t>
+    <t xml:space="preserve">3.55841064453125</t>
   </si>
   <si>
     <t xml:space="preserve">3.67932772636414</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">3.58432126045227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.705237865448</t>
+    <t xml:space="preserve">3.70523834228516</t>
   </si>
   <si>
     <t xml:space="preserve">3.5238630771637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54977369308472</t>
+    <t xml:space="preserve">3.54977345466614</t>
   </si>
   <si>
     <t xml:space="preserve">3.48931527137756</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">3.41158318519592</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51522636413574</t>
+    <t xml:space="preserve">3.51522588729858</t>
   </si>
   <si>
     <t xml:space="preserve">3.68796443939209</t>
@@ -1877,100 +1877,100 @@
     <t xml:space="preserve">3.74842286109924</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66205334663391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61886930465698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86933970451355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82615494728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86070275306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91252493858337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99889373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95570874214172</t>
+    <t xml:space="preserve">3.66205310821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6188690662384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86933922767639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8261547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8607029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91252446174622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99889349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95570850372314</t>
   </si>
   <si>
     <t xml:space="preserve">3.99025678634644</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84342861175537</t>
+    <t xml:space="preserve">3.84342885017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.77433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76569676399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9297981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8866138458252</t>
+    <t xml:space="preserve">3.76569652557373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92979860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661336898804</t>
   </si>
   <si>
     <t xml:space="preserve">3.90388751029968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8779764175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81751799583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
+    <t xml:space="preserve">3.87797617912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81751847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434569358826</t>
   </si>
   <si>
     <t xml:space="preserve">3.89525079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93843507766724</t>
+    <t xml:space="preserve">3.93843483924866</t>
   </si>
   <si>
     <t xml:space="preserve">3.63614296913147</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49795246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42885661125183</t>
+    <t xml:space="preserve">3.4979522228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42885708808899</t>
   </si>
   <si>
     <t xml:space="preserve">3.42021989822388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28202939033508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2561182975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24748158454895</t>
+    <t xml:space="preserve">3.2820291519165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25611853599548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24748134613037</t>
   </si>
   <si>
     <t xml:space="preserve">3.29930305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26475524902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3338508605957</t>
+    <t xml:space="preserve">3.26475548744202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33385062217712</t>
   </si>
   <si>
     <t xml:space="preserve">3.43749380111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37703514099121</t>
+    <t xml:space="preserve">3.37703537940979</t>
   </si>
   <si>
     <t xml:space="preserve">3.40294599533081</t>
@@ -1988,46 +1988,46 @@
     <t xml:space="preserve">3.15247559547424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11792778968811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19565987586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14383864402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97973704338074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06610608100891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53250002861023</t>
+    <t xml:space="preserve">3.11792755126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19566011428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14383840560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97973728179932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06610631942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53249979019165</t>
   </si>
   <si>
     <t xml:space="preserve">3.56704759597778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46340489387512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38567233085632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54223012924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57765245437622</t>
+    <t xml:space="preserve">3.46340465545654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38567209243774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54222989082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57765221595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.56879687309265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5245189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6130747795105</t>
+    <t xml:space="preserve">3.52451872825623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61307454109192</t>
   </si>
   <si>
     <t xml:space="preserve">3.58650803565979</t>
@@ -2045,28 +2045,28 @@
     <t xml:space="preserve">3.33855175971985</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34740734100342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26770710945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30312943458557</t>
+    <t xml:space="preserve">3.34740710258484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26770734786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30312967300415</t>
   </si>
   <si>
     <t xml:space="preserve">3.2322850227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27656269073486</t>
+    <t xml:space="preserve">3.27656292915344</t>
   </si>
   <si>
     <t xml:space="preserve">3.32969617843628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32084059715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28541827201843</t>
+    <t xml:space="preserve">3.32084083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28541851043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.42710757255554</t>
@@ -2084,22 +2084,19 @@
     <t xml:space="preserve">3.48909664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53337430953979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59536361694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55994129180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4979522228241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46252989768982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36511850357056</t>
+    <t xml:space="preserve">3.53337454795837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59536337852478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5599410533905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4625301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36511826515198</t>
   </si>
   <si>
     <t xml:space="preserve">3.41825175285339</t>
@@ -2108,28 +2105,28 @@
     <t xml:space="preserve">3.38282942771912</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44481873512268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45367407798767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48024106025696</t>
+    <t xml:space="preserve">3.44481897354126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45367431640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48024129867554</t>
   </si>
   <si>
     <t xml:space="preserve">3.39168524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24999594688416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08173990249634</t>
+    <t xml:space="preserve">3.24999618530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08174014091492</t>
   </si>
   <si>
     <t xml:space="preserve">3.1437292098999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11716222763062</t>
+    <t xml:space="preserve">3.11716246604919</t>
   </si>
   <si>
     <t xml:space="preserve">3.09059572219849</t>
@@ -2144,7 +2141,7 @@
     <t xml:space="preserve">2.84263968467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86920619010925</t>
+    <t xml:space="preserve">2.86920642852783</t>
   </si>
   <si>
     <t xml:space="preserve">2.74522805213928</t>
@@ -2153,7 +2150,7 @@
     <t xml:space="preserve">2.65667247772217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56811690330505</t>
+    <t xml:space="preserve">2.56811666488647</t>
   </si>
   <si>
     <t xml:space="preserve">2.78950619697571</t>
@@ -2162,10 +2159,10 @@
     <t xml:space="preserve">2.75408363342285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72751712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6832389831543</t>
+    <t xml:space="preserve">2.72751688957214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68323922157288</t>
   </si>
   <si>
     <t xml:space="preserve">2.82492852210999</t>
@@ -2186,7 +2183,7 @@
     <t xml:space="preserve">2.9931845664978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0640287399292</t>
+    <t xml:space="preserve">3.06402897834778</t>
   </si>
   <si>
     <t xml:space="preserve">3.07288455963135</t>
@@ -2195,10 +2192,10 @@
     <t xml:space="preserve">3.01975131034851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09945106506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03746247291565</t>
+    <t xml:space="preserve">3.09945130348206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03746223449707</t>
   </si>
   <si>
     <t xml:space="preserve">2.94005084037781</t>
@@ -2237,25 +2234,25 @@
     <t xml:space="preserve">2.81607294082642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8780620098114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02860689163208</t>
+    <t xml:space="preserve">2.87806177139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0286066532135</t>
   </si>
   <si>
     <t xml:space="preserve">3.05517339706421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17029571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19686269760132</t>
+    <t xml:space="preserve">3.17029595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19686245918274</t>
   </si>
   <si>
     <t xml:space="preserve">3.24114060401917</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25885152816772</t>
+    <t xml:space="preserve">3.2588517665863</t>
   </si>
   <si>
     <t xml:space="preserve">3.16144037246704</t>
@@ -2267,64 +2264,67 @@
     <t xml:space="preserve">3.40054059028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47138524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50680780410767</t>
+    <t xml:space="preserve">3.47138547897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50680756568909</t>
   </si>
   <si>
     <t xml:space="preserve">3.60421919822693</t>
   </si>
   <si>
+    <t xml:space="preserve">3.63078570365906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62193036079407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63964152336121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67674517631531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71351265907288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72270464897156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77785563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69512891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70432090759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78704738616943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75947213172913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8146231174469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76866388320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75028014183044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63997769355774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64916968345642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66755318641663</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.63078594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62193036079407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63964128494263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67674517631531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71351265907288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72270464897156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77785563468933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69512891769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70432090759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78704738616943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75947213172913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8146231174469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76866388320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75028014183044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63997769355774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64916968345642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66755318641663</t>
   </si>
   <si>
     <t xml:space="preserve">3.62159395217896</t>
@@ -19135,7 +19135,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G608" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19161,7 +19161,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19187,7 +19187,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G610" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19213,7 +19213,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G611" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19239,7 +19239,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G612" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19265,7 +19265,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19291,7 +19291,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G614" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19317,7 +19317,7 @@
         <v>2.5</v>
       </c>
       <c r="G615" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19343,7 +19343,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G616" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19369,7 +19369,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19395,7 +19395,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G618" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19421,7 +19421,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G619" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19447,7 +19447,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G620" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19473,7 +19473,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G621" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19499,7 +19499,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G622" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19525,7 +19525,7 @@
         <v>2.75</v>
       </c>
       <c r="G623" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19551,7 +19551,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G624" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19577,7 +19577,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19603,7 +19603,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G626" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19629,7 +19629,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G627" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19655,7 +19655,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G628" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19681,7 +19681,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19707,7 +19707,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19733,7 +19733,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G631" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19759,7 +19759,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G632" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19785,7 +19785,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19811,7 +19811,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G634" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19837,7 +19837,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G635" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19863,7 +19863,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19889,7 +19889,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G637" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19915,7 +19915,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G638" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19941,7 +19941,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G639" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19967,7 +19967,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G640" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -19993,7 +19993,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G641" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20019,7 +20019,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20045,7 +20045,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G643" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20071,7 +20071,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20097,7 +20097,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G645" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20123,7 +20123,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G646" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20149,7 +20149,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G647" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20175,7 +20175,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G648" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20201,7 +20201,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G649" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20227,7 +20227,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G650" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20253,7 +20253,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G651" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20279,7 +20279,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20305,7 +20305,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G653" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20331,7 +20331,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20357,7 +20357,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20383,7 +20383,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20409,7 +20409,7 @@
         <v>2.5</v>
       </c>
       <c r="G657" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20435,7 +20435,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G658" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20461,7 +20461,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G659" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20487,7 +20487,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G660" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20513,7 +20513,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G661" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20539,7 +20539,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G662" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20565,7 +20565,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20591,7 +20591,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G664" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20617,7 +20617,7 @@
         <v>2.75</v>
       </c>
       <c r="G665" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20643,7 +20643,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20669,7 +20669,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20695,7 +20695,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G668" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20721,7 +20721,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20747,7 +20747,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20773,7 +20773,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20799,7 +20799,7 @@
         <v>2.75</v>
       </c>
       <c r="G672" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20825,7 +20825,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20851,7 +20851,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20877,7 +20877,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G675" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20903,7 +20903,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G676" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20929,7 +20929,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G677" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20955,7 +20955,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G678" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20981,7 +20981,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G679" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21007,7 +21007,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G680" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21033,7 +21033,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21059,7 +21059,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21085,7 +21085,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G683" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21111,7 +21111,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G684" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21137,7 +21137,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G685" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21163,7 +21163,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G686" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21189,7 +21189,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21215,7 +21215,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G688" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21241,7 +21241,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21267,7 +21267,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G690" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21293,7 +21293,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G691" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21319,7 +21319,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G692" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21345,7 +21345,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21371,7 +21371,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G694" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21397,7 +21397,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G695" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21423,7 +21423,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21449,7 +21449,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21475,7 +21475,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G698" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21501,7 +21501,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G699" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21527,7 +21527,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G700" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21553,7 +21553,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G701" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21579,7 +21579,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G702" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21605,7 +21605,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G703" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21631,7 +21631,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G704" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21657,7 +21657,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21683,7 +21683,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21709,7 +21709,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G707" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21735,7 +21735,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G708" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21761,7 +21761,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21787,7 +21787,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G710" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21813,7 +21813,7 @@
         <v>2.5</v>
       </c>
       <c r="G711" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21839,7 +21839,7 @@
         <v>2.5</v>
       </c>
       <c r="G712" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21865,7 +21865,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G713" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21891,7 +21891,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21917,7 +21917,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G715" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21943,7 +21943,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21969,7 +21969,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G717" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -21995,7 +21995,7 @@
         <v>2.5</v>
       </c>
       <c r="G718" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22021,7 +22021,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G719" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22047,7 +22047,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G720" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22073,7 +22073,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G721" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22099,7 +22099,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G722" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22125,7 +22125,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22151,7 +22151,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G724" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22177,7 +22177,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G725" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22203,7 +22203,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G726" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22229,7 +22229,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G727" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22255,7 +22255,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G728" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22281,7 +22281,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G729" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22307,7 +22307,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G730" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22333,7 +22333,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22359,7 +22359,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G732" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22385,7 +22385,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22411,7 +22411,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22437,7 +22437,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G735" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22463,7 +22463,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G736" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22489,7 +22489,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G737" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22515,7 +22515,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G738" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22541,7 +22541,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G739" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22567,7 +22567,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G740" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22593,7 +22593,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G741" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22619,7 +22619,7 @@
         <v>2.5</v>
       </c>
       <c r="G742" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22645,7 +22645,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G743" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22671,7 +22671,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G744" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22697,7 +22697,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G745" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22723,7 +22723,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G746" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22749,7 +22749,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G747" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22775,7 +22775,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22801,7 +22801,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G749" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22827,7 +22827,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22853,7 +22853,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G751" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22879,7 +22879,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G752" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22905,7 +22905,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22931,7 +22931,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22957,7 +22957,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G755" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22983,7 +22983,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G756" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23009,7 +23009,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G757" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23035,7 +23035,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G758" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23061,7 +23061,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G759" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23087,7 +23087,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23113,7 +23113,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G761" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23139,7 +23139,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G762" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23165,7 +23165,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G763" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23191,7 +23191,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G764" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23217,7 +23217,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G765" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23243,7 +23243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G766" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23269,7 +23269,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G767" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23295,7 +23295,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G768" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23321,7 +23321,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23347,7 +23347,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G770" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23373,7 +23373,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G771" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23399,7 +23399,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G772" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23425,7 +23425,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G773" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23451,7 +23451,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G774" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23477,7 +23477,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G775" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23503,7 +23503,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G776" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23529,7 +23529,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23555,7 +23555,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G778" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23581,7 +23581,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G779" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23607,7 +23607,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G780" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23633,7 +23633,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23659,7 +23659,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23685,7 +23685,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G783" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23711,7 +23711,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G784" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23737,7 +23737,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G785" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23763,7 +23763,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G786" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23789,7 +23789,7 @@
         <v>2.25</v>
       </c>
       <c r="G787" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23815,7 +23815,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G788" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23841,7 +23841,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G789" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23867,7 +23867,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23893,7 +23893,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23919,7 +23919,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G792" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23945,7 +23945,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G793" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23971,7 +23971,7 @@
         <v>2.5</v>
       </c>
       <c r="G794" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -23997,7 +23997,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G795" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24023,7 +24023,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24049,7 +24049,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24075,7 +24075,7 @@
         <v>2.5</v>
       </c>
       <c r="G798" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24101,7 +24101,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G799" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24127,7 +24127,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G800" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24153,7 +24153,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G801" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24179,7 +24179,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G802" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24205,7 +24205,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G803" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24231,7 +24231,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24257,7 +24257,7 @@
         <v>2.5</v>
       </c>
       <c r="G805" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24283,7 +24283,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G806" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24309,7 +24309,7 @@
         <v>2.5</v>
       </c>
       <c r="G807" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24335,7 +24335,7 @@
         <v>2.5</v>
       </c>
       <c r="G808" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24361,7 +24361,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G809" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24387,7 +24387,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G810" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24413,7 +24413,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G811" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24439,7 +24439,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G812" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24465,7 +24465,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G813" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24491,7 +24491,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24517,7 +24517,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G815" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24543,7 +24543,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24569,7 +24569,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G817" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24595,7 +24595,7 @@
         <v>2.5</v>
       </c>
       <c r="G818" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24621,7 +24621,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24647,7 +24647,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G820" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24673,7 +24673,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24699,7 +24699,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G822" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24725,7 +24725,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G823" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24751,7 +24751,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G824" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24777,7 +24777,7 @@
         <v>2.5</v>
       </c>
       <c r="G825" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24803,7 +24803,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24829,7 +24829,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G827" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24855,7 +24855,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G828" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24881,7 +24881,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G829" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24907,7 +24907,7 @@
         <v>2.5</v>
       </c>
       <c r="G830" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24933,7 +24933,7 @@
         <v>2.5</v>
       </c>
       <c r="G831" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24959,7 +24959,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24985,7 +24985,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G833" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25011,7 +25011,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G834" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25037,7 +25037,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G835" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25063,7 +25063,7 @@
         <v>2.5</v>
       </c>
       <c r="G836" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25089,7 +25089,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G837" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25115,7 +25115,7 @@
         <v>2.5</v>
       </c>
       <c r="G838" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25141,7 +25141,7 @@
         <v>2.5</v>
       </c>
       <c r="G839" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25167,7 +25167,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25193,7 +25193,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G841" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25219,7 +25219,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G842" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25245,7 +25245,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G843" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25271,7 +25271,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G844" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25297,7 +25297,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25323,7 +25323,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G846" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25349,7 +25349,7 @@
         <v>2.5</v>
       </c>
       <c r="G847" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25375,7 +25375,7 @@
         <v>2.5</v>
       </c>
       <c r="G848" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25401,7 +25401,7 @@
         <v>2.5</v>
       </c>
       <c r="G849" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25427,7 +25427,7 @@
         <v>2.5</v>
       </c>
       <c r="G850" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25453,7 +25453,7 @@
         <v>2.5</v>
       </c>
       <c r="G851" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25479,7 +25479,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25505,7 +25505,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25531,7 +25531,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G854" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25557,7 +25557,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G855" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25583,7 +25583,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G856" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25609,7 +25609,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G857" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25635,7 +25635,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25661,7 +25661,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G859" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25687,7 +25687,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25713,7 +25713,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G861" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25739,7 +25739,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G862" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25817,7 +25817,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G865" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -25999,7 +25999,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G872" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26181,7 +26181,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G879" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26207,7 +26207,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G880" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26233,7 +26233,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G881" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -31537,7 +31537,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1085" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32525,7 +32525,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32551,7 +32551,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32629,7 +32629,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1127" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32733,7 +32733,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1131" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32863,7 +32863,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1136" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32993,7 +32993,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1141" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33253,7 +33253,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1151" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33305,7 +33305,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1153" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33331,7 +33331,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1154" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33383,7 +33383,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1156" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34163,7 +34163,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1186" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34241,7 +34241,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1189" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -46929,7 +46929,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1677" t="s">
-        <v>693</v>
+        <v>642</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46955,7 +46955,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1678" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47007,7 +47007,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1680" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47033,7 +47033,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1681" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47163,7 +47163,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1686" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47189,7 +47189,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1687" t="s">
-        <v>693</v>
+        <v>642</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47215,7 +47215,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1688" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47241,7 +47241,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1689" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47319,7 +47319,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1692" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47345,7 +47345,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1693" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47371,7 +47371,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1694" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47449,7 +47449,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1697" t="s">
-        <v>693</v>
+        <v>642</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47475,7 +47475,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1698" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47501,7 +47501,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47527,7 +47527,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1700" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47579,7 +47579,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1702" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47605,7 +47605,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1703" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47631,7 +47631,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1704" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47657,7 +47657,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1705" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47787,7 +47787,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47839,7 +47839,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47865,7 +47865,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1713" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47891,7 +47891,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47917,7 +47917,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1715" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47943,7 +47943,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47969,7 +47969,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1717" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -47995,7 +47995,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48021,7 +48021,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48047,7 +48047,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48073,7 +48073,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48099,7 +48099,7 @@
         <v>3</v>
       </c>
       <c r="G1722" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48125,7 +48125,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1723" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48151,7 +48151,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48177,7 +48177,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1725" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48203,7 +48203,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1726" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48229,7 +48229,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1727" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48255,7 +48255,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48281,7 +48281,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48307,7 +48307,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1730" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48333,7 +48333,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1731" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48359,7 +48359,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48385,7 +48385,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1733" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48411,7 +48411,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1734" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48437,7 +48437,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1735" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48463,7 +48463,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1736" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48489,7 +48489,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1737" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48515,7 +48515,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1738" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48541,7 +48541,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1739" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48567,7 +48567,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1740" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48593,7 +48593,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1741" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48619,7 +48619,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1742" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48645,7 +48645,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48671,7 +48671,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1744" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48697,7 +48697,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1745" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48723,7 +48723,7 @@
         <v>3.5</v>
       </c>
       <c r="G1746" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48749,7 +48749,7 @@
         <v>3.5</v>
       </c>
       <c r="G1747" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48775,7 +48775,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1748" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48801,7 +48801,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1749" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48827,7 +48827,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1750" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48853,7 +48853,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48879,7 +48879,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1752" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48905,7 +48905,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1753" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48931,7 +48931,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1754" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48957,7 +48957,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1755" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48983,7 +48983,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1756" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49009,7 +49009,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1757" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49035,7 +49035,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49061,7 +49061,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1759" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49087,7 +49087,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49113,7 +49113,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1761" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49139,7 +49139,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1762" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49165,7 +49165,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1763" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49191,7 +49191,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1764" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49217,7 +49217,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1765" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49243,7 +49243,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1766" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49269,7 +49269,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1767" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49295,7 +49295,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1768" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49321,7 +49321,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1769" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49347,7 +49347,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1770" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49373,7 +49373,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1771" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49399,7 +49399,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1772" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49425,7 +49425,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1773" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49451,7 +49451,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1774" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49477,7 +49477,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1775" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49503,7 +49503,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1776" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49529,7 +49529,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49555,7 +49555,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1778" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49581,7 +49581,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1779" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49607,7 +49607,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49633,7 +49633,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1781" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49659,7 +49659,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1782" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49685,7 +49685,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49711,7 +49711,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1784" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49737,7 +49737,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1785" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49763,7 +49763,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1786" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49789,7 +49789,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1787" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49815,7 +49815,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49841,7 +49841,7 @@
         <v>3.25</v>
       </c>
       <c r="G1789" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49867,7 +49867,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1790" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49893,7 +49893,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1791" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49919,7 +49919,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1792" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49945,7 +49945,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1793" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49971,7 +49971,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -49997,7 +49997,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50023,7 +50023,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1796" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50049,7 +50049,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1797" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50075,7 +50075,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1798" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50101,7 +50101,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1799" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50127,7 +50127,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1800" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50153,7 +50153,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1801" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50179,7 +50179,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50231,7 +50231,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1804" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50257,7 +50257,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1805" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50283,7 +50283,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1806" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50309,7 +50309,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1807" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50335,7 +50335,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1808" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50413,7 +50413,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1811" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50621,7 +50621,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1819" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50803,7 +50803,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1826" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50829,7 +50829,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1827" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50855,7 +50855,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1828" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50907,7 +50907,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1830" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50933,7 +50933,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50959,7 +50959,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1832" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -50985,7 +50985,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1833" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51011,7 +51011,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51037,7 +51037,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1835" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51115,7 +51115,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1838" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51271,7 +51271,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1844" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51349,7 +51349,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1847" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51531,7 +51531,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1854" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51557,7 +51557,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51583,7 +51583,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1856" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51635,7 +51635,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1858" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51661,7 +51661,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1859" t="s">
-        <v>693</v>
+        <v>642</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51687,7 +51687,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1860" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51739,7 +51739,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51843,7 +51843,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1866" t="s">
-        <v>693</v>
+        <v>642</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51869,7 +51869,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1867" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -51999,7 +51999,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1872" t="s">
-        <v>693</v>
+        <v>642</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52129,7 +52129,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1877" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52181,7 +52181,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1879" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52207,7 +52207,7 @@
         <v>4</v>
       </c>
       <c r="G1880" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52233,7 +52233,7 @@
         <v>4</v>
       </c>
       <c r="G1881" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52259,7 +52259,7 @@
         <v>4</v>
       </c>
       <c r="G1882" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52285,7 +52285,7 @@
         <v>4</v>
       </c>
       <c r="G1883" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52311,7 +52311,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52337,7 +52337,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1885" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52363,7 +52363,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1886" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52389,7 +52389,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52415,7 +52415,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1888" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52441,7 +52441,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1889" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52467,7 +52467,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52493,7 +52493,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1891" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52519,7 +52519,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1892" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52545,7 +52545,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1893" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52571,7 +52571,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1894" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52597,7 +52597,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52623,7 +52623,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1896" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52649,7 +52649,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1897" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52675,7 +52675,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1898" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52701,7 +52701,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1899" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52727,7 +52727,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1900" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52753,7 +52753,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52779,7 +52779,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52805,7 +52805,7 @@
         <v>4</v>
       </c>
       <c r="G1903" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52831,7 +52831,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1904" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52857,7 +52857,7 @@
         <v>4</v>
       </c>
       <c r="G1905" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52883,7 +52883,7 @@
         <v>4</v>
       </c>
       <c r="G1906" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52909,7 +52909,7 @@
         <v>4</v>
       </c>
       <c r="G1907" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52935,7 +52935,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1908" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52961,7 +52961,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1909" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53013,7 +53013,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1911" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53481,7 +53481,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1929" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53585,7 +53585,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1933" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53689,7 +53689,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53715,7 +53715,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1938" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53741,7 +53741,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53767,7 +53767,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1940" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53793,7 +53793,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1941" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53819,7 +53819,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1942" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53871,7 +53871,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1944" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53949,7 +53949,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1947" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53975,7 +53975,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1948" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54001,7 +54001,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1949" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54027,7 +54027,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1950" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54053,7 +54053,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54079,7 +54079,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1952" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54105,7 +54105,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1953" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54131,7 +54131,7 @@
         <v>4</v>
       </c>
       <c r="G1954" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54157,7 +54157,7 @@
         <v>4</v>
       </c>
       <c r="G1955" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54183,7 +54183,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54209,7 +54209,7 @@
         <v>4</v>
       </c>
       <c r="G1957" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54235,7 +54235,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1958" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54859,7 +54859,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1982" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54963,7 +54963,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1986" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55145,7 +55145,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55171,7 +55171,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55249,7 +55249,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1997" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55327,7 +55327,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2000" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55353,7 +55353,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55379,7 +55379,7 @@
         <v>4</v>
       </c>
       <c r="G2002" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55405,7 +55405,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2003" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55457,7 +55457,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2005" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55483,7 +55483,7 @@
         <v>4</v>
       </c>
       <c r="G2006" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55509,7 +55509,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2007" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55535,7 +55535,7 @@
         <v>4</v>
       </c>
       <c r="G2008" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55561,7 +55561,7 @@
         <v>4</v>
       </c>
       <c r="G2009" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55639,7 +55639,7 @@
         <v>4</v>
       </c>
       <c r="G2012" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55665,7 +55665,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2013" t="s">
-        <v>754</v>
+        <v>770</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55691,7 +55691,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2014" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55717,7 +55717,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55743,7 +55743,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55769,7 +55769,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55795,7 +55795,7 @@
         <v>4</v>
       </c>
       <c r="G2018" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55821,7 +55821,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2019" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55847,7 +55847,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2020" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55873,7 +55873,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2021" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55899,7 +55899,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2022" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55925,7 +55925,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2023" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55977,7 +55977,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56003,7 +56003,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56029,7 +56029,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56081,7 +56081,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2029" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56107,7 +56107,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2030" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56133,7 +56133,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2031" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56185,7 +56185,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2033" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56471,7 +56471,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2044" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57121,7 +57121,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2069" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57199,7 +57199,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2072" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57225,7 +57225,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2073" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57303,7 +57303,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2076" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57329,7 +57329,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2077" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -68751,7 +68751,7 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6911226852</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
         <v>37928</v>
@@ -68772,6 +68772,32 @@
         <v>994</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.691099537</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>19294</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>8.80000019073486</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>8.92000007629395</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>988</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -44,67 +44,67 @@
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400782585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71406733989716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6616724729538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67215144634247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64969646930695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57334935665131</t>
+    <t xml:space="preserve">1.74400746822357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71406781673431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67215132713318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64969670772552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921749591827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5733494758606</t>
   </si>
   <si>
     <t xml:space="preserve">1.49625372886658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48053526878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48203229904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637382984161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460713863373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42215216159821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990673542023</t>
+    <t xml:space="preserve">1.48053538799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48203241825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460725784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4221522808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990661621094</t>
   </si>
   <si>
     <t xml:space="preserve">1.4146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41915810108185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40718221664429</t>
+    <t xml:space="preserve">1.41915822029114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.407182097435</t>
   </si>
   <si>
     <t xml:space="preserve">1.3824816942215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38472723960876</t>
+    <t xml:space="preserve">1.38472700119019</t>
   </si>
   <si>
     <t xml:space="preserve">1.3982001543045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35703253746033</t>
+    <t xml:space="preserve">1.35703265666962</t>
   </si>
   <si>
     <t xml:space="preserve">1.33607447147369</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">1.34730207920074</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3428111076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38397860527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478699207306</t>
+    <t xml:space="preserve">1.34281098842621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3839784860611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478687286377</t>
   </si>
   <si>
     <t xml:space="preserve">1.38098466396332</t>
@@ -143,16 +143,16 @@
     <t xml:space="preserve">1.46257126331329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51197242736816</t>
+    <t xml:space="preserve">1.51197218894958</t>
   </si>
   <si>
     <t xml:space="preserve">1.5254453420639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52245140075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54490649700165</t>
+    <t xml:space="preserve">1.52245116233826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54490625858307</t>
   </si>
   <si>
     <t xml:space="preserve">1.54191219806671</t>
@@ -161,160 +161,160 @@
     <t xml:space="preserve">1.5493973493576</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56287050247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60029554367065</t>
+    <t xml:space="preserve">1.56287038326263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60029542446136</t>
   </si>
   <si>
     <t xml:space="preserve">1.60927760601044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63173258304596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63023543357849</t>
+    <t xml:space="preserve">1.63173246383667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424743175507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63023567199707</t>
   </si>
   <si>
     <t xml:space="preserve">1.61676251888275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65418779850006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6437087059021</t>
+    <t xml:space="preserve">1.65418756008148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370882511139</t>
   </si>
   <si>
     <t xml:space="preserve">1.58682239055634</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58831942081451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472652435303</t>
+    <t xml:space="preserve">1.58831930160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472664356232</t>
   </si>
   <si>
     <t xml:space="preserve">1.66017544269562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6691575050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712186813354</t>
+    <t xml:space="preserve">1.66915786266327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712151050568</t>
   </si>
   <si>
     <t xml:space="preserve">1.69161260128021</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69310963153839</t>
+    <t xml:space="preserve">1.69310939311981</t>
   </si>
   <si>
     <t xml:space="preserve">1.72155261039734</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73502588272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658266544342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909775257111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664265632629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68412744998932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66766047477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263065814972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221155643463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64670252799988</t>
+    <t xml:space="preserve">1.73502564430237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358860492706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909751415253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.676642537117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68412756919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66766059398651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263077735901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221167564392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64670240879059</t>
   </si>
   <si>
     <t xml:space="preserve">1.67514550685883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69964492321014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68433284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6919891834259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72108197212219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70576965808868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69505131244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495711803436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72261297702789</t>
+    <t xml:space="preserve">1.69964504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68433272838593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69198906421661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72108173370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70576989650726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69505143165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72261309623718</t>
   </si>
   <si>
     <t xml:space="preserve">1.65370869636536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67208325862885</t>
+    <t xml:space="preserve">1.67208313941956</t>
   </si>
   <si>
     <t xml:space="preserve">1.66902077198029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65217757225037</t>
+    <t xml:space="preserve">1.65217733383179</t>
   </si>
   <si>
     <t xml:space="preserve">1.606241106987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56183576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55417966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202427387238</t>
+    <t xml:space="preserve">1.56183588504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417990684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202451229095</t>
   </si>
   <si>
     <t xml:space="preserve">1.53121161460876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59092903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52891480922699</t>
+    <t xml:space="preserve">1.59092891216278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52891492843628</t>
   </si>
   <si>
     <t xml:space="preserve">1.55111742019653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53886771202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49293148517609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4760879278183</t>
+    <t xml:space="preserve">1.53886783123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4929313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608804702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.52278983592987</t>
@@ -323,40 +323,40 @@
     <t xml:space="preserve">1.46996319293976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589953899384</t>
+    <t xml:space="preserve">1.47761905193329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589965820312</t>
   </si>
   <si>
     <t xml:space="preserve">1.50058746337891</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6077721118927</t>
+    <t xml:space="preserve">1.60777223110199</t>
   </si>
   <si>
     <t xml:space="preserve">1.59705376625061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56949198246002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308442592621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66748940944672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136479377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67667663097382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61542844772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714796066284</t>
+    <t xml:space="preserve">1.56949174404144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308418750763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66748952865601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136467456818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67667675018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61542820930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714784145355</t>
   </si>
   <si>
     <t xml:space="preserve">1.58480417728424</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">1.63839662075043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63380289077759</t>
+    <t xml:space="preserve">1.63380300998688</t>
   </si>
   <si>
     <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54652392864227</t>
+    <t xml:space="preserve">1.54652369022369</t>
   </si>
   <si>
     <t xml:space="preserve">1.56796073913574</t>
@@ -380,19 +380,19 @@
     <t xml:space="preserve">1.54499244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355563640594</t>
+    <t xml:space="preserve">1.52355539798737</t>
   </si>
   <si>
     <t xml:space="preserve">1.54193007946014</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58174169063568</t>
+    <t xml:space="preserve">1.58174180984497</t>
   </si>
   <si>
     <t xml:space="preserve">1.55877351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58021056652069</t>
+    <t xml:space="preserve">1.58021032810211</t>
   </si>
   <si>
     <t xml:space="preserve">1.55264866352081</t>
@@ -401,22 +401,22 @@
     <t xml:space="preserve">1.53044593334198</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5197274684906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50594651699066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671219825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427398204803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56642937660217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57408559322357</t>
+    <t xml:space="preserve">1.51972758769989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50594675540924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671231746674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427422046661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56642961502075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57408571243286</t>
   </si>
   <si>
     <t xml:space="preserve">1.58327293395996</t>
@@ -425,13 +425,13 @@
     <t xml:space="preserve">1.59246015548706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50211870670319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47532248497009</t>
+    <t xml:space="preserve">1.50211882591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824344158173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4753223657608</t>
   </si>
   <si>
     <t xml:space="preserve">1.49675929546356</t>
@@ -440,16 +440,16 @@
     <t xml:space="preserve">1.50747787952423</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52968037128448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60011613368988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58786654472351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489837169647</t>
+    <t xml:space="preserve">1.52968049049377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60011601448059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58786642551422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489825248718</t>
   </si>
   <si>
     <t xml:space="preserve">1.56336712837219</t>
@@ -458,31 +458,31 @@
     <t xml:space="preserve">1.57255434989929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59858512878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59399139881134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60470998287201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64758360385895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64605259895325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68280172348022</t>
+    <t xml:space="preserve">1.5985848903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59399127960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60470974445343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64758372306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64605271816254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68280160427094</t>
   </si>
   <si>
     <t xml:space="preserve">1.63074052333832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686537742615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452147483826</t>
+    <t xml:space="preserve">1.63686513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452135562897</t>
   </si>
   <si>
     <t xml:space="preserve">1.63227164745331</t>
@@ -491,76 +491,76 @@
     <t xml:space="preserve">1.66289579868317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66595840454102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026919364929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558126926422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730090141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423853397369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73792541027069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75936233997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089334487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78386163711548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76854932308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323700904846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486256599426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639380931854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7915176153183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223619937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061100006104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754851341248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682957172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8252044916153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448590755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889101028442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8772656917572</t>
+    <t xml:space="preserve">1.66595852375031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333144187927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026907444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558138847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017476081848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730113983154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423865318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73792505264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75936257839203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089346408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78386151790619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76854944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323736667633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486280441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639392852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79151749610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223631858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061076164246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81754815578461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682981014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520437240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448602676392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889053344727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87726545333862</t>
   </si>
   <si>
     <t xml:space="preserve">1.85429728031158</t>
@@ -569,73 +569,73 @@
     <t xml:space="preserve">1.85582852363586</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85123515129089</t>
+    <t xml:space="preserve">1.85123479366302</t>
   </si>
   <si>
     <t xml:space="preserve">1.86654710769653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84970343112946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348450183868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276639461517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8451099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367289066315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051632881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817242622375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807835102081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923269748688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788972377777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92167043685913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9293270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9247328042984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607553958893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904407024384</t>
+    <t xml:space="preserve">1.84970355033875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348462104797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8527660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745408058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84510982036591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367300987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051668643951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817266464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8680784702301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94923257827759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788996219635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92167067527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932677268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473304271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607565879822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904418945312</t>
   </si>
   <si>
     <t xml:space="preserve">1.99823093414307</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00895023345947</t>
+    <t xml:space="preserve">2.00894975662231</t>
   </si>
   <si>
     <t xml:space="preserve">2.00741839408875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01201224327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99057507514954</t>
+    <t xml:space="preserve">2.01201176643372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99057519435883</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
@@ -644,34 +644,34 @@
     <t xml:space="preserve">2.00588726997375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09207773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051084518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401677131653</t>
+    <t xml:space="preserve">2.09207797050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051060676575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401700973511</t>
   </si>
   <si>
     <t xml:space="preserve">2.08424258232117</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11558389663696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17043256759644</t>
+    <t xml:space="preserve">2.11558437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17043280601501</t>
   </si>
   <si>
     <t xml:space="preserve">2.14692616462708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15006041526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655377388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259694099426</t>
+    <t xml:space="preserve">2.15006017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655401229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259717941284</t>
   </si>
   <si>
     <t xml:space="preserve">2.15162777900696</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">2.13909077644348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16103005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04663157463074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05290031433105</t>
+    <t xml:space="preserve">2.16102981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04663181304932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290007591248</t>
   </si>
   <si>
     <t xml:space="preserve">2.03722929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04819893836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0450644493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06543684005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073594093323</t>
+    <t xml:space="preserve">2.04819917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04506492614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06543707847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073570251465</t>
   </si>
   <si>
     <t xml:space="preserve">2.10774898529053</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">2.12341976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13125514984131</t>
+    <t xml:space="preserve">2.13125538825989</t>
   </si>
   <si>
     <t xml:space="preserve">2.18296933174133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1939389705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647597312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20334196090698</t>
+    <t xml:space="preserve">2.19393944740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2033417224884</t>
   </si>
   <si>
     <t xml:space="preserve">2.19237208366394</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">2.20804309844971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16416454315186</t>
+    <t xml:space="preserve">2.16416430473328</t>
   </si>
   <si>
     <t xml:space="preserve">2.15946292877197</t>
@@ -746,37 +746,37 @@
     <t xml:space="preserve">2.09677910804749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06386995315552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0262598991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827721595764</t>
+    <t xml:space="preserve">2.06386971473694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02625966072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827709674835</t>
   </si>
   <si>
     <t xml:space="preserve">1.99805152416229</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07640671730042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05446720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10461449623108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566241264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954072952271</t>
+    <t xml:space="preserve">2.07640695571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05446743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10461497306824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700396537781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566217422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954096794128</t>
   </si>
   <si>
     <t xml:space="preserve">2.06857132911682</t>
@@ -785,46 +785,46 @@
     <t xml:space="preserve">2.07797384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2409520149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371435165405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117758750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23311638832092</t>
+    <t xml:space="preserve">2.24095225334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371411323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211177110672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2331166267395</t>
   </si>
   <si>
     <t xml:space="preserve">2.23781800270081</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31930708885193</t>
+    <t xml:space="preserve">2.31930732727051</t>
   </si>
   <si>
     <t xml:space="preserve">2.31460571289062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32714295387268</t>
+    <t xml:space="preserve">2.3271427154541</t>
   </si>
   <si>
     <t xml:space="preserve">2.32557559013367</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38982677459717</t>
+    <t xml:space="preserve">2.38982653617859</t>
   </si>
   <si>
     <t xml:space="preserve">2.3866925239563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4446747303009</t>
+    <t xml:space="preserve">2.44467496871948</t>
   </si>
   <si>
     <t xml:space="preserve">2.47601723670959</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48541975021362</t>
+    <t xml:space="preserve">2.48541951179504</t>
   </si>
   <si>
     <t xml:space="preserve">2.49012112617493</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">2.5214626789093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50735926628113</t>
+    <t xml:space="preserve">2.50735878944397</t>
   </si>
   <si>
     <t xml:space="preserve">2.53870105743408</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">2.49168825149536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952363967896</t>
+    <t xml:space="preserve">2.50422501564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952340126038</t>
   </si>
   <si>
     <t xml:space="preserve">2.52303028106689</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">2.53243279457092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51206016540527</t>
+    <t xml:space="preserve">2.51206064224243</t>
   </si>
   <si>
     <t xml:space="preserve">2.50892615318298</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">2.49795651435852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49638915061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616405487061</t>
+    <t xml:space="preserve">2.49638938903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616429328918</t>
   </si>
   <si>
     <t xml:space="preserve">2.54653668403625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5512375831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53713393211365</t>
+    <t xml:space="preserve">2.55123805999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53713417053223</t>
   </si>
   <si>
     <t xml:space="preserve">2.55437207221985</t>
@@ -890,28 +890,28 @@
     <t xml:space="preserve">2.60608649253845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70794749259949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108222007751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205185890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541120529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70324683189392</t>
+    <t xml:space="preserve">2.70794796943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541096687317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70324659347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.67347145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66406917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705589294434</t>
+    <t xml:space="preserve">2.66406893730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705613136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.59981799125671</t>
@@ -920,46 +920,46 @@
     <t xml:space="preserve">2.5872814655304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59825110435486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58571410179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57004308700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56220746040344</t>
+    <t xml:space="preserve">2.59825086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5857138633728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57004284858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56220722198486</t>
   </si>
   <si>
     <t xml:space="preserve">2.54183530807495</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51989603042603</t>
+    <t xml:space="preserve">2.5198962688446</t>
   </si>
   <si>
     <t xml:space="preserve">2.52929854393005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52459740638733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034622192383</t>
+    <t xml:space="preserve">2.52459716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034598350525</t>
   </si>
   <si>
     <t xml:space="preserve">2.47131586074829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4337055683136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39609479904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087445259094</t>
+    <t xml:space="preserve">2.48228526115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43370532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39609503746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087421417236</t>
   </si>
   <si>
     <t xml:space="preserve">2.30206918716431</t>
@@ -971,7 +971,7 @@
     <t xml:space="preserve">2.27699542045593</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28796529769897</t>
+    <t xml:space="preserve">2.2879650592804</t>
   </si>
   <si>
     <t xml:space="preserve">2.34908175468445</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">2.36475300788879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35064911842346</t>
+    <t xml:space="preserve">2.35064888000488</t>
   </si>
   <si>
     <t xml:space="preserve">2.35848450660706</t>
@@ -989,25 +989,25 @@
     <t xml:space="preserve">2.41333293914795</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43683958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62489175796509</t>
+    <t xml:space="preserve">2.43683934211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62489104270935</t>
   </si>
   <si>
     <t xml:space="preserve">2.6327269077301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46818161010742</t>
+    <t xml:space="preserve">2.468181848526</t>
   </si>
   <si>
     <t xml:space="preserve">2.36632013320923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.381991147995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766192436218</t>
+    <t xml:space="preserve">2.38199090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766216278076</t>
   </si>
   <si>
     <t xml:space="preserve">2.45251059532166</t>
@@ -1016,22 +1016,22 @@
     <t xml:space="preserve">2.40549755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42116856575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900395393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363631248474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25662302970886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27229452133179</t>
+    <t xml:space="preserve">2.42116832733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878740310669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363607406616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25662326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27229428291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.2801296710968</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">2.26445865631104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22528123855591</t>
+    <t xml:space="preserve">2.22528100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558413505554</t>
@@ -1049,106 +1049,106 @@
     <t xml:space="preserve">2.1235978603363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09955716133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08352971076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09154319763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01942157745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750273704529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18770670890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29188275337219</t>
+    <t xml:space="preserve">2.09955668449402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08352994918823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09154343605042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01942133903503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339436531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750249862671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1877064704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29188299179077</t>
   </si>
   <si>
     <t xml:space="preserve">2.13962507247925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1636655330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14763879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20373368263245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13161134719849</t>
+    <t xml:space="preserve">2.16366600990295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14763832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20373344421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13161158561707</t>
   </si>
   <si>
     <t xml:space="preserve">2.17167925834656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19572019577026</t>
+    <t xml:space="preserve">2.19571971893311</t>
   </si>
   <si>
     <t xml:space="preserve">2.17969274520874</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10757088661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05948901176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07551598548889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0354483127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05147552490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27585577964783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784181594849</t>
+    <t xml:space="preserve">2.10757064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05948925018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07551646232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03544855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05147576332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27585554122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784229278564</t>
   </si>
   <si>
     <t xml:space="preserve">2.21976065635681</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21174693107605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24380159378052</t>
+    <t xml:space="preserve">2.21174716949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2438018321991</t>
   </si>
   <si>
     <t xml:space="preserve">2.23578786849976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22777438163757</t>
+    <t xml:space="preserve">2.22777414321899</t>
   </si>
   <si>
     <t xml:space="preserve">2.15565228462219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30790996551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02743458747864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04346203804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9953807592392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524493694305</t>
+    <t xml:space="preserve">2.30791020393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0274350643158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.043461561203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99538052082062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524469852448</t>
   </si>
   <si>
     <t xml:space="preserve">1.92325854301453</t>
@@ -1160,103 +1160,103 @@
     <t xml:space="preserve">1.97133994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98736691474915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140761375427</t>
+    <t xml:space="preserve">1.98736679553986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140785217285</t>
   </si>
   <si>
     <t xml:space="preserve">1.81106841564178</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81908202171326</t>
+    <t xml:space="preserve">1.81908190250397</t>
   </si>
   <si>
     <t xml:space="preserve">1.84312260150909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79504120349884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901411056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709538936615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100074291229</t>
+    <t xml:space="preserve">1.79504132270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77901422977448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709527015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77100050449371</t>
   </si>
   <si>
     <t xml:space="preserve">1.73093259334564</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69887828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71490550041199</t>
+    <t xml:space="preserve">1.69887804985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7149053812027</t>
   </si>
   <si>
     <t xml:space="preserve">1.74695980548859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72291898727417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7389463186264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298689842224</t>
+    <t xml:space="preserve">1.72291910648346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73894619941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298666000366</t>
   </si>
   <si>
     <t xml:space="preserve">1.75497317314148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80305457115173</t>
+    <t xml:space="preserve">1.80305469036102</t>
   </si>
   <si>
     <t xml:space="preserve">1.85914957523346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86716341972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510887622833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8751767873764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723121166229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935330867767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928563594818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082943916321</t>
+    <t xml:space="preserve">1.86716318130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8351092338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517690658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935318946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9392853975296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082967758179</t>
   </si>
   <si>
     <t xml:space="preserve">2.01258134841919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9878363609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99608469009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96309149265289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9383465051651</t>
+    <t xml:space="preserve">1.98783612251282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99608480930328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96309173107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93834662437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.97958815097809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03732633590698</t>
+    <t xml:space="preserve">2.03732585906982</t>
   </si>
   <si>
     <t xml:space="preserve">2.06207084655762</t>
@@ -1265,19 +1265,19 @@
     <t xml:space="preserve">2.0538227558136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09506416320801</t>
+    <t xml:space="preserve">2.09506392478943</t>
   </si>
   <si>
     <t xml:space="preserve">2.16929864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16105008125305</t>
+    <t xml:space="preserve">2.16104984283447</t>
   </si>
   <si>
     <t xml:space="preserve">2.11156058311462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10331249237061</t>
+    <t xml:space="preserve">2.10331201553345</t>
   </si>
   <si>
     <t xml:space="preserve">2.12805700302124</t>
@@ -1286,55 +1286,55 @@
     <t xml:space="preserve">2.13630557060242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11980867385864</t>
+    <t xml:space="preserve">2.11980891227722</t>
   </si>
   <si>
     <t xml:space="preserve">2.14455342292786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07856750488281</t>
+    <t xml:space="preserve">2.07856726646423</t>
   </si>
   <si>
     <t xml:space="preserve">2.22703671455383</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21878838539124</t>
+    <t xml:space="preserve">2.21878814697266</t>
   </si>
   <si>
     <t xml:space="preserve">2.25178146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24353313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21054029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26002979278564</t>
+    <t xml:space="preserve">2.24353337287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21053981781006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26002955436707</t>
   </si>
   <si>
     <t xml:space="preserve">2.26827812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33426380157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30951929092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30127096176147</t>
+    <t xml:space="preserve">2.33426427841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30951952934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30127120018005</t>
   </si>
   <si>
     <t xml:space="preserve">2.31776762008667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38375425338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37550568580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601571083069</t>
+    <t xml:space="preserve">2.38375401496887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37550592422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601594924927</t>
   </si>
   <si>
     <t xml:space="preserve">2.27652621269226</t>
@@ -1343,34 +1343,34 @@
     <t xml:space="preserve">2.28477454185486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29302310943604</t>
+    <t xml:space="preserve">2.29302287101746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23528480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200258255005</t>
+    <t xml:space="preserve">2.39200234413147</t>
   </si>
   <si>
     <t xml:space="preserve">2.44974040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43324375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849876403809</t>
+    <t xml:space="preserve">2.41674709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4332435131073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849900245667</t>
   </si>
   <si>
     <t xml:space="preserve">2.42499566078186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798850059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49922966957092</t>
+    <t xml:space="preserve">2.45798873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4992299079895</t>
   </si>
   <si>
     <t xml:space="preserve">2.47448515892029</t>
@@ -1382,10 +1382,10 @@
     <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871964454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4909815788269</t>
+    <t xml:space="preserve">2.54871940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49098181724548</t>
   </si>
   <si>
     <t xml:space="preserve">2.5074782371521</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35076093673706</t>
+    <t xml:space="preserve">2.3507604598999</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025067329407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19404363632202</t>
+    <t xml:space="preserve">2.19404339790344</t>
   </si>
   <si>
     <t xml:space="preserve">2.185795545578</t>
@@ -1409,115 +1409,115 @@
     <t xml:space="preserve">2.04557418823242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87236046791077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060867786407</t>
+    <t xml:space="preserve">1.87236022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060855865479</t>
   </si>
   <si>
     <t xml:space="preserve">1.68264973163605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69089818000793</t>
+    <t xml:space="preserve">1.69089806079865</t>
   </si>
   <si>
     <t xml:space="preserve">1.56717395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71564280986786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64553272724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64140856266022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62491190433502</t>
+    <t xml:space="preserve">1.71564304828644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64553260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64140832424164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62491178512573</t>
   </si>
   <si>
     <t xml:space="preserve">1.77338111400604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78162944316864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74863612651825</t>
+    <t xml:space="preserve">1.78162932395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74863588809967</t>
   </si>
   <si>
     <t xml:space="preserve">1.80637407302856</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86411213874817</t>
+    <t xml:space="preserve">1.86411201953888</t>
   </si>
   <si>
     <t xml:space="preserve">2.00433325767517</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81462240219116</t>
+    <t xml:space="preserve">1.81462216377258</t>
   </si>
   <si>
     <t xml:space="preserve">1.79812586307526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287096977234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84761559963226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111906051636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78987777233124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885676860809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9136016368866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710521697998</t>
+    <t xml:space="preserve">1.82287073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84761548042297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111917972565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78987753391266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885700702667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710533618927</t>
   </si>
   <si>
     <t xml:space="preserve">1.90535342693329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548431634903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907800674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08681559562683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17754721641541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07031917572021</t>
+    <t xml:space="preserve">1.95484352111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907776832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08681583404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17754697799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07031941413879</t>
   </si>
   <si>
     <t xml:space="preserve">2.07786917686462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06938791275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03546380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9845769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609603404999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065248012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99305784702301</t>
+    <t xml:space="preserve">2.06938815116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03546357154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98457670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065271854401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9930579662323</t>
   </si>
   <si>
     <t xml:space="preserve">2.06090712547302</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">2.05242586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04394459724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01002025604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00153923034668</t>
+    <t xml:space="preserve">2.04394435882568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01002049446106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0015389919281</t>
   </si>
   <si>
     <t xml:space="preserve">1.89976596832275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88280379772186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128482341766</t>
+    <t xml:space="preserve">1.88280403614044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128506183624</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850152015686</t>
@@ -1556,40 +1556,40 @@
     <t xml:space="preserve">2.08635020256042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875556945801</t>
+    <t xml:space="preserve">2.12875580787659</t>
   </si>
   <si>
     <t xml:space="preserve">2.12027454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16267991065979</t>
+    <t xml:space="preserve">2.16267967224121</t>
   </si>
   <si>
     <t xml:space="preserve">2.20508527755737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23052906990051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30685877799988</t>
+    <t xml:space="preserve">2.23052883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30685901641846</t>
   </si>
   <si>
     <t xml:space="preserve">2.33230209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34926390647888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35774540901184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42559385299683</t>
+    <t xml:space="preserve">2.34926414489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35774517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42559409141541</t>
   </si>
   <si>
     <t xml:space="preserve">2.44255638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47648048400879</t>
+    <t xml:space="preserve">2.47648072242737</t>
   </si>
   <si>
     <t xml:space="preserve">2.46799969673157</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">2.43407511711121</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41711282730103</t>
+    <t xml:space="preserve">2.41711258888245</t>
   </si>
   <si>
     <t xml:space="preserve">2.51888632774353</t>
@@ -1616,10 +1616,10 @@
     <t xml:space="preserve">2.56977272033691</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54432964324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57825398445129</t>
+    <t xml:space="preserve">2.54432940483093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57825374603271</t>
   </si>
   <si>
     <t xml:space="preserve">2.56129169464111</t>
@@ -1628,10 +1628,10 @@
     <t xml:space="preserve">2.55281043052673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53584861755371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52736711502075</t>
+    <t xml:space="preserve">2.53584837913513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52736735343933</t>
   </si>
   <si>
     <t xml:space="preserve">2.64610242843628</t>
@@ -1643,16 +1643,16 @@
     <t xml:space="preserve">2.66306471824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547008514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69698905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6291401386261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.713951587677</t>
+    <t xml:space="preserve">2.7054705619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69698929786682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62914037704468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71395134925842</t>
   </si>
   <si>
     <t xml:space="preserve">2.7309136390686</t>
@@ -1661,22 +1661,22 @@
     <t xml:space="preserve">2.77331900596619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180003166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84116792678833</t>
+    <t xml:space="preserve">2.78179979324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84116768836975</t>
   </si>
   <si>
     <t xml:space="preserve">2.86661148071289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88357329368591</t>
+    <t xml:space="preserve">2.88357353210449</t>
   </si>
   <si>
     <t xml:space="preserve">2.90901660919189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85812973976135</t>
+    <t xml:space="preserve">2.85812997817993</t>
   </si>
   <si>
     <t xml:space="preserve">2.80724358558655</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">2.7393946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74787569046021</t>
+    <t xml:space="preserve">2.74787616729736</t>
   </si>
   <si>
     <t xml:space="preserve">2.79876232147217</t>
@@ -1703,10 +1703,10 @@
     <t xml:space="preserve">2.83268666267395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82420563697815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91749787330627</t>
+    <t xml:space="preserve">2.82420539855957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9174976348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.01078963279724</t>
@@ -1715,34 +1715,34 @@
     <t xml:space="preserve">3.0362331867218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95990324020386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07863879203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08711957931519</t>
+    <t xml:space="preserve">2.95990300178528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07863855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08711981773376</t>
   </si>
   <si>
     <t xml:space="preserve">3.12104415893555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18041157722473</t>
+    <t xml:space="preserve">3.18041181564331</t>
   </si>
   <si>
     <t xml:space="preserve">3.14648723602295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23977947235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22281718254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23129820823669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24826073646545</t>
+    <t xml:space="preserve">3.2397792339325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23129844665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24826049804688</t>
   </si>
   <si>
     <t xml:space="preserve">3.21433615684509</t>
@@ -1751,16 +1751,16 @@
     <t xml:space="preserve">3.28218483924866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40092062950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42636394500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3669958114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31610918045044</t>
+    <t xml:space="preserve">3.40092039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42636346817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36699604988098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31610941886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066634178162</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.27339220046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35112476348877</t>
+    <t xml:space="preserve">3.35112500190735</t>
   </si>
   <si>
     <t xml:space="preserve">3.34248757362366</t>
@@ -1787,37 +1787,37 @@
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430928230286</t>
+    <t xml:space="preserve">3.39430904388428</t>
   </si>
   <si>
     <t xml:space="preserve">3.44613075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45476746559143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4720413684845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54113698005676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60159540176392</t>
+    <t xml:space="preserve">3.45476770401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47204160690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54113674163818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60159516334534</t>
   </si>
   <si>
     <t xml:space="preserve">3.5929582118988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65341687202454</t>
+    <t xml:space="preserve">3.65341663360596</t>
   </si>
   <si>
     <t xml:space="preserve">3.61023187637329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71387505531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069053649902</t>
+    <t xml:space="preserve">3.71387553215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6706907749176</t>
   </si>
   <si>
     <t xml:space="preserve">3.7829704284668</t>
@@ -1835,10 +1835,10 @@
     <t xml:space="preserve">3.64477968215942</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73978567123413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75705981254578</t>
+    <t xml:space="preserve">3.73978590965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75705933570862</t>
   </si>
   <si>
     <t xml:space="preserve">3.55841040611267</t>
@@ -1853,28 +1853,28 @@
     <t xml:space="preserve">3.58432149887085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70523810386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5238630771637</t>
+    <t xml:space="preserve">3.705237865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52386283874512</t>
   </si>
   <si>
     <t xml:space="preserve">3.5497739315033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48931550979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41158318519592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51522636413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68796420097351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7484233379364</t>
+    <t xml:space="preserve">3.48931503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41158294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51522612571716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74842286109924</t>
   </si>
   <si>
     <t xml:space="preserve">3.66205334663391</t>
@@ -1889,16 +1889,16 @@
     <t xml:space="preserve">3.82615518569946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86070275306702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91252493858337</t>
+    <t xml:space="preserve">3.8607029914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91252446174622</t>
   </si>
   <si>
     <t xml:space="preserve">3.99889373779297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95570874214172</t>
+    <t xml:space="preserve">3.9557089805603</t>
   </si>
   <si>
     <t xml:space="preserve">3.99025630950928</t>
@@ -1910,25 +1910,25 @@
     <t xml:space="preserve">3.77433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76569676399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92979860305786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661336898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90388751029968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8779764175415</t>
+    <t xml:space="preserve">3.76569700241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92979788780212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661360740662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9038872718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87797617912292</t>
   </si>
   <si>
     <t xml:space="preserve">3.81751847267151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434569358826</t>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.89525032043457</t>
@@ -1943,19 +1943,19 @@
     <t xml:space="preserve">3.49795246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885661125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021989822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2820291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25611853599548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29066586494446</t>
+    <t xml:space="preserve">3.42885708808899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42022013664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28202939033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2561182975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29066610336304</t>
   </si>
   <si>
     <t xml:space="preserve">3.24748134613037</t>
@@ -1970,19 +1970,19 @@
     <t xml:space="preserve">3.33385062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43749403953552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37703514099121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40294599533081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3597617149353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21293377876282</t>
+    <t xml:space="preserve">3.43749356269836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37703561782837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40294623374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35976147651672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2129340171814</t>
   </si>
   <si>
     <t xml:space="preserve">3.23020768165588</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">3.14383840560913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97973704338074</t>
+    <t xml:space="preserve">2.97973728179932</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610608100891</t>
@@ -2009,13 +2009,13 @@
     <t xml:space="preserve">3.53250002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56704759597778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46340489387512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38567233085632</t>
+    <t xml:space="preserve">3.5670473575592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46340441703796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38567209243774</t>
   </si>
   <si>
     <t xml:space="preserve">3.54223012924194</t>
@@ -2024,46 +2024,46 @@
     <t xml:space="preserve">3.57765245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56879711151123</t>
+    <t xml:space="preserve">3.56879687309265</t>
   </si>
   <si>
     <t xml:space="preserve">3.5245189666748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6130747795105</t>
+    <t xml:space="preserve">3.61307454109192</t>
   </si>
   <si>
     <t xml:space="preserve">3.58650803565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.294273853302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31198501586914</t>
+    <t xml:space="preserve">3.29427409172058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31198525428772</t>
   </si>
   <si>
     <t xml:space="preserve">3.35626292228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33855199813843</t>
+    <t xml:space="preserve">3.33855175971985</t>
   </si>
   <si>
     <t xml:space="preserve">3.34740734100342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26770734786987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30312967300415</t>
+    <t xml:space="preserve">3.26770710945129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30312943458557</t>
   </si>
   <si>
     <t xml:space="preserve">3.2322850227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27656269073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3296959400177</t>
+    <t xml:space="preserve">3.27656292915344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32969617843628</t>
   </si>
   <si>
     <t xml:space="preserve">3.32084059715271</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">3.55108571052551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40939617156982</t>
+    <t xml:space="preserve">3.4093964099884</t>
   </si>
   <si>
     <t xml:space="preserve">3.48909664154053</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">3.46252989768982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36511826515198</t>
+    <t xml:space="preserve">3.36511850357056</t>
   </si>
   <si>
     <t xml:space="preserve">3.41825175285339</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">3.3828296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44481873512268</t>
+    <t xml:space="preserve">3.44481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">3.45367431640625</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">3.11716246604919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09059572219849</t>
+    <t xml:space="preserve">3.09059548377991</t>
   </si>
   <si>
     <t xml:space="preserve">2.88691759109497</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">2.74522829055786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65667247772217</t>
+    <t xml:space="preserve">2.65667271614075</t>
   </si>
   <si>
     <t xml:space="preserve">2.56811690330505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78950619697571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75408363342285</t>
+    <t xml:space="preserve">2.78950643539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75408387184143</t>
   </si>
   <si>
     <t xml:space="preserve">2.72751688957214</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">2.6832389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82492852210999</t>
+    <t xml:space="preserve">2.82492828369141</t>
   </si>
   <si>
     <t xml:space="preserve">2.80721735954285</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">2.79836177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83378410339355</t>
+    <t xml:space="preserve">2.83378434181213</t>
   </si>
   <si>
     <t xml:space="preserve">2.97547316551208</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.99318432807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06402897834778</t>
+    <t xml:space="preserve">3.06402921676636</t>
   </si>
   <si>
     <t xml:space="preserve">3.07288455963135</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">3.01975131034851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09945106506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03746247291565</t>
+    <t xml:space="preserve">3.09945130348206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03746223449707</t>
   </si>
   <si>
     <t xml:space="preserve">2.94005084037781</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">2.90462851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00204014778137</t>
+    <t xml:space="preserve">3.00203990936279</t>
   </si>
   <si>
     <t xml:space="preserve">2.93119549751282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78065061569214</t>
+    <t xml:space="preserve">2.78065037727356</t>
   </si>
   <si>
     <t xml:space="preserve">2.70980596542358</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">2.77179503440857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81607294082642</t>
+    <t xml:space="preserve">2.81607270240784</t>
   </si>
   <si>
     <t xml:space="preserve">2.8780620098114</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">3.16144037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37397408485413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40054059028625</t>
+    <t xml:space="preserve">3.37397384643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40054082870483</t>
   </si>
   <si>
     <t xml:space="preserve">3.47138524055481</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">3.50680780410767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60421919822693</t>
+    <t xml:space="preserve">3.60421895980835</t>
   </si>
   <si>
     <t xml:space="preserve">3.63078570365906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62193036079407</t>
+    <t xml:space="preserve">3.62193059921265</t>
   </si>
   <si>
     <t xml:space="preserve">3.63964152336121</t>
@@ -68835,7 +68835,7 @@
     </row>
     <row r="2520">
       <c r="A2520" s="1" t="n">
-        <v>45987.6912731481</v>
+        <v>45987.3333333333</v>
       </c>
       <c r="B2520" t="n">
         <v>33395</v>
@@ -68856,6 +68856,32 @@
         <v>992</v>
       </c>
       <c r="H2520" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2521">
+      <c r="A2521" s="1" t="n">
+        <v>45988.6910648148</v>
+      </c>
+      <c r="B2521" t="n">
+        <v>188678</v>
+      </c>
+      <c r="C2521" t="n">
+        <v>9.18000030517578</v>
+      </c>
+      <c r="D2521" t="n">
+        <v>8.23999977111816</v>
+      </c>
+      <c r="E2521" t="n">
+        <v>9.14000034332275</v>
+      </c>
+      <c r="F2521" t="n">
+        <v>8.69999980926514</v>
+      </c>
+      <c r="G2521" t="s">
+        <v>981</v>
+      </c>
+      <c r="H2521" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652267456055</t>
+    <t xml:space="preserve">1.73652255535126</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.74400770664215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71406757831573</t>
+    <t xml:space="preserve">1.71406745910645</t>
   </si>
   <si>
     <t xml:space="preserve">1.66167259216309</t>
@@ -56,40 +56,40 @@
     <t xml:space="preserve">1.67215156555176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969670772552</t>
+    <t xml:space="preserve">1.64969646930695</t>
   </si>
   <si>
     <t xml:space="preserve">1.63921761512756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57334959506989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49625360965729</t>
+    <t xml:space="preserve">1.57334935665131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49625384807587</t>
   </si>
   <si>
     <t xml:space="preserve">1.48053538799286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48203217983246</t>
+    <t xml:space="preserve">1.48203229904175</t>
   </si>
   <si>
     <t xml:space="preserve">1.43637382984161</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44460701942444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42215216159821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990637779236</t>
+    <t xml:space="preserve">1.44460737705231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4221522808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990673542023</t>
   </si>
   <si>
     <t xml:space="preserve">1.41466701030731</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41915833950043</t>
+    <t xml:space="preserve">1.41915810108185</t>
   </si>
   <si>
     <t xml:space="preserve">1.407182097435</t>
@@ -98,40 +98,40 @@
     <t xml:space="preserve">1.38248157501221</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38472712039948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39820027351379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35703253746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33607447147369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34730195999146</t>
+    <t xml:space="preserve">1.38472723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.39820039272308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35703265666962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607459068298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34730207920074</t>
   </si>
   <si>
     <t xml:space="preserve">1.3428111076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38397872447968</t>
+    <t xml:space="preserve">1.38397860527039</t>
   </si>
   <si>
     <t xml:space="preserve">1.35478711128235</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38098466396332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36975717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873899936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113422393799</t>
+    <t xml:space="preserve">1.3809849023819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36975705623627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873911857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43113398551941</t>
   </si>
   <si>
     <t xml:space="preserve">1.41017627716064</t>
@@ -146,121 +146,121 @@
     <t xml:space="preserve">1.51197230815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52544546127319</t>
+    <t xml:space="preserve">1.5254453420639</t>
   </si>
   <si>
     <t xml:space="preserve">1.52245128154755</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54490613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191207885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54939723014832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56287038326263</t>
+    <t xml:space="preserve">1.54490637779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191219806671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5493973493576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56287026405334</t>
   </si>
   <si>
     <t xml:space="preserve">1.60029542446136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60927736759186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173258304596</t>
+    <t xml:space="preserve">1.60927772521973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173270225525</t>
   </si>
   <si>
     <t xml:space="preserve">1.62424755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63023519515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676263809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418791770935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6437087059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682250976562</t>
+    <t xml:space="preserve">1.63023555278778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676251888275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418756008148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370858669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682227134705</t>
   </si>
   <si>
     <t xml:space="preserve">1.58831942081451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63472640514374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66017544269562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915762424469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712151050568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69161283969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69310975074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155261039734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502576351166</t>
+    <t xml:space="preserve">1.63472652435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017556190491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691575050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712162971497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6916127204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6931095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155272960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502564430237</t>
   </si>
   <si>
     <t xml:space="preserve">1.70358872413635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70658278465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909775257111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.676642537117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6841276884079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66766035556793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263053894043</t>
+    <t xml:space="preserve">1.70658266544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909763336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67664265632629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68412756919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66766083240509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263041973114</t>
   </si>
   <si>
     <t xml:space="preserve">1.64221167564392</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64670252799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514538764954</t>
+    <t xml:space="preserve">1.64670264720917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514550685883</t>
   </si>
   <si>
     <t xml:space="preserve">1.69964504241943</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6843329668045</t>
+    <t xml:space="preserve">1.68433284759521</t>
   </si>
   <si>
     <t xml:space="preserve">1.69198894500732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7210818529129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70576953887939</t>
+    <t xml:space="preserve">1.72108173370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70577001571655</t>
   </si>
   <si>
     <t xml:space="preserve">1.69505143165588</t>
@@ -275,46 +275,46 @@
     <t xml:space="preserve">1.65370869636536</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67208313941956</t>
+    <t xml:space="preserve">1.67208325862885</t>
   </si>
   <si>
     <t xml:space="preserve">1.66902077198029</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65217745304108</t>
+    <t xml:space="preserve">1.6521772146225</t>
   </si>
   <si>
     <t xml:space="preserve">1.606241106987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5618360042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55417966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121161460876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59092903137207</t>
+    <t xml:space="preserve">1.56183588504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417990684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202451229095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121173381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59092891216278</t>
   </si>
   <si>
     <t xml:space="preserve">1.5289146900177</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55111742019653</t>
+    <t xml:space="preserve">1.55111730098724</t>
   </si>
   <si>
     <t xml:space="preserve">1.53886771202087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49293124675751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47608816623688</t>
+    <t xml:space="preserve">1.4929313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608804702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.52279007434845</t>
@@ -323,79 +323,79 @@
     <t xml:space="preserve">1.46996319293976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589953899384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50058734416962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6077721118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59705376625061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56949186325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308430671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66748917102814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136479377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67667675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6154283285141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714784145355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58480393886566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63839662075043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63380265235901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57561671733856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5465235710144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56796085834503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54499268531799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54193007946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58174180984497</t>
+    <t xml:space="preserve">1.47761929035187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589977741241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5005875825882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60777199268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5970538854599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56949210166931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308418750763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66748976707458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136455535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6766768693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61542820930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714796066284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58480405807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63839650154114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63380300998688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57561683654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54652369022369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56796061992645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5449925661087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355551719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54192996025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174169063568</t>
   </si>
   <si>
     <t xml:space="preserve">1.55877351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58021032810211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55264890193939</t>
+    <t xml:space="preserve">1.5802104473114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55264866352081</t>
   </si>
   <si>
     <t xml:space="preserve">1.53044605255127</t>
@@ -404,40 +404,40 @@
     <t xml:space="preserve">1.51972758769989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50594675540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671243667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427398204803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56642961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57408559322357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58327293395996</t>
+    <t xml:space="preserve">1.50594651699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671231746674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56642949581146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57408547401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58327305316925</t>
   </si>
   <si>
     <t xml:space="preserve">1.59246015548706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50211882591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824344158173</t>
+    <t xml:space="preserve">1.5021185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824368000031</t>
   </si>
   <si>
     <t xml:space="preserve">1.47532248497009</t>
   </si>
   <si>
-    <t xml:space="preserve">1.49675941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50747787952423</t>
+    <t xml:space="preserve">1.49675953388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50747799873352</t>
   </si>
   <si>
     <t xml:space="preserve">1.52968037128448</t>
@@ -449,40 +449,40 @@
     <t xml:space="preserve">1.58786630630493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56489825248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56336724758148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255434989929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59858500957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59399116039276</t>
+    <t xml:space="preserve">1.56489813327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56336712837219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255446910858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5985848903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59399139881134</t>
   </si>
   <si>
     <t xml:space="preserve">1.60470974445343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64758372306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64605247974396</t>
+    <t xml:space="preserve">1.64758360385895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64605271816254</t>
   </si>
   <si>
     <t xml:space="preserve">1.68280172348022</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63074064254761</t>
+    <t xml:space="preserve">1.63074040412903</t>
   </si>
   <si>
     <t xml:space="preserve">1.63686525821686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64452147483826</t>
+    <t xml:space="preserve">1.64452135562897</t>
   </si>
   <si>
     <t xml:space="preserve">1.63227164745331</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">1.66595852375031</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73333156108856</t>
+    <t xml:space="preserve">1.73333144187927</t>
   </si>
   <si>
     <t xml:space="preserve">1.73026931285858</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">1.74558138847351</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75017499923706</t>
+    <t xml:space="preserve">1.75017488002777</t>
   </si>
   <si>
     <t xml:space="preserve">1.70730113983154</t>
@@ -515,76 +515,76 @@
     <t xml:space="preserve">1.73792541027069</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75936233997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089310646057</t>
+    <t xml:space="preserve">1.75936222076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089346408844</t>
   </si>
   <si>
     <t xml:space="preserve">1.78386151790619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76854920387268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323724746704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486256599426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79151773452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223608016968</t>
+    <t xml:space="preserve">1.76854908466339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323736667633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486304283142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639369010925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79151749610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223619937897</t>
   </si>
   <si>
     <t xml:space="preserve">1.82061064243317</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8175482749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682969093323</t>
+    <t xml:space="preserve">1.81754815578461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682981014252</t>
   </si>
   <si>
     <t xml:space="preserve">1.82520425319672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81448590755463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889077186584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87726545333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85429728031158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582840442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85123479366302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86654698848724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84970343112946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348462104797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276651382446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745419979095</t>
+    <t xml:space="preserve">1.81448578834534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889089107513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87726557254791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85429716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582864284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8512350320816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86654734611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84970378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8634842634201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85276639461517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745396137238</t>
   </si>
   <si>
     <t xml:space="preserve">1.84511005878448</t>
@@ -593,67 +593,67 @@
     <t xml:space="preserve">1.82367300987244</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84051644802094</t>
+    <t xml:space="preserve">1.84051668643951</t>
   </si>
   <si>
     <t xml:space="preserve">1.84817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86807835102081</t>
+    <t xml:space="preserve">1.86807799339294</t>
   </si>
   <si>
     <t xml:space="preserve">1.94923257827759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90788972377777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92167031764984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932689189911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607577800751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904371261597</t>
+    <t xml:space="preserve">1.90788984298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.921670794487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932665348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473316192627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9660758972168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904383182526</t>
   </si>
   <si>
     <t xml:space="preserve">1.99823105335236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894975662231</t>
+    <t xml:space="preserve">2.00894999504089</t>
   </si>
   <si>
     <t xml:space="preserve">2.00741839408875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01201248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99057519435883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0028247833252</t>
+    <t xml:space="preserve">2.01201200485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9905754327774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00282454490662</t>
   </si>
   <si>
     <t xml:space="preserve">2.00588726997375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09207773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051084518433</t>
+    <t xml:space="preserve">2.09207797050476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051036834717</t>
   </si>
   <si>
     <t xml:space="preserve">2.11401724815369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08424210548401</t>
+    <t xml:space="preserve">2.08424258232117</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558437347412</t>
@@ -665,37 +665,37 @@
     <t xml:space="preserve">2.14692616462708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15006017684937</t>
+    <t xml:space="preserve">2.15006041526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.12655401229858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16259717941284</t>
+    <t xml:space="preserve">2.16259741783142</t>
   </si>
   <si>
     <t xml:space="preserve">2.15162777900696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13909101486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16103029251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04663228988647</t>
+    <t xml:space="preserve">2.13909077644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16103005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04663181304932</t>
   </si>
   <si>
     <t xml:space="preserve">2.05290007591248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03722929954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04819917678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04506468772888</t>
+    <t xml:space="preserve">2.03722906112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04819893836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04506492614746</t>
   </si>
   <si>
     <t xml:space="preserve">2.06543684005737</t>
@@ -704,34 +704,34 @@
     <t xml:space="preserve">2.06073594093323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10774898529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11715126037598</t>
+    <t xml:space="preserve">2.10774922370911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11715149879456</t>
   </si>
   <si>
     <t xml:space="preserve">2.12342000007629</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13125491142273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296933174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19393944740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647597312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2033417224884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19237232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20804309844971</t>
+    <t xml:space="preserve">2.13125562667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296909332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19393920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647621154785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20334196090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19237184524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20804286003113</t>
   </si>
   <si>
     <t xml:space="preserve">2.16416454315186</t>
@@ -743,61 +743,61 @@
     <t xml:space="preserve">2.13595652580261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09677886962891</t>
+    <t xml:space="preserve">2.09677910804749</t>
   </si>
   <si>
     <t xml:space="preserve">2.06386995315552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02625966072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827745437622</t>
+    <t xml:space="preserve">2.02625942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827733516693</t>
   </si>
   <si>
     <t xml:space="preserve">1.99805176258087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07640671730042</t>
+    <t xml:space="preserve">2.07640695571899</t>
   </si>
   <si>
     <t xml:space="preserve">2.05446743965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10461449623108</t>
+    <t xml:space="preserve">2.10461473464966</t>
   </si>
   <si>
     <t xml:space="preserve">2.06700396537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03566217422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976630210876</t>
+    <t xml:space="preserve">2.03566193580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976558685303</t>
   </si>
   <si>
     <t xml:space="preserve">2.07954120635986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06857109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797384262085</t>
+    <t xml:space="preserve">2.06857132911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797408103943</t>
   </si>
   <si>
     <t xml:space="preserve">2.24095225334167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22371387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117687225342</t>
+    <t xml:space="preserve">2.22371411323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21117734909058</t>
   </si>
   <si>
     <t xml:space="preserve">2.2331166267395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23781800270081</t>
+    <t xml:space="preserve">2.23781776428223</t>
   </si>
   <si>
     <t xml:space="preserve">2.31930732727051</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">2.3146059513092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32714247703552</t>
+    <t xml:space="preserve">2.32714295387268</t>
   </si>
   <si>
     <t xml:space="preserve">2.32557559013367</t>
@@ -821,40 +821,40 @@
     <t xml:space="preserve">2.44467496871948</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47601723670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48541975021362</t>
+    <t xml:space="preserve">2.47601747512817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48541951179504</t>
   </si>
   <si>
     <t xml:space="preserve">2.49012088775635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5214626789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735950469971</t>
+    <t xml:space="preserve">2.52146315574646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735902786255</t>
   </si>
   <si>
     <t xml:space="preserve">2.53870105743408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53086543083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168825149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952340126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52303051948547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5324330329895</t>
+    <t xml:space="preserve">2.53086590766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168801307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52303004264832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53243255615234</t>
   </si>
   <si>
     <t xml:space="preserve">2.51206040382385</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">2.54653668403625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5512375831604</t>
+    <t xml:space="preserve">2.55123782157898</t>
   </si>
   <si>
     <t xml:space="preserve">2.53713393211365</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">2.60608649253845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70794773101807</t>
+    <t xml:space="preserve">2.70794749259949</t>
   </si>
   <si>
     <t xml:space="preserve">2.71108222007751</t>
@@ -899,19 +899,19 @@
     <t xml:space="preserve">2.72205138206482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69541120529175</t>
+    <t xml:space="preserve">2.69541096687317</t>
   </si>
   <si>
     <t xml:space="preserve">2.70324659347534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67347145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406893730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705589294434</t>
+    <t xml:space="preserve">2.67347168922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705613136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.59981799125671</t>
@@ -923,37 +923,37 @@
     <t xml:space="preserve">2.59825110435486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58571410179138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57004261016846</t>
+    <t xml:space="preserve">2.58571434020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57004308700562</t>
   </si>
   <si>
     <t xml:space="preserve">2.56220746040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54183506965637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5198962688446</t>
+    <t xml:space="preserve">2.54183530807495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51989579200745</t>
   </si>
   <si>
     <t xml:space="preserve">2.52929854393005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52459716796875</t>
+    <t xml:space="preserve">2.52459669113159</t>
   </si>
   <si>
     <t xml:space="preserve">2.46034598350525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47131586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228573799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43370509147644</t>
+    <t xml:space="preserve">2.47131562232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228526115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43370532989502</t>
   </si>
   <si>
     <t xml:space="preserve">2.39609527587891</t>
@@ -962,139 +962,136 @@
     <t xml:space="preserve">2.32087421417236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30206871032715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975775718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27699494361877</t>
+    <t xml:space="preserve">2.30206894874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27699518203735</t>
   </si>
   <si>
     <t xml:space="preserve">2.2879650592804</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34908199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36475324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064911842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848450660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333317756653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43683958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62489175796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6327269077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46818161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36632013320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.381991147995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251059532166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40549802780151</t>
+    <t xml:space="preserve">2.34908223152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36475300788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064935684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848474502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333341598511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43683934211731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62489128112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63272666931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46818208694458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36632037162781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38199090957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766192436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40549755096436</t>
   </si>
   <si>
     <t xml:space="preserve">2.42116856575012</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42900395393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878740310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363631248474</t>
+    <t xml:space="preserve">2.42900419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878764152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363655090332</t>
   </si>
   <si>
     <t xml:space="preserve">2.25662326812744</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27229404449463</t>
+    <t xml:space="preserve">2.27229428291321</t>
   </si>
   <si>
     <t xml:space="preserve">2.2801296710968</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26445889472961</t>
+    <t xml:space="preserve">2.26445865631104</t>
   </si>
   <si>
     <t xml:space="preserve">2.22528123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11558413505554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1235978603363</t>
+    <t xml:space="preserve">2.12359809875488</t>
   </si>
   <si>
     <t xml:space="preserve">2.0995569229126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08352994918823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09154343605042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01942133903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339412689209</t>
+    <t xml:space="preserve">2.08352971076965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09154367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01942110061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339388847351</t>
   </si>
   <si>
     <t xml:space="preserve">2.06750297546387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18770670890808</t>
+    <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13962483406067</t>
+    <t xml:space="preserve">2.13962507247925</t>
   </si>
   <si>
     <t xml:space="preserve">2.16366577148438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14763879776001</t>
+    <t xml:space="preserve">2.14763855934143</t>
   </si>
   <si>
     <t xml:space="preserve">2.20373368263245</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13161134719849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17167949676514</t>
+    <t xml:space="preserve">2.13161158561707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17167925834656</t>
   </si>
   <si>
     <t xml:space="preserve">2.19571995735168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17969250679016</t>
+    <t xml:space="preserve">2.1796932220459</t>
   </si>
   <si>
     <t xml:space="preserve">2.10757088661194</t>
@@ -1103,10 +1100,10 @@
     <t xml:space="preserve">2.05948901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07551622390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0354483127594</t>
+    <t xml:space="preserve">2.07551646232605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03544855117798</t>
   </si>
   <si>
     <t xml:space="preserve">2.05147552490234</t>
@@ -1118,22 +1115,22 @@
     <t xml:space="preserve">2.26784205436707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21976065635681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21174716949463</t>
+    <t xml:space="preserve">2.21976041793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21174740791321</t>
   </si>
   <si>
     <t xml:space="preserve">2.24380159378052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23578763008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22777462005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15565228462219</t>
+    <t xml:space="preserve">2.23578810691833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22777438163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15565252304077</t>
   </si>
   <si>
     <t xml:space="preserve">2.30791020393372</t>
@@ -1148,52 +1145,52 @@
     <t xml:space="preserve">1.99538052082062</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91524481773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325830459595</t>
+    <t xml:space="preserve">1.91524457931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325842380524</t>
   </si>
   <si>
     <t xml:space="preserve">1.96332621574402</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97133994102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9873673915863</t>
+    <t xml:space="preserve">1.9713397026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736679553986</t>
   </si>
   <si>
     <t xml:space="preserve">2.01140761375427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81106841564178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81908178329468</t>
+    <t xml:space="preserve">1.81106853485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81908202171326</t>
   </si>
   <si>
     <t xml:space="preserve">1.84312260150909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79504108428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901434898376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709538936615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.771000623703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73093283176422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69887828826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7149053812027</t>
+    <t xml:space="preserve">1.79504132270813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7790139913559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709550857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77100050449371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73093259334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69887804985046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71490550041199</t>
   </si>
   <si>
     <t xml:space="preserve">1.74695980548859</t>
@@ -1202,82 +1199,85 @@
     <t xml:space="preserve">1.72291898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7389463186264</t>
+    <t xml:space="preserve">1.73894619941711</t>
   </si>
   <si>
     <t xml:space="preserve">1.76298689842224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75497317314148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305469036102</t>
+    <t xml:space="preserve">1.75497353076935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305457115173</t>
   </si>
   <si>
     <t xml:space="preserve">1.85914981365204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8671635389328</t>
+    <t xml:space="preserve">1.86716318130493</t>
   </si>
   <si>
     <t xml:space="preserve">1.83510899543762</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723133087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935330867767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928551673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082920074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258134841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98783659934998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99608469009399</t>
+    <t xml:space="preserve">1.87517702579498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723121166229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935318946838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9392853975296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082943916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133946418762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98783624172211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99608480930328</t>
   </si>
   <si>
     <t xml:space="preserve">1.96309161186218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93834638595581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97958791255951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0373260974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06207060813904</t>
+    <t xml:space="preserve">1.9383465051651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97958827018738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03732585906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06207084655762</t>
   </si>
   <si>
     <t xml:space="preserve">2.05382251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09506416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16929864883423</t>
+    <t xml:space="preserve">2.09506392478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16929888725281</t>
   </si>
   <si>
     <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1115608215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10331225395203</t>
+    <t xml:space="preserve">2.11156058311462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10331249237061</t>
   </si>
   <si>
     <t xml:space="preserve">2.12805700302124</t>
@@ -1289,28 +1289,28 @@
     <t xml:space="preserve">2.11980891227722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14455366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07856774330139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22703671455383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21878838539124</t>
+    <t xml:space="preserve">2.14455342292786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07856726646423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22703623771667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21878862380981</t>
   </si>
   <si>
     <t xml:space="preserve">2.25178146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24353337287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21054029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26002979278564</t>
+    <t xml:space="preserve">2.24353313446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21054005622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26002955436707</t>
   </si>
   <si>
     <t xml:space="preserve">2.26827812194824</t>
@@ -1319,19 +1319,19 @@
     <t xml:space="preserve">2.33426427841187</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30951952934265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30127096176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31776762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38375401496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37550568580627</t>
+    <t xml:space="preserve">2.30951929092407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30127120018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31776785850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38375425338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37550592422485</t>
   </si>
   <si>
     <t xml:space="preserve">2.32601594924927</t>
@@ -1340,16 +1340,16 @@
     <t xml:space="preserve">2.27652621269226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28477454185486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29302287101746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23528480529785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200234413147</t>
+    <t xml:space="preserve">2.28477430343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29302263259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23528504371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200210571289</t>
   </si>
   <si>
     <t xml:space="preserve">2.4497401714325</t>
@@ -1361,22 +1361,22 @@
     <t xml:space="preserve">2.43324375152588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40849876403809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42499542236328</t>
+    <t xml:space="preserve">2.40849900245667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42499589920044</t>
   </si>
   <si>
     <t xml:space="preserve">2.45798850059509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49922966957092</t>
+    <t xml:space="preserve">2.4992299079895</t>
   </si>
   <si>
     <t xml:space="preserve">2.47448539733887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5157265663147</t>
+    <t xml:space="preserve">2.51572632789612</t>
   </si>
   <si>
     <t xml:space="preserve">2.58996105194092</t>
@@ -1385,46 +1385,46 @@
     <t xml:space="preserve">2.54871940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4909815788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5074782371521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44149208068848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35076117515564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40025067329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19404315948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18579506874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04557418823242</t>
+    <t xml:space="preserve">2.49098205566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50747799873352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44149231910706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35076069831848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40025043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19404339790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18579530715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.045574426651</t>
   </si>
   <si>
     <t xml:space="preserve">1.87236046791077</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88060867786407</t>
+    <t xml:space="preserve">1.88060855865479</t>
   </si>
   <si>
     <t xml:space="preserve">1.68264985084534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69089818000793</t>
+    <t xml:space="preserve">1.69089806079865</t>
   </si>
   <si>
     <t xml:space="preserve">1.56717395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71564280986786</t>
+    <t xml:space="preserve">1.71564292907715</t>
   </si>
   <si>
     <t xml:space="preserve">1.64553260803223</t>
@@ -1436,70 +1436,70 @@
     <t xml:space="preserve">1.62491190433502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77338099479675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162944316864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74863612651825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80637407302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411237716675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00433325767517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81462252140045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812610149384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287073135376</t>
+    <t xml:space="preserve">1.77338111400604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162920475006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74863588809967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80637431144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411225795746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00433278083801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81462240219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812586307526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287061214447</t>
   </si>
   <si>
     <t xml:space="preserve">1.84761548042297</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83111917972565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78987765312195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360175609589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8971049785614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90535354614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95484328269958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907800674438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08681559562683</t>
+    <t xml:space="preserve">1.83111894130707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78987753391266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885700702667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360187530518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710533618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90535318851471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9548431634903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907776832581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08681607246399</t>
   </si>
   <si>
     <t xml:space="preserve">2.17754697799683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07031917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07786893844604</t>
+    <t xml:space="preserve">2.07031941413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07786917686462</t>
   </si>
   <si>
     <t xml:space="preserve">2.06938791275024</t>
@@ -1508,31 +1508,31 @@
     <t xml:space="preserve">2.03546357154846</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98457670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609579563141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065224170685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99305784702301</t>
+    <t xml:space="preserve">1.9845769405365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065248012543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9930579662323</t>
   </si>
   <si>
     <t xml:space="preserve">2.06090688705444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02698254585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05242562294006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04394483566284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01002025604248</t>
+    <t xml:space="preserve">2.02698230743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05242586135864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04394459724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01002049446106</t>
   </si>
   <si>
     <t xml:space="preserve">2.0015389919281</t>
@@ -1541,34 +1541,34 @@
     <t xml:space="preserve">1.89976596832275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88280391693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128482341766</t>
+    <t xml:space="preserve">1.88280379772186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128494262695</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850152015686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95913362503052</t>
+    <t xml:space="preserve">1.95913326740265</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875533103943</t>
+    <t xml:space="preserve">2.12875556945801</t>
   </si>
   <si>
     <t xml:space="preserve">2.12027454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16267991065979</t>
+    <t xml:space="preserve">2.16268014907837</t>
   </si>
   <si>
     <t xml:space="preserve">2.20508527755737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23052906990051</t>
+    <t xml:space="preserve">2.23052883148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.30685877799988</t>
@@ -1583,13 +1583,13 @@
     <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559409141541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255614280701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47648048400879</t>
+    <t xml:space="preserve">2.42559432983398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255638122559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47648072242737</t>
   </si>
   <si>
     <t xml:space="preserve">2.46799969673157</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">2.51040506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43407487869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4171130657196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888608932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58673477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977248191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54432964324951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57825398445129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56129169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55281043052673</t>
+    <t xml:space="preserve">2.43407511711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41711258888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888656616211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58673501014709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54432940483093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57825374603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56129193305969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55281019210815</t>
   </si>
   <si>
     <t xml:space="preserve">2.53584837913513</t>
@@ -1637,13 +1637,13 @@
     <t xml:space="preserve">2.64610242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63762164115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66306471824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70547008514404</t>
+    <t xml:space="preserve">2.63762140274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66306495666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70547032356262</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698905944824</t>
@@ -1652,13 +1652,13 @@
     <t xml:space="preserve">2.62914037704468</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71395182609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73091387748718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77331900596619</t>
+    <t xml:space="preserve">2.71395134925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73091340065002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77331876754761</t>
   </si>
   <si>
     <t xml:space="preserve">2.78180003166199</t>
@@ -1673,46 +1673,46 @@
     <t xml:space="preserve">2.88357353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90901660919189</t>
+    <t xml:space="preserve">2.90901684761047</t>
   </si>
   <si>
     <t xml:space="preserve">2.85812997817993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80724382400513</t>
+    <t xml:space="preserve">2.80724334716797</t>
   </si>
   <si>
     <t xml:space="preserve">2.75635695457458</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7393946647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74787569046021</t>
+    <t xml:space="preserve">2.73939490318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74787592887878</t>
   </si>
   <si>
     <t xml:space="preserve">2.79876255989075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79028105735779</t>
+    <t xml:space="preserve">2.79028129577637</t>
   </si>
   <si>
     <t xml:space="preserve">2.84964895248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268642425537</t>
+    <t xml:space="preserve">2.83268666267395</t>
   </si>
   <si>
     <t xml:space="preserve">2.82420563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9174976348877</t>
+    <t xml:space="preserve">2.91749787330627</t>
   </si>
   <si>
     <t xml:space="preserve">3.01078963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0362331867218</t>
+    <t xml:space="preserve">3.03623294830322</t>
   </si>
   <si>
     <t xml:space="preserve">2.95990324020386</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">3.07863879203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08711957931519</t>
+    <t xml:space="preserve">3.08712005615234</t>
   </si>
   <si>
     <t xml:space="preserve">3.12104415893555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18041181564331</t>
+    <t xml:space="preserve">3.18041205406189</t>
   </si>
   <si>
     <t xml:space="preserve">3.14648723602295</t>
@@ -1736,49 +1736,49 @@
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281718254089</t>
+    <t xml:space="preserve">3.22281742095947</t>
   </si>
   <si>
     <t xml:space="preserve">3.23129820823669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24826073646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433615684509</t>
+    <t xml:space="preserve">3.24826049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433591842651</t>
   </si>
   <si>
     <t xml:space="preserve">3.28218483924866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40092039108276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42636394500732</t>
+    <t xml:space="preserve">3.40092062950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42636346817017</t>
   </si>
   <si>
     <t xml:space="preserve">3.3669958114624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31610941886902</t>
+    <t xml:space="preserve">3.3161096572876</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066610336304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27370381355286</t>
+    <t xml:space="preserve">3.27370357513428</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31657695770264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27339220046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35112452507019</t>
+    <t xml:space="preserve">3.31657671928406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27339196205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35112476348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.34248757362366</t>
@@ -1787,7 +1787,7 @@
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430928230286</t>
+    <t xml:space="preserve">3.39430904388428</t>
   </si>
   <si>
     <t xml:space="preserve">3.44613075256348</t>
@@ -1805,25 +1805,25 @@
     <t xml:space="preserve">3.60159516334534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59295797348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65341687202454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61023163795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71387529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7829704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80888104438782</t>
+    <t xml:space="preserve">3.5929582118988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65341639518738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61023187637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71387553215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6706907749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78297090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80888152122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.69660139083862</t>
@@ -1832,52 +1832,52 @@
     <t xml:space="preserve">3.62750577926636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.644779920578</t>
+    <t xml:space="preserve">3.64477968215942</t>
   </si>
   <si>
     <t xml:space="preserve">3.73978567123413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75705981254578</t>
+    <t xml:space="preserve">3.7570595741272</t>
   </si>
   <si>
     <t xml:space="preserve">3.55841040611267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67932772636414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57568430900574</t>
+    <t xml:space="preserve">3.67932748794556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57568454742432</t>
   </si>
   <si>
     <t xml:space="preserve">3.58432149887085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70523810386658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52386283874512</t>
+    <t xml:space="preserve">3.705237865448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5238630771637</t>
   </si>
   <si>
     <t xml:space="preserve">3.5497739315033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48931550979614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41158318519592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51522588729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68796420097351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74842309951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66205358505249</t>
+    <t xml:space="preserve">3.48931503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41158294677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51522612571716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74842286109924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66205334663391</t>
   </si>
   <si>
     <t xml:space="preserve">3.61886930465698</t>
@@ -1886,10 +1886,10 @@
     <t xml:space="preserve">3.86933970451355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8261547088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86070275306702</t>
+    <t xml:space="preserve">3.82615494728088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8607029914856</t>
   </si>
   <si>
     <t xml:space="preserve">3.91252446174622</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">3.9557089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99025654792786</t>
+    <t xml:space="preserve">3.99025583267212</t>
   </si>
   <si>
     <t xml:space="preserve">3.84342885017395</t>
@@ -1913,43 +1913,43 @@
     <t xml:space="preserve">3.76569700241089</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92979836463928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661336898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90388774871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8779764175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81751823425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89525055885315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93843507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63614320755005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4979522228241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42885661125183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42021989822388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2820291519165</t>
+    <t xml:space="preserve">3.92979788780212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661360740662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9038872718811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87797617912292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81751799583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434569358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89525079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93843483924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63614296913147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49795246124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42885684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42022013664246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28202939033508</t>
   </si>
   <si>
     <t xml:space="preserve">3.25611853599548</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">3.29066586494446</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24748158454895</t>
+    <t xml:space="preserve">3.24748134613037</t>
   </si>
   <si>
     <t xml:space="preserve">3.29930305480957</t>
@@ -1973,31 +1973,31 @@
     <t xml:space="preserve">3.43749380111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37703537940979</t>
+    <t xml:space="preserve">3.37703561782837</t>
   </si>
   <si>
     <t xml:space="preserve">3.40294623374939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3597617149353</t>
+    <t xml:space="preserve">3.35976147651672</t>
   </si>
   <si>
     <t xml:space="preserve">3.2129340171814</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23020792007446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15247559547424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11792778968811</t>
+    <t xml:space="preserve">3.23020768165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15247535705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11792802810669</t>
   </si>
   <si>
     <t xml:space="preserve">3.19566011428833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14383840560913</t>
+    <t xml:space="preserve">3.14383864402771</t>
   </si>
   <si>
     <t xml:space="preserve">2.97973704338074</t>
@@ -2006,7 +2006,7 @@
     <t xml:space="preserve">3.06610608100891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53250026702881</t>
+    <t xml:space="preserve">3.53249979019165</t>
   </si>
   <si>
     <t xml:space="preserve">3.56704759597778</t>
@@ -2024,10 +2024,10 @@
     <t xml:space="preserve">3.57765245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56879687309265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5245189666748</t>
+    <t xml:space="preserve">3.56879663467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52451872825623</t>
   </si>
   <si>
     <t xml:space="preserve">3.61307454109192</t>
@@ -2036,13 +2036,13 @@
     <t xml:space="preserve">3.58650803565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29427409172058</t>
+    <t xml:space="preserve">3.294273853302</t>
   </si>
   <si>
     <t xml:space="preserve">3.31198525428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35626292228699</t>
+    <t xml:space="preserve">3.35626316070557</t>
   </si>
   <si>
     <t xml:space="preserve">3.33855175971985</t>
@@ -2066,16 +2066,16 @@
     <t xml:space="preserve">3.32969617843628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32084059715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28541827201843</t>
+    <t xml:space="preserve">3.32084083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28541851043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.42710757255554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51566314697266</t>
+    <t xml:space="preserve">3.51566338539124</t>
   </si>
   <si>
     <t xml:space="preserve">3.55108571052551</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">3.5599410533905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46252989768982</t>
+    <t xml:space="preserve">3.4625301361084</t>
   </si>
   <si>
     <t xml:space="preserve">3.36511850357056</t>
@@ -2126,16 +2126,16 @@
     <t xml:space="preserve">3.08174014091492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14372897148132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11716246604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09059548377991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88691759109497</t>
+    <t xml:space="preserve">3.1437292098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11716222763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09059572219849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88691735267639</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890642166138</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">2.74522829055786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65667271614075</t>
+    <t xml:space="preserve">2.65667247772217</t>
   </si>
   <si>
     <t xml:space="preserve">2.56811690330505</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">2.72751688957214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6832389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82492828369141</t>
+    <t xml:space="preserve">2.68323922157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82492852210999</t>
   </si>
   <si>
     <t xml:space="preserve">2.80721735954285</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">2.79836177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83378434181213</t>
+    <t xml:space="preserve">2.83378410339355</t>
   </si>
   <si>
     <t xml:space="preserve">2.97547316551208</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">2.99318432807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06402921676636</t>
+    <t xml:space="preserve">3.06402897834778</t>
   </si>
   <si>
     <t xml:space="preserve">3.07288455963135</t>
@@ -2204,7 +2204,7 @@
     <t xml:space="preserve">2.94005084037781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01089549064636</t>
+    <t xml:space="preserve">3.01089572906494</t>
   </si>
   <si>
     <t xml:space="preserve">3.04631781578064</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">2.98432874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96661782264709</t>
+    <t xml:space="preserve">2.96661758422852</t>
   </si>
   <si>
     <t xml:space="preserve">2.90462851524353</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">2.93119549751282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78065037727356</t>
+    <t xml:space="preserve">2.78065061569214</t>
   </si>
   <si>
     <t xml:space="preserve">2.70980596542358</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">3.0286066532135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05517339706421</t>
+    <t xml:space="preserve">3.05517363548279</t>
   </si>
   <si>
     <t xml:space="preserve">3.17029571533203</t>
@@ -2252,7 +2252,7 @@
     <t xml:space="preserve">3.19686269760132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24114036560059</t>
+    <t xml:space="preserve">3.24114060401917</t>
   </si>
   <si>
     <t xml:space="preserve">3.25885152816772</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">3.16144037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37397384643555</t>
+    <t xml:space="preserve">3.37397408485413</t>
   </si>
   <si>
     <t xml:space="preserve">3.40054082870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47138524055481</t>
+    <t xml:space="preserve">3.47138547897339</t>
   </si>
   <si>
     <t xml:space="preserve">3.50680780410767</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">3.63078570365906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62193059921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63964152336121</t>
+    <t xml:space="preserve">3.62193036079407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63964128494263</t>
   </si>
   <si>
     <t xml:space="preserve">3.67674517631531</t>
@@ -19144,7 +19144,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G608" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19170,7 +19170,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19196,7 +19196,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G610" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19222,7 +19222,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G611" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19248,7 +19248,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G612" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19274,7 +19274,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19300,7 +19300,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G614" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19326,7 +19326,7 @@
         <v>2.5</v>
       </c>
       <c r="G615" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19352,7 +19352,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G616" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19378,7 +19378,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19404,7 +19404,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G618" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19430,7 +19430,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G619" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19456,7 +19456,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G620" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19482,7 +19482,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G621" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19508,7 +19508,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G622" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19534,7 +19534,7 @@
         <v>2.75</v>
       </c>
       <c r="G623" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19560,7 +19560,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G624" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19586,7 +19586,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19612,7 +19612,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G626" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19638,7 +19638,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G627" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19664,7 +19664,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G628" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19690,7 +19690,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19716,7 +19716,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19742,7 +19742,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G631" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19768,7 +19768,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G632" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19794,7 +19794,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19820,7 +19820,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G634" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19846,7 +19846,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G635" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19872,7 +19872,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19898,7 +19898,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G637" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19924,7 +19924,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G638" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19950,7 +19950,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G639" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19976,7 +19976,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G640" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20002,7 +20002,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G641" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20028,7 +20028,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20054,7 +20054,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G643" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20080,7 +20080,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20106,7 +20106,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G645" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20132,7 +20132,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G646" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20158,7 +20158,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G647" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20184,7 +20184,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G648" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20210,7 +20210,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G649" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20236,7 +20236,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G650" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20262,7 +20262,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G651" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20288,7 +20288,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20314,7 +20314,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G653" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20340,7 +20340,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20366,7 +20366,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20392,7 +20392,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20418,7 +20418,7 @@
         <v>2.5</v>
       </c>
       <c r="G657" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20444,7 +20444,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G658" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20470,7 +20470,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G659" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20496,7 +20496,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G660" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20522,7 +20522,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G661" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20548,7 +20548,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G662" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20574,7 +20574,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20600,7 +20600,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G664" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20626,7 +20626,7 @@
         <v>2.75</v>
       </c>
       <c r="G665" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20652,7 +20652,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20678,7 +20678,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20704,7 +20704,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G668" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20730,7 +20730,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20756,7 +20756,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20782,7 +20782,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20808,7 +20808,7 @@
         <v>2.75</v>
       </c>
       <c r="G672" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20834,7 +20834,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20860,7 +20860,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20886,7 +20886,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G675" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20912,7 +20912,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G676" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20938,7 +20938,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G677" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20964,7 +20964,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G678" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20990,7 +20990,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G679" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21016,7 +21016,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G680" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21042,7 +21042,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21068,7 +21068,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21094,7 +21094,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G683" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21120,7 +21120,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G684" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21146,7 +21146,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G685" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21172,7 +21172,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G686" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21198,7 +21198,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21224,7 +21224,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G688" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21250,7 +21250,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21276,7 +21276,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G690" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21302,7 +21302,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G691" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21328,7 +21328,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G692" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21354,7 +21354,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21380,7 +21380,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G694" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21406,7 +21406,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G695" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21432,7 +21432,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21458,7 +21458,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21484,7 +21484,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G698" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21510,7 +21510,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G699" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21536,7 +21536,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G700" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21562,7 +21562,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G701" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21588,7 +21588,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G702" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21614,7 +21614,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G703" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21640,7 +21640,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G704" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21666,7 +21666,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21692,7 +21692,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21718,7 +21718,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G707" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21744,7 +21744,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G708" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21770,7 +21770,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21796,7 +21796,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G710" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21822,7 +21822,7 @@
         <v>2.5</v>
       </c>
       <c r="G711" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21848,7 +21848,7 @@
         <v>2.5</v>
       </c>
       <c r="G712" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21874,7 +21874,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G713" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21900,7 +21900,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21926,7 +21926,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G715" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21952,7 +21952,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21978,7 +21978,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G717" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22004,7 +22004,7 @@
         <v>2.5</v>
       </c>
       <c r="G718" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22030,7 +22030,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G719" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22056,7 +22056,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G720" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22082,7 +22082,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G721" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22108,7 +22108,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G722" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22134,7 +22134,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22160,7 +22160,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G724" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22186,7 +22186,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G725" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22212,7 +22212,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G726" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22238,7 +22238,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G727" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22264,7 +22264,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G728" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22290,7 +22290,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G729" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22316,7 +22316,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G730" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22342,7 +22342,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22368,7 +22368,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G732" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22394,7 +22394,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22420,7 +22420,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22446,7 +22446,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G735" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22472,7 +22472,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G736" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22498,7 +22498,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G737" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22524,7 +22524,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G738" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22550,7 +22550,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G739" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22576,7 +22576,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G740" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22602,7 +22602,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G741" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22628,7 +22628,7 @@
         <v>2.5</v>
       </c>
       <c r="G742" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22654,7 +22654,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G743" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22680,7 +22680,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G744" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22706,7 +22706,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G745" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22732,7 +22732,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G746" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22758,7 +22758,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G747" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22784,7 +22784,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22810,7 +22810,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G749" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22836,7 +22836,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22862,7 +22862,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G751" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22888,7 +22888,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G752" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22914,7 +22914,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22940,7 +22940,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22966,7 +22966,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G755" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22992,7 +22992,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G756" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23018,7 +23018,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G757" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23044,7 +23044,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G758" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23070,7 +23070,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G759" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23096,7 +23096,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23122,7 +23122,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G761" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23148,7 +23148,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G762" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23174,7 +23174,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G763" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23200,7 +23200,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G764" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23226,7 +23226,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G765" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23252,7 +23252,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G766" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23278,7 +23278,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G767" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23304,7 +23304,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G768" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23330,7 +23330,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23356,7 +23356,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G770" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23382,7 +23382,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G771" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23408,7 +23408,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G772" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23434,7 +23434,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G773" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23460,7 +23460,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G774" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23486,7 +23486,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G775" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23512,7 +23512,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G776" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23538,7 +23538,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23564,7 +23564,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G778" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23590,7 +23590,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G779" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23616,7 +23616,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G780" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23642,7 +23642,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23668,7 +23668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23694,7 +23694,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G783" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23720,7 +23720,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G784" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23746,7 +23746,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G785" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23772,7 +23772,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G786" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23798,7 +23798,7 @@
         <v>2.25</v>
       </c>
       <c r="G787" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23824,7 +23824,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G788" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23850,7 +23850,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G789" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23876,7 +23876,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23902,7 +23902,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23928,7 +23928,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G792" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23954,7 +23954,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G793" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23980,7 +23980,7 @@
         <v>2.5</v>
       </c>
       <c r="G794" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24006,7 +24006,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G795" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24032,7 +24032,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24058,7 +24058,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24084,7 +24084,7 @@
         <v>2.5</v>
       </c>
       <c r="G798" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24110,7 +24110,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G799" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24136,7 +24136,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G800" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24162,7 +24162,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G801" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24188,7 +24188,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G802" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24214,7 +24214,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G803" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24240,7 +24240,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24266,7 +24266,7 @@
         <v>2.5</v>
       </c>
       <c r="G805" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24292,7 +24292,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G806" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24318,7 +24318,7 @@
         <v>2.5</v>
       </c>
       <c r="G807" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24344,7 +24344,7 @@
         <v>2.5</v>
       </c>
       <c r="G808" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24370,7 +24370,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G809" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24396,7 +24396,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G810" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24422,7 +24422,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G811" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24448,7 +24448,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G812" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24474,7 +24474,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G813" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24500,7 +24500,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24526,7 +24526,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G815" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24552,7 +24552,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24578,7 +24578,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G817" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24604,7 +24604,7 @@
         <v>2.5</v>
       </c>
       <c r="G818" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24630,7 +24630,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24656,7 +24656,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G820" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24682,7 +24682,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24708,7 +24708,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G822" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24734,7 +24734,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G823" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24760,7 +24760,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G824" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24786,7 +24786,7 @@
         <v>2.5</v>
       </c>
       <c r="G825" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24812,7 +24812,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24838,7 +24838,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G827" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24864,7 +24864,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G828" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24890,7 +24890,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G829" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24916,7 +24916,7 @@
         <v>2.5</v>
       </c>
       <c r="G830" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24942,7 +24942,7 @@
         <v>2.5</v>
       </c>
       <c r="G831" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24968,7 +24968,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -24994,7 +24994,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G833" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25020,7 +25020,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G834" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25046,7 +25046,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G835" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25072,7 +25072,7 @@
         <v>2.5</v>
       </c>
       <c r="G836" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25098,7 +25098,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G837" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25124,7 +25124,7 @@
         <v>2.5</v>
       </c>
       <c r="G838" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25150,7 +25150,7 @@
         <v>2.5</v>
       </c>
       <c r="G839" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25176,7 +25176,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25202,7 +25202,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G841" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25228,7 +25228,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G842" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25254,7 +25254,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G843" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25280,7 +25280,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G844" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25306,7 +25306,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25332,7 +25332,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G846" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25358,7 +25358,7 @@
         <v>2.5</v>
       </c>
       <c r="G847" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25384,7 +25384,7 @@
         <v>2.5</v>
       </c>
       <c r="G848" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25410,7 +25410,7 @@
         <v>2.5</v>
       </c>
       <c r="G849" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25436,7 +25436,7 @@
         <v>2.5</v>
       </c>
       <c r="G850" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25462,7 +25462,7 @@
         <v>2.5</v>
       </c>
       <c r="G851" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25488,7 +25488,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25514,7 +25514,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25540,7 +25540,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G854" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25566,7 +25566,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G855" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25592,7 +25592,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G856" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25618,7 +25618,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G857" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25644,7 +25644,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25670,7 +25670,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G859" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25696,7 +25696,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25722,7 +25722,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G861" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25748,7 +25748,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G862" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25826,7 +25826,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G865" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26008,7 +26008,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G872" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26190,7 +26190,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G879" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26216,7 +26216,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G880" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26242,7 +26242,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G881" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -31546,7 +31546,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1085" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32534,7 +32534,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32560,7 +32560,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32638,7 +32638,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1127" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32742,7 +32742,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1131" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32872,7 +32872,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1136" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33002,7 +33002,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1141" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33262,7 +33262,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1151" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33314,7 +33314,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1153" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33340,7 +33340,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1154" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33392,7 +33392,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1156" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34172,7 +34172,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1186" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34250,7 +34250,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1189" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -69124,7 +69124,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.691087963</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>12407</v>
@@ -69145,6 +69145,32 @@
         <v>992</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.691099537</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>45606</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>9.03999996185303</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>8.96000003814697</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>984</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="999" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="998">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652255535126</t>
+    <t xml:space="preserve">1.73652279376984</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">1.74400758743286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71406757831573</t>
+    <t xml:space="preserve">1.71406769752502</t>
   </si>
   <si>
     <t xml:space="preserve">1.66167235374451</t>
@@ -56,61 +56,61 @@
     <t xml:space="preserve">1.67215156555176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969646930695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921749591827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57334935665131</t>
+    <t xml:space="preserve">1.64969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5733494758606</t>
   </si>
   <si>
     <t xml:space="preserve">1.49625384807587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48053550720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48203229904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637382984161</t>
+    <t xml:space="preserve">1.48053526878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48203217983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637359142303</t>
   </si>
   <si>
     <t xml:space="preserve">1.44460701942444</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42215240001678</t>
+    <t xml:space="preserve">1.42215216159821</t>
   </si>
   <si>
     <t xml:space="preserve">1.41990661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41466724872589</t>
+    <t xml:space="preserve">1.41466701030731</t>
   </si>
   <si>
     <t xml:space="preserve">1.41915822029114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40718233585358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3824816942215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38472712039948</t>
+    <t xml:space="preserve">1.40718221664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38248157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38472735881805</t>
   </si>
   <si>
     <t xml:space="preserve">1.3982001543045</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35703277587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.33607447147369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34730207920074</t>
+    <t xml:space="preserve">1.35703241825104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607459068298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34730219841003</t>
   </si>
   <si>
     <t xml:space="preserve">1.3428111076355</t>
@@ -119,166 +119,166 @@
     <t xml:space="preserve">1.38397860527039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35478687286377</t>
+    <t xml:space="preserve">1.35478711128235</t>
   </si>
   <si>
     <t xml:space="preserve">1.38098466396332</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36975717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873923778534</t>
+    <t xml:space="preserve">1.36975729465485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873899936676</t>
   </si>
   <si>
     <t xml:space="preserve">1.4311341047287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41017603874207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44535577297211</t>
+    <t xml:space="preserve">1.41017615795135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4453558921814</t>
   </si>
   <si>
     <t xml:space="preserve">1.462571144104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51197218894958</t>
+    <t xml:space="preserve">1.51197230815887</t>
   </si>
   <si>
     <t xml:space="preserve">1.52544546127319</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52245116233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54490637779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191219806671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5493973493576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56287062168121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60029554367065</t>
+    <t xml:space="preserve">1.52245128154755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54490625858307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191243648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54939723014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56287050247192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60029542446136</t>
   </si>
   <si>
     <t xml:space="preserve">1.60927760601044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63173246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424767017365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63023543357849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676251888275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418744087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6437087059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682227134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5883195400238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472664356232</t>
+    <t xml:space="preserve">1.63173270225525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63023555278778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676239967346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418756008148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370858669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682239055634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58831942081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472652435303</t>
   </si>
   <si>
     <t xml:space="preserve">1.66017544269562</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66915738582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6916127204895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69310963153839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155296802521</t>
+    <t xml:space="preserve">1.6691575050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712186813354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69161260128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69310939311981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155284881592</t>
   </si>
   <si>
     <t xml:space="preserve">1.73502564430237</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70358872413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658278465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909739494324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664265632629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68412780761719</t>
+    <t xml:space="preserve">1.70358848571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658266544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909751415253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.676642537117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68412792682648</t>
   </si>
   <si>
     <t xml:space="preserve">1.66766047477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68263041973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221131801605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64670264720917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514538764954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69964480400085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6843329668045</t>
+    <t xml:space="preserve">1.68263018131256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221143722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64670252799988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6751457452774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69964492321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68433284759521</t>
   </si>
   <si>
     <t xml:space="preserve">1.69198894500732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72108173370361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70576977729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6950511932373</t>
+    <t xml:space="preserve">1.72108161449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70576989650726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69505131244659</t>
   </si>
   <si>
     <t xml:space="preserve">1.71495711803436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72261321544647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65370881557465</t>
+    <t xml:space="preserve">1.72261333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65370845794678</t>
   </si>
   <si>
     <t xml:space="preserve">1.67208325862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66902077198029</t>
+    <t xml:space="preserve">1.66902089118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.65217733383179</t>
@@ -287,16 +287,16 @@
     <t xml:space="preserve">1.606241106987</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56183576583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55417990684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202439308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121173381805</t>
+    <t xml:space="preserve">1.56183588504791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5541797876358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202451229095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121161460876</t>
   </si>
   <si>
     <t xml:space="preserve">1.59092903137207</t>
@@ -314,40 +314,40 @@
     <t xml:space="preserve">1.4929313659668</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4760879278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52278983592987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761905193329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50058734416962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6077721118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5970538854599</t>
+    <t xml:space="preserve">1.47608804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52278995513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996319293976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589941978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60777235031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59705364704132</t>
   </si>
   <si>
     <t xml:space="preserve">1.56949198246002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62308418750763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66748952865601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66136491298676</t>
+    <t xml:space="preserve">1.62308430671692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6674896478653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66136479377747</t>
   </si>
   <si>
     <t xml:space="preserve">1.67667675018311</t>
@@ -356,31 +356,31 @@
     <t xml:space="preserve">1.61542820930481</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57714796066284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58480405807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63839662075043</t>
+    <t xml:space="preserve">1.57714784145355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58480381965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63839650154114</t>
   </si>
   <si>
     <t xml:space="preserve">1.63380289077759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57561683654785</t>
+    <t xml:space="preserve">1.57561695575714</t>
   </si>
   <si>
     <t xml:space="preserve">1.54652380943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56796073913574</t>
+    <t xml:space="preserve">1.56796085834503</t>
   </si>
   <si>
     <t xml:space="preserve">1.54499244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355575561523</t>
+    <t xml:space="preserve">1.52355551719666</t>
   </si>
   <si>
     <t xml:space="preserve">1.54193007946014</t>
@@ -389,49 +389,49 @@
     <t xml:space="preserve">1.58174169063568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55877339839935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5802104473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55264866352081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53044593334198</t>
+    <t xml:space="preserve">1.55877351760864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58021032810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5526487827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53044617176056</t>
   </si>
   <si>
     <t xml:space="preserve">1.51972758769989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50594675540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671219825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427398204803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56642961502075</t>
+    <t xml:space="preserve">1.50594663619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671243667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56642949581146</t>
   </si>
   <si>
     <t xml:space="preserve">1.57408559322357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58327305316925</t>
+    <t xml:space="preserve">1.58327293395996</t>
   </si>
   <si>
     <t xml:space="preserve">1.59246003627777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5021185874939</t>
+    <t xml:space="preserve">1.50211870670319</t>
   </si>
   <si>
     <t xml:space="preserve">1.50824344158173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47532260417938</t>
+    <t xml:space="preserve">1.47532248497009</t>
   </si>
   <si>
     <t xml:space="preserve">1.49675941467285</t>
@@ -443,22 +443,22 @@
     <t xml:space="preserve">1.52968037128448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60011613368988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58786642551422</t>
+    <t xml:space="preserve">1.60011625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58786654472351</t>
   </si>
   <si>
     <t xml:space="preserve">1.56489825248718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5633670091629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255434989929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59858512878418</t>
+    <t xml:space="preserve">1.56336724758148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255423069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59858500957489</t>
   </si>
   <si>
     <t xml:space="preserve">1.59399139881134</t>
@@ -467,46 +467,46 @@
     <t xml:space="preserve">1.60470974445343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64758348464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64605271816254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68280136585236</t>
+    <t xml:space="preserve">1.64758384227753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64605259895325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68280160427094</t>
   </si>
   <si>
     <t xml:space="preserve">1.63074052333832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686537742615</t>
+    <t xml:space="preserve">1.63686525821686</t>
   </si>
   <si>
     <t xml:space="preserve">1.64452147483826</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63227164745331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66289556026459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595828533173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333156108856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026943206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558126926422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017488002777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730090141296</t>
+    <t xml:space="preserve">1.63227152824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66289603710175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595816612244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026907444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558138847351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730113983154</t>
   </si>
   <si>
     <t xml:space="preserve">1.70423865318298</t>
@@ -515,130 +515,130 @@
     <t xml:space="preserve">1.73792517185211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75936233997345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089358329773</t>
+    <t xml:space="preserve">1.75936222076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089346408844</t>
   </si>
   <si>
     <t xml:space="preserve">1.78386151790619</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76854920387268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323712825775</t>
+    <t xml:space="preserve">1.76854979991913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323748588562</t>
   </si>
   <si>
     <t xml:space="preserve">1.73486268520355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73639392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79151773452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223643779755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061076164246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754863262177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8252044916153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448578834534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889089107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87726557254791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85429704189301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582852363586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85123467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86654710769653</t>
+    <t xml:space="preserve">1.73639380931854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79151749610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223619937897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061088085175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81754815578461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682969093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520437240601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448554992676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889101028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87726545333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85429728031158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582840442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85123491287231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86654698848724</t>
   </si>
   <si>
     <t xml:space="preserve">1.84970378875732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86348474025726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276627540588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745431900024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511029720306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367289066315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051632881165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817230701447</t>
+    <t xml:space="preserve">1.86348450183868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85276591777802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745408058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84510982036591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367324829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051644802094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817242622375</t>
   </si>
   <si>
     <t xml:space="preserve">1.86807823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94923257827759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788984298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.921670794487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932665348053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9247328042984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607601642609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904407024384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823117256165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894999504089</t>
+    <t xml:space="preserve">1.9492324590683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788972377777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92167055606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932677268982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473304271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607553958893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904395103455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823129177094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894975662231</t>
   </si>
   <si>
     <t xml:space="preserve">2.00741839408875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01201224327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9905754327774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00282454490662</t>
+    <t xml:space="preserve">2.01201248168945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99057495594025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0028247833252</t>
   </si>
   <si>
     <t xml:space="preserve">2.00588726997375</t>
@@ -650,402 +650,402 @@
     <t xml:space="preserve">2.09051060676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11401724815369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424258232117</t>
+    <t xml:space="preserve">2.11401700973511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424234390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17043256759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14692616462708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15006017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655401229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259717941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15162754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13909077644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16103005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0466320514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290007591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03722906112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04819893836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04506468772888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06543684005737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10774898529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1171510219574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12341976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125538825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296957015991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19393944740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647597312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2033417224884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19237232208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20804333686829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1641640663147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946316719055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13595652580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677910804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386995315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02625966072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805176258087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07640671730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05446743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10461449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700444221497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566217422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954120635986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857109069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797360420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24095177650452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371411323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21117758750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23311686515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31460618972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3271427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557559013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982653617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38669204711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467496871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601723670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48541951179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49012088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52146291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735926628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53870105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53086519241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168825149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422501564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52303028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5324330329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5089259147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51362729072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49795651435852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638938903809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616429328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55123829841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53713393211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55437207221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60608673095703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70794796943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541120529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70324635505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67347168922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705613136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981799125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728098869324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5982506275177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58571410179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57004284858704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56220746040344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54183506965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51989579200745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52929830551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52459716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034598350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228526115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4337055683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39609503746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087397575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27699518203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28796529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34908199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36475300788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064911842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848426818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333293914795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43683958053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62489151954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6327269077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46818161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36632013320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.381991147995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251083374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40549778938293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42116856575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900395393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878764152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363655090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25662326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27229428291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2801296710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445889472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558413505554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17043232917786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1469259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15006065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655401229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259717941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15162754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13909077644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04663181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05290031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03722929954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04819869995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04506468772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06543684005737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073594093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10774898529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11715126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12341952323914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125538825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296933174133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1939389705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647597312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20334196090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19237232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20804309844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416454315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13595628738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0638701915741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0262598991394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805152416229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640671730042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05446743965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10461473464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566193580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954096794128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797384262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2409520149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371411323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117734909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2331166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781800270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930708885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31460618972778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32714295387268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3866925239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44467496871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601723670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48541951179504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49012088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5214626789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735902786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53870105743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53086590766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168825149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422501564026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952340126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52303028106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53243279457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206040382385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50892567634583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51362752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4979567527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638915061951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55123805999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53713393211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55437207221985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60608625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70794773101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108222007751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541120529175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70324683189392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67347145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705613136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981822967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58728122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59825086593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5857138633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57004308700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56220746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54183506965637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51989603042603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52929830551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52459692955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43370532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39609479904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975728034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27699542045593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28796529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34908175468445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36475300788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064911842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848450660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333317756653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43683958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62489128112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6327269077301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46818161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36632037162781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.381991147995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40549755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42116856575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900395393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363607406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25662326812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27229428291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28012990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445865631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528100013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11558437347412</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.1235978603363</t>
   </si>
   <si>
@@ -1058,28 +1058,28 @@
     <t xml:space="preserve">2.09154343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942133903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339412689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750273704529</t>
+    <t xml:space="preserve">2.01942157745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339436531067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750249862671</t>
   </si>
   <si>
     <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29188299179077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13962531089783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1636655330658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14763832092285</t>
+    <t xml:space="preserve">2.29188251495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13962507247925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16366577148438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14763879776001</t>
   </si>
   <si>
     <t xml:space="preserve">2.20373392105103</t>
@@ -1088,16 +1088,16 @@
     <t xml:space="preserve">2.13161158561707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17167901992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19571971893311</t>
+    <t xml:space="preserve">2.17167925834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19571995735168</t>
   </si>
   <si>
     <t xml:space="preserve">2.17969298362732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10757088661194</t>
+    <t xml:space="preserve">2.10757064819336</t>
   </si>
   <si>
     <t xml:space="preserve">2.05948901176453</t>
@@ -1106,91 +1106,91 @@
     <t xml:space="preserve">2.07551622390747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0354483127594</t>
+    <t xml:space="preserve">2.03544855117798</t>
   </si>
   <si>
     <t xml:space="preserve">2.05147552490234</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27585577964783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784229278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21976089477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21174693107605</t>
+    <t xml:space="preserve">2.27585554122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784205436707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21976065635681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21174716949463</t>
   </si>
   <si>
     <t xml:space="preserve">2.24380159378052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2357873916626</t>
+    <t xml:space="preserve">2.23578763008118</t>
   </si>
   <si>
     <t xml:space="preserve">2.22777438163757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15565252304077</t>
+    <t xml:space="preserve">2.15565228462219</t>
   </si>
   <si>
     <t xml:space="preserve">2.30791020393372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02743482589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04346179962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9953807592392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524481773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325818538666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9633264541626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9713397026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736715316772</t>
+    <t xml:space="preserve">2.02743530273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04346203804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99538052082062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524505615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325830459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96332621574402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97134006023407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736703395844</t>
   </si>
   <si>
     <t xml:space="preserve">2.01140761375427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81106853485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81908202171326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84312260150909</t>
+    <t xml:space="preserve">1.81106817722321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81908190250397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84312272071838</t>
   </si>
   <si>
     <t xml:space="preserve">1.79504120349884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77901387214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709538936615</t>
+    <t xml:space="preserve">1.7790139913559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709550857544</t>
   </si>
   <si>
     <t xml:space="preserve">1.77100050449371</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73093271255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69887816905975</t>
+    <t xml:space="preserve">1.73093247413635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69887828826904</t>
   </si>
   <si>
     <t xml:space="preserve">1.7149053812027</t>
@@ -1199,100 +1199,100 @@
     <t xml:space="preserve">1.74695980548859</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72291910648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73894608020782</t>
+    <t xml:space="preserve">1.72291898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73894619941711</t>
   </si>
   <si>
     <t xml:space="preserve">1.76298677921295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75497329235077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305457115173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85914957523346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86716341972351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510899543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723121166229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935330867767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928563594818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082967758179</t>
+    <t xml:space="preserve">1.75497317314148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305504798889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85914981365204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86716318130493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510911464691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8751767873764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935342788696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9392853975296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082943916321</t>
   </si>
   <si>
     <t xml:space="preserve">2.01258134841919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9878363609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99608469009399</t>
+    <t xml:space="preserve">1.98783624172211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99608445167542</t>
   </si>
   <si>
     <t xml:space="preserve">1.96309161186218</t>
   </si>
   <si>
-    <t xml:space="preserve">1.93834662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97958791255951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03732585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06207084655762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0538227558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09506392478943</t>
+    <t xml:space="preserve">1.93834638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9795880317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0373260974884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0620710849762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05382251739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09506416320801</t>
   </si>
   <si>
     <t xml:space="preserve">2.16929864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16105031967163</t>
+    <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
     <t xml:space="preserve">2.11156058311462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10331201553345</t>
+    <t xml:space="preserve">2.10331225395203</t>
   </si>
   <si>
     <t xml:space="preserve">2.12805700302124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13630557060242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11980891227722</t>
+    <t xml:space="preserve">2.13630533218384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11980867385864</t>
   </si>
   <si>
     <t xml:space="preserve">2.14455342292786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07856750488281</t>
+    <t xml:space="preserve">2.07856774330139</t>
   </si>
   <si>
     <t xml:space="preserve">2.22703671455383</t>
@@ -1301,22 +1301,22 @@
     <t xml:space="preserve">2.21878838539124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25178170204163</t>
+    <t xml:space="preserve">2.25178146362305</t>
   </si>
   <si>
     <t xml:space="preserve">2.24353337287903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21054005622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26002955436707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26827812194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33426451683044</t>
+    <t xml:space="preserve">2.21054029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26002979278564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26827836036682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33426403999329</t>
   </si>
   <si>
     <t xml:space="preserve">2.30951952934265</t>
@@ -1349,49 +1349,49 @@
     <t xml:space="preserve">2.23528480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200234413147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4497401714325</t>
+    <t xml:space="preserve">2.39200258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44974040985107</t>
   </si>
   <si>
     <t xml:space="preserve">2.41674709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43324327468872</t>
+    <t xml:space="preserve">2.43324375152588</t>
   </si>
   <si>
     <t xml:space="preserve">2.40849876403809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42499542236328</t>
+    <t xml:space="preserve">2.42499566078186</t>
   </si>
   <si>
     <t xml:space="preserve">2.45798850059509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49922966957092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47448492050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5157265663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5899612903595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54871940612793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4909815788269</t>
+    <t xml:space="preserve">2.4992299079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47448515892029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51572632789612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58996105194092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54871964454651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49098181724548</t>
   </si>
   <si>
     <t xml:space="preserve">2.5074782371521</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4414918422699</t>
+    <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
     <t xml:space="preserve">2.35076093673706</t>
@@ -1403,52 +1403,52 @@
     <t xml:space="preserve">2.19404363632202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.185795545578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04557418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87236046791077</t>
+    <t xml:space="preserve">2.18579530715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.045574426651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87236034870148</t>
   </si>
   <si>
     <t xml:space="preserve">1.88060867786407</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68264985084534</t>
+    <t xml:space="preserve">1.68264973163605</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089818000793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56717395782471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71564292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64553272724152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64140856266022</t>
+    <t xml:space="preserve">1.56717383861542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71564304828644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64553248882294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64140844345093</t>
   </si>
   <si>
     <t xml:space="preserve">1.62491190433502</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77338111400604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162944316864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74863600730896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80637407302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411237716675</t>
+    <t xml:space="preserve">1.77338099479675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162920475006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74863612651825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80637395381927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411201953888</t>
   </si>
   <si>
     <t xml:space="preserve">2.00433325767517</t>
@@ -1457,19 +1457,19 @@
     <t xml:space="preserve">1.81462228298187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79812586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287061214447</t>
+    <t xml:space="preserve">1.79812598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287073135376</t>
   </si>
   <si>
     <t xml:space="preserve">1.84761559963226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83111882209778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78987741470337</t>
+    <t xml:space="preserve">1.83111894130707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78987765312195</t>
   </si>
   <si>
     <t xml:space="preserve">1.88885700702667</t>
@@ -1478,55 +1478,55 @@
     <t xml:space="preserve">1.91360187530518</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89710521697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90535342693329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95484328269958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907776832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08681559562683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17754721641541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07031941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07786917686462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06938791275024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03546380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9845769405365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609555721283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065248012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99305808544159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06090712547302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02698230743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05242562294006</t>
+    <t xml:space="preserve">1.89710533618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90535366535187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9548431634903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907800674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08681607246399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17754673957825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07031917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07786893844604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06938815116882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03546333312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98457682132721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609567642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065271854401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99305784702301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06090688705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02698254585266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05242586135864</t>
   </si>
   <si>
     <t xml:space="preserve">2.04394459724426</t>
@@ -1538,19 +1538,19 @@
     <t xml:space="preserve">2.0015389919281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89976596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88280379772186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128506183624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01850152015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913350582123</t>
+    <t xml:space="preserve">1.89976608753204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88280367851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128482341766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01850128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913374423981</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
@@ -1574,19 +1574,19 @@
     <t xml:space="preserve">2.30685877799988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33230185508728</t>
+    <t xml:space="preserve">2.33230233192444</t>
   </si>
   <si>
     <t xml:space="preserve">2.34926414489746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35774493217468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42559409141541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255661964417</t>
+    <t xml:space="preserve">2.35774517059326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42559385299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255638122559</t>
   </si>
   <si>
     <t xml:space="preserve">2.47648048400879</t>
@@ -1595,25 +1595,25 @@
     <t xml:space="preserve">2.46799969673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49344301223755</t>
+    <t xml:space="preserve">2.49344325065613</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040530204773</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43407487869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41711258888245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888608932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58673501014709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977248191833</t>
+    <t xml:space="preserve">2.43407511711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41711282730103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888632774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58673477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977272033691</t>
   </si>
   <si>
     <t xml:space="preserve">2.54432940483093</t>
@@ -1622,19 +1622,19 @@
     <t xml:space="preserve">2.57825374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56129193305969</t>
+    <t xml:space="preserve">2.56129145622253</t>
   </si>
   <si>
     <t xml:space="preserve">2.55281043052673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53584861755371</t>
+    <t xml:space="preserve">2.53584837913513</t>
   </si>
   <si>
     <t xml:space="preserve">2.52736711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6461021900177</t>
+    <t xml:space="preserve">2.64610242843628</t>
   </si>
   <si>
     <t xml:space="preserve">2.63762140274048</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">2.69698929786682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62914037704468</t>
+    <t xml:space="preserve">2.62914061546326</t>
   </si>
   <si>
     <t xml:space="preserve">2.71395134925842</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">2.77331900596619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78179979324341</t>
+    <t xml:space="preserve">2.78180003166199</t>
   </si>
   <si>
     <t xml:space="preserve">2.84116768836975</t>
@@ -1673,28 +1673,28 @@
     <t xml:space="preserve">2.88357353210449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90901660919189</t>
+    <t xml:space="preserve">2.90901684761047</t>
   </si>
   <si>
     <t xml:space="preserve">2.85812997817993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80724334716797</t>
+    <t xml:space="preserve">2.80724358558655</t>
   </si>
   <si>
     <t xml:space="preserve">2.75635671615601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73939490318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74787592887878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79876232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79028153419495</t>
+    <t xml:space="preserve">2.73939442634583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74787569046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79876208305359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79028129577637</t>
   </si>
   <si>
     <t xml:space="preserve">2.84964895248413</t>
@@ -1715,13 +1715,13 @@
     <t xml:space="preserve">3.0362331867218</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95990324020386</t>
+    <t xml:space="preserve">2.95990300178528</t>
   </si>
   <si>
     <t xml:space="preserve">3.07863879203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08711957931519</t>
+    <t xml:space="preserve">3.08711981773376</t>
   </si>
   <si>
     <t xml:space="preserve">3.12104415893555</t>
@@ -1736,34 +1736,34 @@
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281742095947</t>
+    <t xml:space="preserve">3.22281718254089</t>
   </si>
   <si>
     <t xml:space="preserve">3.23129844665527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24826073646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433615684509</t>
+    <t xml:space="preserve">3.24826049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433639526367</t>
   </si>
   <si>
     <t xml:space="preserve">3.28218483924866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40092015266418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42636346817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36699628829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3161096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2906665802002</t>
+    <t xml:space="preserve">3.40092062950134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42636370658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36699604988098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31610941886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29066634178162</t>
   </si>
   <si>
     <t xml:space="preserve">3.27370381355286</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">3.3079400062561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31657671928406</t>
+    <t xml:space="preserve">3.31657695770264</t>
   </si>
   <si>
     <t xml:space="preserve">3.27339220046997</t>
@@ -1793,19 +1793,19 @@
     <t xml:space="preserve">3.44613075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45476770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47204160690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54113674163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60159516334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5929582118988</t>
+    <t xml:space="preserve">3.45476746559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4720413684845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54113698005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60159540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59295845031738</t>
   </si>
   <si>
     <t xml:space="preserve">3.65341663360596</t>
@@ -1814,31 +1814,31 @@
     <t xml:space="preserve">3.61023187637329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71387553215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6706907749176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7829704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80888104438782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69660139083862</t>
+    <t xml:space="preserve">3.71387505531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069029808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78297066688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8088812828064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69660115242004</t>
   </si>
   <si>
     <t xml:space="preserve">3.62750577926636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64477968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73978590965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75705933570862</t>
+    <t xml:space="preserve">3.644779920578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73978567123413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7570595741272</t>
   </si>
   <si>
     <t xml:space="preserve">3.55841040611267</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">3.67932772636414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57568454742432</t>
+    <t xml:space="preserve">3.57568430900574</t>
   </si>
   <si>
     <t xml:space="preserve">3.58432149887085</t>
@@ -1856,16 +1856,16 @@
     <t xml:space="preserve">3.705237865448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52386283874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5497739315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48931503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41158294677734</t>
+    <t xml:space="preserve">3.5238630771637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54977345466614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48931527137756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41158318519592</t>
   </si>
   <si>
     <t xml:space="preserve">3.51522612571716</t>
@@ -1886,70 +1886,70 @@
     <t xml:space="preserve">3.86933970451355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82615518569946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8607029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91252446174622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99889373779297</t>
+    <t xml:space="preserve">3.8261547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86070251464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91252493858337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99889397621155</t>
   </si>
   <si>
     <t xml:space="preserve">3.9557089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99025630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342861175537</t>
+    <t xml:space="preserve">3.99025678634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342885017395</t>
   </si>
   <si>
     <t xml:space="preserve">3.77433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76569700241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92979788780212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661360740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9038872718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87797617912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81751847267151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434617042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89525032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93843507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63614296913147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49795246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42885708808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42022013664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28202939033508</t>
+    <t xml:space="preserve">3.76569676399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9297981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8866138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90388751029968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87797665596008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81751799583435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434569358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89525079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93843483924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63614320755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4979522228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42885684967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021989822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2820291519165</t>
   </si>
   <si>
     <t xml:space="preserve">3.2561182975769</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">3.29066610336304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24748134613037</t>
+    <t xml:space="preserve">3.24748158454895</t>
   </si>
   <si>
     <t xml:space="preserve">3.29930305480957</t>
@@ -1967,28 +1967,28 @@
     <t xml:space="preserve">3.26475524902344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33385062217712</t>
+    <t xml:space="preserve">3.3338508605957</t>
   </si>
   <si>
     <t xml:space="preserve">3.43749356269836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37703561782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40294623374939</t>
+    <t xml:space="preserve">3.37703514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40294599533081</t>
   </si>
   <si>
     <t xml:space="preserve">3.35976147651672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2129340171814</t>
+    <t xml:space="preserve">3.21293377876282</t>
   </si>
   <si>
     <t xml:space="preserve">3.23020768165588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15247535705566</t>
+    <t xml:space="preserve">3.15247559547424</t>
   </si>
   <si>
     <t xml:space="preserve">3.11792778968811</t>
@@ -2000,7 +2000,7 @@
     <t xml:space="preserve">3.14383840560913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97973728179932</t>
+    <t xml:space="preserve">2.97973704338074</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610608100891</t>
@@ -2009,37 +2009,37 @@
     <t xml:space="preserve">3.53250002861023</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5670473575592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46340441703796</t>
+    <t xml:space="preserve">3.56704759597778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46340489387512</t>
   </si>
   <si>
     <t xml:space="preserve">3.38567209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54223012924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57765245437622</t>
+    <t xml:space="preserve">3.54222989082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57765221595764</t>
   </si>
   <si>
     <t xml:space="preserve">3.56879687309265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5245189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61307454109192</t>
+    <t xml:space="preserve">3.52451872825623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6130747795105</t>
   </si>
   <si>
     <t xml:space="preserve">3.58650803565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29427409172058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31198525428772</t>
+    <t xml:space="preserve">3.294273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31198501586914</t>
   </si>
   <si>
     <t xml:space="preserve">3.35626292228699</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">3.2322850227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27656292915344</t>
+    <t xml:space="preserve">3.27656269073486</t>
   </si>
   <si>
     <t xml:space="preserve">3.32969617843628</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">3.48909664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53337454795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59536337852478</t>
+    <t xml:space="preserve">3.53337430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59536361694336</t>
   </si>
   <si>
     <t xml:space="preserve">3.5599410533905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4979522228241</t>
+    <t xml:space="preserve">3.49795198440552</t>
   </si>
   <si>
     <t xml:space="preserve">3.46252989768982</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">3.36511850357056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41825175285339</t>
+    <t xml:space="preserve">3.41825199127197</t>
   </si>
   <si>
     <t xml:space="preserve">3.3828296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44481897354126</t>
+    <t xml:space="preserve">3.44481873512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.45367431640625</t>
@@ -2123,13 +2123,13 @@
     <t xml:space="preserve">3.39168524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24999618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08174014091492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14372897148132</t>
+    <t xml:space="preserve">3.24999594688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08173990249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1437292098999</t>
   </si>
   <si>
     <t xml:space="preserve">3.11716246604919</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">3.09059548377991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88691759109497</t>
+    <t xml:space="preserve">2.88691735267639</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890642166138</t>
@@ -2147,31 +2147,31 @@
     <t xml:space="preserve">2.84263968467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86920619010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74522829055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65667271614075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56811690330505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78950643539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75408387184143</t>
+    <t xml:space="preserve">2.86920642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74522805213928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65667247772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56811666488647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78950619697571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75408363342285</t>
   </si>
   <si>
     <t xml:space="preserve">2.72751688957214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6832389831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82492828369141</t>
+    <t xml:space="preserve">2.68323922157288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82492852210999</t>
   </si>
   <si>
     <t xml:space="preserve">2.80721735954285</t>
@@ -2180,19 +2180,19 @@
     <t xml:space="preserve">2.79836177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83378434181213</t>
+    <t xml:space="preserve">2.83378410339355</t>
   </si>
   <si>
     <t xml:space="preserve">2.97547316551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99318432807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06402921676636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07288455963135</t>
+    <t xml:space="preserve">2.9931845664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0640287399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07288432121277</t>
   </si>
   <si>
     <t xml:space="preserve">3.01975131034851</t>
@@ -2207,7 +2207,7 @@
     <t xml:space="preserve">2.94005084037781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01089549064636</t>
+    <t xml:space="preserve">3.01089572906494</t>
   </si>
   <si>
     <t xml:space="preserve">3.04631781578064</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">2.98432874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96661782264709</t>
+    <t xml:space="preserve">2.96661758422852</t>
   </si>
   <si>
     <t xml:space="preserve">2.90462851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203990936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93119549751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78065037727356</t>
+    <t xml:space="preserve">3.00204014778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93119525909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78065061569214</t>
   </si>
   <si>
     <t xml:space="preserve">2.70980596542358</t>
@@ -2237,25 +2237,25 @@
     <t xml:space="preserve">2.77179503440857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81607270240784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8780620098114</t>
+    <t xml:space="preserve">2.81607294082642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87806177139282</t>
   </si>
   <si>
     <t xml:space="preserve">3.0286066532135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05517339706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17029571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19686269760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24114036560059</t>
+    <t xml:space="preserve">3.05517315864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17029595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19686245918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24114060401917</t>
   </si>
   <si>
     <t xml:space="preserve">3.25885152816772</t>
@@ -2264,22 +2264,22 @@
     <t xml:space="preserve">3.16144037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37397384643555</t>
+    <t xml:space="preserve">3.37397408485413</t>
   </si>
   <si>
     <t xml:space="preserve">3.40054082870483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47138524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50680780410767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60421895980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078570365906</t>
+    <t xml:space="preserve">3.47138547897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50680756568909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60421943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63078594207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.62193059921265</t>
@@ -2297,13 +2297,13 @@
     <t xml:space="preserve">3.72270464897156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77785587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69512867927551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70432114601135</t>
+    <t xml:space="preserve">3.77785563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69512891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70432090759277</t>
   </si>
   <si>
     <t xml:space="preserve">3.78704738616943</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">3.8146231174469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76866364479065</t>
+    <t xml:space="preserve">3.76866388320923</t>
   </si>
   <si>
     <t xml:space="preserve">3.75028014183044</t>
@@ -2324,19 +2324,16 @@
     <t xml:space="preserve">3.63997769355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64916944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66755342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62159419059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53886699676514</t>
+    <t xml:space="preserve">3.64916968345642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66755318641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62159395217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53886723518372</t>
   </si>
   <si>
     <t xml:space="preserve">3.5572509765625</t>
@@ -2351,10 +2348,10 @@
     <t xml:space="preserve">3.52048349380493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4561402797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49290776252747</t>
+    <t xml:space="preserve">3.45614051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49290800094604</t>
   </si>
   <si>
     <t xml:space="preserve">3.56644296646118</t>
@@ -2366,19 +2363,19 @@
     <t xml:space="preserve">3.60321021080017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51129174232483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85139060020447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84219837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90654182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86058211326599</t>
+    <t xml:space="preserve">3.51129150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85139083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84219861030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90654158592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86058235168457</t>
   </si>
   <si>
     <t xml:space="preserve">3.68593716621399</t>
@@ -2387,7 +2384,7 @@
     <t xml:space="preserve">3.74108839035034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58482670783997</t>
+    <t xml:space="preserve">3.58482646942139</t>
   </si>
   <si>
     <t xml:space="preserve">3.65836143493652</t>
@@ -2396,7 +2393,7 @@
     <t xml:space="preserve">3.47452425956726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46533250808716</t>
+    <t xml:space="preserve">3.46533226966858</t>
   </si>
   <si>
     <t xml:space="preserve">3.50209975242615</t>
@@ -2408,7 +2405,7 @@
     <t xml:space="preserve">3.94330906867981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9157338142395</t>
+    <t xml:space="preserve">3.91573357582092</t>
   </si>
   <si>
     <t xml:space="preserve">3.95250105857849</t>
@@ -2417,25 +2414,25 @@
     <t xml:space="preserve">3.92492532730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98926877975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83300685882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96169257164001</t>
+    <t xml:space="preserve">3.98926854133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83300709724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96169281005859</t>
   </si>
   <si>
     <t xml:space="preserve">3.87896609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93411755561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97088503837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98007678985596</t>
+    <t xml:space="preserve">3.93411731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97088479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98007655143738</t>
   </si>
   <si>
     <t xml:space="preserve">3.823814868927</t>
@@ -2444,13 +2441,13 @@
     <t xml:space="preserve">3.79623937606812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88815808296204</t>
+    <t xml:space="preserve">3.88815784454346</t>
   </si>
   <si>
     <t xml:space="preserve">3.86977458000183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89734983444214</t>
+    <t xml:space="preserve">3.89734935760498</t>
   </si>
   <si>
     <t xml:space="preserve">4.13633823394775</t>
@@ -2474,7 +2471,7 @@
     <t xml:space="preserve">4.20068168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42128562927246</t>
+    <t xml:space="preserve">4.42128610610962</t>
   </si>
   <si>
     <t xml:space="preserve">4.66946649551392</t>
@@ -2492,13 +2489,13 @@
     <t xml:space="preserve">4.81653594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9636058807373</t>
+    <t xml:space="preserve">4.96360635757446</t>
   </si>
   <si>
     <t xml:space="preserve">4.85330390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76138496398926</t>
+    <t xml:space="preserve">4.7613844871521</t>
   </si>
   <si>
     <t xml:space="preserve">4.5867395401001</t>
@@ -2522,7 +2519,7 @@
     <t xml:space="preserve">4.90845489501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89007091522217</t>
+    <t xml:space="preserve">4.89007139205933</t>
   </si>
   <si>
     <t xml:space="preserve">5.16600561141968</t>
@@ -52973,7 +52970,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1909" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -52999,7 +52996,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1910" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -53025,7 +53022,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1911" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53051,7 +53048,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1912" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -53077,7 +53074,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1913" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -53103,7 +53100,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1914" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -53129,7 +53126,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1915" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -53155,7 +53152,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1916" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -53181,7 +53178,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1917" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -53207,7 +53204,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1918" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -53233,7 +53230,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1919" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -53259,7 +53256,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1920" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -53285,7 +53282,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1921" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -53311,7 +53308,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1922" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -53337,7 +53334,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1923" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -53363,7 +53360,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1924" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -53389,7 +53386,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1925" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -53415,7 +53412,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1926" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -53441,7 +53438,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1927" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -53467,7 +53464,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1928" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -53519,7 +53516,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G1930" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -53545,7 +53542,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1931" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -53571,7 +53568,7 @@
         <v>4.25</v>
       </c>
       <c r="G1932" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -53623,7 +53620,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G1934" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -53649,7 +53646,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G1935" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -53675,7 +53672,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G1936" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -53857,7 +53854,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1943" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -53909,7 +53906,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1945" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -53935,7 +53932,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1946" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -54247,7 +54244,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1958" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54273,7 +54270,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1959" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -54299,7 +54296,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1960" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -54325,7 +54322,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1961" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -54351,7 +54348,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1962" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -54377,7 +54374,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1963" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -54403,7 +54400,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1964" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -54429,7 +54426,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1965" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -54455,7 +54452,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1966" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -54481,7 +54478,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1967" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -54507,7 +54504,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1968" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -54533,7 +54530,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1969" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -54559,7 +54556,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1970" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -54585,7 +54582,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1971" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -54611,7 +54608,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1972" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -54637,7 +54634,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1973" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -54663,7 +54660,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1974" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -54689,7 +54686,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1975" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -54715,7 +54712,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1976" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -54741,7 +54738,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1977" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -54767,7 +54764,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1978" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -54793,7 +54790,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1979" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -54819,7 +54816,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1980" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -54845,7 +54842,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1981" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -54871,7 +54868,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1982" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54897,7 +54894,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1983" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -54923,7 +54920,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1984" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -54949,7 +54946,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1985" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -54975,7 +54972,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1986" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55001,7 +54998,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1987" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -55027,7 +55024,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1988" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -55053,7 +55050,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1989" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -55079,7 +55076,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1990" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -55105,7 +55102,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1991" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -55131,7 +55128,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1992" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -55157,7 +55154,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55209,7 +55206,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1995" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -55235,7 +55232,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1996" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -55287,7 +55284,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1998" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -55313,7 +55310,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1999" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -55443,7 +55440,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2004" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -55599,7 +55596,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G2010" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -55625,7 +55622,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G2011" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -55677,7 +55674,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2013" t="s">
-        <v>772</v>
+        <v>755</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55963,7 +55960,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G2024" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -56067,7 +56064,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2028" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -56171,7 +56168,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2032" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -56223,7 +56220,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G2034" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -56249,7 +56246,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2035" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -56275,7 +56272,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2036" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -56301,7 +56298,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2037" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -56327,7 +56324,7 @@
         <v>4.26000022888184</v>
       </c>
       <c r="G2038" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -56353,7 +56350,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G2039" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -56379,7 +56376,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2040" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -56405,7 +56402,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2041" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -56431,7 +56428,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2042" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -56457,7 +56454,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2043" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -56509,7 +56506,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2045" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -56535,7 +56532,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2046" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -56561,7 +56558,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2047" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -56587,7 +56584,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2048" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -56613,7 +56610,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2049" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -56639,7 +56636,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G2050" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -56665,7 +56662,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2051" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -56691,7 +56688,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G2052" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -56717,7 +56714,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2053" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -56743,7 +56740,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2054" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -56769,7 +56766,7 @@
         <v>4.30999994277954</v>
       </c>
       <c r="G2055" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -56795,7 +56792,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2056" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -56821,7 +56818,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G2057" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -56847,7 +56844,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2058" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -56873,7 +56870,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G2059" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -56899,7 +56896,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G2060" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -56925,7 +56922,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G2061" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -56951,7 +56948,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2062" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -56977,7 +56974,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2063" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -57003,7 +57000,7 @@
         <v>4.26999998092651</v>
       </c>
       <c r="G2064" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -57029,7 +57026,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2065" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -57055,7 +57052,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G2066" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -57081,7 +57078,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2067" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -57107,7 +57104,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2068" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -57159,7 +57156,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2070" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -57185,7 +57182,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G2071" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -57263,7 +57260,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2074" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -57289,7 +57286,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G2075" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -57367,7 +57364,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2078" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -57393,7 +57390,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G2079" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -57419,7 +57416,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2080" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -57445,7 +57442,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G2081" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -57471,7 +57468,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2082" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -57497,7 +57494,7 @@
         <v>4.23999977111816</v>
       </c>
       <c r="G2083" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -57523,7 +57520,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2084" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -57549,7 +57546,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2085" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -57575,7 +57572,7 @@
         <v>4.19999980926514</v>
       </c>
       <c r="G2086" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -57601,7 +57598,7 @@
         <v>4.32999992370605</v>
       </c>
       <c r="G2087" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -57627,7 +57624,7 @@
         <v>4.5</v>
       </c>
       <c r="G2088" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -57653,7 +57650,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G2089" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -57679,7 +57676,7 @@
         <v>4.59000015258789</v>
       </c>
       <c r="G2090" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -57705,7 +57702,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2091" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -57731,7 +57728,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G2092" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -57757,7 +57754,7 @@
         <v>4.51000022888184</v>
       </c>
       <c r="G2093" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -57783,7 +57780,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G2094" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -57809,7 +57806,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G2095" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -57835,7 +57832,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2096" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -57861,7 +57858,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G2097" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -57887,7 +57884,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2098" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -57913,7 +57910,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2099" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -57939,7 +57936,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2100" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -57965,7 +57962,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2101" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -57991,7 +57988,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2102" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -58017,7 +58014,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2103" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -58043,7 +58040,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2104" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -58069,7 +58066,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2105" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -58095,7 +58092,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2106" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -58121,7 +58118,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2107" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -58147,7 +58144,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2108" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -58173,7 +58170,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2109" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -58199,7 +58196,7 @@
         <v>4.98999977111816</v>
       </c>
       <c r="G2110" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -58225,7 +58222,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G2111" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -58251,7 +58248,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G2112" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -58277,7 +58274,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2113" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -58303,7 +58300,7 @@
         <v>5.1399998664856</v>
       </c>
       <c r="G2114" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -58329,7 +58326,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2115" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -58355,7 +58352,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2116" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -58381,7 +58378,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G2117" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -58407,7 +58404,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2118" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -58433,7 +58430,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2119" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -58459,7 +58456,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2120" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -58485,7 +58482,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2121" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -58511,7 +58508,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2122" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -58537,7 +58534,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2123" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -58563,7 +58560,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2124" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -58589,7 +58586,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2125" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -58615,7 +58612,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2126" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58641,7 +58638,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2127" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -58667,7 +58664,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2128" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -58693,7 +58690,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2129" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -58719,7 +58716,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2130" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -58745,7 +58742,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2131" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -58771,7 +58768,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2132" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -58797,7 +58794,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2133" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -58823,7 +58820,7 @@
         <v>5.19999980926514</v>
       </c>
       <c r="G2134" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -58849,7 +58846,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2135" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -58875,7 +58872,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2136" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -58901,7 +58898,7 @@
         <v>5.23999977111816</v>
       </c>
       <c r="G2137" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -58927,7 +58924,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2138" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -58953,7 +58950,7 @@
         <v>5.21999979019165</v>
       </c>
       <c r="G2139" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -58979,7 +58976,7 @@
         <v>5.28000020980835</v>
       </c>
       <c r="G2140" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -59005,7 +59002,7 @@
         <v>5.34000015258789</v>
       </c>
       <c r="G2141" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -59031,7 +59028,7 @@
         <v>5.30000019073486</v>
       </c>
       <c r="G2142" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -59057,7 +59054,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2143" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -59083,7 +59080,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2144" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -59109,7 +59106,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2145" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -59135,7 +59132,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G2146" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -59161,7 +59158,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G2147" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -59187,7 +59184,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G2148" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -59213,7 +59210,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2149" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -59239,7 +59236,7 @@
         <v>5.3600001335144</v>
       </c>
       <c r="G2150" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -59265,7 +59262,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2151" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -59291,7 +59288,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2152" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -59317,7 +59314,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2153" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -59343,7 +59340,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2154" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -59369,7 +59366,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2155" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -59395,7 +59392,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2156" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -59421,7 +59418,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2157" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -59447,7 +59444,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2158" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -59473,7 +59470,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2159" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -59499,7 +59496,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2160" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -59525,7 +59522,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2161" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -59551,7 +59548,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2162" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -59577,7 +59574,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2163" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -59603,7 +59600,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2164" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -59629,7 +59626,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2165" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -59655,7 +59652,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2166" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -59681,7 +59678,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2167" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -59707,7 +59704,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2168" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -59733,7 +59730,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2169" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -59759,7 +59756,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2170" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -59785,7 +59782,7 @@
         <v>5.55999994277954</v>
       </c>
       <c r="G2171" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -59811,7 +59808,7 @@
         <v>5.5</v>
       </c>
       <c r="G2172" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -59837,7 +59834,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G2173" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -59863,7 +59860,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2174" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -59889,7 +59886,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2175" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -59915,7 +59912,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2176" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -59941,7 +59938,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2177" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -59967,7 +59964,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2178" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -59993,7 +59990,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2179" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -60019,7 +60016,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2180" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -60045,7 +60042,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2181" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -60071,7 +60068,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2182" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -60097,7 +60094,7 @@
         <v>5.32000017166138</v>
       </c>
       <c r="G2183" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -60123,7 +60120,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G2184" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -60149,7 +60146,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2185" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -60175,7 +60172,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2186" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -60201,7 +60198,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2187" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -60227,7 +60224,7 @@
         <v>5.57999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -60253,7 +60250,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2189" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -60279,7 +60276,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2190" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -60305,7 +60302,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2191" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -60331,7 +60328,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2192" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -60357,7 +60354,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2193" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -60383,7 +60380,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2194" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -60409,7 +60406,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2195" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -60435,7 +60432,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2196" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -60461,7 +60458,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2197" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -60487,7 +60484,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2198" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -60513,7 +60510,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2199" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -60539,7 +60536,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2200" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -60565,7 +60562,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2201" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -60591,7 +60588,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2202" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -60617,7 +60614,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2203" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -60643,7 +60640,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2204" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -60669,7 +60666,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -60695,7 +60692,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2206" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -60721,7 +60718,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2207" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -60747,7 +60744,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G2208" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -60773,7 +60770,7 @@
         <v>5.71999979019165</v>
       </c>
       <c r="G2209" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -60799,7 +60796,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2210" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -60825,7 +60822,7 @@
         <v>5.59999990463257</v>
       </c>
       <c r="G2211" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -60851,7 +60848,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2212" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -60877,7 +60874,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2213" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -60903,7 +60900,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2214" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -60929,7 +60926,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2215" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -60955,7 +60952,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2216" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -60981,7 +60978,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2217" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -61007,7 +61004,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2218" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -61033,7 +61030,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G2219" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -61059,7 +61056,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2220" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -61085,7 +61082,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2221" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -61111,7 +61108,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2222" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -61137,7 +61134,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2223" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -61163,7 +61160,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2224" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -61189,7 +61186,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2225" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -61215,7 +61212,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -61241,7 +61238,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G2227" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -61267,7 +61264,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G2228" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -61293,7 +61290,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2229" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -61319,7 +61316,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2230" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -61345,7 +61342,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G2231" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -61371,7 +61368,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2232" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -61397,7 +61394,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G2233" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -61423,7 +61420,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G2234" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -61449,7 +61446,7 @@
         <v>5.73999977111816</v>
       </c>
       <c r="G2235" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -61475,7 +61472,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G2236" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -61501,7 +61498,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G2237" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -61527,7 +61524,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2238" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -61553,7 +61550,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2239" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -61579,7 +61576,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2240" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -61605,7 +61602,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2241" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -61631,7 +61628,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G2242" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -61657,7 +61654,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2243" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -61683,7 +61680,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G2244" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -61709,7 +61706,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G2245" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -61735,7 +61732,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G2246" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -61761,7 +61758,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -61787,7 +61784,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G2248" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -61813,7 +61810,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G2249" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -61839,7 +61836,7 @@
         <v>6.05999994277954</v>
       </c>
       <c r="G2250" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -61865,7 +61862,7 @@
         <v>6</v>
       </c>
       <c r="G2251" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -61891,7 +61888,7 @@
         <v>6.07999992370605</v>
       </c>
       <c r="G2252" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -61917,7 +61914,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G2253" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -61943,7 +61940,7 @@
         <v>6</v>
       </c>
       <c r="G2254" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -61969,7 +61966,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G2255" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -61995,7 +61992,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G2256" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -62021,7 +62018,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2257" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -62047,7 +62044,7 @@
         <v>6.21999979019165</v>
       </c>
       <c r="G2258" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -62073,7 +62070,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2259" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -62099,7 +62096,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G2260" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -62125,7 +62122,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2261" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -62151,7 +62148,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G2262" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -62177,7 +62174,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2263" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -62203,7 +62200,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2264" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -62229,7 +62226,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2265" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -62255,7 +62252,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2266" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -62281,7 +62278,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2267" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -62307,7 +62304,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2268" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -62333,7 +62330,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2269" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -62359,7 +62356,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2270" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -62385,7 +62382,7 @@
         <v>6.32000017166138</v>
       </c>
       <c r="G2271" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -62411,7 +62408,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2272" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -62437,7 +62434,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2273" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -62463,7 +62460,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G2274" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -62489,7 +62486,7 @@
         <v>6.26000022888184</v>
       </c>
       <c r="G2275" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -62515,7 +62512,7 @@
         <v>6.30000019073486</v>
       </c>
       <c r="G2276" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -62541,7 +62538,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G2277" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -62567,7 +62564,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G2278" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -62593,7 +62590,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G2279" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -62619,7 +62616,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2280" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -62645,7 +62642,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G2281" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -62671,7 +62668,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G2282" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -62697,7 +62694,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2283" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -62723,7 +62720,7 @@
         <v>6.38000011444092</v>
       </c>
       <c r="G2284" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -62749,7 +62746,7 @@
         <v>6.34000015258789</v>
       </c>
       <c r="G2285" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -62775,7 +62772,7 @@
         <v>6.5</v>
       </c>
       <c r="G2286" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -62801,7 +62798,7 @@
         <v>6.5</v>
       </c>
       <c r="G2287" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -62827,7 +62824,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G2288" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -62853,7 +62850,7 @@
         <v>6.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -62879,7 +62876,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G2290" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -62905,7 +62902,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2291" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -62931,7 +62928,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2292" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -62957,7 +62954,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2293" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -62983,7 +62980,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G2294" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -63009,7 +63006,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G2295" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -63035,7 +63032,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2296" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -63061,7 +63058,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G2297" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -63087,7 +63084,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G2298" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -63113,7 +63110,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2299" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -63139,7 +63136,7 @@
         <v>6.67999982833862</v>
       </c>
       <c r="G2300" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -63165,7 +63162,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G2301" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -63191,7 +63188,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2302" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -63217,7 +63214,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2303" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -63243,7 +63240,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2304" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -63269,7 +63266,7 @@
         <v>7</v>
       </c>
       <c r="G2305" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -63295,7 +63292,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2306" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -63321,7 +63318,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2307" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -63347,7 +63344,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G2308" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -63373,7 +63370,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2309" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -63399,7 +63396,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2310" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -63425,7 +63422,7 @@
         <v>7</v>
       </c>
       <c r="G2311" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -63451,7 +63448,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2312" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -63477,7 +63474,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2313" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -63503,7 +63500,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2314" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -63529,7 +63526,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2315" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -63555,7 +63552,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2316" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -63581,7 +63578,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2317" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -63607,7 +63604,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2318" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -63633,7 +63630,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2319" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -63659,7 +63656,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2320" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -63685,7 +63682,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2321" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -63711,7 +63708,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2322" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -63737,7 +63734,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2323" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -63763,7 +63760,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2324" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -63789,7 +63786,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2325" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -63815,7 +63812,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2326" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -63841,7 +63838,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2327" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -63867,7 +63864,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2328" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -63893,7 +63890,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G2329" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -63919,7 +63916,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2330" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -63945,7 +63942,7 @@
         <v>7.28000020980835</v>
       </c>
       <c r="G2331" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -63971,7 +63968,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2332" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -63997,7 +63994,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2333" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -64023,7 +64020,7 @@
         <v>7.5</v>
       </c>
       <c r="G2334" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -64049,7 +64046,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2335" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -64075,7 +64072,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2336" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -64101,7 +64098,7 @@
         <v>7.5</v>
       </c>
       <c r="G2337" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -64127,7 +64124,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2338" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -64153,7 +64150,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2339" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -64179,7 +64176,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2340" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -64205,7 +64202,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G2341" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -64231,7 +64228,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G2342" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -64257,7 +64254,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G2343" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -64283,7 +64280,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2344" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -64309,7 +64306,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G2345" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -64335,7 +64332,7 @@
         <v>7.5</v>
       </c>
       <c r="G2346" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -64361,7 +64358,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2347" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -64387,7 +64384,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2348" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -64413,7 +64410,7 @@
         <v>7.5</v>
       </c>
       <c r="G2349" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -64439,7 +64436,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G2350" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -64465,7 +64462,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G2351" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -64491,7 +64488,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2352" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -64517,7 +64514,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2353" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -64543,7 +64540,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2354" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -64569,7 +64566,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2355" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -64595,7 +64592,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G2356" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -64621,7 +64618,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G2357" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -64647,7 +64644,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2358" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -64673,7 +64670,7 @@
         <v>6.42000007629395</v>
       </c>
       <c r="G2359" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -64699,7 +64696,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G2360" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -64725,7 +64722,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G2361" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -64751,7 +64748,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2362" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -64777,7 +64774,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2363" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -64803,7 +64800,7 @@
         <v>6.76000022888184</v>
       </c>
       <c r="G2364" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -64829,7 +64826,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G2365" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -64855,7 +64852,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G2366" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -64881,7 +64878,7 @@
         <v>6.73999977111816</v>
       </c>
       <c r="G2367" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -64907,7 +64904,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G2368" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -64933,7 +64930,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2369" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -64959,7 +64956,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2370" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -64985,7 +64982,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2371" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -65011,7 +65008,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2372" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -65037,7 +65034,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2373" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -65063,7 +65060,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2374" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -65089,7 +65086,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2375" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -65115,7 +65112,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2376" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -65141,7 +65138,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G2377" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -65167,7 +65164,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2378" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -65193,7 +65190,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2379" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -65219,7 +65216,7 @@
         <v>7.42000007629395</v>
       </c>
       <c r="G2380" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -65245,7 +65242,7 @@
         <v>7.44000005722046</v>
       </c>
       <c r="G2381" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -65271,7 +65268,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2382" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -65297,7 +65294,7 @@
         <v>7.46000003814697</v>
       </c>
       <c r="G2383" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -65323,7 +65320,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2384" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -65349,7 +65346,7 @@
         <v>7.48000001907349</v>
       </c>
       <c r="G2385" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -65375,7 +65372,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2386" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -65401,7 +65398,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2387" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -65427,7 +65424,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2388" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -65453,7 +65450,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2389" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -65479,7 +65476,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G2390" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -65505,7 +65502,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2391" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -65531,7 +65528,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2392" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -65557,7 +65554,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2393" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -65583,7 +65580,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2394" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -65609,7 +65606,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2395" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -65635,7 +65632,7 @@
         <v>6.80000019073486</v>
       </c>
       <c r="G2396" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -65661,7 +65658,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2397" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -65687,7 +65684,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2398" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -65713,7 +65710,7 @@
         <v>7.21999979019165</v>
       </c>
       <c r="G2399" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -65739,7 +65736,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2400" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -65765,7 +65762,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2401" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -65791,7 +65788,7 @@
         <v>6.98000001907349</v>
       </c>
       <c r="G2402" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -65817,7 +65814,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2403" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -65843,7 +65840,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2404" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -65869,7 +65866,7 @@
         <v>7</v>
       </c>
       <c r="G2405" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -65895,7 +65892,7 @@
         <v>6.92000007629395</v>
       </c>
       <c r="G2406" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -65921,7 +65918,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G2407" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -65947,7 +65944,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2408" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -65973,7 +65970,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2409" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -65999,7 +65996,7 @@
         <v>6.96000003814697</v>
       </c>
       <c r="G2410" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -66025,7 +66022,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2411" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -66051,7 +66048,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2412" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -66077,7 +66074,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2413" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -66103,7 +66100,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2414" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -66129,7 +66126,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2415" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -66155,7 +66152,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2416" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -66181,7 +66178,7 @@
         <v>7.19999980926514</v>
       </c>
       <c r="G2417" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -66207,7 +66204,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2418" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -66233,7 +66230,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2419" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -66259,7 +66256,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2420" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -66285,7 +66282,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2421" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -66311,7 +66308,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G2422" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -66337,7 +66334,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2423" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -66363,7 +66360,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2424" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -66389,7 +66386,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2425" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -66415,7 +66412,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2426" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -66441,7 +66438,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2427" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -66467,7 +66464,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2428" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -66493,7 +66490,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2429" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -66519,7 +66516,7 @@
         <v>7.05999994277954</v>
       </c>
       <c r="G2430" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -66545,7 +66542,7 @@
         <v>7</v>
       </c>
       <c r="G2431" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -66571,7 +66568,7 @@
         <v>7</v>
       </c>
       <c r="G2432" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -66597,7 +66594,7 @@
         <v>7</v>
       </c>
       <c r="G2433" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -66623,7 +66620,7 @@
         <v>7</v>
       </c>
       <c r="G2434" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -66649,7 +66646,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G2435" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -66675,7 +66672,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2436" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -66701,7 +66698,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2437" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -66727,7 +66724,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2438" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -66753,7 +66750,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2439" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -66779,7 +66776,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2440" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -66805,7 +66802,7 @@
         <v>7.15999984741211</v>
       </c>
       <c r="G2441" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -66831,7 +66828,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G2442" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -66857,7 +66854,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G2443" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -66883,7 +66880,7 @@
         <v>7.03999996185303</v>
       </c>
       <c r="G2444" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -66909,7 +66906,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G2445" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -66935,7 +66932,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G2446" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -66961,7 +66958,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G2447" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -66987,7 +66984,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2448" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -67013,7 +67010,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2449" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -67039,7 +67036,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2450" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -67065,7 +67062,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2451" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -67091,7 +67088,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2452" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -67117,7 +67114,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2453" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -67143,7 +67140,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2454" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -67169,7 +67166,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G2455" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -67195,7 +67192,7 @@
         <v>7.38000011444092</v>
       </c>
       <c r="G2456" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -67221,7 +67218,7 @@
         <v>7.3600001335144</v>
       </c>
       <c r="G2457" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -67247,7 +67244,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G2458" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -67273,7 +67270,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G2459" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -67299,7 +67296,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G2460" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -67325,7 +67322,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G2461" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -67351,7 +67348,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G2462" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -67377,7 +67374,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G2463" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -67403,7 +67400,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2464" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -67429,7 +67426,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2465" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -67455,7 +67452,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G2466" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -67481,7 +67478,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G2467" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -67507,7 +67504,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G2468" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -67533,7 +67530,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2469" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -67559,7 +67556,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2470" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -67585,7 +67582,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2471" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -67611,7 +67608,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2472" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -67637,7 +67634,7 @@
         <v>8.5</v>
       </c>
       <c r="G2473" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -67663,7 +67660,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G2474" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -67689,7 +67686,7 @@
         <v>8.5</v>
       </c>
       <c r="G2475" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -67715,7 +67712,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G2476" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -67741,7 +67738,7 @@
         <v>8.5</v>
       </c>
       <c r="G2477" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -67767,7 +67764,7 @@
         <v>8.46000003814697</v>
       </c>
       <c r="G2478" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -67793,7 +67790,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G2479" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -67819,7 +67816,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2480" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -67845,7 +67842,7 @@
         <v>8.4399995803833</v>
       </c>
       <c r="G2481" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -67871,7 +67868,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G2482" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -67897,7 +67894,7 @@
         <v>8.53999996185303</v>
       </c>
       <c r="G2483" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -67923,7 +67920,7 @@
         <v>8.61999988555908</v>
       </c>
       <c r="G2484" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -67949,7 +67946,7 @@
         <v>8.5</v>
       </c>
       <c r="G2485" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -67975,7 +67972,7 @@
         <v>9</v>
       </c>
       <c r="G2486" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -68001,7 +67998,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2487" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -68027,7 +68024,7 @@
         <v>8.77999973297119</v>
       </c>
       <c r="G2488" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -68053,7 +68050,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2489" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -68079,7 +68076,7 @@
         <v>9</v>
       </c>
       <c r="G2490" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -68105,7 +68102,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2491" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -68131,7 +68128,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G2492" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -68157,7 +68154,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G2493" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -68183,7 +68180,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2494" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -68209,7 +68206,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2495" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -68235,7 +68232,7 @@
         <v>8.9399995803833</v>
       </c>
       <c r="G2496" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -68261,7 +68258,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G2497" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -68287,7 +68284,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2498" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -68313,7 +68310,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G2499" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -68339,7 +68336,7 @@
         <v>9</v>
       </c>
       <c r="G2500" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -68365,7 +68362,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2501" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -68391,7 +68388,7 @@
         <v>9</v>
       </c>
       <c r="G2502" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -68417,7 +68414,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2503" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -68443,7 +68440,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2504" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -68469,7 +68466,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2505" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -68495,7 +68492,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2506" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -68521,7 +68518,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G2507" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -68547,7 +68544,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G2508" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -68573,7 +68570,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G2509" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -68599,7 +68596,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2510" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -68625,7 +68622,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2511" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -68651,7 +68648,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2512" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -68677,7 +68674,7 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2513" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -68703,7 +68700,7 @@
         <v>8.76000022888184</v>
       </c>
       <c r="G2514" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -68729,7 +68726,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G2515" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -68755,7 +68752,7 @@
         <v>8.89999961853027</v>
       </c>
       <c r="G2516" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -68781,7 +68778,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2517" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -68807,7 +68804,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2518" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2518" t="s">
         <v>9</v>
@@ -68833,7 +68830,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2519" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2519" t="s">
         <v>9</v>
@@ -68859,7 +68856,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G2520" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="H2520" t="s">
         <v>9</v>
@@ -68885,7 +68882,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G2521" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H2521" t="s">
         <v>9</v>
@@ -68911,7 +68908,7 @@
         <v>8.97999954223633</v>
       </c>
       <c r="G2522" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H2522" t="s">
         <v>9</v>
@@ -68937,7 +68934,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2523" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2523" t="s">
         <v>9</v>
@@ -68963,7 +68960,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2524" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2524" t="s">
         <v>9</v>
@@ -68989,7 +68986,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G2525" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="H2525" t="s">
         <v>9</v>
@@ -69015,7 +69012,7 @@
         <v>8.85999965667725</v>
       </c>
       <c r="G2526" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="H2526" t="s">
         <v>9</v>
@@ -69041,7 +69038,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G2527" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H2527" t="s">
         <v>9</v>
@@ -69067,7 +69064,7 @@
         <v>9</v>
       </c>
       <c r="G2528" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H2528" t="s">
         <v>9</v>
@@ -69093,7 +69090,7 @@
         <v>9.03999996185303</v>
       </c>
       <c r="G2529" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H2529" t="s">
         <v>9</v>
@@ -69119,7 +69116,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G2530" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H2530" t="s">
         <v>9</v>
@@ -69145,7 +69142,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G2531" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="H2531" t="s">
         <v>9</v>
@@ -69171,7 +69168,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2532" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2532" t="s">
         <v>9</v>
@@ -69197,7 +69194,7 @@
         <v>8.96000003814697</v>
       </c>
       <c r="G2533" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H2533" t="s">
         <v>9</v>
@@ -69205,7 +69202,7 @@
     </row>
     <row r="2534">
       <c r="A2534" s="1" t="n">
-        <v>46007.6920023148</v>
+        <v>46007.3333333333</v>
       </c>
       <c r="B2534" t="n">
         <v>21225</v>
@@ -69223,9 +69220,35 @@
         <v>8.88000011444092</v>
       </c>
       <c r="G2534" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H2534" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2535">
+      <c r="A2535" s="1" t="n">
+        <v>46008.6912152778</v>
+      </c>
+      <c r="B2535" t="n">
+        <v>25946</v>
+      </c>
+      <c r="C2535" t="n">
+        <v>9.10000038146973</v>
+      </c>
+      <c r="D2535" t="n">
+        <v>8.81999969482422</v>
+      </c>
+      <c r="E2535" t="n">
+        <v>8.88000011444092</v>
+      </c>
+      <c r="F2535" t="n">
+        <v>9</v>
+      </c>
+      <c r="G2535" t="s">
+        <v>977</v>
+      </c>
+      <c r="H2535" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="1000">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="1001">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,28 +47,28 @@
     <t xml:space="preserve">1.74400746822357</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71406757831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167223453522</t>
+    <t xml:space="preserve">1.71406781673431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167259216309</t>
   </si>
   <si>
     <t xml:space="preserve">1.67215144634247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969658851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921773433685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57334959506989</t>
+    <t xml:space="preserve">1.64969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921737670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5733494758606</t>
   </si>
   <si>
     <t xml:space="preserve">1.49625384807587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48053538799286</t>
+    <t xml:space="preserve">1.48053514957428</t>
   </si>
   <si>
     <t xml:space="preserve">1.48203229904175</t>
@@ -77,16 +77,16 @@
     <t xml:space="preserve">1.43637371063232</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44460713863373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42215204238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990673542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4146671295166</t>
+    <t xml:space="preserve">1.44460725784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42215216159821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41466724872589</t>
   </si>
   <si>
     <t xml:space="preserve">1.41915822029114</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">1.40718221664429</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38248157501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38472723960876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.39820027351379</t>
+    <t xml:space="preserve">1.3824816942215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38472712039948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3982001543045</t>
   </si>
   <si>
     <t xml:space="preserve">1.35703253746033</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">1.34730195999146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3428111076355</t>
+    <t xml:space="preserve">1.34281122684479</t>
   </si>
   <si>
     <t xml:space="preserve">1.38397860527039</t>
   </si>
   <si>
-    <t xml:space="preserve">1.35478711128235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38098478317261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36975717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873911857605</t>
+    <t xml:space="preserve">1.35478699207306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38098454475403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36975729465485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873923778534</t>
   </si>
   <si>
     <t xml:space="preserve">1.4311341047287</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">1.41017603874207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44535553455353</t>
+    <t xml:space="preserve">1.44535577297211</t>
   </si>
   <si>
     <t xml:space="preserve">1.46257138252258</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">1.52245140075684</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54490637779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.541912317276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54939723014832</t>
+    <t xml:space="preserve">1.54490625858307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191243648529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54939746856689</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287038326263</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">1.60029542446136</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60927760601044</t>
+    <t xml:space="preserve">1.60927772521973</t>
   </si>
   <si>
     <t xml:space="preserve">1.63173258304596</t>
@@ -176,172 +176,172 @@
     <t xml:space="preserve">1.62424755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63023555278778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676251888275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418744087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64370858669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682227134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58831965923309</t>
+    <t xml:space="preserve">1.63023567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676228046417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418756008148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370846748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682250976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58831942081451</t>
   </si>
   <si>
     <t xml:space="preserve">1.63472652435303</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66017544269562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915774345398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712151050568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69161283969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69310975074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155284881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502564430237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358860492706</t>
+    <t xml:space="preserve">1.66017532348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66915762424469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712174892426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69161260128021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6931095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155272960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502576351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358872413635</t>
   </si>
   <si>
     <t xml:space="preserve">1.70658254623413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69909763336182</t>
+    <t xml:space="preserve">1.69909751415253</t>
   </si>
   <si>
     <t xml:space="preserve">1.67664241790771</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68412744998932</t>
+    <t xml:space="preserve">1.68412733078003</t>
   </si>
   <si>
     <t xml:space="preserve">1.66766047477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68263053894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221143722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6467022895813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67514562606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69964468479156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68433260917664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69198882579803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7210818529129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70576965808868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6950511932373</t>
+    <t xml:space="preserve">1.68263030052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221155643463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64670252799988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67514550685883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69964504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68433284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69198906421661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72108149528503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70576977729797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69505131244659</t>
   </si>
   <si>
     <t xml:space="preserve">1.71495687961578</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72261297702789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65370857715607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208313941956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66902077198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6521772146225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60624098777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56183588504791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5541797876358</t>
+    <t xml:space="preserve">1.72261333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65370845794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208325862885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66902101039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65217745304108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.606241106987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56183576583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417990684509</t>
   </si>
   <si>
     <t xml:space="preserve">1.52202451229095</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121185302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59092891216278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5289146900177</t>
+    <t xml:space="preserve">1.53121173381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59092903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52891492843628</t>
   </si>
   <si>
     <t xml:space="preserve">1.55111742019653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53886771202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4929313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4760879278183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52279007434845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996307373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761917114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51589953899384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5005875825882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6077721118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59705364704132</t>
+    <t xml:space="preserve">1.53886759281158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49293148517609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608816623688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52278983592987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996319293976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761905193329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51589965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058734416962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60777199268341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5970538854599</t>
   </si>
   <si>
     <t xml:space="preserve">1.56949198246002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62308418750763</t>
+    <t xml:space="preserve">1.62308430671692</t>
   </si>
   <si>
     <t xml:space="preserve">1.66748952865601</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">1.66136467456818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67667698860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6154283285141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714796066284</t>
+    <t xml:space="preserve">1.6766768693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61542809009552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714807987213</t>
   </si>
   <si>
     <t xml:space="preserve">1.58480393886566</t>
@@ -368,25 +368,25 @@
     <t xml:space="preserve">1.63380289077759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57561683654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54652380943298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56796073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54499244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355551719666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54192996025085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5817414522171</t>
+    <t xml:space="preserve">1.57561707496643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54652369022369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56796085834503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5449925661087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355563640594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54193019866943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174157142639</t>
   </si>
   <si>
     <t xml:space="preserve">1.55877351760864</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">1.5802104473114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55264866352081</t>
+    <t xml:space="preserve">1.5526487827301</t>
   </si>
   <si>
     <t xml:space="preserve">1.53044605255127</t>
@@ -404,16 +404,16 @@
     <t xml:space="preserve">1.51972758769989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50594675540924</t>
+    <t xml:space="preserve">1.50594663619995</t>
   </si>
   <si>
     <t xml:space="preserve">1.50671231746674</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53427386283875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56642961502075</t>
+    <t xml:space="preserve">1.53427410125732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56642949581146</t>
   </si>
   <si>
     <t xml:space="preserve">1.57408559322357</t>
@@ -422,19 +422,19 @@
     <t xml:space="preserve">1.58327293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59245979785919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5021185874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824368000031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4753223657608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49675953388214</t>
+    <t xml:space="preserve">1.59245991706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50211870670319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824356079102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47532248497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49675941467285</t>
   </si>
   <si>
     <t xml:space="preserve">1.50747787952423</t>
@@ -446,22 +446,22 @@
     <t xml:space="preserve">1.60011613368988</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58786642551422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489813327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5633670091629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255411148071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59858500957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59399139881134</t>
+    <t xml:space="preserve">1.58786618709564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489825248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56336724758148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255423069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59858512878418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59399127960205</t>
   </si>
   <si>
     <t xml:space="preserve">1.60470974445343</t>
@@ -470,85 +470,85 @@
     <t xml:space="preserve">1.64758372306824</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64605271816254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68280172348022</t>
+    <t xml:space="preserve">1.64605283737183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68280160427094</t>
   </si>
   <si>
     <t xml:space="preserve">1.63074052333832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686525821686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452135562897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63227164745331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66289591789246</t>
+    <t xml:space="preserve">1.63686513900757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452123641968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6322717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66289579868317</t>
   </si>
   <si>
     <t xml:space="preserve">1.66595828533173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73333168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026943206787</t>
+    <t xml:space="preserve">1.73333156108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026931285858</t>
   </si>
   <si>
     <t xml:space="preserve">1.74558126926422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75017499923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730113983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423865318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7379252910614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75936210155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089358329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7838613986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76854944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323724746704</t>
+    <t xml:space="preserve">1.75017488002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730125904083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423829555511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73792505264282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75936222076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089334487915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78386127948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76854979991913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323748588562</t>
   </si>
   <si>
     <t xml:space="preserve">1.73486304283142</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73639380931854</t>
+    <t xml:space="preserve">1.73639416694641</t>
   </si>
   <si>
     <t xml:space="preserve">1.79151773452759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80223643779755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061064243317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754815578461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682945251465</t>
+    <t xml:space="preserve">1.80223631858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061052322388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8175482749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682957172394</t>
   </si>
   <si>
     <t xml:space="preserve">1.8252044916153</t>
@@ -557,43 +557,43 @@
     <t xml:space="preserve">1.81448566913605</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85889089107513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87726557254791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85429728031158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582888126373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85123479366302</t>
+    <t xml:space="preserve">1.85889112949371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87726545333862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85429704189301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582864284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85123491287231</t>
   </si>
   <si>
     <t xml:space="preserve">1.86654710769653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84970378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348450183868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8527660369873</t>
+    <t xml:space="preserve">1.84970343112946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348462104797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85276639461517</t>
   </si>
   <si>
     <t xml:space="preserve">1.83745384216309</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84511005878448</t>
+    <t xml:space="preserve">1.84511017799377</t>
   </si>
   <si>
     <t xml:space="preserve">1.82367312908173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84051668643951</t>
+    <t xml:space="preserve">1.84051656723022</t>
   </si>
   <si>
     <t xml:space="preserve">1.84817242622375</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">1.86807835102081</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94923233985901</t>
+    <t xml:space="preserve">1.94923210144043</t>
   </si>
   <si>
     <t xml:space="preserve">1.90788996219635</t>
@@ -611,61 +611,61 @@
     <t xml:space="preserve">1.92167043685913</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92932641506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473316192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9660758972168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904383182526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823081493378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00894951820374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00741791725159</t>
+    <t xml:space="preserve">1.92932665348053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473304271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607577800751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823093414307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894999504089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00741839408875</t>
   </si>
   <si>
     <t xml:space="preserve">2.01201224327087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99057471752167</t>
+    <t xml:space="preserve">1.99057507514954</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00588750839233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09207797050476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051108360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401700973511</t>
+    <t xml:space="preserve">2.00588703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0920774936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051084518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401724815369</t>
   </si>
   <si>
     <t xml:space="preserve">2.08424234390259</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11558413505554</t>
+    <t xml:space="preserve">2.11558437347412</t>
   </si>
   <si>
     <t xml:space="preserve">2.17043280601501</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14692616462708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15006065368652</t>
+    <t xml:space="preserve">2.14692640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15006017684937</t>
   </si>
   <si>
     <t xml:space="preserve">2.12655377388</t>
@@ -674,28 +674,28 @@
     <t xml:space="preserve">2.16259717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15162777900696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13909101486206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16103029251099</t>
+    <t xml:space="preserve">2.15162754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1390905380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16103005409241</t>
   </si>
   <si>
     <t xml:space="preserve">2.04663181304932</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05290031433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03722882270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04819869995117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0450644493103</t>
+    <t xml:space="preserve">2.0528998374939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03722906112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04819941520691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04506421089172</t>
   </si>
   <si>
     <t xml:space="preserve">2.06543684005737</t>
@@ -710,148 +710,148 @@
     <t xml:space="preserve">2.11715126037598</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12342000007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125514984131</t>
+    <t xml:space="preserve">2.12342023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125538825989</t>
   </si>
   <si>
     <t xml:space="preserve">2.18296957015991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1939389705658</t>
+    <t xml:space="preserve">2.19393920898438</t>
   </si>
   <si>
     <t xml:space="preserve">2.20647597312927</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2033417224884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19237232208252</t>
+    <t xml:space="preserve">2.20334196090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19237208366394</t>
   </si>
   <si>
     <t xml:space="preserve">2.20804309844971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1641640663147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946316719055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13595676422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06386971473694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02625918388367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827685832977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805176258087</t>
+    <t xml:space="preserve">2.16416454315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13595652580261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677910804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386995315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02625942230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805152416229</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640695571899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05446696281433</t>
+    <t xml:space="preserve">2.05446743965149</t>
   </si>
   <si>
     <t xml:space="preserve">2.10461449623108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06700396537781</t>
+    <t xml:space="preserve">2.06700444221497</t>
   </si>
   <si>
     <t xml:space="preserve">2.03566217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04976582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954144477844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857132911682</t>
+    <t xml:space="preserve">2.04976606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857109069824</t>
   </si>
   <si>
     <t xml:space="preserve">2.07797384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2409520149231</t>
+    <t xml:space="preserve">2.24095225334167</t>
   </si>
   <si>
     <t xml:space="preserve">2.22371411323547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21117687225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2331166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930708885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3146059513092</t>
+    <t xml:space="preserve">2.211177110672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23311686515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781824111938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31460571289062</t>
   </si>
   <si>
     <t xml:space="preserve">2.3271427154541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32557559013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982653617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3866925239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4446747303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601723670959</t>
+    <t xml:space="preserve">2.32557535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982677459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38669228553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467496871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601699829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.48541975021362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49012088775635</t>
+    <t xml:space="preserve">2.49012112617493</t>
   </si>
   <si>
     <t xml:space="preserve">2.52146291732788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50735902786255</t>
+    <t xml:space="preserve">2.50735926628113</t>
   </si>
   <si>
     <t xml:space="preserve">2.53870105743408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53086566925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168801307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952387809753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52302980422974</t>
+    <t xml:space="preserve">2.53086543083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4916877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422501564026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52303004264832</t>
   </si>
   <si>
     <t xml:space="preserve">2.53243279457092</t>
@@ -872,40 +872,40 @@
     <t xml:space="preserve">2.49638938903809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52616381645203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653668403625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55123805999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53713369369507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55437183380127</t>
+    <t xml:space="preserve">2.52616429328918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55123782157898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53713417053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55437231063843</t>
   </si>
   <si>
     <t xml:space="preserve">2.60608625411987</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70794796943665</t>
+    <t xml:space="preserve">2.70794773101807</t>
   </si>
   <si>
     <t xml:space="preserve">2.71108198165894</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7220516204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541096687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70324659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67347192764282</t>
+    <t xml:space="preserve">2.72205185890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541120529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70324683189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67347121238708</t>
   </si>
   <si>
     <t xml:space="preserve">2.66406917572021</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">2.61705589294434</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59981822967529</t>
+    <t xml:space="preserve">2.59981799125671</t>
   </si>
   <si>
     <t xml:space="preserve">2.58728122711182</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">2.57004308700562</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56220769882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54183483123779</t>
+    <t xml:space="preserve">2.5622079372406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54183530807495</t>
   </si>
   <si>
     <t xml:space="preserve">2.51989579200745</t>
@@ -941,31 +941,31 @@
     <t xml:space="preserve">2.52929854393005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52459692955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034598350525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131562232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228526115417</t>
+    <t xml:space="preserve">2.52459740638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228549957275</t>
   </si>
   <si>
     <t xml:space="preserve">2.43370532989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39609527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975704193115</t>
+    <t xml:space="preserve">2.39609503746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087397575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206871032715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975751876831</t>
   </si>
   <si>
     <t xml:space="preserve">2.27699542045593</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">2.28796529769897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34908199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36475276947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064959526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848498344421</t>
+    <t xml:space="preserve">2.34908175468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36475300788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064911842346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848450660706</t>
   </si>
   <si>
     <t xml:space="preserve">2.41333317756653</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">2.62489151954651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63272714614868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.468181848526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36632037162781</t>
+    <t xml:space="preserve">2.6327269077301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46818161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36632013320923</t>
   </si>
   <si>
     <t xml:space="preserve">2.38199090957642</t>
@@ -1013,25 +1013,25 @@
     <t xml:space="preserve">2.45251059532166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40549755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42116904258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900419235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878740310669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363607406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25662302970886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27229428291321</t>
+    <t xml:space="preserve">2.40549731254578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42116856575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878787994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363631248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25662350654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27229452133179</t>
   </si>
   <si>
     <t xml:space="preserve">2.28012990951538</t>
@@ -1043,22 +1043,19 @@
     <t xml:space="preserve">2.22528123855591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11558437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12359809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09955716133118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08352947235107</t>
+    <t xml:space="preserve">2.1235978603363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0995569229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08352994918823</t>
   </si>
   <si>
     <t xml:space="preserve">2.09154319763184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942110061646</t>
+    <t xml:space="preserve">2.01942157745361</t>
   </si>
   <si>
     <t xml:space="preserve">2.00339412689209</t>
@@ -1067,43 +1064,43 @@
     <t xml:space="preserve">2.06750273704529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18770670890808</t>
+    <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188275337219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13962507247925</t>
+    <t xml:space="preserve">2.13962483406067</t>
   </si>
   <si>
     <t xml:space="preserve">2.1636655330658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14763855934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20373368263245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13161134719849</t>
+    <t xml:space="preserve">2.14763879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20373344421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13161158561707</t>
   </si>
   <si>
     <t xml:space="preserve">2.17167925834656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19571995735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17969274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10757088661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05948948860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07551646232605</t>
+    <t xml:space="preserve">2.19572019577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17969298362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10757064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05948925018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07551598548889</t>
   </si>
   <si>
     <t xml:space="preserve">2.03544855117798</t>
@@ -1115,7 +1112,7 @@
     <t xml:space="preserve">2.27585577964783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26784205436707</t>
+    <t xml:space="preserve">2.26784229278564</t>
   </si>
   <si>
     <t xml:space="preserve">2.21976065635681</t>
@@ -1130,127 +1127,130 @@
     <t xml:space="preserve">2.23578763008118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22777390480042</t>
+    <t xml:space="preserve">2.22777438163757</t>
   </si>
   <si>
     <t xml:space="preserve">2.15565204620361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30790996551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0274350643158</t>
+    <t xml:space="preserve">2.30791044235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02743482589722</t>
   </si>
   <si>
     <t xml:space="preserve">2.04346203804016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99538052082062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524505615234</t>
+    <t xml:space="preserve">1.99538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524469852448</t>
   </si>
   <si>
     <t xml:space="preserve">1.92325830459595</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96332621574402</t>
+    <t xml:space="preserve">1.96332681179047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9713397026062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736691474915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140737533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81106841564178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81908166408539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84312236309052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79504120349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77901387214661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709550857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.771000623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73093235492706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69887816905975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7149053812027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695992469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72291922569275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73894619941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298701763153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75497329235077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85914969444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86716330051422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8351092338562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517702579498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935354709625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93928563594818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258134841919</t>
   </si>
   <si>
     <t xml:space="preserve">1.97133994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98736703395844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140761375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81106841564178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81908190250397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84312272071838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79504108428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901375293732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709538936615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100050449371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73093259334564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69887804985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7149053812027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7469596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72291910648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73894608020782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298666000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75497353076935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305469036102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85914969444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86716318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510899543762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517702579498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723121166229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9392853975296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082943916321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258087158203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98783624172211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9960845708847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9630913734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834674358368</t>
+    <t xml:space="preserve">1.98783648014069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99608480930328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96309149265289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93834638595581</t>
   </si>
   <si>
     <t xml:space="preserve">1.9795880317688</t>
@@ -1259,25 +1259,25 @@
     <t xml:space="preserve">2.0373260974884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06207084655762</t>
+    <t xml:space="preserve">2.0620710849762</t>
   </si>
   <si>
     <t xml:space="preserve">2.05382251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09506416320801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16929864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16105031967163</t>
+    <t xml:space="preserve">2.09506392478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16929888725281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
     <t xml:space="preserve">2.11156034469604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10331249237061</t>
+    <t xml:space="preserve">2.10331225395203</t>
   </si>
   <si>
     <t xml:space="preserve">2.12805724143982</t>
@@ -1292,52 +1292,52 @@
     <t xml:space="preserve">2.14455366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07856750488281</t>
+    <t xml:space="preserve">2.07856774330139</t>
   </si>
   <si>
     <t xml:space="preserve">2.22703647613525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21878862380981</t>
+    <t xml:space="preserve">2.21878838539124</t>
   </si>
   <si>
     <t xml:space="preserve">2.25178146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24353313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21054005622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26002955436707</t>
+    <t xml:space="preserve">2.24353337287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21054029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26002979278564</t>
   </si>
   <si>
     <t xml:space="preserve">2.26827812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33426427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30951929092407</t>
+    <t xml:space="preserve">2.33426403999329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30951976776123</t>
   </si>
   <si>
     <t xml:space="preserve">2.30127096176147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31776785850525</t>
+    <t xml:space="preserve">2.31776762008667</t>
   </si>
   <si>
     <t xml:space="preserve">2.38375425338745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550592422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601571083069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27652597427368</t>
+    <t xml:space="preserve">2.37550568580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601594924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27652645111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.28477454185486</t>
@@ -1346,22 +1346,22 @@
     <t xml:space="preserve">2.29302263259888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23528504371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4497401714325</t>
+    <t xml:space="preserve">2.23528480529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44974040985107</t>
   </si>
   <si>
     <t xml:space="preserve">2.41674709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43324375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849900245667</t>
+    <t xml:space="preserve">2.43324398994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849876403809</t>
   </si>
   <si>
     <t xml:space="preserve">2.42499542236328</t>
@@ -1370,19 +1370,19 @@
     <t xml:space="preserve">2.45798850059509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4992299079895</t>
+    <t xml:space="preserve">2.49923014640808</t>
   </si>
   <si>
     <t xml:space="preserve">2.47448515892029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5157265663147</t>
+    <t xml:space="preserve">2.51572632789612</t>
   </si>
   <si>
     <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871988296509</t>
+    <t xml:space="preserve">2.54871940612793</t>
   </si>
   <si>
     <t xml:space="preserve">2.4909815788269</t>
@@ -1394,97 +1394,97 @@
     <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35076069831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40025043487549</t>
+    <t xml:space="preserve">2.35076093673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40025067329407</t>
   </si>
   <si>
     <t xml:space="preserve">2.19404363632202</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18579530715942</t>
+    <t xml:space="preserve">2.18579506874084</t>
   </si>
   <si>
     <t xml:space="preserve">2.045574426651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87236022949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8806084394455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264997005463</t>
+    <t xml:space="preserve">1.8723601102829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060867786407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264985084534</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089818000793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56717371940613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71564292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64553260803223</t>
+    <t xml:space="preserve">1.56717383861542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71564280986786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64553248882294</t>
   </si>
   <si>
     <t xml:space="preserve">1.64140844345093</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62491178512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77338111400604</t>
+    <t xml:space="preserve">1.62491190433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77338123321533</t>
   </si>
   <si>
     <t xml:space="preserve">1.78162920475006</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74863588809967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80637431144714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411213874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00433301925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81462240219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287085056305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84761524200439</t>
+    <t xml:space="preserve">1.74863600730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80637407302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411225795746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00433278083801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81462252140045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287096977234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84761536121368</t>
   </si>
   <si>
     <t xml:space="preserve">1.83111894130707</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78987753391266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885688781738</t>
+    <t xml:space="preserve">1.78987765312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885724544525</t>
   </si>
   <si>
     <t xml:space="preserve">1.9136016368866</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89710509777069</t>
+    <t xml:space="preserve">1.89710521697998</t>
   </si>
   <si>
     <t xml:space="preserve">1.90535342693329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548431634903</t>
+    <t xml:space="preserve">1.95484340190887</t>
   </si>
   <si>
     <t xml:space="preserve">2.02907776832581</t>
@@ -1493,10 +1493,10 @@
     <t xml:space="preserve">2.08681583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17754673957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07031917572021</t>
+    <t xml:space="preserve">2.17754697799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07031893730164</t>
   </si>
   <si>
     <t xml:space="preserve">2.07786893844604</t>
@@ -1505,19 +1505,19 @@
     <t xml:space="preserve">2.06938791275024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03546333312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98457670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609567642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95065248012543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9930579662323</t>
+    <t xml:space="preserve">2.03546357154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98457705974579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609603404999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95065259933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99305772781372</t>
   </si>
   <si>
     <t xml:space="preserve">2.06090688705444</t>
@@ -1532,25 +1532,25 @@
     <t xml:space="preserve">2.04394459724426</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0100200176239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00153875350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89976572990417</t>
+    <t xml:space="preserve">2.01002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0015389919281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89976608753204</t>
   </si>
   <si>
     <t xml:space="preserve">1.88280379772186</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89128482341766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01850152015686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95913350582123</t>
+    <t xml:space="preserve">1.89128494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01850128173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95913362503052</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
@@ -1565,13 +1565,13 @@
     <t xml:space="preserve">2.16268014907837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20508527755737</t>
+    <t xml:space="preserve">2.20508551597595</t>
   </si>
   <si>
     <t xml:space="preserve">2.23052883148193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3068585395813</t>
+    <t xml:space="preserve">2.30685877799988</t>
   </si>
   <si>
     <t xml:space="preserve">2.33230209350586</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559385299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255638122559</t>
+    <t xml:space="preserve">2.42559409141541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255661964417</t>
   </si>
   <si>
     <t xml:space="preserve">2.47648072242737</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">2.46799969673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49344277381897</t>
+    <t xml:space="preserve">2.49344301223755</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040506362915</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">2.41711282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888632774353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58673501014709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977272033691</t>
+    <t xml:space="preserve">2.51888608932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58673477172852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977248191833</t>
   </si>
   <si>
     <t xml:space="preserve">2.54432940483093</t>
@@ -1622,43 +1622,43 @@
     <t xml:space="preserve">2.57825374603271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56129169464111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55281043052673</t>
+    <t xml:space="preserve">2.56129121780396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55281066894531</t>
   </si>
   <si>
     <t xml:space="preserve">2.53584837913513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52736711502075</t>
+    <t xml:space="preserve">2.52736735343933</t>
   </si>
   <si>
     <t xml:space="preserve">2.64610242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63762164115906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66306495666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70547080039978</t>
+    <t xml:space="preserve">2.63762140274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66306519508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70547032356262</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62914037704468</t>
+    <t xml:space="preserve">2.6291401386261</t>
   </si>
   <si>
     <t xml:space="preserve">2.713951587677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7309136390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77331900596619</t>
+    <t xml:space="preserve">2.73091387748718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77331924438477</t>
   </si>
   <si>
     <t xml:space="preserve">2.78180003166199</t>
@@ -1667,10 +1667,10 @@
     <t xml:space="preserve">2.84116792678833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86661124229431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88357353210449</t>
+    <t xml:space="preserve">2.86661100387573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88357377052307</t>
   </si>
   <si>
     <t xml:space="preserve">2.90901684761047</t>
@@ -1679,19 +1679,19 @@
     <t xml:space="preserve">2.85812997817993</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80724358558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75635695457458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7393946647644</t>
+    <t xml:space="preserve">2.80724310874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75635671615601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73939442634583</t>
   </si>
   <si>
     <t xml:space="preserve">2.74787569046021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79876208305359</t>
+    <t xml:space="preserve">2.79876232147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.79028129577637</t>
@@ -1700,10 +1700,10 @@
     <t xml:space="preserve">2.84964871406555</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268642425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82420539855957</t>
+    <t xml:space="preserve">2.83268690109253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82420563697815</t>
   </si>
   <si>
     <t xml:space="preserve">2.9174976348877</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">3.01078987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0362331867218</t>
+    <t xml:space="preserve">3.03623294830322</t>
   </si>
   <si>
     <t xml:space="preserve">2.95990324020386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07863903045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08711981773376</t>
+    <t xml:space="preserve">3.07863879203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08711957931519</t>
   </si>
   <si>
     <t xml:space="preserve">3.12104415893555</t>
@@ -1730,10 +1730,10 @@
     <t xml:space="preserve">3.18041181564331</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14648747444153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2397792339325</t>
+    <t xml:space="preserve">3.14648723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
     <t xml:space="preserve">3.22281718254089</t>
@@ -1745,31 +1745,31 @@
     <t xml:space="preserve">3.24826049804688</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21433615684509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28218483924866</t>
+    <t xml:space="preserve">3.21433639526367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28218507766724</t>
   </si>
   <si>
     <t xml:space="preserve">3.40092062950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42636370658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36699604988098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31610941886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29066586494446</t>
+    <t xml:space="preserve">3.42636346817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3669958114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31610918045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29066634178162</t>
   </si>
   <si>
     <t xml:space="preserve">3.27370381355286</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3079400062561</t>
+    <t xml:space="preserve">3.30794024467468</t>
   </si>
   <si>
     <t xml:space="preserve">3.31657671928406</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">3.27339220046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35112452507019</t>
+    <t xml:space="preserve">3.35112476348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.34248757362366</t>
@@ -1787,52 +1787,52 @@
     <t xml:space="preserve">3.36839842796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39430928230286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44613075256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45476770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4720413684845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54113674163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60159516334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59295797348022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65341687202454</t>
+    <t xml:space="preserve">3.39430904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4461305141449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45476746559143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47204160690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54113698005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60159540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59295845031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65341663360596</t>
   </si>
   <si>
     <t xml:space="preserve">3.61023187637329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71387553215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78297090530396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80888104438782</t>
+    <t xml:space="preserve">3.71387505531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069029808044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78297066688538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8088812828064</t>
   </si>
   <si>
     <t xml:space="preserve">3.69660115242004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62750554084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64477968215942</t>
+    <t xml:space="preserve">3.62750601768494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.644779920578</t>
   </si>
   <si>
     <t xml:space="preserve">3.73978567123413</t>
@@ -1841,10 +1841,10 @@
     <t xml:space="preserve">3.7570595741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55841064453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67932748794556</t>
+    <t xml:space="preserve">3.55841016769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67932772636414</t>
   </si>
   <si>
     <t xml:space="preserve">3.57568430900574</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">3.58432126045227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70523834228516</t>
+    <t xml:space="preserve">3.705237865448</t>
   </si>
   <si>
     <t xml:space="preserve">3.5238630771637</t>
@@ -1865,10 +1865,10 @@
     <t xml:space="preserve">3.48931527137756</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41158294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51522588729858</t>
+    <t xml:space="preserve">3.41158318519592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51522636413574</t>
   </si>
   <si>
     <t xml:space="preserve">3.68796443939209</t>
@@ -1880,85 +1880,85 @@
     <t xml:space="preserve">3.66205334663391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6188690662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86933922767639</t>
+    <t xml:space="preserve">3.61886930465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86933970451355</t>
   </si>
   <si>
     <t xml:space="preserve">3.82615494728088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8607029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91252446174622</t>
+    <t xml:space="preserve">3.86070275306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91252493858337</t>
   </si>
   <si>
     <t xml:space="preserve">3.99889373779297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9557089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99025630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342885017395</t>
+    <t xml:space="preserve">3.95570874214172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99025678634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342861175537</t>
   </si>
   <si>
     <t xml:space="preserve">3.77433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76569652557373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92979836463928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661360740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9038872718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87797617912292</t>
+    <t xml:space="preserve">3.76569676399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9297981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8866138458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90388751029968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8779764175415</t>
   </si>
   <si>
     <t xml:space="preserve">3.81751799583435</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434569358826</t>
+    <t xml:space="preserve">3.96434617042542</t>
   </si>
   <si>
     <t xml:space="preserve">3.89525079727173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93843483924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63614273071289</t>
+    <t xml:space="preserve">3.93843507766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63614296913147</t>
   </si>
   <si>
     <t xml:space="preserve">3.49795246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885708808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42022013664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2820291519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25611877441406</t>
+    <t xml:space="preserve">3.42885661125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021989822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28202939033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2561182975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066610336304</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24748134613037</t>
+    <t xml:space="preserve">3.24748158454895</t>
   </si>
   <si>
     <t xml:space="preserve">3.29930305480957</t>
@@ -1967,16 +1967,16 @@
     <t xml:space="preserve">3.26475524902344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33385062217712</t>
+    <t xml:space="preserve">3.3338508605957</t>
   </si>
   <si>
     <t xml:space="preserve">3.43749380111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37703561782837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40294623374939</t>
+    <t xml:space="preserve">3.37703514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40294599533081</t>
   </si>
   <si>
     <t xml:space="preserve">3.3597617149353</t>
@@ -1988,34 +1988,34 @@
     <t xml:space="preserve">3.23020768165588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15247535705566</t>
+    <t xml:space="preserve">3.15247559547424</t>
   </si>
   <si>
     <t xml:space="preserve">3.11792778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19566011428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14383840560913</t>
+    <t xml:space="preserve">3.19565987586975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14383864402771</t>
   </si>
   <si>
     <t xml:space="preserve">2.97973704338074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06610631942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53249979019165</t>
+    <t xml:space="preserve">3.06610608100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53250002861023</t>
   </si>
   <si>
     <t xml:space="preserve">3.56704759597778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46340465545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38567209243774</t>
+    <t xml:space="preserve">3.46340489387512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38567233085632</t>
   </si>
   <si>
     <t xml:space="preserve">3.54223012924194</t>
@@ -2024,13 +2024,13 @@
     <t xml:space="preserve">3.57765245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56879663467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52451872825623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61307454109192</t>
+    <t xml:space="preserve">3.56879687309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5245189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6130747795105</t>
   </si>
   <si>
     <t xml:space="preserve">3.58650803565979</t>
@@ -2039,10 +2039,10 @@
     <t xml:space="preserve">3.294273853302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31198525428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35626316070557</t>
+    <t xml:space="preserve">3.31198501586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35626292228699</t>
   </si>
   <si>
     <t xml:space="preserve">3.33855175971985</t>
@@ -2060,16 +2060,16 @@
     <t xml:space="preserve">3.2322850227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27656292915344</t>
+    <t xml:space="preserve">3.27656269073486</t>
   </si>
   <si>
     <t xml:space="preserve">3.32969617843628</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32084083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28541851043701</t>
+    <t xml:space="preserve">3.32084059715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28541827201843</t>
   </si>
   <si>
     <t xml:space="preserve">3.42710757255554</t>
@@ -2087,16 +2087,19 @@
     <t xml:space="preserve">3.48909664154053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53337454795837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59536337852478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5599410533905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4625301361084</t>
+    <t xml:space="preserve">3.53337430953979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59536361694336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55994129180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4979522228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46252989768982</t>
   </si>
   <si>
     <t xml:space="preserve">3.36511850357056</t>
@@ -2105,13 +2108,13 @@
     <t xml:space="preserve">3.41825175285339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3828296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44481897354126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45367431640625</t>
+    <t xml:space="preserve">3.38282942771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44481873512268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45367407798767</t>
   </si>
   <si>
     <t xml:space="preserve">3.48024106025696</t>
@@ -2120,10 +2123,10 @@
     <t xml:space="preserve">3.39168524742126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24999618530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08174014091492</t>
+    <t xml:space="preserve">3.24999594688416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08173990249634</t>
   </si>
   <si>
     <t xml:space="preserve">3.1437292098999</t>
@@ -2147,7 +2150,7 @@
     <t xml:space="preserve">2.86920619010925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74522829055786</t>
+    <t xml:space="preserve">2.74522805213928</t>
   </si>
   <si>
     <t xml:space="preserve">2.65667247772217</t>
@@ -2156,16 +2159,16 @@
     <t xml:space="preserve">2.56811690330505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78950643539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75408387184143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72751688957214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68323922157288</t>
+    <t xml:space="preserve">2.78950619697571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75408363342285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72751712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6832389831543</t>
   </si>
   <si>
     <t xml:space="preserve">2.82492852210999</t>
@@ -2183,10 +2186,10 @@
     <t xml:space="preserve">2.97547316551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99318432807922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06402897834778</t>
+    <t xml:space="preserve">2.9931845664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0640287399292</t>
   </si>
   <si>
     <t xml:space="preserve">3.07288455963135</t>
@@ -2195,10 +2198,10 @@
     <t xml:space="preserve">3.01975131034851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09945130348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03746223449707</t>
+    <t xml:space="preserve">3.09945106506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03746247291565</t>
   </si>
   <si>
     <t xml:space="preserve">2.94005084037781</t>
@@ -2219,10 +2222,10 @@
     <t xml:space="preserve">2.90462851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203990936279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93119549751282</t>
+    <t xml:space="preserve">3.00204014778137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93119525909424</t>
   </si>
   <si>
     <t xml:space="preserve">2.78065061569214</t>
@@ -2234,16 +2237,16 @@
     <t xml:space="preserve">2.77179503440857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81607270240784</t>
+    <t xml:space="preserve">2.81607294082642</t>
   </si>
   <si>
     <t xml:space="preserve">2.8780620098114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0286066532135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05517363548279</t>
+    <t xml:space="preserve">3.02860689163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05517339706421</t>
   </si>
   <si>
     <t xml:space="preserve">3.17029571533203</t>
@@ -2264,19 +2267,19 @@
     <t xml:space="preserve">3.37397408485413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40054082870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47138547897339</t>
+    <t xml:space="preserve">3.40054059028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47138524055481</t>
   </si>
   <si>
     <t xml:space="preserve">3.50680780410767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60421895980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078570365906</t>
+    <t xml:space="preserve">3.60421919822693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63078594207764</t>
   </si>
   <si>
     <t xml:space="preserve">3.62193036079407</t>
@@ -2294,13 +2297,13 @@
     <t xml:space="preserve">3.72270464897156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77785587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69512867927551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70432114601135</t>
+    <t xml:space="preserve">3.77785563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69512891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70432090759277</t>
   </si>
   <si>
     <t xml:space="preserve">3.78704738616943</t>
@@ -2312,7 +2315,7 @@
     <t xml:space="preserve">3.8146231174469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76866364479065</t>
+    <t xml:space="preserve">3.76866388320923</t>
   </si>
   <si>
     <t xml:space="preserve">3.75028014183044</t>
@@ -2321,19 +2324,16 @@
     <t xml:space="preserve">3.63997769355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64916944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66755342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63078594207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62159419059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53886699676514</t>
+    <t xml:space="preserve">3.64916968345642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66755318641663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62159395217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53886723518372</t>
   </si>
   <si>
     <t xml:space="preserve">3.5572509765625</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">3.52048349380493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4561402797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49290776252747</t>
+    <t xml:space="preserve">3.45614051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49290800094604</t>
   </si>
   <si>
     <t xml:space="preserve">3.56644296646118</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">3.60321021080017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51129174232483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85139060020447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84219837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90654182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86058211326599</t>
+    <t xml:space="preserve">3.51129150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85139083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84219861030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90654158592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86058235168457</t>
   </si>
   <si>
     <t xml:space="preserve">3.68593716621399</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">3.74108839035034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58482670783997</t>
+    <t xml:space="preserve">3.58482646942139</t>
   </si>
   <si>
     <t xml:space="preserve">3.65836143493652</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">3.47452425956726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46533250808716</t>
+    <t xml:space="preserve">3.46533226966858</t>
   </si>
   <si>
     <t xml:space="preserve">3.50209975242615</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">3.94330906867981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9157338142395</t>
+    <t xml:space="preserve">3.91573357582092</t>
   </si>
   <si>
     <t xml:space="preserve">3.95250105857849</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">3.92492532730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98926877975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83300685882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96169257164001</t>
+    <t xml:space="preserve">3.98926854133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83300709724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96169281005859</t>
   </si>
   <si>
     <t xml:space="preserve">3.87896609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93411755561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97088503837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98007678985596</t>
+    <t xml:space="preserve">3.93411731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97088479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98007655143738</t>
   </si>
   <si>
     <t xml:space="preserve">3.823814868927</t>
@@ -2441,13 +2441,13 @@
     <t xml:space="preserve">3.79623937606812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88815808296204</t>
+    <t xml:space="preserve">3.88815784454346</t>
   </si>
   <si>
     <t xml:space="preserve">3.86977458000183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89734983444214</t>
+    <t xml:space="preserve">3.89734935760498</t>
   </si>
   <si>
     <t xml:space="preserve">4.13633823394775</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">4.20068168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42128562927246</t>
+    <t xml:space="preserve">4.42128610610962</t>
   </si>
   <si>
     <t xml:space="preserve">4.66946649551392</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">4.81653594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9636058807373</t>
+    <t xml:space="preserve">4.96360635757446</t>
   </si>
   <si>
     <t xml:space="preserve">4.85330390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76138496398926</t>
+    <t xml:space="preserve">4.7613844871521</t>
   </si>
   <si>
     <t xml:space="preserve">4.5867395401001</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">4.90845489501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89007091522217</t>
+    <t xml:space="preserve">4.89007139205933</t>
   </si>
   <si>
     <t xml:space="preserve">5.16600561141968</t>
@@ -3012,6 +3012,9 @@
   </si>
   <si>
     <t xml:space="preserve">9.26000022888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30000019073486</t>
   </si>
 </sst>
 </file>
@@ -19150,7 +19153,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G608" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19176,7 +19179,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19202,7 +19205,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G610" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19228,7 +19231,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G611" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19254,7 +19257,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G612" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19280,7 +19283,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19306,7 +19309,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G614" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19332,7 +19335,7 @@
         <v>2.5</v>
       </c>
       <c r="G615" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19358,7 +19361,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G616" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19384,7 +19387,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19410,7 +19413,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G618" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19436,7 +19439,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G619" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19462,7 +19465,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G620" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19488,7 +19491,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G621" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19514,7 +19517,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G622" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19540,7 +19543,7 @@
         <v>2.75</v>
       </c>
       <c r="G623" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19566,7 +19569,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G624" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19592,7 +19595,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19618,7 +19621,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G626" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19644,7 +19647,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G627" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19670,7 +19673,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G628" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19696,7 +19699,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19722,7 +19725,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19748,7 +19751,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G631" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19774,7 +19777,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G632" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19800,7 +19803,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19826,7 +19829,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G634" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19852,7 +19855,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G635" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19878,7 +19881,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19904,7 +19907,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G637" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19930,7 +19933,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G638" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19956,7 +19959,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G639" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -19982,7 +19985,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G640" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20008,7 +20011,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G641" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20034,7 +20037,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20060,7 +20063,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G643" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20086,7 +20089,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20112,7 +20115,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G645" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20138,7 +20141,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G646" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20164,7 +20167,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G647" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20190,7 +20193,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G648" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20216,7 +20219,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G649" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20242,7 +20245,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G650" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20268,7 +20271,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G651" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20294,7 +20297,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20320,7 +20323,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G653" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20346,7 +20349,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20372,7 +20375,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20398,7 +20401,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20424,7 +20427,7 @@
         <v>2.5</v>
       </c>
       <c r="G657" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20450,7 +20453,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G658" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20476,7 +20479,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G659" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20502,7 +20505,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G660" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20528,7 +20531,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G661" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20554,7 +20557,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G662" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20580,7 +20583,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20606,7 +20609,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G664" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20632,7 +20635,7 @@
         <v>2.75</v>
       </c>
       <c r="G665" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20658,7 +20661,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20684,7 +20687,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20710,7 +20713,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G668" t="s">
-        <v>343</v>
+        <v>214</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20736,7 +20739,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20762,7 +20765,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20788,7 +20791,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20814,7 +20817,7 @@
         <v>2.75</v>
       </c>
       <c r="G672" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20840,7 +20843,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20866,7 +20869,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20892,7 +20895,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G675" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20918,7 +20921,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G676" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20944,7 +20947,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G677" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -20970,7 +20973,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G678" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -20996,7 +20999,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G679" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21022,7 +21025,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G680" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21048,7 +21051,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21074,7 +21077,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21100,7 +21103,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G683" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21126,7 +21129,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G684" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21152,7 +21155,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G685" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21178,7 +21181,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G686" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21204,7 +21207,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21230,7 +21233,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G688" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21256,7 +21259,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21282,7 +21285,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G690" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21308,7 +21311,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G691" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21334,7 +21337,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G692" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21360,7 +21363,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21386,7 +21389,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G694" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21412,7 +21415,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G695" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21438,7 +21441,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21464,7 +21467,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21490,7 +21493,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G698" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21516,7 +21519,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G699" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21542,7 +21545,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G700" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21568,7 +21571,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G701" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21594,7 +21597,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G702" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21620,7 +21623,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G703" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21646,7 +21649,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G704" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21672,7 +21675,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21698,7 +21701,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21724,7 +21727,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G707" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21750,7 +21753,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G708" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21776,7 +21779,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21802,7 +21805,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G710" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21828,7 +21831,7 @@
         <v>2.5</v>
       </c>
       <c r="G711" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21854,7 +21857,7 @@
         <v>2.5</v>
       </c>
       <c r="G712" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21880,7 +21883,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G713" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21906,7 +21909,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21932,7 +21935,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G715" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21958,7 +21961,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -21984,7 +21987,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G717" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22010,7 +22013,7 @@
         <v>2.5</v>
       </c>
       <c r="G718" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22036,7 +22039,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G719" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22062,7 +22065,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G720" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22088,7 +22091,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G721" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22114,7 +22117,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G722" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22140,7 +22143,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22166,7 +22169,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G724" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22192,7 +22195,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G725" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22218,7 +22221,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G726" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22244,7 +22247,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G727" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22270,7 +22273,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G728" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22296,7 +22299,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G729" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22322,7 +22325,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G730" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22348,7 +22351,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22374,7 +22377,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G732" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22400,7 +22403,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22426,7 +22429,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22452,7 +22455,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G735" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22478,7 +22481,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G736" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22504,7 +22507,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G737" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22530,7 +22533,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G738" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22556,7 +22559,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G739" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22582,7 +22585,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G740" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22608,7 +22611,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G741" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22634,7 +22637,7 @@
         <v>2.5</v>
       </c>
       <c r="G742" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22660,7 +22663,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G743" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22686,7 +22689,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G744" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22712,7 +22715,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G745" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22738,7 +22741,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G746" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22764,7 +22767,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G747" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22790,7 +22793,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22816,7 +22819,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G749" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22842,7 +22845,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22868,7 +22871,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G751" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22894,7 +22897,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G752" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22920,7 +22923,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22946,7 +22949,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -22972,7 +22975,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G755" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -22998,7 +23001,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G756" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23024,7 +23027,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G757" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23050,7 +23053,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G758" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23076,7 +23079,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G759" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23102,7 +23105,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23128,7 +23131,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G761" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23154,7 +23157,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G762" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23180,7 +23183,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G763" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23206,7 +23209,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G764" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23232,7 +23235,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G765" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23258,7 +23261,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G766" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23284,7 +23287,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G767" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23310,7 +23313,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G768" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23336,7 +23339,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23362,7 +23365,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G770" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23388,7 +23391,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G771" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23414,7 +23417,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G772" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23440,7 +23443,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G773" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23466,7 +23469,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G774" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23492,7 +23495,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G775" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23518,7 +23521,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G776" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23544,7 +23547,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23570,7 +23573,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G778" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23596,7 +23599,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G779" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23622,7 +23625,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G780" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23648,7 +23651,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23674,7 +23677,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23700,7 +23703,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G783" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23726,7 +23729,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G784" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23752,7 +23755,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G785" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23778,7 +23781,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G786" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23804,7 +23807,7 @@
         <v>2.25</v>
       </c>
       <c r="G787" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23830,7 +23833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G788" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23856,7 +23859,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G789" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23882,7 +23885,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23908,7 +23911,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23934,7 +23937,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G792" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23960,7 +23963,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G793" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -23986,7 +23989,7 @@
         <v>2.5</v>
       </c>
       <c r="G794" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24012,7 +24015,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G795" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24038,7 +24041,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24064,7 +24067,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24090,7 +24093,7 @@
         <v>2.5</v>
       </c>
       <c r="G798" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24116,7 +24119,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G799" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24142,7 +24145,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G800" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24168,7 +24171,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G801" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24194,7 +24197,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G802" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24220,7 +24223,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G803" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24246,7 +24249,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24272,7 +24275,7 @@
         <v>2.5</v>
       </c>
       <c r="G805" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24298,7 +24301,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G806" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24324,7 +24327,7 @@
         <v>2.5</v>
       </c>
       <c r="G807" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24350,7 +24353,7 @@
         <v>2.5</v>
       </c>
       <c r="G808" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24376,7 +24379,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G809" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24402,7 +24405,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G810" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24428,7 +24431,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G811" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24454,7 +24457,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G812" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24480,7 +24483,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G813" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24506,7 +24509,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24532,7 +24535,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G815" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24558,7 +24561,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24584,7 +24587,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G817" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24610,7 +24613,7 @@
         <v>2.5</v>
       </c>
       <c r="G818" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24636,7 +24639,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24662,7 +24665,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G820" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24688,7 +24691,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24714,7 +24717,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G822" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24740,7 +24743,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G823" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24766,7 +24769,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G824" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24792,7 +24795,7 @@
         <v>2.5</v>
       </c>
       <c r="G825" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24818,7 +24821,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24844,7 +24847,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G827" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24870,7 +24873,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G828" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24896,7 +24899,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G829" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24922,7 +24925,7 @@
         <v>2.5</v>
       </c>
       <c r="G830" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24948,7 +24951,7 @@
         <v>2.5</v>
       </c>
       <c r="G831" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -24974,7 +24977,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25000,7 +25003,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G833" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25026,7 +25029,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G834" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25052,7 +25055,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G835" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25078,7 +25081,7 @@
         <v>2.5</v>
       </c>
       <c r="G836" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25104,7 +25107,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G837" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25130,7 +25133,7 @@
         <v>2.5</v>
       </c>
       <c r="G838" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25156,7 +25159,7 @@
         <v>2.5</v>
       </c>
       <c r="G839" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25182,7 +25185,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25208,7 +25211,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G841" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25234,7 +25237,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G842" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25260,7 +25263,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G843" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25286,7 +25289,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G844" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25312,7 +25315,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25338,7 +25341,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G846" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25364,7 +25367,7 @@
         <v>2.5</v>
       </c>
       <c r="G847" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25390,7 +25393,7 @@
         <v>2.5</v>
       </c>
       <c r="G848" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25416,7 +25419,7 @@
         <v>2.5</v>
       </c>
       <c r="G849" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25442,7 +25445,7 @@
         <v>2.5</v>
       </c>
       <c r="G850" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25468,7 +25471,7 @@
         <v>2.5</v>
       </c>
       <c r="G851" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25494,7 +25497,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25520,7 +25523,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25546,7 +25549,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G854" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25572,7 +25575,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G855" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25598,7 +25601,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G856" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25624,7 +25627,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G857" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25650,7 +25653,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25676,7 +25679,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G859" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25702,7 +25705,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25728,7 +25731,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G861" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25754,7 +25757,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G862" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25832,7 +25835,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G865" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26014,7 +26017,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G872" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26196,7 +26199,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G879" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26222,7 +26225,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G880" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26248,7 +26251,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G881" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -31552,7 +31555,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1085" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32540,7 +32543,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32566,7 +32569,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32644,7 +32647,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1127" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32748,7 +32751,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1131" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32878,7 +32881,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1136" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33008,7 +33011,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1141" t="s">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33268,7 +33271,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1151" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33320,7 +33323,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1153" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33346,7 +33349,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1154" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33398,7 +33401,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1156" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34178,7 +34181,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1186" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34256,7 +34259,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1189" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -46944,7 +46947,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1677" t="s">
-        <v>642</v>
+        <v>694</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -46970,7 +46973,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1678" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -47022,7 +47025,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1680" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -47048,7 +47051,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1681" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -47178,7 +47181,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1686" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -47204,7 +47207,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1687" t="s">
-        <v>642</v>
+        <v>694</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -47230,7 +47233,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1688" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -47256,7 +47259,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1689" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -47334,7 +47337,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1692" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -47360,7 +47363,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1693" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -47386,7 +47389,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G1694" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -47464,7 +47467,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1697" t="s">
-        <v>642</v>
+        <v>694</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -47490,7 +47493,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1698" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -47516,7 +47519,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1699" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -47542,7 +47545,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1700" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -47594,7 +47597,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1702" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -47620,7 +47623,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1703" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -47646,7 +47649,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1704" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -47672,7 +47675,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1705" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -47802,7 +47805,7 @@
         <v>3.67000007629395</v>
       </c>
       <c r="G1710" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -47854,7 +47857,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1712" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -47880,7 +47883,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1713" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -47906,7 +47909,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1714" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -47932,7 +47935,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1715" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -47958,7 +47961,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1716" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -47984,7 +47987,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1717" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -48010,7 +48013,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1718" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -48036,7 +48039,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G1719" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -48062,7 +48065,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1720" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -48088,7 +48091,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1721" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -48114,7 +48117,7 @@
         <v>3</v>
       </c>
       <c r="G1722" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -48140,7 +48143,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1723" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -48166,7 +48169,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1724" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -48192,7 +48195,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1725" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -48218,7 +48221,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1726" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -48244,7 +48247,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1727" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -48270,7 +48273,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1728" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -48296,7 +48299,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1729" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -48322,7 +48325,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1730" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -48348,7 +48351,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1731" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -48374,7 +48377,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1732" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -48400,7 +48403,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1733" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -48426,7 +48429,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1734" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -48452,7 +48455,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1735" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -48478,7 +48481,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1736" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -48504,7 +48507,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1737" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -48530,7 +48533,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G1738" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -48556,7 +48559,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1739" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -48582,7 +48585,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1740" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -48608,7 +48611,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1741" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -48634,7 +48637,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1742" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -48660,7 +48663,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1743" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -48686,7 +48689,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G1744" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -48712,7 +48715,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1745" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -48738,7 +48741,7 @@
         <v>3.5</v>
       </c>
       <c r="G1746" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -48764,7 +48767,7 @@
         <v>3.5</v>
       </c>
       <c r="G1747" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -48790,7 +48793,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1748" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -48816,7 +48819,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1749" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -48842,7 +48845,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1750" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -48868,7 +48871,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1751" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -48894,7 +48897,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1752" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -48920,7 +48923,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1753" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -48946,7 +48949,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1754" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -48972,7 +48975,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1755" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -48998,7 +49001,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1756" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -49024,7 +49027,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1757" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -49050,7 +49053,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1758" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -49076,7 +49079,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1759" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -49102,7 +49105,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1760" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -49128,7 +49131,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1761" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -49154,7 +49157,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1762" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -49180,7 +49183,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1763" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -49206,7 +49209,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1764" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -49232,7 +49235,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1765" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -49258,7 +49261,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1766" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -49284,7 +49287,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G1767" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -49310,7 +49313,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1768" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -49336,7 +49339,7 @@
         <v>3.30999994277954</v>
       </c>
       <c r="G1769" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -49362,7 +49365,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1770" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -49388,7 +49391,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1771" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -49414,7 +49417,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1772" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -49440,7 +49443,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1773" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -49466,7 +49469,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G1774" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -49492,7 +49495,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1775" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -49518,7 +49521,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1776" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -49544,7 +49547,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G1777" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -49570,7 +49573,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G1778" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -49596,7 +49599,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1779" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -49622,7 +49625,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G1780" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -49648,7 +49651,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G1781" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -49674,7 +49677,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1782" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -49700,7 +49703,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1783" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -49726,7 +49729,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1784" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -49752,7 +49755,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1785" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -49778,7 +49781,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1786" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -49804,7 +49807,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1787" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -49830,7 +49833,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -49856,7 +49859,7 @@
         <v>3.25</v>
       </c>
       <c r="G1789" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -49882,7 +49885,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1790" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -49908,7 +49911,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1791" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -49934,7 +49937,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1792" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -49960,7 +49963,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1793" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -49986,7 +49989,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1794" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -50012,7 +50015,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1795" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -50038,7 +50041,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1796" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -50064,7 +50067,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1797" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -50090,7 +50093,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1798" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -50116,7 +50119,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1799" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -50142,7 +50145,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1800" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -50168,7 +50171,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1801" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -50194,7 +50197,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1802" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -50246,7 +50249,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1804" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -50272,7 +50275,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1805" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -50298,7 +50301,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1806" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -50324,7 +50327,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1807" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -50350,7 +50353,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1808" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -50428,7 +50431,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1811" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -50636,7 +50639,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1819" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -50818,7 +50821,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1826" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -50844,7 +50847,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1827" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -50870,7 +50873,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1828" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -50922,7 +50925,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1830" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -50948,7 +50951,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1831" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -50974,7 +50977,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1832" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -51000,7 +51003,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1833" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -51026,7 +51029,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -51052,7 +51055,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1835" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -51130,7 +51133,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1838" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -51286,7 +51289,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1844" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -51364,7 +51367,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1847" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -51546,7 +51549,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1854" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -51572,7 +51575,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1855" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -51598,7 +51601,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1856" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -51650,7 +51653,7 @@
         <v>3.9300000667572</v>
       </c>
       <c r="G1858" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -51676,7 +51679,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1859" t="s">
-        <v>642</v>
+        <v>694</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -51702,7 +51705,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1860" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -51754,7 +51757,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1862" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -51858,7 +51861,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1866" t="s">
-        <v>642</v>
+        <v>694</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -51884,7 +51887,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1867" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -52014,7 +52017,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1872" t="s">
-        <v>642</v>
+        <v>694</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -52144,7 +52147,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1877" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -52196,7 +52199,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1879" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -52222,7 +52225,7 @@
         <v>4</v>
       </c>
       <c r="G1880" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -52248,7 +52251,7 @@
         <v>4</v>
       </c>
       <c r="G1881" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -52274,7 +52277,7 @@
         <v>4</v>
       </c>
       <c r="G1882" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -52300,7 +52303,7 @@
         <v>4</v>
       </c>
       <c r="G1883" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -52326,7 +52329,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1884" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -52352,7 +52355,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1885" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -52378,7 +52381,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1886" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -52404,7 +52407,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1887" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -52430,7 +52433,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1888" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -52456,7 +52459,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1889" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -52482,7 +52485,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1890" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -52508,7 +52511,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1891" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -52534,7 +52537,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1892" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -52560,7 +52563,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1893" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -52586,7 +52589,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1894" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -52612,7 +52615,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -52638,7 +52641,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1896" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -52664,7 +52667,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1897" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -52690,7 +52693,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1898" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -52716,7 +52719,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1899" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -52742,7 +52745,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1900" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -52768,7 +52771,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G1901" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -52794,7 +52797,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1902" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -52820,7 +52823,7 @@
         <v>4</v>
       </c>
       <c r="G1903" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -52846,7 +52849,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1904" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -52872,7 +52875,7 @@
         <v>4</v>
       </c>
       <c r="G1905" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -52898,7 +52901,7 @@
         <v>4</v>
       </c>
       <c r="G1906" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -52924,7 +52927,7 @@
         <v>4</v>
       </c>
       <c r="G1907" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -52950,7 +52953,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1908" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -52976,7 +52979,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1909" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -53028,7 +53031,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1911" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -53496,7 +53499,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1929" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -53600,7 +53603,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1933" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -53704,7 +53707,7 @@
         <v>4.11999988555908</v>
       </c>
       <c r="G1937" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -53730,7 +53733,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1938" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -53756,7 +53759,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1939" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -53782,7 +53785,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G1940" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -53808,7 +53811,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1941" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -53834,7 +53837,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1942" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -53886,7 +53889,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1944" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -53964,7 +53967,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1947" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -53990,7 +53993,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1948" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -54016,7 +54019,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1949" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -54042,7 +54045,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G1950" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -54068,7 +54071,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G1951" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -54094,7 +54097,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G1952" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -54120,7 +54123,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1953" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -54146,7 +54149,7 @@
         <v>4</v>
       </c>
       <c r="G1954" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -54172,7 +54175,7 @@
         <v>4</v>
       </c>
       <c r="G1955" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -54198,7 +54201,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1956" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -54224,7 +54227,7 @@
         <v>4</v>
       </c>
       <c r="G1957" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -54250,7 +54253,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1958" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -54874,7 +54877,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1982" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -54978,7 +54981,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1986" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -55160,7 +55163,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1993" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -55186,7 +55189,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1994" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -55264,7 +55267,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G1997" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -55342,7 +55345,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2000" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -55368,7 +55371,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2001" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -55394,7 +55397,7 @@
         <v>4</v>
       </c>
       <c r="G2002" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -55420,7 +55423,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2003" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -55472,7 +55475,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G2005" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -55498,7 +55501,7 @@
         <v>4</v>
       </c>
       <c r="G2006" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -55524,7 +55527,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2007" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -55550,7 +55553,7 @@
         <v>4</v>
       </c>
       <c r="G2008" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -55576,7 +55579,7 @@
         <v>4</v>
       </c>
       <c r="G2009" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -55654,7 +55657,7 @@
         <v>4</v>
       </c>
       <c r="G2012" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -55680,7 +55683,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G2013" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -55706,7 +55709,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2014" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -55732,7 +55735,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2015" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -55758,7 +55761,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2016" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -55784,7 +55787,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G2017" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -55810,7 +55813,7 @@
         <v>4</v>
       </c>
       <c r="G2018" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -55836,7 +55839,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2019" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -55862,7 +55865,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2020" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -55888,7 +55891,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2021" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -55914,7 +55917,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G2022" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -55940,7 +55943,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2023" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -55992,7 +55995,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2025" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -56018,7 +56021,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2026" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -56044,7 +56047,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G2027" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -56096,7 +56099,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2029" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -56122,7 +56125,7 @@
         <v>4.1100001335144</v>
       </c>
       <c r="G2030" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -56148,7 +56151,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2031" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -56200,7 +56203,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2033" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -56486,7 +56489,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2044" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -57136,7 +57139,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2069" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -57214,7 +57217,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G2072" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -57240,7 +57243,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G2073" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -57318,7 +57321,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G2076" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -57344,7 +57347,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G2077" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -69364,7 +69367,7 @@
     </row>
     <row r="2540">
       <c r="A2540" s="1" t="n">
-        <v>46020.691087963</v>
+        <v>46020.3333333333</v>
       </c>
       <c r="B2540" t="n">
         <v>83721</v>
@@ -69385,6 +69388,32 @@
         <v>999</v>
       </c>
       <c r="H2540" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2541">
+      <c r="A2541" s="1" t="n">
+        <v>46021.6913078704</v>
+      </c>
+      <c r="B2541" t="n">
+        <v>42834</v>
+      </c>
+      <c r="C2541" t="n">
+        <v>9.42000007629395</v>
+      </c>
+      <c r="D2541" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2541" t="n">
+        <v>9.19999980926514</v>
+      </c>
+      <c r="F2541" t="n">
+        <v>9.30000019073486</v>
+      </c>
+      <c r="G2541" t="s">
+        <v>1000</v>
+      </c>
+      <c r="H2541" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652255535126</t>
+    <t xml:space="preserve">1.73652243614197</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400770664215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71406757831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6616724729538</t>
+    <t xml:space="preserve">1.74400758743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71406733989716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167259216309</t>
   </si>
   <si>
     <t xml:space="preserve">1.67215144634247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969646930695</t>
+    <t xml:space="preserve">1.64969635009766</t>
   </si>
   <si>
     <t xml:space="preserve">1.63921773433685</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57334959506989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49625384807587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48053538799286</t>
+    <t xml:space="preserve">1.5733494758606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49625372886658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48053526878357</t>
   </si>
   <si>
     <t xml:space="preserve">1.48203229904175</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43637371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460725784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4221522808075</t>
+    <t xml:space="preserve">1.43637382984161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460701942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42215216159821</t>
   </si>
   <si>
     <t xml:space="preserve">1.41990661621094</t>
@@ -89,10 +89,10 @@
     <t xml:space="preserve">1.4146671295166</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41915822029114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.407182097435</t>
+    <t xml:space="preserve">1.41915810108185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40718221664429</t>
   </si>
   <si>
     <t xml:space="preserve">1.3824816942215</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">1.35703265666962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33607459068298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34730195999146</t>
+    <t xml:space="preserve">1.33607447147369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34730207920074</t>
   </si>
   <si>
     <t xml:space="preserve">1.3428111076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38397860527039</t>
+    <t xml:space="preserve">1.3839784860611</t>
   </si>
   <si>
     <t xml:space="preserve">1.35478699207306</t>
@@ -125,25 +125,25 @@
     <t xml:space="preserve">1.38098478317261</t>
   </si>
   <si>
-    <t xml:space="preserve">1.36975705623627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873923778534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113422393799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41017603874207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44535577297211</t>
+    <t xml:space="preserve">1.36975693702698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873935699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43113386631012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41017615795135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44535601139069</t>
   </si>
   <si>
     <t xml:space="preserve">1.462571144104</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51197230815887</t>
+    <t xml:space="preserve">1.51197218894958</t>
   </si>
   <si>
     <t xml:space="preserve">1.5254453420639</t>
@@ -158,19 +158,19 @@
     <t xml:space="preserve">1.54191207885742</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54939746856689</t>
+    <t xml:space="preserve">1.5493973493576</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287038326263</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60029530525208</t>
+    <t xml:space="preserve">1.60029554367065</t>
   </si>
   <si>
     <t xml:space="preserve">1.60927760601044</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63173270225525</t>
+    <t xml:space="preserve">1.63173258304596</t>
   </si>
   <si>
     <t xml:space="preserve">1.62424743175507</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">1.65418756008148</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64370882511139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682239055634</t>
+    <t xml:space="preserve">1.64370858669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682227134705</t>
   </si>
   <si>
     <t xml:space="preserve">1.58831930160522</t>
@@ -200,34 +200,34 @@
     <t xml:space="preserve">1.66017556190491</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66915762424469</t>
+    <t xml:space="preserve">1.66915774345398</t>
   </si>
   <si>
     <t xml:space="preserve">1.68712139129639</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69161248207092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6931095123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155261039734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502588272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358884334564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658266544342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909775257111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664277553558</t>
+    <t xml:space="preserve">1.6916127204895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69310927391052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155272960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502576351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358860492706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658254623413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909739494324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.676642537117</t>
   </si>
   <si>
     <t xml:space="preserve">1.68412744998932</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">1.66766047477722</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68263041973114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221155643463</t>
+    <t xml:space="preserve">1.68263018131256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221167564392</t>
   </si>
   <si>
     <t xml:space="preserve">1.64670264720917</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">1.67514550685883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69964480400085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6843329668045</t>
+    <t xml:space="preserve">1.69964492321014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68433284759521</t>
   </si>
   <si>
     <t xml:space="preserve">1.69198894500732</t>
@@ -260,37 +260,37 @@
     <t xml:space="preserve">1.72108173370361</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70576977729797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69505143165588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72261309623718</t>
+    <t xml:space="preserve">1.70576965808868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69505131244659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495711803436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72261297702789</t>
   </si>
   <si>
     <t xml:space="preserve">1.65370857715607</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67208302021027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66902089118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65217733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60624122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56183588504791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55417990684509</t>
+    <t xml:space="preserve">1.67208313941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66902077198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65217745304108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.606241106987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5618360042572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417966842651</t>
   </si>
   <si>
     <t xml:space="preserve">1.52202439308167</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">1.53121173381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59092879295349</t>
+    <t xml:space="preserve">1.59092903137207</t>
   </si>
   <si>
     <t xml:space="preserve">1.52891480922699</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">1.55111742019653</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53886759281158</t>
+    <t xml:space="preserve">1.53886783123016</t>
   </si>
   <si>
     <t xml:space="preserve">1.49293148517609</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">1.47608804702759</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52278995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996319293976</t>
+    <t xml:space="preserve">1.52278983592987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996307373047</t>
   </si>
   <si>
     <t xml:space="preserve">1.47761917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589965820312</t>
+    <t xml:space="preserve">1.51589953899384</t>
   </si>
   <si>
     <t xml:space="preserve">1.50058734416962</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60777223110199</t>
+    <t xml:space="preserve">1.60777235031128</t>
   </si>
   <si>
     <t xml:space="preserve">1.5970538854599</t>
@@ -344,31 +344,31 @@
     <t xml:space="preserve">1.62308430671692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66748976707458</t>
+    <t xml:space="preserve">1.6674896478653</t>
   </si>
   <si>
     <t xml:space="preserve">1.66136467456818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.6766768693924</t>
+    <t xml:space="preserve">1.67667675018311</t>
   </si>
   <si>
     <t xml:space="preserve">1.6154283285141</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57714784145355</t>
+    <t xml:space="preserve">1.57714796066284</t>
   </si>
   <si>
     <t xml:space="preserve">1.58480417728424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63839650154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63380300998688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57561671733856</t>
+    <t xml:space="preserve">1.63839673995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63380312919617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
     <t xml:space="preserve">1.54652380943298</t>
@@ -383,16 +383,16 @@
     <t xml:space="preserve">1.52355551719666</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54193007946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58174169063568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55877339839935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5802104473114</t>
+    <t xml:space="preserve">1.54192996025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174157142639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55877327919006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58021032810211</t>
   </si>
   <si>
     <t xml:space="preserve">1.55264866352081</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">1.53427398204803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56642961502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57408547401428</t>
+    <t xml:space="preserve">1.56642949581146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57408559322357</t>
   </si>
   <si>
     <t xml:space="preserve">1.58327305316925</t>
@@ -425,70 +425,70 @@
     <t xml:space="preserve">1.59246003627777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50211882591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824344158173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47532224655151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49675941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50747799873352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52968060970306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60011613368988</t>
+    <t xml:space="preserve">1.5021185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824332237244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47532248497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49675953388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50747776031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52968037128448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60011601448059</t>
   </si>
   <si>
     <t xml:space="preserve">1.58786642551422</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56489825248718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56336712837219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255423069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59858500957489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59399127960205</t>
+    <t xml:space="preserve">1.56489813327789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5633670091629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255434989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5985848903656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59399151802063</t>
   </si>
   <si>
     <t xml:space="preserve">1.60470986366272</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64758372306824</t>
+    <t xml:space="preserve">1.64758360385895</t>
   </si>
   <si>
     <t xml:space="preserve">1.64605271816254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68280160427094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63074040412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63686513900757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64452123641968</t>
+    <t xml:space="preserve">1.68280172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63074052333832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63686537742615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64452147483826</t>
   </si>
   <si>
     <t xml:space="preserve">1.6322717666626</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66289579868317</t>
+    <t xml:space="preserve">1.66289591789246</t>
   </si>
   <si>
     <t xml:space="preserve">1.66595852375031</t>
@@ -497,13 +497,13 @@
     <t xml:space="preserve">1.73333144187927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73026907444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558138847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017488002777</t>
+    <t xml:space="preserve">1.73026931285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558115005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017499923706</t>
   </si>
   <si>
     <t xml:space="preserve">1.70730102062225</t>
@@ -515,43 +515,43 @@
     <t xml:space="preserve">1.7379252910614</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75936210155487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76089334487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78386163711548</t>
+    <t xml:space="preserve">1.75936198234558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76089346408844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78386151790619</t>
   </si>
   <si>
     <t xml:space="preserve">1.76854920387268</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75323736667633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486280441284</t>
+    <t xml:space="preserve">1.75323724746704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486256599426</t>
   </si>
   <si>
     <t xml:space="preserve">1.73639416694641</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79151773452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223619937897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061052322388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754815578461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520413398743</t>
+    <t xml:space="preserve">1.79151737689972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223608016968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061076164246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8175482749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682969093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520425319672</t>
   </si>
   <si>
     <t xml:space="preserve">1.81448578834534</t>
@@ -560,73 +560,73 @@
     <t xml:space="preserve">1.85889077186584</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87726545333862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85429680347443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582828521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85123515129089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86654710769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84970378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348462104797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276615619659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745419979095</t>
+    <t xml:space="preserve">1.87726557254791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85429716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582864284515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8512350320816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86654698848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84970366954803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348474025726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8527660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745431900024</t>
   </si>
   <si>
     <t xml:space="preserve">1.84511005878448</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82367312908173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051668643951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817254543304</t>
+    <t xml:space="preserve">1.82367336750031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051656723022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817266464233</t>
   </si>
   <si>
     <t xml:space="preserve">1.86807823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94923233985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788984298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92167067527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932665348053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473328113556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607613563538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904418945312</t>
+    <t xml:space="preserve">1.94923269748688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788996219635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92167043685913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932641506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473304271698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607601642609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904383182526</t>
   </si>
   <si>
     <t xml:space="preserve">1.99823117256165</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00894951820374</t>
+    <t xml:space="preserve">2.00895023345947</t>
   </si>
   <si>
     <t xml:space="preserve">2.00741863250732</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">2.01201200485229</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99057495594025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0028247833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00588726997375</t>
+    <t xml:space="preserve">1.99057483673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00282502174377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00588703155518</t>
   </si>
   <si>
     <t xml:space="preserve">2.09207797050476</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09051060676575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401724815369</t>
+    <t xml:space="preserve">2.09051084518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401700973511</t>
   </si>
   <si>
     <t xml:space="preserve">2.08424234390259</t>
@@ -659,43 +659,43 @@
     <t xml:space="preserve">2.11558413505554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17043280601501</t>
+    <t xml:space="preserve">2.17043256759644</t>
   </si>
   <si>
     <t xml:space="preserve">2.14692616462708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15006041526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655377388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259694099426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15162754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13909077644348</t>
+    <t xml:space="preserve">2.15006065368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655401229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259717941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15162777900696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1390905380249</t>
   </si>
   <si>
     <t xml:space="preserve">2.16103005409241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04663181304932</t>
+    <t xml:space="preserve">2.0466320514679</t>
   </si>
   <si>
     <t xml:space="preserve">2.05290007591248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03722882270813</t>
+    <t xml:space="preserve">2.03722906112671</t>
   </si>
   <si>
     <t xml:space="preserve">2.04819893836975</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04506492614746</t>
+    <t xml:space="preserve">2.04506468772888</t>
   </si>
   <si>
     <t xml:space="preserve">2.06543707847595</t>
@@ -704,43 +704,43 @@
     <t xml:space="preserve">2.06073570251465</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10774874687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11715126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12341928482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125538825989</t>
+    <t xml:space="preserve">2.10774898529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11715149879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12342023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125491142273</t>
   </si>
   <si>
     <t xml:space="preserve">2.18296933174133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19393944740295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647621154785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2033417224884</t>
+    <t xml:space="preserve">2.19393920898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647597312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20334196090698</t>
   </si>
   <si>
     <t xml:space="preserve">2.19237208366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20804286003113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416430473328</t>
+    <t xml:space="preserve">2.20804309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16416454315186</t>
   </si>
   <si>
     <t xml:space="preserve">2.15946292877197</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13595628738403</t>
+    <t xml:space="preserve">2.13595676422119</t>
   </si>
   <si>
     <t xml:space="preserve">2.09677910804749</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">2.06386995315552</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827709674835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805152416229</t>
+    <t xml:space="preserve">2.02625966072083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805176258087</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640671730042</t>
@@ -764,13 +764,13 @@
     <t xml:space="preserve">2.05446743965149</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10461497306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700396537781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566217422485</t>
+    <t xml:space="preserve">2.10461449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566193580627</t>
   </si>
   <si>
     <t xml:space="preserve">2.04976606369019</t>
@@ -779,43 +779,43 @@
     <t xml:space="preserve">2.07954120635986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0685715675354</t>
+    <t xml:space="preserve">2.06857132911682</t>
   </si>
   <si>
     <t xml:space="preserve">2.07797384262085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24095249176025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371411323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117734909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23311638832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31460571289062</t>
+    <t xml:space="preserve">2.24095225334167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371435165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21117758750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23311614990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781800270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930708885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31460618972778</t>
   </si>
   <si>
     <t xml:space="preserve">2.32714295387268</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32557582855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982653617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3866925239563</t>
+    <t xml:space="preserve">2.32557535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982629776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38669276237488</t>
   </si>
   <si>
     <t xml:space="preserve">2.44467520713806</t>
@@ -827,58 +827,58 @@
     <t xml:space="preserve">2.48541975021362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49012112617493</t>
+    <t xml:space="preserve">2.49012088775635</t>
   </si>
   <si>
     <t xml:space="preserve">2.5214626789093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50735926628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5387008190155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53086590766907</t>
+    <t xml:space="preserve">2.50735902786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53870105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53086566925049</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168825149536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50422525405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952340126038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52302980422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53243255615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206064224243</t>
+    <t xml:space="preserve">2.50422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952387809753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52303004264832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53243279457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206088066101</t>
   </si>
   <si>
     <t xml:space="preserve">2.5089259147644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51362752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795651435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638938903809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616429328918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55123782157898</t>
+    <t xml:space="preserve">2.51362729072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4979567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638915061951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616453170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653668403625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55123805999756</t>
   </si>
   <si>
     <t xml:space="preserve">2.53713393211365</t>
@@ -893,37 +893,37 @@
     <t xml:space="preserve">2.70794773101807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71108222007751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220516204834</t>
+    <t xml:space="preserve">2.71108198165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205138206482</t>
   </si>
   <si>
     <t xml:space="preserve">2.69541096687317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70324659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67347145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406893730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705613136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981799125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58728122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5982506275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58571434020996</t>
+    <t xml:space="preserve">2.70324683189392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67347168922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705589294434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728098869324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59825086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58571410179138</t>
   </si>
   <si>
     <t xml:space="preserve">2.57004308700562</t>
@@ -932,61 +932,61 @@
     <t xml:space="preserve">2.56220746040344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54183530807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51989579200745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52929830551147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52459716796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034622192383</t>
+    <t xml:space="preserve">2.54183554649353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51989555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52929854393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52459692955017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034598350525</t>
   </si>
   <si>
     <t xml:space="preserve">2.47131586074829</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43370509147644</t>
+    <t xml:space="preserve">2.48228573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43370532989502</t>
   </si>
   <si>
     <t xml:space="preserve">2.39609503746033</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32087397575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27699542045593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2879650592804</t>
+    <t xml:space="preserve">2.32087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206894874573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975728034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27699518203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28796553611755</t>
   </si>
   <si>
     <t xml:space="preserve">2.34908199310303</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36475324630737</t>
+    <t xml:space="preserve">2.36475276947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.35064911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35848474502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333293914795</t>
+    <t xml:space="preserve">2.35848450660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333317756653</t>
   </si>
   <si>
     <t xml:space="preserve">2.43683934211731</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">2.62489128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63272714614868</t>
+    <t xml:space="preserve">2.6327269077301</t>
   </si>
   <si>
     <t xml:space="preserve">2.468181848526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36632037162781</t>
+    <t xml:space="preserve">2.36632013320923</t>
   </si>
   <si>
     <t xml:space="preserve">2.381991147995</t>
@@ -1016,28 +1016,28 @@
     <t xml:space="preserve">2.40549778938293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42116832733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900395393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878740310669</t>
+    <t xml:space="preserve">2.42116856575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878764152527</t>
   </si>
   <si>
     <t xml:space="preserve">2.30363631248474</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25662326812744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27229428291321</t>
+    <t xml:space="preserve">2.25662350654602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27229404449463</t>
   </si>
   <si>
     <t xml:space="preserve">2.28012990951538</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26445865631104</t>
+    <t xml:space="preserve">2.26445889472961</t>
   </si>
   <si>
     <t xml:space="preserve">2.22528123855591</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">2.11558437347412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12359762191772</t>
+    <t xml:space="preserve">2.1235978603363</t>
   </si>
   <si>
     <t xml:space="preserve">2.0995569229126</t>
@@ -1058,16 +1058,16 @@
     <t xml:space="preserve">2.09154343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942133903503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00339388847351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750249862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1877064704895</t>
+    <t xml:space="preserve">2.01942110061646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00339412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750273704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18770623207092</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188275337219</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">2.13962507247925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16366577148438</t>
+    <t xml:space="preserve">2.1636655330658</t>
   </si>
   <si>
     <t xml:space="preserve">2.14763855934143</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">2.20373344421387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13161158561707</t>
+    <t xml:space="preserve">2.13161134719849</t>
   </si>
   <si>
     <t xml:space="preserve">2.17167925834656</t>
@@ -1094,28 +1094,28 @@
     <t xml:space="preserve">2.19572019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17969250679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10757088661194</t>
+    <t xml:space="preserve">2.17969298362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10757064819336</t>
   </si>
   <si>
     <t xml:space="preserve">2.05948901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07551646232605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0354483127594</t>
+    <t xml:space="preserve">2.07551622390747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03544855117798</t>
   </si>
   <si>
     <t xml:space="preserve">2.05147576332092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27585601806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784229278564</t>
+    <t xml:space="preserve">2.27585577964783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784205436707</t>
   </si>
   <si>
     <t xml:space="preserve">2.21976041793823</t>
@@ -1130,7 +1130,7 @@
     <t xml:space="preserve">2.23578786849976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22777414321899</t>
+    <t xml:space="preserve">2.22777438163757</t>
   </si>
   <si>
     <t xml:space="preserve">2.15565228462219</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">2.30791020393372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02743530273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04346179962158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99538052082062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524469852448</t>
+    <t xml:space="preserve">2.0274350643158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04346203804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9953807592392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524481773376</t>
   </si>
   <si>
     <t xml:space="preserve">1.92325842380524</t>
@@ -1160,46 +1160,46 @@
     <t xml:space="preserve">1.97133994102478</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98736727237701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140761375427</t>
+    <t xml:space="preserve">1.98736715316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140785217285</t>
   </si>
   <si>
     <t xml:space="preserve">1.8110682964325</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81908190250397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8431224822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79504132270813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901411056519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709538936615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100050449371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73093247413635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69887804985046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71490550041199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7469596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72291910648346</t>
+    <t xml:space="preserve">1.81908178329468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84312260150909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79504108428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7790139913559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709527015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.771000623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73093259334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69887793064117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71490561962128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74695992469788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72291922569275</t>
   </si>
   <si>
     <t xml:space="preserve">1.73894619941711</t>
@@ -1208,37 +1208,37 @@
     <t xml:space="preserve">1.76298677921295</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75497353076935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305469036102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85914981365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86716318130493</t>
+    <t xml:space="preserve">1.75497341156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305457115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85914969444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86716330051422</t>
   </si>
   <si>
     <t xml:space="preserve">1.83510887622833</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87517690658569</t>
+    <t xml:space="preserve">1.87517666816711</t>
   </si>
   <si>
     <t xml:space="preserve">1.90723145008087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97935318946838</t>
+    <t xml:space="preserve">1.97935307025909</t>
   </si>
   <si>
     <t xml:space="preserve">1.93928563594818</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02082967758179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258111000061</t>
+    <t xml:space="preserve">2.02082943916321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258134841919</t>
   </si>
   <si>
     <t xml:space="preserve">1.9713397026062</t>
@@ -1247,37 +1247,37 @@
     <t xml:space="preserve">1.98783659934998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99608480930328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96309173107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834674358368</t>
+    <t xml:space="preserve">1.99608469009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96309161186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93834662437439</t>
   </si>
   <si>
     <t xml:space="preserve">1.97958815097809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03732585906982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06207060813904</t>
+    <t xml:space="preserve">2.03732562065125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06207084655762</t>
   </si>
   <si>
     <t xml:space="preserve">2.0538227558136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09506392478943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16929888725281</t>
+    <t xml:space="preserve">2.09506416320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16929864883423</t>
   </si>
   <si>
     <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11156058311462</t>
+    <t xml:space="preserve">2.1115608215332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10331225395203</t>
@@ -1301,13 +1301,13 @@
     <t xml:space="preserve">2.22703647613525</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21878862380981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25178146362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24353289604187</t>
+    <t xml:space="preserve">2.21878838539124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25178122520447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24353337287903</t>
   </si>
   <si>
     <t xml:space="preserve">2.21054005622864</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">2.32601571083069</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27652621269226</t>
+    <t xml:space="preserve">2.27652645111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.28477430343628</t>
@@ -1352,13 +1352,13 @@
     <t xml:space="preserve">2.23528480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200234413147</t>
+    <t xml:space="preserve">2.39200210571289</t>
   </si>
   <si>
     <t xml:space="preserve">2.44974040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4167468547821</t>
+    <t xml:space="preserve">2.41674709320068</t>
   </si>
   <si>
     <t xml:space="preserve">2.43324375152588</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">2.40849900245667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42499589920044</t>
+    <t xml:space="preserve">2.42499566078186</t>
   </si>
   <si>
     <t xml:space="preserve">2.45798850059509</t>
@@ -1376,10 +1376,10 @@
     <t xml:space="preserve">2.49922966957092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47448515892029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5157265663147</t>
+    <t xml:space="preserve">2.47448492050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51572632789612</t>
   </si>
   <si>
     <t xml:space="preserve">2.58996105194092</t>
@@ -1388,7 +1388,7 @@
     <t xml:space="preserve">2.54871940612793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49098205566406</t>
+    <t xml:space="preserve">2.49098181724548</t>
   </si>
   <si>
     <t xml:space="preserve">2.5074782371521</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3507604598999</t>
+    <t xml:space="preserve">2.35076069831848</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025067329407</t>
@@ -1406,7 +1406,7 @@
     <t xml:space="preserve">2.19404339790344</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18579506874084</t>
+    <t xml:space="preserve">2.18579530715942</t>
   </si>
   <si>
     <t xml:space="preserve">2.045574426651</t>
@@ -1421,10 +1421,10 @@
     <t xml:space="preserve">1.68264985084534</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69089818000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56717395782471</t>
+    <t xml:space="preserve">1.69089806079865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.567174077034</t>
   </si>
   <si>
     <t xml:space="preserve">1.71564292907715</t>
@@ -1433,16 +1433,16 @@
     <t xml:space="preserve">1.64553260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64140844345093</t>
+    <t xml:space="preserve">1.64140856266022</t>
   </si>
   <si>
     <t xml:space="preserve">1.62491178512573</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77338111400604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162920475006</t>
+    <t xml:space="preserve">1.77338123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162932395935</t>
   </si>
   <si>
     <t xml:space="preserve">1.74863588809967</t>
@@ -1451,19 +1451,19 @@
     <t xml:space="preserve">1.80637431144714</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86411201953888</t>
+    <t xml:space="preserve">1.86411213874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.00433301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81462228298187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287073135376</t>
+    <t xml:space="preserve">1.81462240219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287085056305</t>
   </si>
   <si>
     <t xml:space="preserve">1.84761559963226</t>
@@ -1478,7 +1478,7 @@
     <t xml:space="preserve">1.88885676860809</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91360187530518</t>
+    <t xml:space="preserve">1.91360175609589</t>
   </si>
   <si>
     <t xml:space="preserve">1.89710521697998</t>
@@ -1487,19 +1487,19 @@
     <t xml:space="preserve">1.90535342693329</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95484328269958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02907776832581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08681607246399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17754697799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07031917572021</t>
+    <t xml:space="preserve">1.95484340190887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02907800674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08681583404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17754721641541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07031941413879</t>
   </si>
   <si>
     <t xml:space="preserve">2.07786917686462</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">2.06938791275024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98457682132721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609567642212</t>
+    <t xml:space="preserve">2.03546380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98457670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609579563141</t>
   </si>
   <si>
     <t xml:space="preserve">1.95065248012543</t>
@@ -1529,7 +1529,7 @@
     <t xml:space="preserve">2.02698230743408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05242586135864</t>
+    <t xml:space="preserve">2.05242562294006</t>
   </si>
   <si>
     <t xml:space="preserve">2.04394483566284</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">2.0015389919281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.89976608753204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88280379772186</t>
+    <t xml:space="preserve">1.89976596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88280367851257</t>
   </si>
   <si>
     <t xml:space="preserve">1.89128494262695</t>
@@ -1562,19 +1562,19 @@
     <t xml:space="preserve">2.12875556945801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12027430534363</t>
+    <t xml:space="preserve">2.12027454376221</t>
   </si>
   <si>
     <t xml:space="preserve">2.16267991065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20508527755737</t>
+    <t xml:space="preserve">2.20508503913879</t>
   </si>
   <si>
     <t xml:space="preserve">2.23052906990051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3068585395813</t>
+    <t xml:space="preserve">2.30685877799988</t>
   </si>
   <si>
     <t xml:space="preserve">2.33230185508728</t>
@@ -1598,7 +1598,7 @@
     <t xml:space="preserve">2.46799969673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49344325065613</t>
+    <t xml:space="preserve">2.49344301223755</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040506362915</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">2.51888632774353</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58673501014709</t>
+    <t xml:space="preserve">2.58673477172852</t>
   </si>
   <si>
     <t xml:space="preserve">2.56977248191833</t>
@@ -1628,16 +1628,16 @@
     <t xml:space="preserve">2.56129193305969</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55281043052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53584837913513</t>
+    <t xml:space="preserve">2.55281019210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53584861755371</t>
   </si>
   <si>
     <t xml:space="preserve">2.52736711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64610266685486</t>
+    <t xml:space="preserve">2.64610242843628</t>
   </si>
   <si>
     <t xml:space="preserve">2.63762140274048</t>
@@ -1652,7 +1652,7 @@
     <t xml:space="preserve">2.69698929786682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62914037704468</t>
+    <t xml:space="preserve">2.6291401386261</t>
   </si>
   <si>
     <t xml:space="preserve">2.71395134925842</t>
@@ -1679,7 +1679,7 @@
     <t xml:space="preserve">2.90901684761047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85813021659851</t>
+    <t xml:space="preserve">2.85812997817993</t>
   </si>
   <si>
     <t xml:space="preserve">2.80724334716797</t>
@@ -1688,10 +1688,10 @@
     <t xml:space="preserve">2.75635671615601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73939490318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74787569046021</t>
+    <t xml:space="preserve">2.7393946647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74787592887878</t>
   </si>
   <si>
     <t xml:space="preserve">2.79876232147217</t>
@@ -1703,13 +1703,13 @@
     <t xml:space="preserve">2.84964895248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268666267395</t>
+    <t xml:space="preserve">2.83268690109253</t>
   </si>
   <si>
     <t xml:space="preserve">2.82420563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91749787330627</t>
+    <t xml:space="preserve">2.9174976348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.01078963279724</t>
@@ -1718,16 +1718,16 @@
     <t xml:space="preserve">3.03623294830322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95990324020386</t>
+    <t xml:space="preserve">2.95990347862244</t>
   </si>
   <si>
     <t xml:space="preserve">3.07863855361938</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08712005615234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12104415893555</t>
+    <t xml:space="preserve">3.08711981773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12104392051697</t>
   </si>
   <si>
     <t xml:space="preserve">3.18041205406189</t>
@@ -1745,10 +1745,10 @@
     <t xml:space="preserve">3.23129820823669</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24826049804688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433615684509</t>
+    <t xml:space="preserve">3.24826073646545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433591842651</t>
   </si>
   <si>
     <t xml:space="preserve">3.28218483924866</t>
@@ -1757,16 +1757,16 @@
     <t xml:space="preserve">3.40092039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42636322975159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3669958114624</t>
+    <t xml:space="preserve">3.42636346817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36699604988098</t>
   </si>
   <si>
     <t xml:space="preserve">3.31610941886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29066634178162</t>
+    <t xml:space="preserve">3.2906665802002</t>
   </si>
   <si>
     <t xml:space="preserve">3.27370381355286</t>
@@ -69715,7 +69715,7 @@
     </row>
     <row r="2552">
       <c r="A2552" s="1" t="n">
-        <v>46038.6911458333</v>
+        <v>46038.3333333333</v>
       </c>
       <c r="B2552" t="n">
         <v>47167</v>
@@ -69736,6 +69736,32 @@
         <v>1012</v>
       </c>
       <c r="H2552" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2553">
+      <c r="A2553" s="1" t="n">
+        <v>46041.6911574074</v>
+      </c>
+      <c r="B2553" t="n">
+        <v>34396</v>
+      </c>
+      <c r="C2553" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="D2553" t="n">
+        <v>9.85999965667725</v>
+      </c>
+      <c r="E2553" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2553" t="n">
+        <v>9.96000003814697</v>
+      </c>
+      <c r="G2553" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H2553" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652267456055</t>
+    <t xml:space="preserve">1.73652243614197</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400782585144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71406769752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167271137238</t>
+    <t xml:space="preserve">1.74400758743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71406781673431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167259216309</t>
   </si>
   <si>
     <t xml:space="preserve">1.67215144634247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969670772552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921761512756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57334935665131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49625372886658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48053514957428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48203241825104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4363739490509</t>
+    <t xml:space="preserve">1.64969635009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921749591827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57334923744202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49625384807587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48053538799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48203229904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637371063232</t>
   </si>
   <si>
     <t xml:space="preserve">1.44460713863373</t>
   </si>
   <si>
-    <t xml:space="preserve">1.42215216159821</t>
+    <t xml:space="preserve">1.42215204238892</t>
   </si>
   <si>
     <t xml:space="preserve">1.41990661621094</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">1.41915822029114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.40718221664429</t>
+    <t xml:space="preserve">1.407182097435</t>
   </si>
   <si>
     <t xml:space="preserve">1.38248157501221</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">1.38472712039948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39820027351379</t>
+    <t xml:space="preserve">1.39820003509521</t>
   </si>
   <si>
     <t xml:space="preserve">1.35703253746033</t>
   </si>
   <si>
-    <t xml:space="preserve">1.33607459068298</t>
+    <t xml:space="preserve">1.3360743522644</t>
   </si>
   <si>
     <t xml:space="preserve">1.34730195999146</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">1.3428111076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38397860527039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478723049164</t>
+    <t xml:space="preserve">1.3839784860611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478699207306</t>
   </si>
   <si>
     <t xml:space="preserve">1.38098466396332</t>
@@ -128,73 +128,73 @@
     <t xml:space="preserve">1.36975717544556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37873899936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113434314728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41017603874207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44535565376282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46257138252258</t>
+    <t xml:space="preserve">1.37873935699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4311341047287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41017615795135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44535577297211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46257126331329</t>
   </si>
   <si>
     <t xml:space="preserve">1.51197230815887</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52544558048248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52245116233826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54490613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191207885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5493973493576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56287062168121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60029554367065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60927772521973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173270225525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6302353143692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676251888275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418756008148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64370858669281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682239055634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58831930160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472664356232</t>
+    <t xml:space="preserve">1.5254453420639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52245128154755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54490637779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191219806671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54939723014832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56287038326263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60029566287994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60927748680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173258304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424731254578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63023567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676263809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418744087219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370846748352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682227134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58831942081451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472652435303</t>
   </si>
   <si>
     <t xml:space="preserve">1.66017544269562</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">1.66915762424469</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68712162971497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69161283969879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69310975074768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72155261039734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502588272095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.706582903862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909763336182</t>
+    <t xml:space="preserve">1.68712151050568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69161248207092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6931095123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72155284881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502564430237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358860492706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70658278465271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909739494324</t>
   </si>
   <si>
     <t xml:space="preserve">1.676642537117</t>
@@ -233,19 +233,19 @@
     <t xml:space="preserve">1.68412756919861</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66766035556793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263053894043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64221143722534</t>
+    <t xml:space="preserve">1.66766059398651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263030052185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64221155643463</t>
   </si>
   <si>
     <t xml:space="preserve">1.64670264720917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67514550685883</t>
+    <t xml:space="preserve">1.6751457452774</t>
   </si>
   <si>
     <t xml:space="preserve">1.69964504241943</t>
@@ -257,19 +257,19 @@
     <t xml:space="preserve">1.69198882579803</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7210818529129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7057694196701</t>
+    <t xml:space="preserve">1.72108161449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70576977729797</t>
   </si>
   <si>
     <t xml:space="preserve">1.69505143165588</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71495699882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72261309623718</t>
+    <t xml:space="preserve">1.71495711803436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72261321544647</t>
   </si>
   <si>
     <t xml:space="preserve">1.65370857715607</t>
@@ -278,43 +278,43 @@
     <t xml:space="preserve">1.67208325862885</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66902089118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65217733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60624098777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5618360042572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5541797876358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202451229095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53121185302734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59092915058136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52891480922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55111753940582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53886783123016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49293160438538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4760879278183</t>
+    <t xml:space="preserve">1.66902077198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65217745304108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.606241106987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56183576583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55417990684509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202439308167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53121173381805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59092903137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52891492843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55111730098724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53886771202087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4929313659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608804702759</t>
   </si>
   <si>
     <t xml:space="preserve">1.52279007434845</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">1.47761917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589965820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5005875825882</t>
+    <t xml:space="preserve">1.51589953899384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058746337891</t>
   </si>
   <si>
     <t xml:space="preserve">1.6077721118927</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59705376625061</t>
+    <t xml:space="preserve">1.5970538854599</t>
   </si>
   <si>
     <t xml:space="preserve">1.56949198246002</t>
@@ -344,28 +344,28 @@
     <t xml:space="preserve">1.62308418750763</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66748929023743</t>
+    <t xml:space="preserve">1.6674896478653</t>
   </si>
   <si>
     <t xml:space="preserve">1.66136467456818</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67667675018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61542820930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714772224426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58480405807495</t>
+    <t xml:space="preserve">1.6766768693924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61542844772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714807987213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58480393886566</t>
   </si>
   <si>
     <t xml:space="preserve">1.63839650154114</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63380289077759</t>
+    <t xml:space="preserve">1.6338027715683</t>
   </si>
   <si>
     <t xml:space="preserve">1.57561683654785</t>
@@ -374,43 +374,43 @@
     <t xml:space="preserve">1.54652380943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56796097755432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54499244689941</t>
+    <t xml:space="preserve">1.56796073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54499232769012</t>
   </si>
   <si>
     <t xml:space="preserve">1.52355563640594</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54193007946014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58174157142639</t>
+    <t xml:space="preserve">1.54192996025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174169063568</t>
   </si>
   <si>
     <t xml:space="preserve">1.55877351760864</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58021020889282</t>
+    <t xml:space="preserve">1.58021056652069</t>
   </si>
   <si>
     <t xml:space="preserve">1.5526487827301</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53044593334198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51972770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50594651699066</t>
+    <t xml:space="preserve">1.53044617176056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5197274684906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50594663619995</t>
   </si>
   <si>
     <t xml:space="preserve">1.50671219825745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53427398204803</t>
+    <t xml:space="preserve">1.53427410125732</t>
   </si>
   <si>
     <t xml:space="preserve">1.56642961502075</t>
@@ -419,25 +419,25 @@
     <t xml:space="preserve">1.57408571243286</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58327293395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59246003627777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50211882591248</t>
+    <t xml:space="preserve">1.58327281475067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59246015548706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5021185874939</t>
   </si>
   <si>
     <t xml:space="preserve">1.50824344158173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47532248497009</t>
+    <t xml:space="preserve">1.4753223657608</t>
   </si>
   <si>
     <t xml:space="preserve">1.49675929546356</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50747799873352</t>
+    <t xml:space="preserve">1.50747787952423</t>
   </si>
   <si>
     <t xml:space="preserve">1.52968049049377</t>
@@ -446,70 +446,70 @@
     <t xml:space="preserve">1.60011625289917</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58786642551422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489813327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56336712837219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255423069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59858524799347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59399127960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60470974445343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64758360385895</t>
+    <t xml:space="preserve">1.58786630630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489825248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5633670091629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255434989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59858500957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59399139881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60470998287201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64758384227753</t>
   </si>
   <si>
     <t xml:space="preserve">1.64605271816254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68280136585236</t>
+    <t xml:space="preserve">1.68280160427094</t>
   </si>
   <si>
     <t xml:space="preserve">1.63074052333832</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63686549663544</t>
+    <t xml:space="preserve">1.63686525821686</t>
   </si>
   <si>
     <t xml:space="preserve">1.64452135562897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63227164745331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66289567947388</t>
+    <t xml:space="preserve">1.6322717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66289591789246</t>
   </si>
   <si>
     <t xml:space="preserve">1.66595840454102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73333168029785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026943206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7455815076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017464160919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730102062225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423889160156</t>
+    <t xml:space="preserve">1.73333144187927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026907444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558115005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730090141296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423877239227</t>
   </si>
   <si>
     <t xml:space="preserve">1.73792517185211</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">1.75936222076416</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76089334487915</t>
+    <t xml:space="preserve">1.76089358329773</t>
   </si>
   <si>
     <t xml:space="preserve">1.78386175632477</t>
@@ -536,64 +536,64 @@
     <t xml:space="preserve">1.73639380931854</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79151785373688</t>
+    <t xml:space="preserve">1.79151773452759</t>
   </si>
   <si>
     <t xml:space="preserve">1.80223619937897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82061076164246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81754815578461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682981014252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82520425319672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448554992676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889077186584</t>
+    <t xml:space="preserve">1.82061064243317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8175482749939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682945251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8252044916153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448543071747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889101028442</t>
   </si>
   <si>
     <t xml:space="preserve">1.87726557254791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85429728031158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582852363586</t>
+    <t xml:space="preserve">1.85429751873016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582864284515</t>
   </si>
   <si>
     <t xml:space="preserve">1.85123479366302</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86654686927795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84970378875732</t>
+    <t xml:space="preserve">1.86654734611511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84970355033875</t>
   </si>
   <si>
     <t xml:space="preserve">1.86348462104797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85276579856873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511005878448</t>
+    <t xml:space="preserve">1.85276639461517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745396137238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84511017799377</t>
   </si>
   <si>
     <t xml:space="preserve">1.82367324829102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84051632881165</t>
+    <t xml:space="preserve">1.84051644802094</t>
   </si>
   <si>
     <t xml:space="preserve">1.84817266464233</t>
@@ -602,25 +602,25 @@
     <t xml:space="preserve">1.86807823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94923269748688</t>
+    <t xml:space="preserve">1.9492324590683</t>
   </si>
   <si>
     <t xml:space="preserve">1.90788984298706</t>
   </si>
   <si>
-    <t xml:space="preserve">1.921670794487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932677268982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473292350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607613563538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904383182526</t>
+    <t xml:space="preserve">1.92167055606842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932641506195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9247328042984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607577800751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904407024384</t>
   </si>
   <si>
     <t xml:space="preserve">1.99823117256165</t>
@@ -629,420 +629,423 @@
     <t xml:space="preserve">2.00894975662231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00741863250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01201224327087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99057495594025</t>
+    <t xml:space="preserve">2.00741839408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01201200485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99057519435883</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00588726997375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0920774936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051084518433</t>
+    <t xml:space="preserve">2.00588703155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09207773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051060676575</t>
   </si>
   <si>
     <t xml:space="preserve">2.11401700973511</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08424258232117</t>
+    <t xml:space="preserve">2.08424234390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558413505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17043280601501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14692640304565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15006017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655425071716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259694099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15162754058838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13909077644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16102981567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0466320514679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290007591248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03722929954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04819917678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0450644493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06543660163879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10774850845337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11715149879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12342023849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125562667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296933174133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1939389705658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647597312927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20334196090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19237208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20804309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16416430473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946292877197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13595676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677934646606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386995315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0262598991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827697753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805200099945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07640671730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05446720123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10461449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566241264343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954096794128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06857132911682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797360420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2409520149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371411323547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.211177110672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23311638832092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781800270081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930732727051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31460618972778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32714295387268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557535171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982653617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38669228553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467449188232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601723670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4854199886322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49012088775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52146291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735926628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53870105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53086566925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168801307678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952387809753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52303028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53243279457092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50892615318298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51362752914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4979567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638962745667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52616453170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54653644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55123805999756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53713393211365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55437183380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60608625411987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70794773101807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108222007751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541120529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70324635505676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67347145080566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705636978149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981799125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728122711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59825086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58571410179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57004308700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56220722198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54183506965637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51989603042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52929854393005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52459716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034622192383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131562232971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228526115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4337055683136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39609503746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087421417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206918716431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975751876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27699542045593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28796529769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34908175468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36475276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064888000488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35848450660706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333317756653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43683958053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62489151954651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63272714614868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46818161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36632013320923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38199138641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766192436218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251107215881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40549755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42116856575012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900395393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878764152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363631248474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25662326812744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27229428291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28012943267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445889472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528100013733</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558437347412</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17043280601501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14692640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15006017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655401229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259717941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15162754058838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1390905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16103005409241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04663181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05290007591248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03722906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04819893836975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0450644493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06543707847595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073594093323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10774850845337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11715126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12341976165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125538825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1939389705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647597312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2033417224884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19237232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20804309844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416454315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13595652580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06387042999268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02625966072083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805164337158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07640695571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05446743965149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1046142578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700420379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566217422485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954120635986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0685715675354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797360420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2409520149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371411323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21117758750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23311686515808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781800270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930708885193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3146059513092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32714295387268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557559013367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982653617859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38669228553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44467496871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601699829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48541975021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49012112617493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52146291732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735926628113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53870105743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53086543083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168801307678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422525405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952363967896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52303028106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53243279457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206064224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5089259147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51362729072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795651435852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638962745667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52616405487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54653644561768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55123805999756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53713393211365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55437183380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60608649253845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70794796943665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205185890198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541144371033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70324659347534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67347168922424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705613136292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981822967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58728122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5982506275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5857138633728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57004308700562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56220746040344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54183554649353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51989579200745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5292980670929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52459692955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034574508667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131562232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43370509147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39609503746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206918716431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975751876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27699518203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28796529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34908199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36475300788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064911842346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35848474502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333293914795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43683958053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62489151954651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63272666931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46818161010742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36631989479065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38199090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766216278076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251083374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40549755096436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42116856575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900443077087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363607406616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25662350654602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27229428291321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28012990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445889472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528123855591</t>
-  </si>
-  <si>
     <t xml:space="preserve">2.1235978603363</t>
   </si>
   <si>
@@ -1058,19 +1061,19 @@
     <t xml:space="preserve">2.01942133903503</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00339436531067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06750249862671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18770670890808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29188251495361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13962483406067</t>
+    <t xml:space="preserve">2.00339412689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06750273704529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1877064704895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29188275337219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13962507247925</t>
   </si>
   <si>
     <t xml:space="preserve">2.16366577148438</t>
@@ -1091,22 +1094,22 @@
     <t xml:space="preserve">2.19572019577026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17969274520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10757064819336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05948925018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07551622390747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0354483127594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05147552490234</t>
+    <t xml:space="preserve">2.17969298362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10757088661194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05948901176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07551598548889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03544855117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05147576332092</t>
   </si>
   <si>
     <t xml:space="preserve">2.27585577964783</t>
@@ -1115,7 +1118,7 @@
     <t xml:space="preserve">2.26784205436707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21976065635681</t>
+    <t xml:space="preserve">2.21976089477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.21174716949463</t>
@@ -1130,16 +1133,16 @@
     <t xml:space="preserve">2.22777438163757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15565228462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30790996551514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02743530273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04346203804016</t>
+    <t xml:space="preserve">2.15565204620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30791044235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02743482589722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04346227645874</t>
   </si>
   <si>
     <t xml:space="preserve">1.9953807592392</t>
@@ -1148,16 +1151,16 @@
     <t xml:space="preserve">1.91524481773376</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92325854301453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96332621574402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97134006023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736703395844</t>
+    <t xml:space="preserve">1.92325842380524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96332633495331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9873673915863</t>
   </si>
   <si>
     <t xml:space="preserve">2.01140761375427</t>
@@ -1166,7 +1169,7 @@
     <t xml:space="preserve">1.81106817722321</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81908202171326</t>
+    <t xml:space="preserve">1.81908178329468</t>
   </si>
   <si>
     <t xml:space="preserve">1.84312272071838</t>
@@ -1175,10 +1178,10 @@
     <t xml:space="preserve">1.79504120349884</t>
   </si>
   <si>
-    <t xml:space="preserve">1.77901387214661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709562778473</t>
+    <t xml:space="preserve">1.77901422977448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709538936615</t>
   </si>
   <si>
     <t xml:space="preserve">1.77100050449371</t>
@@ -1187,76 +1190,73 @@
     <t xml:space="preserve">1.73093247413635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69887828826904</t>
+    <t xml:space="preserve">1.69887793064117</t>
   </si>
   <si>
     <t xml:space="preserve">1.7149053812027</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7469596862793</t>
+    <t xml:space="preserve">1.74695980548859</t>
   </si>
   <si>
     <t xml:space="preserve">1.72291898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73894619941711</t>
+    <t xml:space="preserve">1.73894608020782</t>
   </si>
   <si>
     <t xml:space="preserve">1.76298689842224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75497329235077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8030549287796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85914981365204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86716318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510899543762</t>
+    <t xml:space="preserve">1.75497341156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305480957031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85914993286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86716330051422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510911464691</t>
   </si>
   <si>
     <t xml:space="preserve">1.8751767873764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.907231092453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93928563594818</t>
+    <t xml:space="preserve">1.90723156929016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935354709625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93928587436676</t>
   </si>
   <si>
     <t xml:space="preserve">2.02082943916321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01258111000061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97133982181549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98783624172211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99608469009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9630913734436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834662437439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97958827018738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0373260974884</t>
+    <t xml:space="preserve">2.01258134841919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98783659934998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99608492851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96309161186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93834638595581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97958815097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03732585906982</t>
   </si>
   <si>
     <t xml:space="preserve">2.0620710849762</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">2.0538227558136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09506392478943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16929864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16105031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11156058311462</t>
+    <t xml:space="preserve">2.09506416320801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16929841041565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16105008125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1115608215332</t>
   </si>
   <si>
     <t xml:space="preserve">2.10331225395203</t>
@@ -1286,10 +1286,10 @@
     <t xml:space="preserve">2.13630533218384</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11980891227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14455366134644</t>
+    <t xml:space="preserve">2.11980867385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14455342292786</t>
   </si>
   <si>
     <t xml:space="preserve">2.07856750488281</t>
@@ -1301,25 +1301,25 @@
     <t xml:space="preserve">2.21878838539124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25178170204163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24353313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21054029464722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26003003120422</t>
+    <t xml:space="preserve">2.25178146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24353361129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21054005622864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26002979278564</t>
   </si>
   <si>
     <t xml:space="preserve">2.26827812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33426403999329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30951929092407</t>
+    <t xml:space="preserve">2.33426427841187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30951952934265</t>
   </si>
   <si>
     <t xml:space="preserve">2.30127096176147</t>
@@ -1331,13 +1331,13 @@
     <t xml:space="preserve">2.38375401496887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550568580627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601594924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27652621269226</t>
+    <t xml:space="preserve">2.37550592422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601571083069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27652645111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.28477454185486</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">2.29302287101746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23528504371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39200258255005</t>
+    <t xml:space="preserve">2.23528480529785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39200210571289</t>
   </si>
   <si>
     <t xml:space="preserve">2.44974040985107</t>
@@ -1358,10 +1358,10 @@
     <t xml:space="preserve">2.41674709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43324375152588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40849900245667</t>
+    <t xml:space="preserve">2.43324398994446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40849876403809</t>
   </si>
   <si>
     <t xml:space="preserve">2.42499542236328</t>
@@ -1370,7 +1370,7 @@
     <t xml:space="preserve">2.45798850059509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4992299079895</t>
+    <t xml:space="preserve">2.49922966957092</t>
   </si>
   <si>
     <t xml:space="preserve">2.47448492050171</t>
@@ -1382,19 +1382,19 @@
     <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871964454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4909815788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50747799873352</t>
+    <t xml:space="preserve">2.54871940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49098181724548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50747847557068</t>
   </si>
   <si>
     <t xml:space="preserve">2.44149231910706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35076117515564</t>
+    <t xml:space="preserve">2.35076093673706</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025067329407</t>
@@ -1409,22 +1409,22 @@
     <t xml:space="preserve">2.045574426651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87236046791077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264973163605</t>
+    <t xml:space="preserve">1.87236034870148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264985084534</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089818000793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56717383861542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71564292907715</t>
+    <t xml:space="preserve">1.567174077034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71564304828644</t>
   </si>
   <si>
     <t xml:space="preserve">1.64553260803223</t>
@@ -1439,79 +1439,79 @@
     <t xml:space="preserve">1.77338099479675</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78162920475006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74863612651825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80637407302856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411201953888</t>
+    <t xml:space="preserve">1.78162944316864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74863588809967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80637419223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411213874817</t>
   </si>
   <si>
     <t xml:space="preserve">2.00433301925659</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81462240219116</t>
+    <t xml:space="preserve">1.81462252140045</t>
   </si>
   <si>
     <t xml:space="preserve">1.79812586307526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287073135376</t>
+    <t xml:space="preserve">1.82287085056305</t>
   </si>
   <si>
     <t xml:space="preserve">1.84761559963226</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83111882209778</t>
+    <t xml:space="preserve">1.83111894130707</t>
   </si>
   <si>
     <t xml:space="preserve">1.78987765312195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88885688781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360187530518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710533618927</t>
+    <t xml:space="preserve">1.88885700702667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360175609589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710521697998</t>
   </si>
   <si>
     <t xml:space="preserve">1.90535366535187</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9548431634903</t>
+    <t xml:space="preserve">1.95484340190887</t>
   </si>
   <si>
     <t xml:space="preserve">2.02907800674438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08681607246399</t>
+    <t xml:space="preserve">2.08681583404541</t>
   </si>
   <si>
     <t xml:space="preserve">2.17754697799683</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07031917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07786893844604</t>
+    <t xml:space="preserve">2.07031941413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07786917686462</t>
   </si>
   <si>
     <t xml:space="preserve">2.06938791275024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03546357154846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98457682132721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9760959148407</t>
+    <t xml:space="preserve">2.03546380996704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98457670211792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609579563141</t>
   </si>
   <si>
     <t xml:space="preserve">1.95065248012543</t>
@@ -1529,25 +1529,25 @@
     <t xml:space="preserve">2.05242586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04394459724426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0100200176239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00153923034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89976608753204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88280355930328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128482341766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01850128173828</t>
+    <t xml:space="preserve">2.04394483566284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01002025604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00153875350952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89976596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88280367851257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128494262695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01850152015686</t>
   </si>
   <si>
     <t xml:space="preserve">1.95913374423981</t>
@@ -1565,22 +1565,22 @@
     <t xml:space="preserve">2.16267991065979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20508527755737</t>
+    <t xml:space="preserve">2.20508503913879</t>
   </si>
   <si>
     <t xml:space="preserve">2.23052883148193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30685877799988</t>
+    <t xml:space="preserve">2.30685901641846</t>
   </si>
   <si>
     <t xml:space="preserve">2.33230209350586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34926414489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35774540901184</t>
+    <t xml:space="preserve">2.34926438331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
     <t xml:space="preserve">2.42559385299683</t>
@@ -1589,13 +1589,13 @@
     <t xml:space="preserve">2.44255638122559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47648072242737</t>
+    <t xml:space="preserve">2.47648048400879</t>
   </si>
   <si>
     <t xml:space="preserve">2.46799969673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49344301223755</t>
+    <t xml:space="preserve">2.49344277381897</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040530204773</t>
@@ -1604,7 +1604,7 @@
     <t xml:space="preserve">2.43407487869263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4171130657196</t>
+    <t xml:space="preserve">2.41711282730103</t>
   </si>
   <si>
     <t xml:space="preserve">2.51888632774353</t>
@@ -1613,25 +1613,25 @@
     <t xml:space="preserve">2.58673477172852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56977272033691</t>
+    <t xml:space="preserve">2.56977248191833</t>
   </si>
   <si>
     <t xml:space="preserve">2.54432940483093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57825374603271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56129145622253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55281043052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53584837913513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52736711502075</t>
+    <t xml:space="preserve">2.57825398445129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56129169464111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55281019210815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53584861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52736735343933</t>
   </si>
   <si>
     <t xml:space="preserve">2.64610242843628</t>
@@ -1649,25 +1649,25 @@
     <t xml:space="preserve">2.69698929786682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62914061546326</t>
+    <t xml:space="preserve">2.6291401386261</t>
   </si>
   <si>
     <t xml:space="preserve">2.71395134925842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73091387748718</t>
+    <t xml:space="preserve">2.7309136390686</t>
   </si>
   <si>
     <t xml:space="preserve">2.77331900596619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84116792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86661148071289</t>
+    <t xml:space="preserve">2.78180003166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84116768836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86661124229431</t>
   </si>
   <si>
     <t xml:space="preserve">2.88357353210449</t>
@@ -1685,13 +1685,13 @@
     <t xml:space="preserve">2.75635671615601</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73939442634583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74787569046021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79876208305359</t>
+    <t xml:space="preserve">2.7393946647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74787592887878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79876232147217</t>
   </si>
   <si>
     <t xml:space="preserve">2.79028129577637</t>
@@ -1700,31 +1700,31 @@
     <t xml:space="preserve">2.84964895248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268666267395</t>
+    <t xml:space="preserve">2.83268690109253</t>
   </si>
   <si>
     <t xml:space="preserve">2.82420563697815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91749787330627</t>
+    <t xml:space="preserve">2.9174976348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.01078963279724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03623294830322</t>
+    <t xml:space="preserve">3.03623342514038</t>
   </si>
   <si>
     <t xml:space="preserve">2.95990324020386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07863903045654</t>
+    <t xml:space="preserve">3.07863879203796</t>
   </si>
   <si>
     <t xml:space="preserve">3.08711981773376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12104415893555</t>
+    <t xml:space="preserve">3.12104392051697</t>
   </si>
   <si>
     <t xml:space="preserve">3.18041181564331</t>
@@ -1736,22 +1736,22 @@
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281718254089</t>
+    <t xml:space="preserve">3.22281742095947</t>
   </si>
   <si>
     <t xml:space="preserve">3.23129844665527</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2482602596283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433639526367</t>
+    <t xml:space="preserve">3.24826073646545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433615684509</t>
   </si>
   <si>
     <t xml:space="preserve">3.28218483924866</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40092062950134</t>
+    <t xml:space="preserve">3.40092039108276</t>
   </si>
   <si>
     <t xml:space="preserve">3.42636370658875</t>
@@ -1763,10 +1763,10 @@
     <t xml:space="preserve">3.31610941886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29066634178162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27370381355286</t>
+    <t xml:space="preserve">3.2906665802002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27370405197144</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079400062561</t>
@@ -19189,7 +19189,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G608" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -19215,7 +19215,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G609" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -19241,7 +19241,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G610" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -19267,7 +19267,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G611" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -19293,7 +19293,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G612" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -19319,7 +19319,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G613" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -19345,7 +19345,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G614" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -19371,7 +19371,7 @@
         <v>2.5</v>
       </c>
       <c r="G615" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -19397,7 +19397,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G616" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -19423,7 +19423,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G617" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -19449,7 +19449,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G618" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -19475,7 +19475,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G619" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -19501,7 +19501,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G620" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -19527,7 +19527,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G621" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -19553,7 +19553,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G622" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -19579,7 +19579,7 @@
         <v>2.75</v>
       </c>
       <c r="G623" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -19605,7 +19605,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G624" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -19631,7 +19631,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G625" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -19657,7 +19657,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G626" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -19683,7 +19683,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G627" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -19709,7 +19709,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G628" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -19735,7 +19735,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G629" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -19761,7 +19761,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G630" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -19787,7 +19787,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G631" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -19813,7 +19813,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G632" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -19839,7 +19839,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G633" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -19865,7 +19865,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G634" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -19891,7 +19891,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G635" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -19917,7 +19917,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G636" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -19943,7 +19943,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G637" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -19969,7 +19969,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G638" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -19995,7 +19995,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G639" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -20021,7 +20021,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G640" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -20047,7 +20047,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G641" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -20073,7 +20073,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G642" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -20099,7 +20099,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G643" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -20125,7 +20125,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G644" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -20151,7 +20151,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G645" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -20177,7 +20177,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G646" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -20203,7 +20203,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G647" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -20229,7 +20229,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G648" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -20255,7 +20255,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G649" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -20281,7 +20281,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G650" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -20307,7 +20307,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G651" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -20333,7 +20333,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G652" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -20359,7 +20359,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G653" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -20385,7 +20385,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G654" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -20411,7 +20411,7 @@
         <v>2.5</v>
       </c>
       <c r="G655" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -20437,7 +20437,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G656" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -20463,7 +20463,7 @@
         <v>2.5</v>
       </c>
       <c r="G657" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -20489,7 +20489,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G658" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -20515,7 +20515,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G659" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -20541,7 +20541,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G660" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -20567,7 +20567,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G661" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -20593,7 +20593,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G662" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -20619,7 +20619,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G663" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -20645,7 +20645,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G664" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -20671,7 +20671,7 @@
         <v>2.75</v>
       </c>
       <c r="G665" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -20697,7 +20697,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G666" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -20723,7 +20723,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G667" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -20749,7 +20749,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G668" t="s">
-        <v>214</v>
+        <v>343</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -20775,7 +20775,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G669" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -20801,7 +20801,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G670" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -20827,7 +20827,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G671" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -20853,7 +20853,7 @@
         <v>2.75</v>
       </c>
       <c r="G672" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -20879,7 +20879,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G673" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -20905,7 +20905,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G674" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -20931,7 +20931,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G675" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -20957,7 +20957,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G676" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -20983,7 +20983,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G677" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -21009,7 +21009,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G678" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -21035,7 +21035,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G679" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -21061,7 +21061,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G680" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -21087,7 +21087,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G681" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -21113,7 +21113,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G682" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -21139,7 +21139,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G683" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -21165,7 +21165,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G684" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -21191,7 +21191,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G685" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -21217,7 +21217,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G686" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -21243,7 +21243,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G687" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -21269,7 +21269,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G688" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -21295,7 +21295,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G689" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -21321,7 +21321,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G690" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -21347,7 +21347,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G691" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -21373,7 +21373,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G692" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -21399,7 +21399,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G693" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -21425,7 +21425,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G694" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -21451,7 +21451,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G695" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -21477,7 +21477,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G696" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -21503,7 +21503,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -21529,7 +21529,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G698" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -21555,7 +21555,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G699" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -21581,7 +21581,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G700" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -21607,7 +21607,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G701" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -21633,7 +21633,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G702" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -21659,7 +21659,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G703" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -21685,7 +21685,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G704" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -21711,7 +21711,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G705" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -21737,7 +21737,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G706" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -21763,7 +21763,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G707" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -21789,7 +21789,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G708" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -21815,7 +21815,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G709" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -21841,7 +21841,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G710" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -21867,7 +21867,7 @@
         <v>2.5</v>
       </c>
       <c r="G711" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -21893,7 +21893,7 @@
         <v>2.5</v>
       </c>
       <c r="G712" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -21919,7 +21919,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G713" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -21945,7 +21945,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G714" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -21971,7 +21971,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G715" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -21997,7 +21997,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -22023,7 +22023,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G717" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -22049,7 +22049,7 @@
         <v>2.5</v>
       </c>
       <c r="G718" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -22075,7 +22075,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G719" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -22101,7 +22101,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G720" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -22127,7 +22127,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G721" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -22153,7 +22153,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G722" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -22179,7 +22179,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G723" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -22205,7 +22205,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G724" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -22231,7 +22231,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G725" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -22257,7 +22257,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G726" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -22283,7 +22283,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G727" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -22309,7 +22309,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G728" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -22335,7 +22335,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G729" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -22361,7 +22361,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G730" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -22387,7 +22387,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G731" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -22413,7 +22413,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G732" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -22439,7 +22439,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G733" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -22465,7 +22465,7 @@
         <v>2.5</v>
       </c>
       <c r="G734" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -22491,7 +22491,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G735" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -22517,7 +22517,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G736" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -22543,7 +22543,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G737" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -22569,7 +22569,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G738" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -22595,7 +22595,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G739" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -22621,7 +22621,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G740" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -22647,7 +22647,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G741" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -22673,7 +22673,7 @@
         <v>2.5</v>
       </c>
       <c r="G742" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -22699,7 +22699,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G743" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -22725,7 +22725,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G744" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -22751,7 +22751,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G745" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -22777,7 +22777,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G746" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -22803,7 +22803,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G747" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -22829,7 +22829,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -22855,7 +22855,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G749" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -22881,7 +22881,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G750" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -22907,7 +22907,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G751" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -22933,7 +22933,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G752" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -22959,7 +22959,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G753" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -22985,7 +22985,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G754" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -23011,7 +23011,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G755" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -23037,7 +23037,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G756" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -23063,7 +23063,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G757" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -23089,7 +23089,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G758" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -23115,7 +23115,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G759" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -23141,7 +23141,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -23167,7 +23167,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G761" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -23193,7 +23193,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G762" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -23219,7 +23219,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G763" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -23245,7 +23245,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G764" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -23271,7 +23271,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G765" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -23297,7 +23297,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G766" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -23323,7 +23323,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G767" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -23349,7 +23349,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G768" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -23375,7 +23375,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -23401,7 +23401,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G770" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -23427,7 +23427,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G771" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -23453,7 +23453,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G772" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -23479,7 +23479,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G773" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -23505,7 +23505,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G774" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -23531,7 +23531,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G775" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -23557,7 +23557,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G776" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -23583,7 +23583,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G777" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -23609,7 +23609,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G778" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -23635,7 +23635,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G779" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -23661,7 +23661,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G780" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -23687,7 +23687,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -23713,7 +23713,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -23739,7 +23739,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G783" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -23765,7 +23765,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G784" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -23791,7 +23791,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G785" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -23817,7 +23817,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G786" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -23843,7 +23843,7 @@
         <v>2.25</v>
       </c>
       <c r="G787" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -23869,7 +23869,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G788" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -23895,7 +23895,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G789" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -23921,7 +23921,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G790" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -23947,7 +23947,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G791" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -23973,7 +23973,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G792" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -23999,7 +23999,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G793" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -24025,7 +24025,7 @@
         <v>2.5</v>
       </c>
       <c r="G794" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -24051,7 +24051,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G795" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -24077,7 +24077,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G796" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -24103,7 +24103,7 @@
         <v>2.5</v>
       </c>
       <c r="G797" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -24129,7 +24129,7 @@
         <v>2.5</v>
       </c>
       <c r="G798" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -24155,7 +24155,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G799" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -24181,7 +24181,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G800" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -24207,7 +24207,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G801" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -24233,7 +24233,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G802" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -24259,7 +24259,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G803" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -24285,7 +24285,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G804" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -24311,7 +24311,7 @@
         <v>2.5</v>
       </c>
       <c r="G805" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -24337,7 +24337,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G806" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -24363,7 +24363,7 @@
         <v>2.5</v>
       </c>
       <c r="G807" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -24389,7 +24389,7 @@
         <v>2.5</v>
       </c>
       <c r="G808" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -24415,7 +24415,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G809" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -24441,7 +24441,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G810" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -24467,7 +24467,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G811" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -24493,7 +24493,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G812" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -24519,7 +24519,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G813" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -24545,7 +24545,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G814" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -24571,7 +24571,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G815" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -24597,7 +24597,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G816" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -24623,7 +24623,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G817" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -24649,7 +24649,7 @@
         <v>2.5</v>
       </c>
       <c r="G818" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -24675,7 +24675,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G819" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -24701,7 +24701,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G820" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -24727,7 +24727,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G821" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -24753,7 +24753,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G822" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -24779,7 +24779,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G823" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -24805,7 +24805,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G824" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -24831,7 +24831,7 @@
         <v>2.5</v>
       </c>
       <c r="G825" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -24857,7 +24857,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G826" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -24883,7 +24883,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G827" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -24909,7 +24909,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G828" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -24935,7 +24935,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G829" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -24961,7 +24961,7 @@
         <v>2.5</v>
       </c>
       <c r="G830" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -24987,7 +24987,7 @@
         <v>2.5</v>
       </c>
       <c r="G831" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -25013,7 +25013,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G832" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -25039,7 +25039,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G833" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -25065,7 +25065,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G834" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -25091,7 +25091,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G835" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -25117,7 +25117,7 @@
         <v>2.5</v>
       </c>
       <c r="G836" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -25143,7 +25143,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G837" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -25169,7 +25169,7 @@
         <v>2.5</v>
       </c>
       <c r="G838" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -25195,7 +25195,7 @@
         <v>2.5</v>
       </c>
       <c r="G839" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -25221,7 +25221,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G840" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -25247,7 +25247,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G841" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -25273,7 +25273,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G842" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -25299,7 +25299,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G843" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -25325,7 +25325,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G844" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -25351,7 +25351,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G845" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -25377,7 +25377,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G846" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -25403,7 +25403,7 @@
         <v>2.5</v>
       </c>
       <c r="G847" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -25429,7 +25429,7 @@
         <v>2.5</v>
       </c>
       <c r="G848" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -25455,7 +25455,7 @@
         <v>2.5</v>
       </c>
       <c r="G849" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -25481,7 +25481,7 @@
         <v>2.5</v>
       </c>
       <c r="G850" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -25507,7 +25507,7 @@
         <v>2.5</v>
       </c>
       <c r="G851" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -25533,7 +25533,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G852" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -25559,7 +25559,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G853" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -25585,7 +25585,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G854" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -25611,7 +25611,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G855" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -25637,7 +25637,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G856" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -25663,7 +25663,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G857" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H857" t="s">
         <v>9</v>
@@ -25689,7 +25689,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G858" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H858" t="s">
         <v>9</v>
@@ -25715,7 +25715,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G859" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H859" t="s">
         <v>9</v>
@@ -25741,7 +25741,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G860" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H860" t="s">
         <v>9</v>
@@ -25767,7 +25767,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G861" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H861" t="s">
         <v>9</v>
@@ -25793,7 +25793,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G862" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25871,7 +25871,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G865" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H865" t="s">
         <v>9</v>
@@ -26053,7 +26053,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G872" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26235,7 +26235,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G879" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26261,7 +26261,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G880" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H880" t="s">
         <v>9</v>
@@ -26287,7 +26287,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G881" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H881" t="s">
         <v>9</v>
@@ -31591,7 +31591,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1085" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1085" t="s">
         <v>9</v>
@@ -32579,7 +32579,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1123" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1123" t="s">
         <v>9</v>
@@ -32605,7 +32605,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1124" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1124" t="s">
         <v>9</v>
@@ -32683,7 +32683,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1127" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1127" t="s">
         <v>9</v>
@@ -32787,7 +32787,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1131" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1131" t="s">
         <v>9</v>
@@ -32917,7 +32917,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1136" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -33047,7 +33047,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1141" t="s">
-        <v>408</v>
+        <v>381</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33307,7 +33307,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1151" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1151" t="s">
         <v>9</v>
@@ -33359,7 +33359,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1153" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1153" t="s">
         <v>9</v>
@@ -33385,7 +33385,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1154" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1154" t="s">
         <v>9</v>
@@ -33437,7 +33437,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1156" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1156" t="s">
         <v>9</v>
@@ -34217,7 +34217,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1186" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1186" t="s">
         <v>9</v>
@@ -34295,7 +34295,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1189" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1189" t="s">
         <v>9</v>
@@ -69767,7 +69767,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6910069444</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>17756</v>
@@ -69788,6 +69788,32 @@
         <v>1012</v>
       </c>
       <c r="H2554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46043.691099537</v>
+      </c>
+      <c r="B2555" t="n">
+        <v>36721</v>
+      </c>
+      <c r="C2555" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>9.72000026702881</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>9.72000026702881</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>9.9399995803833</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H2555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652255535126</t>
+    <t xml:space="preserve">1.73652267456055</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400734901428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71406757831573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167235374451</t>
+    <t xml:space="preserve">1.74400770664215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71406781673431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167259216309</t>
   </si>
   <si>
     <t xml:space="preserve">1.67215156555176</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969658851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921761512756</t>
+    <t xml:space="preserve">1.64969682693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921725749969</t>
   </si>
   <si>
     <t xml:space="preserve">1.57334935665131</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">1.49625372886658</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48053538799286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48203229904175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637359142303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460725784302</t>
+    <t xml:space="preserve">1.48053526878357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48203217983246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637371063232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460701942444</t>
   </si>
   <si>
     <t xml:space="preserve">1.42215216159821</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">1.41990673542023</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4146671295166</t>
+    <t xml:space="preserve">1.41466724872589</t>
   </si>
   <si>
     <t xml:space="preserve">1.41915822029114</t>
@@ -95,25 +95,25 @@
     <t xml:space="preserve">1.407182097435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38248157501221</t>
+    <t xml:space="preserve">1.3824816942215</t>
   </si>
   <si>
     <t xml:space="preserve">1.38472723960876</t>
   </si>
   <si>
-    <t xml:space="preserve">1.39820003509521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35703253746033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3360743522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.34730184078217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3428111076355</t>
+    <t xml:space="preserve">1.39820027351379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35703265666962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607459068298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34730207920074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34281122684479</t>
   </si>
   <si>
     <t xml:space="preserve">1.38397860527039</t>
@@ -128,37 +128,37 @@
     <t xml:space="preserve">1.36975717544556</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37873911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4311341047287</t>
+    <t xml:space="preserve">1.37873923778534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43113398551941</t>
   </si>
   <si>
     <t xml:space="preserve">1.41017603874207</t>
   </si>
   <si>
-    <t xml:space="preserve">1.44535577297211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.462571144104</t>
+    <t xml:space="preserve">1.44535565376282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46257138252258</t>
   </si>
   <si>
     <t xml:space="preserve">1.51197218894958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52544558048248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52245104312897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54490637779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191243648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54939723014832</t>
+    <t xml:space="preserve">1.52544546127319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52245116233826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54490625858307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191219806671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5493973493576</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287038326263</t>
@@ -170,43 +170,43 @@
     <t xml:space="preserve">1.60927772521973</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63173246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424755096436</t>
+    <t xml:space="preserve">1.63173258304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424778938293</t>
   </si>
   <si>
     <t xml:space="preserve">1.63023543357849</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61676239967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418744087219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64370846748352</t>
+    <t xml:space="preserve">1.61676251888275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418767929077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6437087059021</t>
   </si>
   <si>
     <t xml:space="preserve">1.58682227134705</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58831965923309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63472652435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66017544269562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66915774345398</t>
+    <t xml:space="preserve">1.5883195400238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63472640514374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017532348633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6691575050354</t>
   </si>
   <si>
     <t xml:space="preserve">1.68712151050568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69161236286163</t>
+    <t xml:space="preserve">1.6916127204895</t>
   </si>
   <si>
     <t xml:space="preserve">1.69310963153839</t>
@@ -215,34 +215,34 @@
     <t xml:space="preserve">1.72155272960663</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73502576351166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358848571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70658254623413</t>
+    <t xml:space="preserve">1.73502564430237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358884334564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.706582903862</t>
   </si>
   <si>
     <t xml:space="preserve">1.69909763336182</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67664241790771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6841276884079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66766047477722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263065814972</t>
+    <t xml:space="preserve">1.676642537117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68412756919861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66766059398651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263041973114</t>
   </si>
   <si>
     <t xml:space="preserve">1.64221155643463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64670240879059</t>
+    <t xml:space="preserve">1.64670264720917</t>
   </si>
   <si>
     <t xml:space="preserve">1.67514550685883</t>
@@ -251,85 +251,85 @@
     <t xml:space="preserve">1.69964480400085</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68433284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69198882579803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7210818529129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70576965808868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69505131244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495676040649</t>
+    <t xml:space="preserve">1.6843329668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69198894500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72108161449432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70576989650726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69505107402802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495699882507</t>
   </si>
   <si>
     <t xml:space="preserve">1.72261309623718</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65370857715607</t>
+    <t xml:space="preserve">1.65370869636536</t>
   </si>
   <si>
     <t xml:space="preserve">1.67208313941956</t>
   </si>
   <si>
-    <t xml:space="preserve">1.669020652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6521772146225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.606241106987</t>
+    <t xml:space="preserve">1.66902077198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65217733383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60624098777771</t>
   </si>
   <si>
     <t xml:space="preserve">1.56183588504791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55417966842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52202427387238</t>
+    <t xml:space="preserve">1.5541797876358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52202439308167</t>
   </si>
   <si>
     <t xml:space="preserve">1.53121173381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59092903137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52891480922699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55111753940582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53886771202087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.4929313659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47608804702759</t>
+    <t xml:space="preserve">1.59092879295349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5289146900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55111730098724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53886783123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49293148517609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608816623688</t>
   </si>
   <si>
     <t xml:space="preserve">1.52278995513916</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46996319293976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47761905193329</t>
+    <t xml:space="preserve">1.46996307373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47761917114258</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589953899384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50058734416962</t>
+    <t xml:space="preserve">1.5005875825882</t>
   </si>
   <si>
     <t xml:space="preserve">1.6077721118927</t>
@@ -341,49 +341,49 @@
     <t xml:space="preserve">1.56949198246002</t>
   </si>
   <si>
-    <t xml:space="preserve">1.62308430671692</t>
+    <t xml:space="preserve">1.62308418750763</t>
   </si>
   <si>
     <t xml:space="preserve">1.66748940944672</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66136479377747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67667698860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61542820930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714807987213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58480405807495</t>
+    <t xml:space="preserve">1.66136491298676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67667651176453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6154283285141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714784145355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58480393886566</t>
   </si>
   <si>
     <t xml:space="preserve">1.63839638233185</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63380300998688</t>
+    <t xml:space="preserve">1.6338027715683</t>
   </si>
   <si>
     <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
-    <t xml:space="preserve">1.54652380943298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56796073913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54499244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355563640594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54193007946014</t>
+    <t xml:space="preserve">1.54652369022369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56796085834503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54499232769012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355551719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54193019866943</t>
   </si>
   <si>
     <t xml:space="preserve">1.58174169063568</t>
@@ -401,70 +401,70 @@
     <t xml:space="preserve">1.53044605255127</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51972770690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50594675540924</t>
+    <t xml:space="preserve">1.51972758769989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50594651699066</t>
   </si>
   <si>
     <t xml:space="preserve">1.50671219825745</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53427386283875</t>
+    <t xml:space="preserve">1.53427422046661</t>
   </si>
   <si>
     <t xml:space="preserve">1.56642949581146</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57408559322357</t>
+    <t xml:space="preserve">1.57408571243286</t>
   </si>
   <si>
     <t xml:space="preserve">1.58327293395996</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59246003627777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50211846828461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47532248497009</t>
+    <t xml:space="preserve">1.59245991706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5021185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824344158173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47532260417938</t>
   </si>
   <si>
     <t xml:space="preserve">1.49675941467285</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50747811794281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52968049049377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60011601448059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58786630630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489813327789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5633670091629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255423069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59858512878418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59399163722992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60470998287201</t>
+    <t xml:space="preserve">1.50747776031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52968037128448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60011625289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58786642551422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489825248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56336712837219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255434989929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59858500957489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59399139881134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60470962524414</t>
   </si>
   <si>
     <t xml:space="preserve">1.64758372306824</t>
@@ -473,88 +473,88 @@
     <t xml:space="preserve">1.64605271816254</t>
   </si>
   <si>
-    <t xml:space="preserve">1.68280160427094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63074040412903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63686525821686</t>
+    <t xml:space="preserve">1.68280172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63074052333832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63686513900757</t>
   </si>
   <si>
     <t xml:space="preserve">1.64452135562897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63227188587189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66289591789246</t>
+    <t xml:space="preserve">1.63227164745331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66289567947388</t>
   </si>
   <si>
     <t xml:space="preserve">1.66595840454102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73333144187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026907444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558115005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017476081848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730090141296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423877239227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73792541027069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75936210155487</t>
+    <t xml:space="preserve">1.73333179950714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026931285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7455815076828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017488002777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730102062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7379252910614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75936233997345</t>
   </si>
   <si>
     <t xml:space="preserve">1.76089334487915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7838613986969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76854932308197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323736667633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639392852783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79151773452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223631858826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061064243317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8175482749939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80682957172394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8252044916153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81448578834534</t>
+    <t xml:space="preserve">1.78386151790619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76854944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323748588562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486268520355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639380931854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79151749610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223619937897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061076164246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81754839420319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80682981014252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82520425319672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81448566913605</t>
   </si>
   <si>
     <t xml:space="preserve">1.85889077186584</t>
@@ -563,79 +563,79 @@
     <t xml:space="preserve">1.87726533412933</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85429739952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582876205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85123467445374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86654710769653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84970355033875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86348462104797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85276615619659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745384216309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511017799377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367312908173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84051656723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817254543304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8680784702301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923233985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90788984298706</t>
+    <t xml:space="preserve">1.85429716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582840442657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8512350320816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86654698848724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8497040271759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86348474025726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8527660369873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745408058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84511041641235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367289066315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84051644802094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817266464233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807811260223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9492324590683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788972377777</t>
   </si>
   <si>
     <t xml:space="preserve">1.92167055606842</t>
   </si>
   <si>
-    <t xml:space="preserve">1.92932641506195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473304271698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96607601642609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98904407024384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823117256165</t>
+    <t xml:space="preserve">1.92932689189911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473292350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96607577800751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98904418945312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823105335236</t>
   </si>
   <si>
     <t xml:space="preserve">2.00895023345947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00741839408875</t>
+    <t xml:space="preserve">2.0074188709259</t>
   </si>
   <si>
     <t xml:space="preserve">2.01201224327087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99057507514954</t>
+    <t xml:space="preserve">1.99057495594025</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
@@ -644,31 +644,31 @@
     <t xml:space="preserve">2.00588726997375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09207773208618</t>
+    <t xml:space="preserve">2.09207797050476</t>
   </si>
   <si>
     <t xml:space="preserve">2.09051060676575</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11401677131653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424234390259</t>
+    <t xml:space="preserve">2.11401724815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424210548401</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558413505554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17043304443359</t>
+    <t xml:space="preserve">2.17043280601501</t>
   </si>
   <si>
     <t xml:space="preserve">2.14692616462708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15006065368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655401229858</t>
+    <t xml:space="preserve">2.15006041526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655377388</t>
   </si>
   <si>
     <t xml:space="preserve">2.16259717941284</t>
@@ -677,22 +677,22 @@
     <t xml:space="preserve">2.15162777900696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1390905380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16102981567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04663181304932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05290031433105</t>
+    <t xml:space="preserve">2.13909077644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16103005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04663228988647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290055274963</t>
   </si>
   <si>
     <t xml:space="preserve">2.03722929954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04819893836975</t>
+    <t xml:space="preserve">2.04819869995117</t>
   </si>
   <si>
     <t xml:space="preserve">2.04506468772888</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">2.06543684005737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06073594093323</t>
+    <t xml:space="preserve">2.06073570251465</t>
   </si>
   <si>
     <t xml:space="preserve">2.10774874687195</t>
@@ -710,10 +710,10 @@
     <t xml:space="preserve">2.1171510219574</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12342000007629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13125514984131</t>
+    <t xml:space="preserve">2.12341976165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13125538825989</t>
   </si>
   <si>
     <t xml:space="preserve">2.18296980857849</t>
@@ -728,100 +728,100 @@
     <t xml:space="preserve">2.2033417224884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19237232208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20804309844971</t>
+    <t xml:space="preserve">2.19237208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20804333686829</t>
   </si>
   <si>
     <t xml:space="preserve">2.16416454315186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15946292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13595652580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0638701915741</t>
+    <t xml:space="preserve">2.15946269035339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13595676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677910804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386995315552</t>
   </si>
   <si>
     <t xml:space="preserve">2.02625966072083</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96827673912048</t>
+    <t xml:space="preserve">1.96827721595764</t>
   </si>
   <si>
     <t xml:space="preserve">1.99805176258087</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07640695571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05446720123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10461497306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700396537781</t>
+    <t xml:space="preserve">2.07640671730042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05446743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10461473464966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700420379639</t>
   </si>
   <si>
     <t xml:space="preserve">2.03566217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04976582527161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954096794128</t>
+    <t xml:space="preserve">2.04976606369019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954120635986</t>
   </si>
   <si>
     <t xml:space="preserve">2.06857085227966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07797408103943</t>
+    <t xml:space="preserve">2.07797384262085</t>
   </si>
   <si>
     <t xml:space="preserve">2.2409520149231</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22371411323547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.211177110672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23311638832092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781824111938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930708885193</t>
+    <t xml:space="preserve">2.22371435165405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21117734909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23311686515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930732727051</t>
   </si>
   <si>
     <t xml:space="preserve">2.3146059513092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32714295387268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38669276237488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4446747303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601747512817</t>
+    <t xml:space="preserve">2.32714247703552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557559013367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982653617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3866925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467496871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601699829102</t>
   </si>
   <si>
     <t xml:space="preserve">2.48541975021362</t>
@@ -833,52 +833,52 @@
     <t xml:space="preserve">2.52146291732788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50735902786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53870129585266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53086590766907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4916877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422477722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952411651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52303004264832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53243279457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206040382385</t>
+    <t xml:space="preserve">2.50735926628113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53870105743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53086543083191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168825149536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422525405884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952363967896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52303028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5324330329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206064224243</t>
   </si>
   <si>
     <t xml:space="preserve">2.5089259147644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51362752914429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795699119568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49638962745667</t>
+    <t xml:space="preserve">2.51362729072571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4979567527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49638938903809</t>
   </si>
   <si>
     <t xml:space="preserve">2.52616405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54653668403625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55123805999756</t>
+    <t xml:space="preserve">2.54653644561768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5512375831604</t>
   </si>
   <si>
     <t xml:space="preserve">2.53713393211365</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">2.60608649253845</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70794773101807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71108222007751</t>
+    <t xml:space="preserve">2.70794796943665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71108198165894</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220516204834</t>
@@ -902,31 +902,31 @@
     <t xml:space="preserve">2.69541120529175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70324635505676</t>
+    <t xml:space="preserve">2.70324659347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.67347145080566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66406917572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705589294434</t>
+    <t xml:space="preserve">2.66406893730164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705613136292</t>
   </si>
   <si>
     <t xml:space="preserve">2.59981799125671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58728122711182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59825086593628</t>
+    <t xml:space="preserve">2.58728098869324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59825110435486</t>
   </si>
   <si>
     <t xml:space="preserve">2.58571410179138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57004308700562</t>
+    <t xml:space="preserve">2.57004284858704</t>
   </si>
   <si>
     <t xml:space="preserve">2.56220746040344</t>
@@ -938,49 +938,49 @@
     <t xml:space="preserve">2.51989603042603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52929854393005</t>
+    <t xml:space="preserve">2.52929830551147</t>
   </si>
   <si>
     <t xml:space="preserve">2.52459716796875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46034622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131562232971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4337055683136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39609479904175</t>
+    <t xml:space="preserve">2.46034646034241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228526115417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43370532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39609503746033</t>
   </si>
   <si>
     <t xml:space="preserve">2.32087397575378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30206894874573</t>
+    <t xml:space="preserve">2.30206918716431</t>
   </si>
   <si>
     <t xml:space="preserve">2.25975751876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27699542045593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28796529769897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34908175468445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36475324630737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35064888000488</t>
+    <t xml:space="preserve">2.27699565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28796553611755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34908223152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36475276947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35064911842346</t>
   </si>
   <si>
     <t xml:space="preserve">2.35848450660706</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">2.41333317756653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43683934211731</t>
+    <t xml:space="preserve">2.43683958053589</t>
   </si>
   <si>
     <t xml:space="preserve">2.62489175796509</t>
@@ -998,58 +998,58 @@
     <t xml:space="preserve">2.6327269077301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.468181848526</t>
+    <t xml:space="preserve">2.46818137168884</t>
   </si>
   <si>
     <t xml:space="preserve">2.36632013320923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38199138641357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3976616859436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45251083374023</t>
+    <t xml:space="preserve">2.381991147995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766216278076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45251059532166</t>
   </si>
   <si>
     <t xml:space="preserve">2.40549755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42116856575012</t>
+    <t xml:space="preserve">2.42116904258728</t>
   </si>
   <si>
     <t xml:space="preserve">2.42900395393372</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24878764152527</t>
+    <t xml:space="preserve">2.24878787994385</t>
   </si>
   <si>
     <t xml:space="preserve">2.30363607406616</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25662350654602</t>
+    <t xml:space="preserve">2.25662326812744</t>
   </si>
   <si>
     <t xml:space="preserve">2.27229404449463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28012943267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445889472961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528100013733</t>
+    <t xml:space="preserve">2.2801296710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445865631104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528123855591</t>
   </si>
   <si>
     <t xml:space="preserve">2.11558389663696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12359809875488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09955716133118</t>
+    <t xml:space="preserve">2.1235978603363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09955739974976</t>
   </si>
   <si>
     <t xml:space="preserve">2.08352994918823</t>
@@ -1058,13 +1058,13 @@
     <t xml:space="preserve">2.09154343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01942110061646</t>
+    <t xml:space="preserve">2.01942133903503</t>
   </si>
   <si>
     <t xml:space="preserve">2.00339412689209</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06750249862671</t>
+    <t xml:space="preserve">2.06750273704529</t>
   </si>
   <si>
     <t xml:space="preserve">2.1877064704895</t>
@@ -1076,13 +1076,13 @@
     <t xml:space="preserve">2.13962507247925</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16366577148438</t>
+    <t xml:space="preserve">2.1636655330658</t>
   </si>
   <si>
     <t xml:space="preserve">2.14763832092285</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20373368263245</t>
+    <t xml:space="preserve">2.20373344421387</t>
   </si>
   <si>
     <t xml:space="preserve">2.13161134719849</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">2.19571995735168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17969250679016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10757088661194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.05948901176453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07551622390747</t>
+    <t xml:space="preserve">2.17969298362732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10757064819336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05948925018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07551646232605</t>
   </si>
   <si>
     <t xml:space="preserve">2.03544855117798</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">2.27585577964783</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26784229278564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21976113319397</t>
+    <t xml:space="preserve">2.26784253120422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21976089477539</t>
   </si>
   <si>
     <t xml:space="preserve">2.21174716949463</t>
@@ -1127,100 +1127,100 @@
     <t xml:space="preserve">2.24380135536194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23578763008118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22777414321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15565228462219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30791044235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02743482589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04346227645874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9953807592392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524493694305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325830459595</t>
+    <t xml:space="preserve">2.23578786849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22777438163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15565204620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30791020393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02743458747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04346203804016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99538040161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524469852448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325866222382</t>
   </si>
   <si>
     <t xml:space="preserve">1.96332609653473</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97133994102478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736715316772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01140761375427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81106817722321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81908190250397</t>
+    <t xml:space="preserve">1.97133982181549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736703395844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01140809059143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8110682964325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81908214092255</t>
   </si>
   <si>
     <t xml:space="preserve">1.84312260150909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79504096508026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.7790139913559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82709538936615</t>
+    <t xml:space="preserve">1.79504120349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77901411056519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82709550857544</t>
   </si>
   <si>
     <t xml:space="preserve">1.77100038528442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73093247413635</t>
+    <t xml:space="preserve">1.73093271255493</t>
   </si>
   <si>
     <t xml:space="preserve">1.69887804985046</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7149053812027</t>
+    <t xml:space="preserve">1.71490550041199</t>
   </si>
   <si>
     <t xml:space="preserve">1.7469596862793</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72291910648346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73894619941711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298677921295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75497341156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305480957031</t>
+    <t xml:space="preserve">1.72291898727417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7389463186264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298689842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75497329235077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305457115173</t>
   </si>
   <si>
     <t xml:space="preserve">1.85914969444275</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86716318130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510911464691</t>
+    <t xml:space="preserve">1.86716330051422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510899543762</t>
   </si>
   <si>
     <t xml:space="preserve">1.87517690658569</t>
@@ -1232,37 +1232,37 @@
     <t xml:space="preserve">1.97935330867767</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9392853975296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02082920074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01258134841919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98783659934998</t>
+    <t xml:space="preserve">1.93928551673889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02082967758179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01258111000061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9878363609314</t>
   </si>
   <si>
     <t xml:space="preserve">1.99608469009399</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96309161186218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834662437439</t>
+    <t xml:space="preserve">1.96309173107147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9383465051651</t>
   </si>
   <si>
     <t xml:space="preserve">1.97958815097809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03732585906982</t>
+    <t xml:space="preserve">2.03732633590698</t>
   </si>
   <si>
     <t xml:space="preserve">2.06207084655762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0538227558136</t>
+    <t xml:space="preserve">2.05382227897644</t>
   </si>
   <si>
     <t xml:space="preserve">2.09506392478943</t>
@@ -1271,13 +1271,13 @@
     <t xml:space="preserve">2.16929864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16105031967163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11156058311462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10331249237061</t>
+    <t xml:space="preserve">2.16105008125305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1115608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10331201553345</t>
   </si>
   <si>
     <t xml:space="preserve">2.12805700302124</t>
@@ -1289,25 +1289,25 @@
     <t xml:space="preserve">2.11980891227722</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14455366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07856726646423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22703647613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21878838539124</t>
+    <t xml:space="preserve">2.14455389976501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07856750488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22703671455383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21878814697266</t>
   </si>
   <si>
     <t xml:space="preserve">2.25178146362305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24353313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21053981781006</t>
+    <t xml:space="preserve">2.24353289604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21054005622864</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002979278564</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">2.26827788352966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33426451683044</t>
+    <t xml:space="preserve">2.33426427841187</t>
   </si>
   <si>
     <t xml:space="preserve">2.30951952934265</t>
@@ -1325,25 +1325,25 @@
     <t xml:space="preserve">2.30127120018005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31776785850525</t>
+    <t xml:space="preserve">2.31776762008667</t>
   </si>
   <si>
     <t xml:space="preserve">2.38375401496887</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37550616264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601571083069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27652621269226</t>
+    <t xml:space="preserve">2.37550592422485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601594924927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27652597427368</t>
   </si>
   <si>
     <t xml:space="preserve">2.28477454185486</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29302263259888</t>
+    <t xml:space="preserve">2.29302310943604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23528480529785</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">2.44974040985107</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43324375152588</t>
+    <t xml:space="preserve">2.41674709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4332435131073</t>
   </si>
   <si>
     <t xml:space="preserve">2.40849876403809</t>
@@ -1367,10 +1367,10 @@
     <t xml:space="preserve">2.42499542236328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45798850059509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49922966957092</t>
+    <t xml:space="preserve">2.45798873901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4992299079895</t>
   </si>
   <si>
     <t xml:space="preserve">2.47448492050171</t>
@@ -1382,25 +1382,25 @@
     <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871964454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49098181724548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50747847557068</t>
+    <t xml:space="preserve">2.54871988296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4909815788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5074782371521</t>
   </si>
   <si>
     <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35076093673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40025067329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19404339790344</t>
+    <t xml:space="preserve">2.35076069831848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40025043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19404363632202</t>
   </si>
   <si>
     <t xml:space="preserve">2.185795545578</t>
@@ -1409,10 +1409,10 @@
     <t xml:space="preserve">2.04557418823242</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87236046791077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060855865479</t>
+    <t xml:space="preserve">1.87236022949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060867786407</t>
   </si>
   <si>
     <t xml:space="preserve">1.68264985084534</t>
@@ -1430,55 +1430,55 @@
     <t xml:space="preserve">1.64553260803223</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64140856266022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62491190433502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77338123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78162932395935</t>
+    <t xml:space="preserve">1.64140844345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62491202354431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77338087558746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78162956237793</t>
   </si>
   <si>
     <t xml:space="preserve">1.74863600730896</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80637431144714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411201953888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00433301925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81462228298187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812574386597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287061214447</t>
+    <t xml:space="preserve">1.80637419223785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411213874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00433325767517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81462252140045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287073135376</t>
   </si>
   <si>
     <t xml:space="preserve">1.84761536121368</t>
   </si>
   <si>
-    <t xml:space="preserve">1.83111882209778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.78987753391266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885700702667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91360175609589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710521697998</t>
+    <t xml:space="preserve">1.83111894130707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.78987765312195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885712623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360151767731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710509777069</t>
   </si>
   <si>
     <t xml:space="preserve">1.90535342693329</t>
@@ -1493,34 +1493,34 @@
     <t xml:space="preserve">2.08681583404541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17754673957825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07031941413879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07786893844604</t>
+    <t xml:space="preserve">2.17754697799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07031917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07786917686462</t>
   </si>
   <si>
     <t xml:space="preserve">2.06938791275024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03546357154846</t>
+    <t xml:space="preserve">2.03546380996704</t>
   </si>
   <si>
     <t xml:space="preserve">1.9845769405365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97609555721283</t>
+    <t xml:space="preserve">1.97609579563141</t>
   </si>
   <si>
     <t xml:space="preserve">1.95065248012543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99305808544159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06090688705444</t>
+    <t xml:space="preserve">1.99305784702301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06090712547302</t>
   </si>
   <si>
     <t xml:space="preserve">2.02698254585266</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">2.05242562294006</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04394483566284</t>
+    <t xml:space="preserve">2.04394459724426</t>
   </si>
   <si>
     <t xml:space="preserve">2.0100200176239</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0015389919281</t>
+    <t xml:space="preserve">2.00153923034668</t>
   </si>
   <si>
     <t xml:space="preserve">1.89976572990417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88280355930328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128494262695</t>
+    <t xml:space="preserve">1.88280379772186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128482341766</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850152015686</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">2.12027454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16268014907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20508527755737</t>
+    <t xml:space="preserve">2.16267967224121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20508551597595</t>
   </si>
   <si>
     <t xml:space="preserve">2.23052906990051</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">2.33230185508728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34926438331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35774493217468</t>
+    <t xml:space="preserve">2.34926414489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35774540901184</t>
   </si>
   <si>
     <t xml:space="preserve">2.42559385299683</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">2.47648048400879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46799969673157</t>
+    <t xml:space="preserve">2.46799945831299</t>
   </si>
   <si>
     <t xml:space="preserve">2.49344277381897</t>
@@ -1601,13 +1601,13 @@
     <t xml:space="preserve">2.51040506362915</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43407487869263</t>
+    <t xml:space="preserve">2.43407535552979</t>
   </si>
   <si>
     <t xml:space="preserve">2.41711282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888632774353</t>
+    <t xml:space="preserve">2.51888608932495</t>
   </si>
   <si>
     <t xml:space="preserve">2.58673501014709</t>
@@ -1625,67 +1625,67 @@
     <t xml:space="preserve">2.56129169464111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55281043052673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53584837913513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52736711502075</t>
+    <t xml:space="preserve">2.55281066894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53584814071655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52736735343933</t>
   </si>
   <si>
     <t xml:space="preserve">2.64610242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63762140274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66306471824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7054705619812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69698905944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6291401386261</t>
+    <t xml:space="preserve">2.63762164115906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66306495666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70547032356262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6969895362854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62914037704468</t>
   </si>
   <si>
     <t xml:space="preserve">2.71395134925842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7309136390686</t>
+    <t xml:space="preserve">2.73091340065002</t>
   </si>
   <si>
     <t xml:space="preserve">2.77331924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180003166199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84116792678833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86661148071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88357353210449</t>
+    <t xml:space="preserve">2.78180027008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84116768836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86661124229431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88357329368591</t>
   </si>
   <si>
     <t xml:space="preserve">2.90901684761047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85812997817993</t>
+    <t xml:space="preserve">2.85812973976135</t>
   </si>
   <si>
     <t xml:space="preserve">2.80724358558655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75635671615601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73939490318298</t>
+    <t xml:space="preserve">2.75635695457458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7393946647644</t>
   </si>
   <si>
     <t xml:space="preserve">2.74787592887878</t>
@@ -1697,31 +1697,31 @@
     <t xml:space="preserve">2.79028129577637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84964895248413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268642425537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82420587539673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91749787330627</t>
+    <t xml:space="preserve">2.84964871406555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268666267395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82420563697815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9174976348877</t>
   </si>
   <si>
     <t xml:space="preserve">3.01078987121582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03623342514038</t>
+    <t xml:space="preserve">3.0362331867218</t>
   </si>
   <si>
     <t xml:space="preserve">2.95990347862244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07863903045654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08711957931519</t>
+    <t xml:space="preserve">3.07863879203796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08711981773376</t>
   </si>
   <si>
     <t xml:space="preserve">3.12104415893555</t>
@@ -1736,16 +1736,16 @@
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281718254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23129844665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24826073646545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21433615684509</t>
+    <t xml:space="preserve">3.22281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23129820823669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24826049804688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21433591842651</t>
   </si>
   <si>
     <t xml:space="preserve">3.28218483924866</t>
@@ -1754,13 +1754,13 @@
     <t xml:space="preserve">3.40092039108276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42636370658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36699628829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3161096572876</t>
+    <t xml:space="preserve">3.42636346817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36699604988098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31610941886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.29066610336304</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">3.60159516334534</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59295797348022</t>
+    <t xml:space="preserve">3.5929582118988</t>
   </si>
   <si>
     <t xml:space="preserve">3.65341687202454</t>
@@ -1814,28 +1814,28 @@
     <t xml:space="preserve">3.61023187637329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71387553215027</t>
+    <t xml:space="preserve">3.71387529373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.67069053649902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78297090530396</t>
+    <t xml:space="preserve">3.7829704284668</t>
   </si>
   <si>
     <t xml:space="preserve">3.80888104438782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69660115242004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62750554084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64477968215942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73978567123413</t>
+    <t xml:space="preserve">3.6966016292572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62750577926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.644779920578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73978590965271</t>
   </si>
   <si>
     <t xml:space="preserve">3.7570595741272</t>
@@ -1844,7 +1844,7 @@
     <t xml:space="preserve">3.55841064453125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67932748794556</t>
+    <t xml:space="preserve">3.67932772636414</t>
   </si>
   <si>
     <t xml:space="preserve">3.57568430900574</t>
@@ -1853,43 +1853,43 @@
     <t xml:space="preserve">3.58432126045227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70523834228516</t>
+    <t xml:space="preserve">3.70523810386658</t>
   </si>
   <si>
     <t xml:space="preserve">3.5238630771637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54977369308472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48931527137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41158294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51522588729858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68796443939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74842286109924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66205334663391</t>
+    <t xml:space="preserve">3.5497739315033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48931550979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41158318519592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51522612571716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68796420097351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74842309951782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66205358505249</t>
   </si>
   <si>
     <t xml:space="preserve">3.6188690662384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86933922767639</t>
+    <t xml:space="preserve">3.86933994293213</t>
   </si>
   <si>
     <t xml:space="preserve">3.82615494728088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8607029914856</t>
+    <t xml:space="preserve">3.86070275306702</t>
   </si>
   <si>
     <t xml:space="preserve">3.91252446174622</t>
@@ -1901,16 +1901,16 @@
     <t xml:space="preserve">3.9557089805603</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99025630950928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342885017395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77433347702026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76569652557373</t>
+    <t xml:space="preserve">3.9902560710907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342861175537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77433323860168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76569676399231</t>
   </si>
   <si>
     <t xml:space="preserve">3.92979836463928</t>
@@ -1922,34 +1922,34 @@
     <t xml:space="preserve">3.9038872718811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87797617912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81751799583435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96434569358826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89525079727173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93843483924866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63614273071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49795246124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42885708808899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42022013664246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2820291519165</t>
+    <t xml:space="preserve">3.8779764175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81751847267151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96434617042542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89525032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93843507766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63614320755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4979522228241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42885661125183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42021989822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28202891349792</t>
   </si>
   <si>
     <t xml:space="preserve">3.25611877441406</t>
@@ -1970,13 +1970,13 @@
     <t xml:space="preserve">3.43749380111694</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37703561782837</t>
+    <t xml:space="preserve">3.37703537940979</t>
   </si>
   <si>
     <t xml:space="preserve">3.40294623374939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3597617149353</t>
+    <t xml:space="preserve">3.35976147651672</t>
   </si>
   <si>
     <t xml:space="preserve">3.21293377876282</t>
@@ -1985,13 +1985,13 @@
     <t xml:space="preserve">3.23020768165588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15247535705566</t>
+    <t xml:space="preserve">3.15247559547424</t>
   </si>
   <si>
     <t xml:space="preserve">3.11792778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19566011428833</t>
+    <t xml:space="preserve">3.19565987586975</t>
   </si>
   <si>
     <t xml:space="preserve">3.14383840560913</t>
@@ -2000,10 +2000,10 @@
     <t xml:space="preserve">2.97973704338074</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06610631942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53249979019165</t>
+    <t xml:space="preserve">3.06610608100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53250002861023</t>
   </si>
   <si>
     <t xml:space="preserve">3.56704759597778</t>
@@ -2021,13 +2021,13 @@
     <t xml:space="preserve">3.57765245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56879663467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52451872825623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61307454109192</t>
+    <t xml:space="preserve">3.56879711151123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5245189666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6130747795105</t>
   </si>
   <si>
     <t xml:space="preserve">3.58650803565979</t>
@@ -2036,49 +2036,49 @@
     <t xml:space="preserve">3.294273853302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31198525428772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35626316070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33855175971985</t>
+    <t xml:space="preserve">3.31198501586914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35626292228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33855199813843</t>
   </si>
   <si>
     <t xml:space="preserve">3.34740734100342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26770710945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30312943458557</t>
+    <t xml:space="preserve">3.26770734786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30312967300415</t>
   </si>
   <si>
     <t xml:space="preserve">3.2322850227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27656292915344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32969617843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32084083557129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28541851043701</t>
+    <t xml:space="preserve">3.27656269073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3296959400177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32084059715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28541827201843</t>
   </si>
   <si>
     <t xml:space="preserve">3.42710757255554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51566338539124</t>
+    <t xml:space="preserve">3.51566314697266</t>
   </si>
   <si>
     <t xml:space="preserve">3.55108571052551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4093964099884</t>
+    <t xml:space="preserve">3.40939617156982</t>
   </si>
   <si>
     <t xml:space="preserve">3.48909664154053</t>
@@ -2093,10 +2093,10 @@
     <t xml:space="preserve">3.5599410533905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4625301361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36511850357056</t>
+    <t xml:space="preserve">3.46252989768982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36511826515198</t>
   </si>
   <si>
     <t xml:space="preserve">3.41825175285339</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">3.3828296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44481897354126</t>
+    <t xml:space="preserve">3.44481873512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.45367431640625</t>
@@ -2123,16 +2123,16 @@
     <t xml:space="preserve">3.08174014091492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1437292098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11716222763062</t>
+    <t xml:space="preserve">3.14372897148132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11716246604919</t>
   </si>
   <si>
     <t xml:space="preserve">3.09059572219849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88691735267639</t>
+    <t xml:space="preserve">2.88691759109497</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890642166138</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">2.56811690330505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78950643539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75408387184143</t>
+    <t xml:space="preserve">2.78950619697571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75408363342285</t>
   </si>
   <si>
     <t xml:space="preserve">2.72751688957214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68323922157288</t>
+    <t xml:space="preserve">2.6832389831543</t>
   </si>
   <si>
     <t xml:space="preserve">2.82492852210999</t>
@@ -2192,16 +2192,16 @@
     <t xml:space="preserve">3.01975131034851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09945130348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03746223449707</t>
+    <t xml:space="preserve">3.09945106506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03746247291565</t>
   </si>
   <si>
     <t xml:space="preserve">2.94005084037781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01089572906494</t>
+    <t xml:space="preserve">3.01089549064636</t>
   </si>
   <si>
     <t xml:space="preserve">3.04631781578064</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">2.98432874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96661758422852</t>
+    <t xml:space="preserve">2.96661782264709</t>
   </si>
   <si>
     <t xml:space="preserve">2.90462851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203990936279</t>
+    <t xml:space="preserve">3.00204014778137</t>
   </si>
   <si>
     <t xml:space="preserve">2.93119549751282</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">2.77179503440857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81607270240784</t>
+    <t xml:space="preserve">2.81607294082642</t>
   </si>
   <si>
     <t xml:space="preserve">2.8780620098114</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">3.0286066532135</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05517363548279</t>
+    <t xml:space="preserve">3.05517339706421</t>
   </si>
   <si>
     <t xml:space="preserve">3.17029571533203</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">3.19686269760132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24114060401917</t>
+    <t xml:space="preserve">3.24114036560059</t>
   </si>
   <si>
     <t xml:space="preserve">3.25885152816772</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">3.37397408485413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40054082870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47138547897339</t>
+    <t xml:space="preserve">3.40054059028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47138524055481</t>
   </si>
   <si>
     <t xml:space="preserve">3.50680780410767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60421895980835</t>
+    <t xml:space="preserve">3.60421919822693</t>
   </si>
   <si>
     <t xml:space="preserve">3.63078570365906</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">3.62193036079407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63964128494263</t>
+    <t xml:space="preserve">3.63964152336121</t>
   </si>
   <si>
     <t xml:space="preserve">3.67674517631531</t>
@@ -69926,13 +69926,13 @@
     </row>
     <row r="2560">
       <c r="A2560" s="1" t="n">
-        <v>46050.6910069444</v>
+        <v>46050.3333333333</v>
       </c>
       <c r="B2560" t="n">
         <v>36630</v>
       </c>
       <c r="C2560" t="n">
-        <v>10.1999998092651</v>
+        <v>10.25</v>
       </c>
       <c r="D2560" t="n">
         <v>9.96000003814697</v>
@@ -69947,6 +69947,32 @@
         <v>1013</v>
       </c>
       <c r="H2560" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2561">
+      <c r="A2561" s="1" t="n">
+        <v>46051.6909953704</v>
+      </c>
+      <c r="B2561" t="n">
+        <v>56417</v>
+      </c>
+      <c r="C2561" t="n">
+        <v>10.3000001907349</v>
+      </c>
+      <c r="D2561" t="n">
+        <v>9.96000003814697</v>
+      </c>
+      <c r="E2561" t="n">
+        <v>10.0500001907349</v>
+      </c>
+      <c r="F2561" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2561" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H2561" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652279376984</t>
+    <t xml:space="preserve">1.73652267456055</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">1.74400770664215</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71406769752502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167271137238</t>
+    <t xml:space="preserve">1.71406745910645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167259216309</t>
   </si>
   <si>
     <t xml:space="preserve">1.67215144634247</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64969646930695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63921761512756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5733494758606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49625360965729</t>
+    <t xml:space="preserve">1.64969670772552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63921725749969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57334935665131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49625372886658</t>
   </si>
   <si>
     <t xml:space="preserve">1.48053538799286</t>
@@ -74,19 +74,19 @@
     <t xml:space="preserve">1.48203217983246</t>
   </si>
   <si>
-    <t xml:space="preserve">1.43637371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460725784302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42215204238892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41990673542023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41466701030731</t>
+    <t xml:space="preserve">1.43637359142303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460701942444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4221522808075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41990661621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4146671295166</t>
   </si>
   <si>
     <t xml:space="preserve">1.41915822029114</t>
@@ -95,10 +95,10 @@
     <t xml:space="preserve">1.407182097435</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3824816942215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38472712039948</t>
+    <t xml:space="preserve">1.38248157501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38472723960876</t>
   </si>
   <si>
     <t xml:space="preserve">1.3982001543045</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">1.33607447147369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.34730184078217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3428111076355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3839784860611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478711128235</t>
+    <t xml:space="preserve">1.34730195999146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.34281122684479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38397872447968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478687286377</t>
   </si>
   <si>
     <t xml:space="preserve">1.38098466396332</t>
@@ -128,37 +128,37 @@
     <t xml:space="preserve">1.36975705623627</t>
   </si>
   <si>
-    <t xml:space="preserve">1.37873899936676</t>
+    <t xml:space="preserve">1.37873911857605</t>
   </si>
   <si>
     <t xml:space="preserve">1.4311341047287</t>
   </si>
   <si>
-    <t xml:space="preserve">1.41017603874207</t>
+    <t xml:space="preserve">1.41017615795135</t>
   </si>
   <si>
     <t xml:space="preserve">1.44535577297211</t>
   </si>
   <si>
-    <t xml:space="preserve">1.46257126331329</t>
+    <t xml:space="preserve">1.46257138252258</t>
   </si>
   <si>
     <t xml:space="preserve">1.51197242736816</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52544546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52245140075684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54490613937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191243648529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54939746856689</t>
+    <t xml:space="preserve">1.52544522285461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52245128154755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54490637779236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191219806671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54939723014832</t>
   </si>
   <si>
     <t xml:space="preserve">1.56287050247192</t>
@@ -167,43 +167,43 @@
     <t xml:space="preserve">1.60029554367065</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60927736759186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173246383667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62424755096436</t>
+    <t xml:space="preserve">1.60927748680115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173258304596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62424767017365</t>
   </si>
   <si>
     <t xml:space="preserve">1.6302353143692</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61676263809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418767929077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64370846748352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58682239055634</t>
+    <t xml:space="preserve">1.61676275730133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418779850006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64370858669281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58682227134705</t>
   </si>
   <si>
     <t xml:space="preserve">1.58831942081451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63472652435303</t>
+    <t xml:space="preserve">1.63472628593445</t>
   </si>
   <si>
     <t xml:space="preserve">1.66017532348633</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66915738582611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68712174892426</t>
+    <t xml:space="preserve">1.6691575050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68712151050568</t>
   </si>
   <si>
     <t xml:space="preserve">1.6916127204895</t>
@@ -212,22 +212,22 @@
     <t xml:space="preserve">1.69310963153839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72155249118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502576351166</t>
+    <t xml:space="preserve">1.72155272960663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502564430237</t>
   </si>
   <si>
     <t xml:space="preserve">1.70358872413635</t>
   </si>
   <si>
-    <t xml:space="preserve">1.70658254623413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69909763336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664265632629</t>
+    <t xml:space="preserve">1.70658266544342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69909739494324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67664229869843</t>
   </si>
   <si>
     <t xml:space="preserve">1.68412756919861</t>
@@ -239,16 +239,16 @@
     <t xml:space="preserve">1.68263053894043</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64221131801605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64670240879059</t>
+    <t xml:space="preserve">1.64221155643463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64670264720917</t>
   </si>
   <si>
     <t xml:space="preserve">1.67514550685883</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69964492321014</t>
+    <t xml:space="preserve">1.69964504241943</t>
   </si>
   <si>
     <t xml:space="preserve">1.68433284759521</t>
@@ -257,46 +257,46 @@
     <t xml:space="preserve">1.69198906421661</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72108197212219</t>
+    <t xml:space="preserve">1.72108209133148</t>
   </si>
   <si>
     <t xml:space="preserve">1.70576965808868</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69505143165588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495699882507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72261321544647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65370869636536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208313941956</t>
+    <t xml:space="preserve">1.69505107402802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495687961578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72261309623718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65370881557465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208302021027</t>
   </si>
   <si>
     <t xml:space="preserve">1.66902089118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65217733383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60624122619629</t>
+    <t xml:space="preserve">1.65217757225037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60624098777771</t>
   </si>
   <si>
     <t xml:space="preserve">1.56183588504791</t>
   </si>
   <si>
-    <t xml:space="preserve">1.55417990684509</t>
+    <t xml:space="preserve">1.5541797876358</t>
   </si>
   <si>
     <t xml:space="preserve">1.52202439308167</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53121161460876</t>
+    <t xml:space="preserve">1.53121149539948</t>
   </si>
   <si>
     <t xml:space="preserve">1.59092903137207</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">1.55111753940582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53886783123016</t>
+    <t xml:space="preserve">1.53886759281158</t>
   </si>
   <si>
     <t xml:space="preserve">1.4929313659668</t>
@@ -317,40 +317,40 @@
     <t xml:space="preserve">1.47608816623688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52278995513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46996331214905</t>
+    <t xml:space="preserve">1.52278983592987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46996319293976</t>
   </si>
   <si>
     <t xml:space="preserve">1.47761917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">1.51589953899384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50058746337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60777199268341</t>
+    <t xml:space="preserve">1.51589965820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50058734416962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6077721118927</t>
   </si>
   <si>
     <t xml:space="preserve">1.59705364704132</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56949186325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308442592621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66748929023743</t>
+    <t xml:space="preserve">1.56949174404144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308430671692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66748940944672</t>
   </si>
   <si>
     <t xml:space="preserve">1.66136479377747</t>
   </si>
   <si>
-    <t xml:space="preserve">1.67667663097382</t>
+    <t xml:space="preserve">1.67667675018311</t>
   </si>
   <si>
     <t xml:space="preserve">1.6154283285141</t>
@@ -362,52 +362,52 @@
     <t xml:space="preserve">1.58480405807495</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63839650154114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6338027715683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57561671733856</t>
+    <t xml:space="preserve">1.63839662075043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63380289077759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
     <t xml:space="preserve">1.54652380943298</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56796097755432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5449925661087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52355575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54193019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58174157142639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55877351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5802104473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55264866352081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53044593334198</t>
+    <t xml:space="preserve">1.56796073913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54499244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52355551719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54192996025085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174169063568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55877339839935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58021056652069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5526487827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53044605255127</t>
   </si>
   <si>
     <t xml:space="preserve">1.51972758769989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50594687461853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671231746674</t>
+    <t xml:space="preserve">1.50594651699066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671255588531</t>
   </si>
   <si>
     <t xml:space="preserve">1.53427410125732</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">1.59246003627777</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50211870670319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50824356079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47532248497009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49675941467285</t>
+    <t xml:space="preserve">1.5021185874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50824344158173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47532224655151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49675929546356</t>
   </si>
   <si>
     <t xml:space="preserve">1.50747787952423</t>
@@ -446,25 +446,25 @@
     <t xml:space="preserve">1.60011601448059</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58786642551422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56489837169647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.56336736679077</t>
+    <t xml:space="preserve">1.58786654472351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56489825248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56336724758148</t>
   </si>
   <si>
     <t xml:space="preserve">1.57255434989929</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59858500957489</t>
+    <t xml:space="preserve">1.59858524799347</t>
   </si>
   <si>
     <t xml:space="preserve">1.59399151802063</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60470974445343</t>
+    <t xml:space="preserve">1.60470986366272</t>
   </si>
   <si>
     <t xml:space="preserve">1.64758372306824</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">1.63686525821686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64452135562897</t>
+    <t xml:space="preserve">1.64452147483826</t>
   </si>
   <si>
     <t xml:space="preserve">1.6322717666626</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">1.73026931285858</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7455815076828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017511844635</t>
+    <t xml:space="preserve">1.74558115005493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017488002777</t>
   </si>
   <si>
     <t xml:space="preserve">1.70730102062225</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">1.70423889160156</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73792517185211</t>
+    <t xml:space="preserve">1.73792505264282</t>
   </si>
   <si>
     <t xml:space="preserve">1.75936233997345</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">1.78386163711548</t>
   </si>
   <si>
-    <t xml:space="preserve">1.76854944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323736667633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486280441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639404773712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79151737689972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80223608016968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82061088085175</t>
+    <t xml:space="preserve">1.76854920387268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323712825775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486268520355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639380931854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7915176153183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80223631858826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82061076164246</t>
   </si>
   <si>
     <t xml:space="preserve">1.81754839420319</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">1.80682957172394</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82520425319672</t>
+    <t xml:space="preserve">1.82520437240601</t>
   </si>
   <si>
     <t xml:space="preserve">1.81448590755463</t>
@@ -560,19 +560,19 @@
     <t xml:space="preserve">1.85889101028442</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87726521492004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85429716110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582876205444</t>
+    <t xml:space="preserve">1.87726557254791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85429739952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582864284515</t>
   </si>
   <si>
     <t xml:space="preserve">1.85123491287231</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86654698848724</t>
+    <t xml:space="preserve">1.86654710769653</t>
   </si>
   <si>
     <t xml:space="preserve">1.84970378875732</t>
@@ -581,37 +581,37 @@
     <t xml:space="preserve">1.86348462104797</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8527660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8374537229538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84511005878448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82367265224457</t>
+    <t xml:space="preserve">1.85276639461517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745408058167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8451099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82367289066315</t>
   </si>
   <si>
     <t xml:space="preserve">1.84051620960236</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84817266464233</t>
+    <t xml:space="preserve">1.84817290306091</t>
   </si>
   <si>
     <t xml:space="preserve">1.86807823181152</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9492324590683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90789008140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92167055606842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932677268982</t>
+    <t xml:space="preserve">1.94923269748688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788972377777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92167067527771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932665348053</t>
   </si>
   <si>
     <t xml:space="preserve">1.92473304271698</t>
@@ -623,73 +623,73 @@
     <t xml:space="preserve">1.98904371261597</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99823105335236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00895023345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00741863250732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01201248168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99057519435883</t>
+    <t xml:space="preserve">1.99823117256165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00894951820374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00741839408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01201224327087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99057507514954</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00588703155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09207773208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051108360291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401700973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424210548401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1155846118927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17043232917786</t>
+    <t xml:space="preserve">2.00588726997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0920774936676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051060676575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401677131653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424258232117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558437347412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17043256759644</t>
   </si>
   <si>
     <t xml:space="preserve">2.14692616462708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15006017684937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655401229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259741783142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15162801742554</t>
+    <t xml:space="preserve">2.15006041526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655377388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259694099426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15162777900696</t>
   </si>
   <si>
     <t xml:space="preserve">2.13909077644348</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16103029251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0466320514679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0528998374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03722906112671</t>
+    <t xml:space="preserve">2.16103005409241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04663157463074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.05290031433105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03722929954529</t>
   </si>
   <si>
     <t xml:space="preserve">2.04819893836975</t>
@@ -707,10 +707,10 @@
     <t xml:space="preserve">2.10774874687195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11715126037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12341952323914</t>
+    <t xml:space="preserve">2.11715149879456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12341976165771</t>
   </si>
   <si>
     <t xml:space="preserve">2.13125514984131</t>
@@ -722,31 +722,31 @@
     <t xml:space="preserve">2.19393920898438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20647597312927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20334148406982</t>
+    <t xml:space="preserve">2.20647573471069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20334196090698</t>
   </si>
   <si>
     <t xml:space="preserve">2.19237208366394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20804333686829</t>
+    <t xml:space="preserve">2.20804309844971</t>
   </si>
   <si>
     <t xml:space="preserve">2.16416430473328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15946292877197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13595652580261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09677886962891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06386971473694</t>
+    <t xml:space="preserve">2.15946316719055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13595676422119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09677910804749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386995315552</t>
   </si>
   <si>
     <t xml:space="preserve">2.02625966072083</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">1.96827721595764</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99805176258087</t>
+    <t xml:space="preserve">1.99805152416229</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640671730042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05446767807007</t>
+    <t xml:space="preserve">2.05446743965149</t>
   </si>
   <si>
     <t xml:space="preserve">2.10461449623108</t>
@@ -773,10 +773,10 @@
     <t xml:space="preserve">2.03566217422485</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04976606369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954120635986</t>
+    <t xml:space="preserve">2.04976582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954096794128</t>
   </si>
   <si>
     <t xml:space="preserve">2.06857132911682</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">2.22371411323547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.211177110672</t>
+    <t xml:space="preserve">2.21117734909058</t>
   </si>
   <si>
     <t xml:space="preserve">2.23311686515808</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23781800270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930732727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31460618972778</t>
+    <t xml:space="preserve">2.23781776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930708885193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3146059513092</t>
   </si>
   <si>
     <t xml:space="preserve">2.3271427154541</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">2.38669228553772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44467496871948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601699829102</t>
+    <t xml:space="preserve">2.4446747303009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601723670959</t>
   </si>
   <si>
     <t xml:space="preserve">2.48541975021362</t>
@@ -830,43 +830,43 @@
     <t xml:space="preserve">2.49012112617493</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5214626789093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735950469971</t>
+    <t xml:space="preserve">2.52146291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735926628113</t>
   </si>
   <si>
     <t xml:space="preserve">2.53870129585266</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53086543083191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49168825149536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50422525405884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49952363967896</t>
+    <t xml:space="preserve">2.53086590766907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49168848991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50422477722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49952387809753</t>
   </si>
   <si>
     <t xml:space="preserve">2.52303004264832</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53243279457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206016540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5089259147644</t>
+    <t xml:space="preserve">2.5324330329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206040382385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50892615318298</t>
   </si>
   <si>
     <t xml:space="preserve">2.51362752914429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49795627593994</t>
+    <t xml:space="preserve">2.49795651435852</t>
   </si>
   <si>
     <t xml:space="preserve">2.49638938903809</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">2.52616405487061</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54653644561768</t>
+    <t xml:space="preserve">2.54653668403625</t>
   </si>
   <si>
     <t xml:space="preserve">2.55123782157898</t>
@@ -884,52 +884,52 @@
     <t xml:space="preserve">2.53713393211365</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55437231063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60608625411987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70794773101807</t>
+    <t xml:space="preserve">2.55437207221985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60608649253845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70794749259949</t>
   </si>
   <si>
     <t xml:space="preserve">2.71108222007751</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72205138206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541120529175</t>
+    <t xml:space="preserve">2.72205185890198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541144371033</t>
   </si>
   <si>
     <t xml:space="preserve">2.70324635505676</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67347145080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66406869888306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61705589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981799125671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58728098869324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59825086593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58571434020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57004284858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56220722198486</t>
+    <t xml:space="preserve">2.67347168922424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66406941413879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61705613136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981822967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728122711182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59825110435486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58571410179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57004308700562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56220746040344</t>
   </si>
   <si>
     <t xml:space="preserve">2.54183506965637</t>
@@ -941,31 +941,31 @@
     <t xml:space="preserve">2.52929854393005</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52459764480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131609916687</t>
+    <t xml:space="preserve">2.52459740638733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034598350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131586074829</t>
   </si>
   <si>
     <t xml:space="preserve">2.48228549957275</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43370532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39609527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087397575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206894874573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25975751876831</t>
+    <t xml:space="preserve">2.43370580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39609503746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087445259094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206942558289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25975728034973</t>
   </si>
   <si>
     <t xml:space="preserve">2.27699542045593</t>
@@ -983,25 +983,25 @@
     <t xml:space="preserve">2.35064911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35848450660706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41333293914795</t>
+    <t xml:space="preserve">2.35848474502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41333317756653</t>
   </si>
   <si>
     <t xml:space="preserve">2.43683958053589</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62489151954651</t>
+    <t xml:space="preserve">2.62489175796509</t>
   </si>
   <si>
     <t xml:space="preserve">2.63272714614868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.468181848526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36631989479065</t>
+    <t xml:space="preserve">2.46818161010742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36632037162781</t>
   </si>
   <si>
     <t xml:space="preserve">2.381991147995</t>
@@ -1010,46 +1010,46 @@
     <t xml:space="preserve">2.39766216278076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45251035690308</t>
+    <t xml:space="preserve">2.45251083374023</t>
   </si>
   <si>
     <t xml:space="preserve">2.40549755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4211688041687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900395393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878764152527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363655090332</t>
+    <t xml:space="preserve">2.42116832733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900371551514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878787994385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363631248474</t>
   </si>
   <si>
     <t xml:space="preserve">2.25662302970886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27229404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28012990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445865631104</t>
+    <t xml:space="preserve">2.27229428291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2801296710968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445913314819</t>
   </si>
   <si>
     <t xml:space="preserve">2.22528100013733</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11558437347412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1235978603363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09955668449402</t>
+    <t xml:space="preserve">2.11558413505554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12359762191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09955716133118</t>
   </si>
   <si>
     <t xml:space="preserve">2.08352971076965</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">2.01942157745361</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00339388847351</t>
+    <t xml:space="preserve">2.00339436531067</t>
   </si>
   <si>
     <t xml:space="preserve">2.06750297546387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1877064704895</t>
+    <t xml:space="preserve">2.18770670890808</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188275337219</t>
@@ -1076,25 +1076,25 @@
     <t xml:space="preserve">2.13962483406067</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16366600990295</t>
+    <t xml:space="preserve">2.16366577148438</t>
   </si>
   <si>
     <t xml:space="preserve">2.14763879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20373344421387</t>
+    <t xml:space="preserve">2.20373368263245</t>
   </si>
   <si>
     <t xml:space="preserve">2.13161134719849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17167901992798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19571995735168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17969274520874</t>
+    <t xml:space="preserve">2.17167925834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19572019577026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17969250679016</t>
   </si>
   <si>
     <t xml:space="preserve">2.10757088661194</t>
@@ -1103,13 +1103,13 @@
     <t xml:space="preserve">2.05948901176453</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07551622390747</t>
+    <t xml:space="preserve">2.07551598548889</t>
   </si>
   <si>
     <t xml:space="preserve">2.03544855117798</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05147552490234</t>
+    <t xml:space="preserve">2.05147576332092</t>
   </si>
   <si>
     <t xml:space="preserve">2.27585554122925</t>
@@ -1118,13 +1118,13 @@
     <t xml:space="preserve">2.26784205436707</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21976041793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21174740791321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24380135536194</t>
+    <t xml:space="preserve">2.21976065635681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21174693107605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24380159378052</t>
   </si>
   <si>
     <t xml:space="preserve">2.23578786849976</t>
@@ -1133,34 +1133,34 @@
     <t xml:space="preserve">2.22777438163757</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15565204620361</t>
+    <t xml:space="preserve">2.15565228462219</t>
   </si>
   <si>
     <t xml:space="preserve">2.30790996551514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02743482589722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04346203804016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99538052082062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524481773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325806617737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96332597732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97134017944336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98736727237701</t>
+    <t xml:space="preserve">2.02743458747864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04346179962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9953807592392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524493694305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325830459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96332633495331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97133994102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98736691474915</t>
   </si>
   <si>
     <t xml:space="preserve">2.01140761375427</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">1.77901411056519</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82709562778473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77100050449371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73093283176422</t>
+    <t xml:space="preserve">1.82709538936615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.771000623703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73093271255493</t>
   </si>
   <si>
     <t xml:space="preserve">1.69887816905975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7149053812027</t>
+    <t xml:space="preserve">1.71490550041199</t>
   </si>
   <si>
     <t xml:space="preserve">1.74695980548859</t>
@@ -1202,37 +1202,37 @@
     <t xml:space="preserve">1.72291898727417</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73894619941711</t>
+    <t xml:space="preserve">1.7389463186264</t>
   </si>
   <si>
     <t xml:space="preserve">1.76298689842224</t>
   </si>
   <si>
-    <t xml:space="preserve">1.75497329235077</t>
+    <t xml:space="preserve">1.75497317314148</t>
   </si>
   <si>
     <t xml:space="preserve">1.80305469036102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85914969444275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8671635389328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510911464691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87517666816711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723133087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935342788696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9392853975296</t>
+    <t xml:space="preserve">1.85914981365204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86716341972351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510899543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8751767873764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723145008087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935330867767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93928563594818</t>
   </si>
   <si>
     <t xml:space="preserve">2.02082943916321</t>
@@ -1241,31 +1241,31 @@
     <t xml:space="preserve">2.01258134841919</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98783624172211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9960845708847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96309161186218</t>
+    <t xml:space="preserve">1.9878363609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99608469009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96309149265289</t>
   </si>
   <si>
     <t xml:space="preserve">1.9383465051651</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9795880317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0373260974884</t>
+    <t xml:space="preserve">1.97958815097809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03732633590698</t>
   </si>
   <si>
     <t xml:space="preserve">2.06207084655762</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05382251739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09506392478943</t>
+    <t xml:space="preserve">2.0538227558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09506416320801</t>
   </si>
   <si>
     <t xml:space="preserve">2.16929864883423</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11156034469604</t>
+    <t xml:space="preserve">2.11156058311462</t>
   </si>
   <si>
     <t xml:space="preserve">2.10331249237061</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.13630557060242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11980891227722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14455366134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07856774330139</t>
+    <t xml:space="preserve">2.11980867385864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14455342292786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07856750488281</t>
   </si>
   <si>
     <t xml:space="preserve">2.22703671455383</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">2.24353313446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2105405330658</t>
+    <t xml:space="preserve">2.21054029464722</t>
   </si>
   <si>
     <t xml:space="preserve">2.26002979278564</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">2.26827812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33426427841187</t>
+    <t xml:space="preserve">2.33426380157471</t>
   </si>
   <si>
     <t xml:space="preserve">2.30951929092407</t>
@@ -1325,46 +1325,46 @@
     <t xml:space="preserve">2.30127096176147</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31776785850525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38375449180603</t>
+    <t xml:space="preserve">2.31776762008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38375425338745</t>
   </si>
   <si>
     <t xml:space="preserve">2.37550568580627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32601594924927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27652645111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28477430343628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29302287101746</t>
+    <t xml:space="preserve">2.32601571083069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27652621269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28477454185486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29302310943604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23528480529785</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39200210571289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44973993301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41674709320068</t>
+    <t xml:space="preserve">2.39200258255005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44974040985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41674733161926</t>
   </si>
   <si>
     <t xml:space="preserve">2.43324375152588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40849852561951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42499589920044</t>
+    <t xml:space="preserve">2.40849876403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42499566078186</t>
   </si>
   <si>
     <t xml:space="preserve">2.45798850059509</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">2.47448515892029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51572632789612</t>
+    <t xml:space="preserve">2.5157265663147</t>
   </si>
   <si>
     <t xml:space="preserve">2.58996105194092</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">2.54871964454651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49098181724548</t>
+    <t xml:space="preserve">2.4909815788269</t>
   </si>
   <si>
     <t xml:space="preserve">2.5074782371521</t>
@@ -1394,49 +1394,49 @@
     <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35076069831848</t>
+    <t xml:space="preserve">2.35076093673706</t>
   </si>
   <si>
     <t xml:space="preserve">2.40025067329407</t>
   </si>
   <si>
-    <t xml:space="preserve">2.19404315948486</t>
+    <t xml:space="preserve">2.19404363632202</t>
   </si>
   <si>
     <t xml:space="preserve">2.185795545578</t>
   </si>
   <si>
-    <t xml:space="preserve">2.045574426651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87236034870148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060879707336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264985084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69089806079865</t>
+    <t xml:space="preserve">2.04557418823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87236046791077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060867786407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264973163605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69089818000793</t>
   </si>
   <si>
     <t xml:space="preserve">1.56717395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71564292907715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64553260803223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64140868186951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62491178512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77338099479675</t>
+    <t xml:space="preserve">1.71564280986786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64553272724152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64140856266022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62491190433502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77338111400604</t>
   </si>
   <si>
     <t xml:space="preserve">1.78162944316864</t>
@@ -1445,13 +1445,13 @@
     <t xml:space="preserve">1.74863612651825</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80637419223785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411225795746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00433278083801</t>
+    <t xml:space="preserve">1.80637407302856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411213874817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00433325767517</t>
   </si>
   <si>
     <t xml:space="preserve">1.81462240219116</t>
@@ -1460,7 +1460,7 @@
     <t xml:space="preserve">1.79812586307526</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82287073135376</t>
+    <t xml:space="preserve">1.82287096977234</t>
   </si>
   <si>
     <t xml:space="preserve">1.84761559963226</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">1.83111906051636</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78987765312195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88885688781738</t>
+    <t xml:space="preserve">1.78987777233124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88885676860809</t>
   </si>
   <si>
     <t xml:space="preserve">1.9136016368866</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">1.89710521697998</t>
   </si>
   <si>
-    <t xml:space="preserve">1.90535354614258</t>
+    <t xml:space="preserve">1.90535342693329</t>
   </si>
   <si>
     <t xml:space="preserve">1.9548431634903</t>
@@ -1490,40 +1490,40 @@
     <t xml:space="preserve">2.02907800674438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08681583404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17754697799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07031893730164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07786893844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06938815116882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03546333312988</t>
+    <t xml:space="preserve">2.08681559562683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17754721641541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07031917572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07786917686462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06938791275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03546380996704</t>
   </si>
   <si>
     <t xml:space="preserve">1.9845769405365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9760959148407</t>
+    <t xml:space="preserve">1.97609603404999</t>
   </si>
   <si>
     <t xml:space="preserve">1.95065248012543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.9930579662323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06090688705444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02698278427124</t>
+    <t xml:space="preserve">1.99305784702301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06090712547302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.02698254585266</t>
   </si>
   <si>
     <t xml:space="preserve">2.05242586135864</t>
@@ -1535,40 +1535,40 @@
     <t xml:space="preserve">2.01002025604248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00153875350952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89976608753204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88280391693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128494262695</t>
+    <t xml:space="preserve">2.00153923034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89976596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88280379772186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128482341766</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850152015686</t>
   </si>
   <si>
-    <t xml:space="preserve">1.95913374423981</t>
+    <t xml:space="preserve">1.95913350582123</t>
   </si>
   <si>
     <t xml:space="preserve">2.08635020256042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875533103943</t>
+    <t xml:space="preserve">2.12875556945801</t>
   </si>
   <si>
     <t xml:space="preserve">2.12027454376221</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16268014907837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20508551597595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23052883148193</t>
+    <t xml:space="preserve">2.16267991065979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20508527755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23052906990051</t>
   </si>
   <si>
     <t xml:space="preserve">2.30685877799988</t>
@@ -1583,10 +1583,10 @@
     <t xml:space="preserve">2.35774540901184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42559409141541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44255614280701</t>
+    <t xml:space="preserve">2.42559385299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44255638122559</t>
   </si>
   <si>
     <t xml:space="preserve">2.47648048400879</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">2.46799969673157</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49344325065613</t>
+    <t xml:space="preserve">2.49344301223755</t>
   </si>
   <si>
     <t xml:space="preserve">2.51040506362915</t>
@@ -1607,31 +1607,31 @@
     <t xml:space="preserve">2.41711282730103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51888608932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58673477172852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56977248191833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54432940483093</t>
+    <t xml:space="preserve">2.51888632774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58673501014709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56977272033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54432964324951</t>
   </si>
   <si>
     <t xml:space="preserve">2.57825398445129</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56129193305969</t>
+    <t xml:space="preserve">2.56129169464111</t>
   </si>
   <si>
     <t xml:space="preserve">2.55281043052673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53584837913513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52736735343933</t>
+    <t xml:space="preserve">2.53584861755371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52736711502075</t>
   </si>
   <si>
     <t xml:space="preserve">2.64610242843628</t>
@@ -1643,16 +1643,16 @@
     <t xml:space="preserve">2.66306471824646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70547032356262</t>
+    <t xml:space="preserve">2.70547008514404</t>
   </si>
   <si>
     <t xml:space="preserve">2.69698905944824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62914037704468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71395182609558</t>
+    <t xml:space="preserve">2.6291401386261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.713951587677</t>
   </si>
   <si>
     <t xml:space="preserve">2.7309136390686</t>
@@ -1661,13 +1661,13 @@
     <t xml:space="preserve">2.77331900596619</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78180027008057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84116816520691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86661124229431</t>
+    <t xml:space="preserve">2.78180003166199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84116792678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86661148071289</t>
   </si>
   <si>
     <t xml:space="preserve">2.88357329368591</t>
@@ -1676,7 +1676,7 @@
     <t xml:space="preserve">2.90901660919189</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85812997817993</t>
+    <t xml:space="preserve">2.85812973976135</t>
   </si>
   <si>
     <t xml:space="preserve">2.80724358558655</t>
@@ -1688,19 +1688,19 @@
     <t xml:space="preserve">2.7393946647644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74787592887878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79876255989075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79028105735779</t>
+    <t xml:space="preserve">2.74787569046021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79876232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79028129577637</t>
   </si>
   <si>
     <t xml:space="preserve">2.84964895248413</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268642425537</t>
+    <t xml:space="preserve">2.83268666267395</t>
   </si>
   <si>
     <t xml:space="preserve">2.82420563697815</t>
@@ -1709,10 +1709,10 @@
     <t xml:space="preserve">2.91749787330627</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01078939437866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03623294830322</t>
+    <t xml:space="preserve">3.01078963279724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0362331867218</t>
   </si>
   <si>
     <t xml:space="preserve">2.95990324020386</t>
@@ -1721,13 +1721,13 @@
     <t xml:space="preserve">3.07863879203796</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08711981773376</t>
+    <t xml:space="preserve">3.08711957931519</t>
   </si>
   <si>
     <t xml:space="preserve">3.12104415893555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18041181564331</t>
+    <t xml:space="preserve">3.18041157722473</t>
   </si>
   <si>
     <t xml:space="preserve">3.14648723602295</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">3.23977947235107</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22281742095947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23129796981812</t>
+    <t xml:space="preserve">3.22281718254089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23129820823669</t>
   </si>
   <si>
     <t xml:space="preserve">3.24826073646545</t>
@@ -1748,28 +1748,28 @@
     <t xml:space="preserve">3.21433615684509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28218507766724</t>
+    <t xml:space="preserve">3.28218483924866</t>
   </si>
   <si>
     <t xml:space="preserve">3.40092062950134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42636370658875</t>
+    <t xml:space="preserve">3.42636394500732</t>
   </si>
   <si>
     <t xml:space="preserve">3.3669958114624</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3161096572876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29066610336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27370357513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30794024467468</t>
+    <t xml:space="preserve">3.31610918045044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29066634178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27370381355286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3079400062561</t>
   </si>
   <si>
     <t xml:space="preserve">3.31657671928406</t>
@@ -1793,31 +1793,31 @@
     <t xml:space="preserve">3.44613075256348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45476770401001</t>
+    <t xml:space="preserve">3.45476746559143</t>
   </si>
   <si>
     <t xml:space="preserve">3.4720413684845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54113674163818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60159516334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59295797348022</t>
+    <t xml:space="preserve">3.54113698005676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60159540176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5929582118988</t>
   </si>
   <si>
     <t xml:space="preserve">3.65341687202454</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61023163795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71387529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6706907749176</t>
+    <t xml:space="preserve">3.61023187637329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71387505531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67069053649902</t>
   </si>
   <si>
     <t xml:space="preserve">3.7829704284668</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">3.69660139083862</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62750554084778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.644779920578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73978590965271</t>
+    <t xml:space="preserve">3.62750577926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64477968215942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73978567123413</t>
   </si>
   <si>
     <t xml:space="preserve">3.75705981254578</t>
@@ -1853,7 +1853,7 @@
     <t xml:space="preserve">3.58432149887085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.705237865448</t>
+    <t xml:space="preserve">3.70523810386658</t>
   </si>
   <si>
     <t xml:space="preserve">3.5238630771637</t>
@@ -1862,22 +1862,22 @@
     <t xml:space="preserve">3.5497739315033</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48931527137756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41158294677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51522588729858</t>
+    <t xml:space="preserve">3.48931550979614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41158318519592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51522636413574</t>
   </si>
   <si>
     <t xml:space="preserve">3.68796420097351</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74842309951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66205358505249</t>
+    <t xml:space="preserve">3.7484233379364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66205334663391</t>
   </si>
   <si>
     <t xml:space="preserve">3.61886930465698</t>
@@ -1886,64 +1886,64 @@
     <t xml:space="preserve">3.86933970451355</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82615494728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8607029914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91252446174622</t>
+    <t xml:space="preserve">3.82615518569946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86070275306702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91252493858337</t>
   </si>
   <si>
     <t xml:space="preserve">3.99889373779297</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9557089805603</t>
+    <t xml:space="preserve">3.95570874214172</t>
   </si>
   <si>
     <t xml:space="preserve">3.99025630950928</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84342885017395</t>
+    <t xml:space="preserve">3.84342861175537</t>
   </si>
   <si>
     <t xml:space="preserve">3.77433347702026</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76569700241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92979836463928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661313056946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90388774871826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87797617912292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81751823425293</t>
+    <t xml:space="preserve">3.76569676399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92979860305786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661336898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90388751029968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8779764175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81751847267151</t>
   </si>
   <si>
     <t xml:space="preserve">3.96434569358826</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89525079727173</t>
+    <t xml:space="preserve">3.89525032043457</t>
   </si>
   <si>
     <t xml:space="preserve">3.93843507766724</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63614320755005</t>
+    <t xml:space="preserve">3.63614296913147</t>
   </si>
   <si>
     <t xml:space="preserve">3.49795246124268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885684967041</t>
+    <t xml:space="preserve">3.42885661125183</t>
   </si>
   <si>
     <t xml:space="preserve">3.42021989822388</t>
@@ -1970,37 +1970,37 @@
     <t xml:space="preserve">3.33385062217712</t>
   </si>
   <si>
-    <t xml:space="preserve">3.43749380111694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37703537940979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40294623374939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35976147651672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21293425559998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23020792007446</t>
+    <t xml:space="preserve">3.43749403953552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37703514099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40294599533081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3597617149353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.21293377876282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23020768165588</t>
   </si>
   <si>
     <t xml:space="preserve">3.15247535705566</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11792802810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19566011428833</t>
+    <t xml:space="preserve">3.11792778968811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19565987586975</t>
   </si>
   <si>
     <t xml:space="preserve">3.14383840560913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97973680496216</t>
+    <t xml:space="preserve">2.97973704338074</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610608100891</t>
@@ -2012,10 +2012,10 @@
     <t xml:space="preserve">3.56704759597778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46340465545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38567209243774</t>
+    <t xml:space="preserve">3.46340489387512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38567233085632</t>
   </si>
   <si>
     <t xml:space="preserve">3.54223012924194</t>
@@ -2024,46 +2024,46 @@
     <t xml:space="preserve">3.57765245437622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56879687309265</t>
+    <t xml:space="preserve">3.56879711151123</t>
   </si>
   <si>
     <t xml:space="preserve">3.5245189666748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61307454109192</t>
+    <t xml:space="preserve">3.6130747795105</t>
   </si>
   <si>
     <t xml:space="preserve">3.58650803565979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29427409172058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31198525428772</t>
+    <t xml:space="preserve">3.294273853302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31198501586914</t>
   </si>
   <si>
     <t xml:space="preserve">3.35626292228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33855175971985</t>
+    <t xml:space="preserve">3.33855199813843</t>
   </si>
   <si>
     <t xml:space="preserve">3.34740734100342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26770710945129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30312943458557</t>
+    <t xml:space="preserve">3.26770734786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30312967300415</t>
   </si>
   <si>
     <t xml:space="preserve">3.2322850227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27656292915344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32969617843628</t>
+    <t xml:space="preserve">3.27656269073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3296959400177</t>
   </si>
   <si>
     <t xml:space="preserve">3.32084059715271</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">3.55108571052551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4093964099884</t>
+    <t xml:space="preserve">3.40939617156982</t>
   </si>
   <si>
     <t xml:space="preserve">3.48909664154053</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">3.46252989768982</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36511850357056</t>
+    <t xml:space="preserve">3.36511826515198</t>
   </si>
   <si>
     <t xml:space="preserve">3.41825175285339</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">3.3828296661377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44481897354126</t>
+    <t xml:space="preserve">3.44481873512268</t>
   </si>
   <si>
     <t xml:space="preserve">3.45367431640625</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">3.11716246604919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09059548377991</t>
+    <t xml:space="preserve">3.09059572219849</t>
   </si>
   <si>
     <t xml:space="preserve">2.88691759109497</t>
@@ -2153,16 +2153,16 @@
     <t xml:space="preserve">2.74522829055786</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65667271614075</t>
+    <t xml:space="preserve">2.65667247772217</t>
   </si>
   <si>
     <t xml:space="preserve">2.56811690330505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78950643539429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75408387184143</t>
+    <t xml:space="preserve">2.78950619697571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75408363342285</t>
   </si>
   <si>
     <t xml:space="preserve">2.72751688957214</t>
@@ -2171,7 +2171,7 @@
     <t xml:space="preserve">2.6832389831543</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82492828369141</t>
+    <t xml:space="preserve">2.82492852210999</t>
   </si>
   <si>
     <t xml:space="preserve">2.80721735954285</t>
@@ -2180,7 +2180,7 @@
     <t xml:space="preserve">2.79836177825928</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83378434181213</t>
+    <t xml:space="preserve">2.83378410339355</t>
   </si>
   <si>
     <t xml:space="preserve">2.97547316551208</t>
@@ -2189,7 +2189,7 @@
     <t xml:space="preserve">2.99318432807922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06402921676636</t>
+    <t xml:space="preserve">3.06402897834778</t>
   </si>
   <si>
     <t xml:space="preserve">3.07288455963135</t>
@@ -2198,10 +2198,10 @@
     <t xml:space="preserve">3.01975131034851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09945130348206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03746223449707</t>
+    <t xml:space="preserve">3.09945106506348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03746247291565</t>
   </si>
   <si>
     <t xml:space="preserve">2.94005084037781</t>
@@ -2222,13 +2222,13 @@
     <t xml:space="preserve">2.90462851524353</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203990936279</t>
+    <t xml:space="preserve">3.00204014778137</t>
   </si>
   <si>
     <t xml:space="preserve">2.93119549751282</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78065037727356</t>
+    <t xml:space="preserve">2.78065061569214</t>
   </si>
   <si>
     <t xml:space="preserve">2.70980596542358</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">2.77179503440857</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81607270240784</t>
+    <t xml:space="preserve">2.81607294082642</t>
   </si>
   <si>
     <t xml:space="preserve">2.8780620098114</t>
@@ -2264,10 +2264,10 @@
     <t xml:space="preserve">3.16144037246704</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37397384643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40054082870483</t>
+    <t xml:space="preserve">3.37397408485413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40054059028625</t>
   </si>
   <si>
     <t xml:space="preserve">3.47138524055481</t>
@@ -2276,13 +2276,13 @@
     <t xml:space="preserve">3.50680780410767</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60421895980835</t>
+    <t xml:space="preserve">3.60421919822693</t>
   </si>
   <si>
     <t xml:space="preserve">3.63078570365906</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62193059921265</t>
+    <t xml:space="preserve">3.62193036079407</t>
   </si>
   <si>
     <t xml:space="preserve">3.63964152336121</t>
@@ -70123,7 +70123,7 @@
     </row>
     <row r="2567">
       <c r="A2567" s="1" t="n">
-        <v>46059.6912384259</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2567" t="n">
         <v>21156</v>
@@ -70144,6 +70144,32 @@
         <v>1010</v>
       </c>
       <c r="H2567" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2568">
+      <c r="A2568" s="1" t="n">
+        <v>46062.6910185185</v>
+      </c>
+      <c r="B2568" t="n">
+        <v>45862</v>
+      </c>
+      <c r="C2568" t="n">
+        <v>10.3999996185303</v>
+      </c>
+      <c r="D2568" t="n">
+        <v>10.1000003814697</v>
+      </c>
+      <c r="E2568" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F2568" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="G2568" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H2568" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/CALT.MI.xlsx
+++ b/data/CALT.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">1.73652243614197</t>
+    <t xml:space="preserve">1.73652255535126</t>
   </si>
   <si>
     <t xml:space="preserve">CALT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">1.74400758743286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71406781673431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66167235374451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67215132713318</t>
+    <t xml:space="preserve">1.74400734901428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71406769752502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66167259216309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67215144634247</t>
   </si>
   <si>
     <t xml:space="preserve">1.64969646930695</t>
@@ -62,34 +62,34 @@
     <t xml:space="preserve">1.63921761512756</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57334923744202</t>
+    <t xml:space="preserve">1.5733494758606</t>
   </si>
   <si>
     <t xml:space="preserve">1.49625384807587</t>
   </si>
   <si>
-    <t xml:space="preserve">1.48053526878357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.48203217983246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43637371063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44460713863373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42215216159821</t>
+    <t xml:space="preserve">1.48053538799286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48203229904175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43637359142303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44460725784302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4221522808075</t>
   </si>
   <si>
     <t xml:space="preserve">1.41990661621094</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4146671295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41915833950043</t>
+    <t xml:space="preserve">1.41466701030731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41915810108185</t>
   </si>
   <si>
     <t xml:space="preserve">1.407182097435</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">1.38472712039948</t>
   </si>
   <si>
-    <t xml:space="preserve">1.3982001543045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35703265666962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.3360743522644</t>
+    <t xml:space="preserve">1.39820003509521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35703253746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.33607447147369</t>
   </si>
   <si>
     <t xml:space="preserve">1.34730207920074</t>
@@ -116,88 +116,88 @@
     <t xml:space="preserve">1.3428111076355</t>
   </si>
   <si>
-    <t xml:space="preserve">1.38397872447968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35478687286377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38098454475403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.36975717544556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.37873911857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.43113398551941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41017627716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44535577297211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.462571144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.51197230815887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52544546127319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52245128154755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54490649700165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54191243648529</t>
+    <t xml:space="preserve">1.38397860527039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35478699207306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.38098478317261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.36975693702698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.37873923778534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.43113422393799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41017603874207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4453558921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46257126331329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51197218894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5254453420639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52245140075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54490625858307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54191219806671</t>
   </si>
   <si>
     <t xml:space="preserve">1.54939746856689</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56287038326263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60029530525208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60927736759186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63173246383667</t>
+    <t xml:space="preserve">1.56287026405334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60029542446136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60927760601044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63173270225525</t>
   </si>
   <si>
     <t xml:space="preserve">1.62424755096436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63023543357849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.61676239967346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65418756008148</t>
+    <t xml:space="preserve">1.63023567199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.61676251888275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65418744087219</t>
   </si>
   <si>
     <t xml:space="preserve">1.64370858669281</t>
   </si>
   <si>
-    <t xml:space="preserve">1.58682239055634</t>
+    <t xml:space="preserve">1.58682227134705</t>
   </si>
   <si>
     <t xml:space="preserve">1.58831942081451</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63472664356232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66017532348633</t>
+    <t xml:space="preserve">1.63472652435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66017520427704</t>
   </si>
   <si>
     <t xml:space="preserve">1.66915762424469</t>
@@ -206,85 +206,85 @@
     <t xml:space="preserve">1.68712151050568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69161260128021</t>
+    <t xml:space="preserve">1.6916127204895</t>
   </si>
   <si>
     <t xml:space="preserve">1.69310963153839</t>
   </si>
   <si>
-    <t xml:space="preserve">1.72155249118805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73502612113953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70358860492706</t>
+    <t xml:space="preserve">1.72155261039734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73502576351166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70358872413635</t>
   </si>
   <si>
     <t xml:space="preserve">1.70658254623413</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69909751415253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67664241790771</t>
+    <t xml:space="preserve">1.69909775257111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67664265632629</t>
   </si>
   <si>
     <t xml:space="preserve">1.68412744998932</t>
   </si>
   <si>
-    <t xml:space="preserve">1.66766059398651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68263077735901</t>
+    <t xml:space="preserve">1.6676607131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68263041973114</t>
   </si>
   <si>
     <t xml:space="preserve">1.64221155643463</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64670252799988</t>
+    <t xml:space="preserve">1.64670264720917</t>
   </si>
   <si>
     <t xml:space="preserve">1.67514562606812</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69964480400085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68433284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.69198894500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.72108209133148</t>
+    <t xml:space="preserve">1.69964504241943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6843329668045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.69198882579803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.72108173370361</t>
   </si>
   <si>
     <t xml:space="preserve">1.70576989650726</t>
   </si>
   <si>
-    <t xml:space="preserve">1.69505131244659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.71495687961578</t>
+    <t xml:space="preserve">1.69505143165588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71495711803436</t>
   </si>
   <si>
     <t xml:space="preserve">1.72261297702789</t>
   </si>
   <si>
-    <t xml:space="preserve">1.65370845794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.67208325862885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66902077198029</t>
+    <t xml:space="preserve">1.65370857715607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.67208313941956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66902089118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.65217745304108</t>
   </si>
   <si>
-    <t xml:space="preserve">1.60624086856842</t>
+    <t xml:space="preserve">1.606241106987</t>
   </si>
   <si>
     <t xml:space="preserve">1.56183588504791</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">1.5541797876358</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52202439308167</t>
+    <t xml:space="preserve">1.52202451229095</t>
   </si>
   <si>
     <t xml:space="preserve">1.53121173381805</t>
   </si>
   <si>
-    <t xml:space="preserve">1.59092903137207</t>
+    <t xml:space="preserve">1.59092891216278</t>
   </si>
   <si>
     <t xml:space="preserve">1.52891480922699</t>
@@ -308,43 +308,43 @@
     <t xml:space="preserve">1.55111753940582</t>
   </si>
   <si>
-    <t xml:space="preserve">1.53886759281158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49293160438538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.47608816623688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52279019355774</t>
+    <t xml:space="preserve">1.53886783123016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49293148517609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.47608804702759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52278995513916</t>
   </si>
   <si>
     <t xml:space="preserve">1.46996319293976</t>
   </si>
   <si>
-    <t xml:space="preserve">1.47761917114258</t>
+    <t xml:space="preserve">1.47761929035187</t>
   </si>
   <si>
     <t xml:space="preserve">1.51589953899384</t>
   </si>
   <si>
-    <t xml:space="preserve">1.5005875825882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.6077721118927</t>
+    <t xml:space="preserve">1.50058746337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60777223110199</t>
   </si>
   <si>
     <t xml:space="preserve">1.59705376625061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56949186325073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62308430671692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66748952865601</t>
+    <t xml:space="preserve">1.56949198246002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62308418750763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6674896478653</t>
   </si>
   <si>
     <t xml:space="preserve">1.66136467456818</t>
@@ -353,109 +353,109 @@
     <t xml:space="preserve">1.6766768693924</t>
   </si>
   <si>
-    <t xml:space="preserve">1.61542809009552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57714807987213</t>
+    <t xml:space="preserve">1.61542820930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57714784145355</t>
   </si>
   <si>
     <t xml:space="preserve">1.58480417728424</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63839638233185</t>
+    <t xml:space="preserve">1.63839662075043</t>
   </si>
   <si>
     <t xml:space="preserve">1.63380300998688</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57561695575714</t>
+    <t xml:space="preserve">1.57561683654785</t>
   </si>
   <si>
     <t xml:space="preserve">1.54652369022369</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56796097755432</t>
+    <t xml:space="preserve">1.56796073913574</t>
   </si>
   <si>
     <t xml:space="preserve">1.54499244689941</t>
   </si>
   <si>
-    <t xml:space="preserve">1.52355575561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54193019866943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58174157142639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55877351760864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5802104473114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55264854431152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53044617176056</t>
+    <t xml:space="preserve">1.52355551719666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54193007946014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58174169063568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.55877363681793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58021032810211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5526487827301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53044605255127</t>
   </si>
   <si>
     <t xml:space="preserve">1.51972758769989</t>
   </si>
   <si>
-    <t xml:space="preserve">1.50594675540924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50671231746674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.53427410125732</t>
+    <t xml:space="preserve">1.50594663619995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50671255588531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.53427398204803</t>
   </si>
   <si>
     <t xml:space="preserve">1.56642961502075</t>
   </si>
   <si>
-    <t xml:space="preserve">1.57408571243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.58327281475067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.59246003627777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5021185874939</t>
+    <t xml:space="preserve">1.57408547401428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58327317237854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.59245991706848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50211870670319</t>
   </si>
   <si>
     <t xml:space="preserve">1.50824344158173</t>
   </si>
   <si>
-    <t xml:space="preserve">1.4753223657608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.49675941467285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50747799873352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.52968049049377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.60011613368988</t>
+    <t xml:space="preserve">1.47532248497009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49675953388214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50747776031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.52968037128448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.60011625289917</t>
   </si>
   <si>
     <t xml:space="preserve">1.58786630630493</t>
   </si>
   <si>
-    <t xml:space="preserve">1.56489837169647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.5633670091629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.57255434989929</t>
+    <t xml:space="preserve">1.56489825248718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.56336724758148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.57255423069</t>
   </si>
   <si>
     <t xml:space="preserve">1.5985848903656</t>
@@ -467,109 +467,109 @@
     <t xml:space="preserve">1.60470974445343</t>
   </si>
   <si>
-    <t xml:space="preserve">1.64758372306824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64605247974396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68280148506165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63074052333832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.63686501979828</t>
+    <t xml:space="preserve">1.64758360385895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64605271816254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68280172348022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63074064254761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.63686525821686</t>
   </si>
   <si>
     <t xml:space="preserve">1.64452135562897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.63227152824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66289579868317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.66595852375031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73333144187927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73026907444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74558115005493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75017488002777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70730113983154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.70423853397369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73792517185211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75936233997345</t>
+    <t xml:space="preserve">1.6322717666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66289603710175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66595828533173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73333156108856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73026931285858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74558126926422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75017499923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70730102062225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.70423889160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73792541027069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75936198234558</t>
   </si>
   <si>
     <t xml:space="preserve">1.76089334487915</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78386151790619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76854956150055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75323748588562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73486292362213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73639416694641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79151749610901</t>
+    <t xml:space="preserve">1.78386127948761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76854944229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75323736667633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73486256599426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73639380931854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7915176153183</t>
   </si>
   <si>
     <t xml:space="preserve">1.80223619937897</t>
   </si>
   <si>
-    <t xml:space="preserve">1.82061064243317</t>
+    <t xml:space="preserve">1.82061040401459</t>
   </si>
   <si>
     <t xml:space="preserve">1.81754815578461</t>
   </si>
   <si>
-    <t xml:space="preserve">1.80682957172394</t>
+    <t xml:space="preserve">1.80682969093323</t>
   </si>
   <si>
     <t xml:space="preserve">1.82520437240601</t>
   </si>
   <si>
-    <t xml:space="preserve">1.81448578834534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85889112949371</t>
+    <t xml:space="preserve">1.81448590755463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85889077186584</t>
   </si>
   <si>
     <t xml:space="preserve">1.87726545333862</t>
   </si>
   <si>
-    <t xml:space="preserve">1.85429728031158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85582840442657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8512350320816</t>
+    <t xml:space="preserve">1.85429716110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85582852363586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85123467445374</t>
   </si>
   <si>
     <t xml:space="preserve">1.86654698848724</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">1.84970378875732</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86348438262939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8527660369873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83745384216309</t>
+    <t xml:space="preserve">1.86348450183868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85276615619659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83745408058167</t>
   </si>
   <si>
     <t xml:space="preserve">1.84511017799377</t>
@@ -593,37 +593,37 @@
     <t xml:space="preserve">1.82367324829102</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84051620960236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84817218780518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86807835102081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94923233985901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90789008140564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92167067527771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92932665348053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92473316192627</t>
+    <t xml:space="preserve">1.84051668643951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84817242622375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86807823181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9492324590683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90788996219635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.921670794487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92932653427124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92473292350769</t>
   </si>
   <si>
     <t xml:space="preserve">1.96607577800751</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98904407024384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99823093414307</t>
+    <t xml:space="preserve">1.98904371261597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99823081493378</t>
   </si>
   <si>
     <t xml:space="preserve">2.00894975662231</t>
@@ -635,43 +635,43 @@
     <t xml:space="preserve">2.01201224327087</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99057483673096</t>
+    <t xml:space="preserve">1.99057495594025</t>
   </si>
   <si>
     <t xml:space="preserve">2.0028247833252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.00588703155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0920774936676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09051036834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11401700973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08424234390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11558437347412</t>
+    <t xml:space="preserve">2.00588726997375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09207773208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09051060676575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11401724815369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08424210548401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11558413505554</t>
   </si>
   <si>
     <t xml:space="preserve">2.17043256759644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14692640304565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15006041526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12655353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16259741783142</t>
+    <t xml:space="preserve">2.1469259262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15006017684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12655401229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16259717941284</t>
   </si>
   <si>
     <t xml:space="preserve">2.15162754058838</t>
@@ -689,157 +689,157 @@
     <t xml:space="preserve">2.05290007591248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03722906112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04819869995117</t>
+    <t xml:space="preserve">2.03722929954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04819917678833</t>
   </si>
   <si>
     <t xml:space="preserve">2.0450644493103</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06543731689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06073570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10774874687195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11715149879456</t>
+    <t xml:space="preserve">2.06543707847595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06073594093323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10774898529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11715126037598</t>
   </si>
   <si>
     <t xml:space="preserve">2.12341976165771</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13125514984131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18296957015991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1939389705658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20647597312927</t>
+    <t xml:space="preserve">2.13125538825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18296909332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19393944740295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20647621154785</t>
   </si>
   <si>
     <t xml:space="preserve">2.2033417224884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1923725605011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20804333686829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16416454315186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15946316719055</t>
+    <t xml:space="preserve">2.19237208366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20804309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16416430473328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15946292877197</t>
   </si>
   <si>
     <t xml:space="preserve">2.13595652580261</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09677934646606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06386971473694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.02625942230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96827697753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99805188179016</t>
+    <t xml:space="preserve">2.09677886962891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06386995315552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0262598991394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96827721595764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99805176258087</t>
   </si>
   <si>
     <t xml:space="preserve">2.07640671730042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05446767807007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10461473464966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06700444221497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03566241264343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04976630210876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07954072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06857109069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07797408103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24095225334167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22371435165405</t>
+    <t xml:space="preserve">2.05446743965149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10461449623108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06700420379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03566193580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04976582527161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07954144477844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0685715675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07797360420227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2409520149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22371411323547</t>
   </si>
   <si>
     <t xml:space="preserve">2.21117734909058</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2331166267395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23781800270081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31930708885193</t>
+    <t xml:space="preserve">2.23311686515808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23781776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31930732727051</t>
   </si>
   <si>
     <t xml:space="preserve">2.31460571289062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32714295387268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32557535171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38982677459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38669228553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4446747303009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47601723670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48541975021362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49012088775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52146315574646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50735878944397</t>
+    <t xml:space="preserve">2.3271427154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32557511329651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38982653617859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3866925239563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44467496871948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47601699829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48541951179504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49012064933777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52146291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50735902786255</t>
   </si>
   <si>
     <t xml:space="preserve">2.53870105743408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53086543083191</t>
+    <t xml:space="preserve">2.53086590766907</t>
   </si>
   <si>
     <t xml:space="preserve">2.49168825149536</t>
@@ -851,22 +851,22 @@
     <t xml:space="preserve">2.49952387809753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52302980422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53243279457092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51206040382385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.50892615318298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51362729072571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49795627593994</t>
+    <t xml:space="preserve">2.52303028106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53243231773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51206064224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5089259147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51362752914429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49795651435852</t>
   </si>
   <si>
     <t xml:space="preserve">2.49638938903809</t>
@@ -878,10 +878,10 @@
     <t xml:space="preserve">2.54653644561768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5512375831604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53713440895081</t>
+    <t xml:space="preserve">2.55123829841614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53713417053223</t>
   </si>
   <si>
     <t xml:space="preserve">2.55437207221985</t>
@@ -893,16 +893,16 @@
     <t xml:space="preserve">2.70794773101807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71108198165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205138206482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69541096687317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70324635505676</t>
+    <t xml:space="preserve">2.71108222007751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220516204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69541120529175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70324659347534</t>
   </si>
   <si>
     <t xml:space="preserve">2.67347168922424</t>
@@ -911,25 +911,25 @@
     <t xml:space="preserve">2.66406917572021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61705589294434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59981846809387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5872814655304</t>
+    <t xml:space="preserve">2.61705613136292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59981799125671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58728098869324</t>
   </si>
   <si>
     <t xml:space="preserve">2.59825086593628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58571362495422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57004284858704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56220769882202</t>
+    <t xml:space="preserve">2.58571410179138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57004261016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56220746040344</t>
   </si>
   <si>
     <t xml:space="preserve">2.54183530807495</t>
@@ -938,43 +938,43 @@
     <t xml:space="preserve">2.51989579200745</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52929854393005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52459692955017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46034622192383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47131586074829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48228526115417</t>
+    <t xml:space="preserve">2.52929830551147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52459716796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46034598350525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47131609916687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48228549957275</t>
   </si>
   <si>
     <t xml:space="preserve">2.43370532989502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39609527587891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32087421417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30206894874573</t>
+    <t xml:space="preserve">2.39609503746033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32087397575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30206918716431</t>
   </si>
   <si>
     <t xml:space="preserve">2.25975751876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27699565887451</t>
+    <t xml:space="preserve">2.27699542045593</t>
   </si>
   <si>
     <t xml:space="preserve">2.28796529769897</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34908223152161</t>
+    <t xml:space="preserve">2.34908199310303</t>
   </si>
   <si>
     <t xml:space="preserve">2.36475300788879</t>
@@ -983,82 +983,82 @@
     <t xml:space="preserve">2.35064911842346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35848474502563</t>
+    <t xml:space="preserve">2.35848450660706</t>
   </si>
   <si>
     <t xml:space="preserve">2.41333317756653</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43683981895447</t>
+    <t xml:space="preserve">2.43683934211731</t>
   </si>
   <si>
     <t xml:space="preserve">2.62489128112793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6327269077301</t>
+    <t xml:space="preserve">2.63272714614868</t>
   </si>
   <si>
     <t xml:space="preserve">2.468181848526</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36632013320923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38199090957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39766192436218</t>
+    <t xml:space="preserve">2.36632037162781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.381991147995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39766216278076</t>
   </si>
   <si>
     <t xml:space="preserve">2.45251083374023</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40549778938293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42116856575012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42900395393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24878787994385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30363631248474</t>
+    <t xml:space="preserve">2.40549755096436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42116832733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42900419235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24878764152527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30363655090332</t>
   </si>
   <si>
     <t xml:space="preserve">2.25662302970886</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27229404449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28012990951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26445865631104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22528123855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11558413505554</t>
+    <t xml:space="preserve">2.27229428291321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28012943267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26445889472961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22528100013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1155846118927</t>
   </si>
   <si>
     <t xml:space="preserve">2.1235978603363</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09955668449402</t>
+    <t xml:space="preserve">2.0995569229126</t>
   </si>
   <si>
     <t xml:space="preserve">2.08352994918823</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09154343605042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01942133903503</t>
+    <t xml:space="preserve">2.09154319763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01942110061646</t>
   </si>
   <si>
     <t xml:space="preserve">2.00339412689209</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">2.06750273704529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18770670890808</t>
+    <t xml:space="preserve">2.1877064704895</t>
   </si>
   <si>
     <t xml:space="preserve">2.29188275337219</t>
@@ -1079,25 +1079,25 @@
     <t xml:space="preserve">2.1636655330658</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14763855934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20373344421387</t>
+    <t xml:space="preserve">2.14763879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20373368263245</t>
   </si>
   <si>
     <t xml:space="preserve">2.13161134719849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17167949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19571995735168</t>
+    <t xml:space="preserve">2.17167925834656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19571971893311</t>
   </si>
   <si>
     <t xml:space="preserve">2.17969298362732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10757064819336</t>
+    <t xml:space="preserve">2.10757088661194</t>
   </si>
   <si>
     <t xml:space="preserve">2.05948901176453</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">2.0354483127594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05147528648376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27585577964783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26784229278564</t>
+    <t xml:space="preserve">2.05147576332092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27585554122925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26784205436707</t>
   </si>
   <si>
     <t xml:space="preserve">2.21976065635681</t>
@@ -1124,76 +1124,76 @@
     <t xml:space="preserve">2.21174716949463</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24380111694336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23578810691833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22777414321899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15565204620361</t>
+    <t xml:space="preserve">2.24380159378052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23578786849976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22777438163757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15565228462219</t>
   </si>
   <si>
     <t xml:space="preserve">2.30790996551514</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02743482589722</t>
+    <t xml:space="preserve">2.0274350643158</t>
   </si>
   <si>
     <t xml:space="preserve">2.04346203804016</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99538087844849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91524493694305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.92325806617737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96332657337189</t>
+    <t xml:space="preserve">1.99538052082062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91524481773376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.92325830459595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9633264541626</t>
   </si>
   <si>
     <t xml:space="preserve">1.97133982181549</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98736691474915</t>
+    <t xml:space="preserve">1.98736703395844</t>
   </si>
   <si>
     <t xml:space="preserve">2.01140761375427</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8110682964325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81908190250397</t>
+    <t xml:space="preserve">1.81106841564178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81908214092255</t>
   </si>
   <si>
     <t xml:space="preserve">1.84312260150909</t>
   </si>
   <si>
-    <t xml:space="preserve">1.79504108428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77901375293732</t>
+    <t xml:space="preserve">1.79504120349884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77901411056519</t>
   </si>
   <si>
     <t xml:space="preserve">1.82709538936615</t>
   </si>
   <si>
-    <t xml:space="preserve">1.771000623703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.73093235492706</t>
+    <t xml:space="preserve">1.77100050449371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.73093259334564</t>
   </si>
   <si>
     <t xml:space="preserve">1.69887816905975</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7149053812027</t>
+    <t xml:space="preserve">1.71490550041199</t>
   </si>
   <si>
     <t xml:space="preserve">1.74695980548859</t>
@@ -1202,34 +1202,34 @@
     <t xml:space="preserve">1.72291910648346</t>
   </si>
   <si>
-    <t xml:space="preserve">1.7389463186264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.76298677921295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.75497329235077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80305469036102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.85914957523346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86716330051422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83510911464691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8751767873764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90723121166229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97935354709625</t>
+    <t xml:space="preserve">1.73894619941711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.76298689842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.75497341156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80305457115173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.85914969444275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86716294288635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83510899543762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87517702579498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90723133087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97935318946838</t>
   </si>
   <si>
     <t xml:space="preserve">1.93928563594818</t>
@@ -1241,46 +1241,43 @@
     <t xml:space="preserve">2.01258111000061</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97134006023407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98783659934998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99608492851257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96309173107147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93834662437439</t>
+    <t xml:space="preserve">1.98783648014069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99608469009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96309161186218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93834686279297</t>
   </si>
   <si>
     <t xml:space="preserve">1.9795880317688</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0373260974884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06207060813904</t>
+    <t xml:space="preserve">2.03732585906982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06207084655762</t>
   </si>
   <si>
     <t xml:space="preserve">2.05382251739502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09506368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.16929864883423</t>
+    <t xml:space="preserve">2.09506392478943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.16929888725281</t>
   </si>
   <si>
     <t xml:space="preserve">2.16105008125305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11156034469604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10331249237061</t>
+    <t xml:space="preserve">2.1115608215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10331225395203</t>
   </si>
   <si>
     <t xml:space="preserve">2.12805724143982</t>
@@ -1295,7 +1292,7 @@
     <t xml:space="preserve">2.14455366134644</t>
   </si>
   <si>
-    <t xml:space="preserve">2.07856750488281</t>
+    <t xml:space="preserve">2.07856726646423</t>
   </si>
   <si>
     <t xml:space="preserve">2.22703647613525</t>
@@ -1304,52 +1301,52 @@
     <t xml:space="preserve">2.21878838539124</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25178170204163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24353313446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21054005622864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26002979278564</t>
+    <t xml:space="preserve">2.25178146362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24353337287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21054029464722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26002955436707</t>
   </si>
   <si>
     <t xml:space="preserve">2.26827812194824</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33426427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30951929092407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30127143859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31776762008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38375401496887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3755054473877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32601618766785</t>
+    <t xml:space="preserve">2.33426403999329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30951952934265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30127120018005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31776785850525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38375425338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37550568580627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32601571083069</t>
   </si>
   <si>
     <t xml:space="preserve">2.27652621269226</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28477478027344</t>
+    <t xml:space="preserve">2.28477454185486</t>
   </si>
   <si>
     <t xml:space="preserve">2.29302287101746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23528504371643</t>
+    <t xml:space="preserve">2.23528480529785</t>
   </si>
   <si>
     <t xml:space="preserve">2.39200234413147</t>
@@ -1367,58 +1364,58 @@
     <t xml:space="preserve">2.40849876403809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4249951839447</t>
+    <t xml:space="preserve">2.42499566078186</t>
   </si>
   <si>
     <t xml:space="preserve">2.45798850059509</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49923014640808</t>
+    <t xml:space="preserve">2.49922966957092</t>
   </si>
   <si>
     <t xml:space="preserve">2.47448515892029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5157265663147</t>
+    <t xml:space="preserve">2.51572632789612</t>
   </si>
   <si>
     <t xml:space="preserve">2.58996105194092</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54871964454651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4909815788269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5074782371521</t>
+    <t xml:space="preserve">2.54871940612793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49098205566406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.50747799873352</t>
   </si>
   <si>
     <t xml:space="preserve">2.44149208068848</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35076069831848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40025067329407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.19404363632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.185795545578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04557418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87236034870148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.88060867786407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68264985084534</t>
+    <t xml:space="preserve">2.35076093673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40025043487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.19404339790344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18579530715942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.045574426651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87236058712006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.88060855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68264973163605</t>
   </si>
   <si>
     <t xml:space="preserve">1.69089818000793</t>
@@ -1427,13 +1424,13 @@
     <t xml:space="preserve">1.56717395782471</t>
   </si>
   <si>
-    <t xml:space="preserve">1.71564280986786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64553248882294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.64140856266022</t>
+    <t xml:space="preserve">1.71564292907715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64553260803223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.64140844345093</t>
   </si>
   <si>
     <t xml:space="preserve">1.62491190433502</t>
@@ -1442,61 +1439,61 @@
     <t xml:space="preserve">1.77338111400604</t>
   </si>
   <si>
-    <t xml:space="preserve">1.78162920475006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.74863612651825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80637419223785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86411213874817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.00433301925659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81462228298187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.79812586307526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82287085056305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84761536121368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83111882209778</t>
+    <t xml:space="preserve">1.78162932395935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.74863600730896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80637431144714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86411225795746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.00433325767517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81462240219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.79812598228455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82287073135376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84761559963226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83111906051636</t>
   </si>
   <si>
     <t xml:space="preserve">1.78987765312195</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88885700702667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9136016368866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89710509777069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90535366535187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.95484340190887</t>
+    <t xml:space="preserve">1.88885688781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91360175609589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89710521697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.905353307724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.95484328269958</t>
   </si>
   <si>
     <t xml:space="preserve">2.02907776832581</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08681559562683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17754697799683</t>
+    <t xml:space="preserve">2.08681583404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17754721641541</t>
   </si>
   <si>
     <t xml:space="preserve">2.07031917572021</t>
@@ -1508,31 +1505,31 @@
     <t xml:space="preserve">2.06938791275024</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03546380996704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98457670211792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97609579563141</t>
+    <t xml:space="preserve">2.03546357154846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98457682132721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97609567642212</t>
   </si>
   <si>
     <t xml:space="preserve">1.95065248012543</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99305784702301</t>
+    <t xml:space="preserve">1.99305808544159</t>
   </si>
   <si>
     <t xml:space="preserve">2.06090688705444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.02698254585266</t>
+    <t xml:space="preserve">2.02698230743408</t>
   </si>
   <si>
     <t xml:space="preserve">2.05242586135864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04394459724426</t>
+    <t xml:space="preserve">2.04394483566284</t>
   </si>
   <si>
     <t xml:space="preserve">2.01002025604248</t>
@@ -1544,10 +1541,10 @@
     <t xml:space="preserve">1.89976608753204</t>
   </si>
   <si>
-    <t xml:space="preserve">1.88280391693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.89128482341766</t>
+    <t xml:space="preserve">1.88280379772186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.89128494262695</t>
   </si>
   <si>
     <t xml:space="preserve">2.01850152015686</t>
@@ -1559,10 +1556,10 @@
     <t xml:space="preserve">2.08635020256042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.12875533103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12027478218079</t>
+    <t xml:space="preserve">2.12875556945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.12027430534363</t>
   </si>
   <si>
     <t xml:space="preserve">2.16267991065979</t>
@@ -1574,43 +1571,43 @@
     <t xml:space="preserve">2.23052906990051</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30685877799988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33230209350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34926414489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35774540901184</t>
+    <t xml:space="preserve">2.3068585395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33230185508728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34926390647888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35774517059326</t>
   </si>
   <si>
     <t xml:space="preserve">2.42559409141541</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44255661964417</t>
+    <t xml:space="preserve">2.44255638122559</t>
   </si>
   <si>
     <t xml:space="preserve">2.47648072242737</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46799945831299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.49344301223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51040530204773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43407487869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41711282730103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51888608932495</t>
+    <t xml:space="preserve">2.46799969673157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.49344325065613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51040506362915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43407511711121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41711258888245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51888632774353</t>
   </si>
   <si>
     <t xml:space="preserve">2.58673501014709</t>
@@ -1622,28 +1619,28 @@
     <t xml:space="preserve">2.54432940483093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57825398445129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56129169464111</t>
+    <t xml:space="preserve">2.57825374603271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56129193305969</t>
   </si>
   <si>
     <t xml:space="preserve">2.55281043052673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53584814071655</t>
+    <t xml:space="preserve">2.53584837913513</t>
   </si>
   <si>
     <t xml:space="preserve">2.52736711502075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64610242843628</t>
+    <t xml:space="preserve">2.64610266685486</t>
   </si>
   <si>
     <t xml:space="preserve">2.63762140274048</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66306495666504</t>
+    <t xml:space="preserve">2.66306471824646</t>
   </si>
   <si>
     <t xml:space="preserve">2.70547032356262</t>
@@ -1661,31 +1658,31 @@
     <t xml:space="preserve">2.7309136390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77331924438477</t>
+    <t xml:space="preserve">2.77331900596619</t>
   </si>
   <si>
     <t xml:space="preserve">2.78180003166199</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84116816520691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86661100387573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88357329368591</t>
+    <t xml:space="preserve">2.84116768836975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86661124229431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88357353210449</t>
   </si>
   <si>
     <t xml:space="preserve">2.90901684761047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85812997817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80724358558655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75635719299316</t>
+    <t xml:space="preserve">2.85813021659851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80724334716797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75635671615601</t>
   </si>
   <si>
     <t xml:space="preserve">2.73939490318298</t>
@@ -1697,10 +1694,10 @@
     <t xml:space="preserve">2.79876232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79028105735779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84964871406555</t>
+    <t xml:space="preserve">2.79028129577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84964895248413</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268666267395</t>
@@ -1721,28 +1718,28 @@
     <t xml:space="preserve">2.95990324020386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07863879203796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08711981773376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12104392051697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18041157722473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14648747444153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23977971076965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22281718254089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23129844665527</t>
+    <t xml:space="preserve">3.07863855361938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.08712005615234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12104415893555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18041205406189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14648723602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23977947235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22281742095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23129820823669</t>
   </si>
   <si>
     <t xml:space="preserve">3.24826049804688</t>
@@ -1751,13 +1748,13 @@
     <t xml:space="preserve">3.21433615684509</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28218507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40092062950134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42636370658875</t>
+    <t xml:space="preserve">3.28218483924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40092039108276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42636322975159</t>
   </si>
   <si>
     <t xml:space="preserve">3.3669958114624</t>
@@ -1766,10 +1763,10 @@
     <t xml:space="preserve">3.31610941886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29066610336304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27370357513428</t>
+    <t xml:space="preserve">3.29066634178162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27370381355286</t>
   </si>
   <si>
     <t xml:space="preserve">3.3079400062561</t>
@@ -1778,10 +1775,10 @@
     <t xml:space="preserve">3.31657671928406</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27339220046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35112452507019</t>
+    <t xml:space="preserve">3.27339196205139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35112500190735</t>
   </si>
   <si>
     <t xml:space="preserve">3.34248757362366</t>
@@ -1811,22 +1808,22 @@
     <t xml:space="preserve">3.5929582118988</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65341687202454</t>
+    <t xml:space="preserve">3.65341663360596</t>
   </si>
   <si>
     <t xml:space="preserve">3.61023187637329</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71387529373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67069053649902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7829704284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80888104438782</t>
+    <t xml:space="preserve">3.71387553215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6706907749176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78297090530396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80888152122498</t>
   </si>
   <si>
     <t xml:space="preserve">3.6966016292572</t>
@@ -1835,37 +1832,37 @@
     <t xml:space="preserve">3.62750577926636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.644779920578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73978590965271</t>
+    <t xml:space="preserve">3.64477944374084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73978567123413</t>
   </si>
   <si>
     <t xml:space="preserve">3.7570595741272</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55841064453125</t>
+    <t xml:space="preserve">3.55841040611267</t>
   </si>
   <si>
     <t xml:space="preserve">3.67932772636414</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57568430900574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58432126045227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70523810386658</t>
+    <t xml:space="preserve">3.57568454742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58432149887085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.705237865448</t>
   </si>
   <si>
     <t xml:space="preserve">3.5238630771637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5497739315033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48931550979614</t>
+    <t xml:space="preserve">3.54977369308472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48931503295898</t>
   </si>
   <si>
     <t xml:space="preserve">3.41158318519592</t>
@@ -1874,88 +1871,91 @@
     <t xml:space="preserve">3.51522612571716</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68796420097351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74842309951782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66205358505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6188690662384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86933994293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82615494728088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86070275306702</t>
+    <t xml:space="preserve">3.68796443939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74842286109924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66205310821533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61886930465698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86933970451355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8261547088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8607029914856</t>
   </si>
   <si>
     <t xml:space="preserve">3.91252446174622</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99889373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9557089805603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9902560710907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84342861175537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77433323860168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76569676399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92979836463928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88661360740662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9038872718811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8779764175415</t>
+    <t xml:space="preserve">3.99889349937439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95570850372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99025630950928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84342885017395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77433347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76569700241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9297981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88661336898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90388751029968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87797617912292</t>
   </si>
   <si>
     <t xml:space="preserve">3.81751847267151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96434617042542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89525032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93843507766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63614320755005</t>
+    <t xml:space="preserve">3.96434569358826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89525079727173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93843483924866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63614296913147</t>
   </si>
   <si>
     <t xml:space="preserve">3.4979522228241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42885661125183</t>
+    <t xml:space="preserve">3.42885684967041</t>
   </si>
   <si>
     <t xml:space="preserve">3.42021989822388</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28202891349792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25611877441406</t>
+    <t xml:space="preserve">3.28202939033508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2561182975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29066586494446</t>
   </si>
   <si>
     <t xml:space="preserve">3.24748134613037</t>
@@ -1964,7 +1964,7 @@
     <t xml:space="preserve">3.29930305480957</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26475524902344</t>
+    <t xml:space="preserve">3.26475548744202</t>
   </si>
   <si>
     <t xml:space="preserve">3.33385062217712</t>
@@ -1976,13 +1976,13 @@
     <t xml:space="preserve">3.37703537940979</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40294623374939</t>
+    <t xml:space="preserve">3.40294599533081</t>
   </si>
   <si>
     <t xml:space="preserve">3.35976147651672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21293377876282</t>
+    <t xml:space="preserve">3.2129340171814</t>
   </si>
   <si>
     <t xml:space="preserve">3.23020768165588</t>
@@ -1994,19 +1994,19 @@
     <t xml:space="preserve">3.11792778968811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19565987586975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14383840560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97973704338074</t>
+    <t xml:space="preserve">3.19566011428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14383864402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97973728179932</t>
   </si>
   <si>
     <t xml:space="preserve">3.06610608100891</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53250002861023</t>
+    <t xml:space="preserve">3.53249979019165</t>
   </si>
   <si>
     <t xml:space="preserve">3.56704759597778</t>
@@ -2018,19 +2018,19 @@
     <t xml:space="preserve">3.38567209243774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54223012924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57765245437622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56879711151123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5245189666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6130747795105</t>
+    <t xml:space="preserve">3.54222989082336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57765221595764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56879687309265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52451872825623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61307454109192</t>
   </si>
   <si>
     <t xml:space="preserve">3.58650803565979</t>
@@ -2045,10 +2045,10 @@
     <t xml:space="preserve">3.35626292228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33855199813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34740734100342</t>
+    <t xml:space="preserve">3.33855175971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34740710258484</t>
   </si>
   <si>
     <t xml:space="preserve">3.26770734786987</t>
@@ -2060,28 +2060,28 @@
     <t xml:space="preserve">3.2322850227356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27656269073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3296959400177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32084059715271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28541827201843</t>
+    <t xml:space="preserve">3.27656292915344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32969617843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32084083557129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28541851043701</t>
   </si>
   <si>
     <t xml:space="preserve">3.42710757255554</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51566314697266</t>
+    <t xml:space="preserve">3.51566338539124</t>
   </si>
   <si>
     <t xml:space="preserve">3.55108571052551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40939617156982</t>
+    <t xml:space="preserve">3.4093964099884</t>
   </si>
   <si>
     <t xml:space="preserve">3.48909664154053</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">3.5599410533905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46252989768982</t>
+    <t xml:space="preserve">3.4625301361084</t>
   </si>
   <si>
     <t xml:space="preserve">3.36511826515198</t>
@@ -2105,16 +2105,16 @@
     <t xml:space="preserve">3.41825175285339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3828296661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44481873512268</t>
+    <t xml:space="preserve">3.38282942771912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44481897354126</t>
   </si>
   <si>
     <t xml:space="preserve">3.45367431640625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48024106025696</t>
+    <t xml:space="preserve">3.48024129867554</t>
   </si>
   <si>
     <t xml:space="preserve">3.39168524742126</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">3.08174014091492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14372897148132</t>
+    <t xml:space="preserve">3.1437292098999</t>
   </si>
   <si>
     <t xml:space="preserve">3.11716246604919</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">3.09059572219849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88691759109497</t>
+    <t xml:space="preserve">2.88691735267639</t>
   </si>
   <si>
     <t xml:space="preserve">2.94890642166138</t>
@@ -2144,16 +2144,16 @@
     <t xml:space="preserve">2.84263968467712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86920619010925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74522829055786</t>
+    <t xml:space="preserve">2.86920642852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74522805213928</t>
   </si>
   <si>
     <t xml:space="preserve">2.65667247772217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56811690330505</t>
+    <t xml:space="preserve">2.56811666488647</t>
   </si>
   <si>
     <t xml:space="preserve">2.78950619697571</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">2.72751688957214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6832389831543</t>
+    <t xml:space="preserve">2.68323922157288</t>
   </si>
   <si>
     <t xml:space="preserve">2.82492852210999</t>
@@ -2183,7 +2183,7 @@
     <t xml:space="preserve">2.97547316551208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99318432807922</t>
+    <t xml:space="preserve">2.9931845664978</t>
   </si>
   <si>
     <t xml:space="preserve">3.06402897834778</t>
@@ -2195,16 +2195,16 @@
     <t xml:space="preserve">3.01975131034851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09945106506348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03746247291565</t>
+    <t xml:space="preserve">3.09945130348206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03746223449707</t>
   </si>
   <si>
     <t xml:space="preserve">2.94005084037781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01089549064636</t>
+    <t xml:space="preserve">3.01089572906494</t>
   </si>
   <si>
     <t xml:space="preserve">3.04631781578064</t>
@@ -2213,7 +2213,7 @@
     <t xml:space="preserve">2.98432874679565</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96661782264709</t>
+    <t xml:space="preserve">2.96661758422852</t>
   </si>
   <si>
     <t xml:space="preserve">2.90462851524353</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">3.00204014778137</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93119549751282</t>
+    <t xml:space="preserve">2.93119525909424</t>
   </si>
   <si>
     <t xml:space="preserve">2.78065061569214</t>
@@ -2237,7 +2237,7 @@
     <t xml:space="preserve">2.81607294082642</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8780620098114</t>
+    <t xml:space="preserve">2.87806177139282</t>
   </si>
   <si>
     <t xml:space="preserve">3.0286066532135</t>
@@ -2246,16 +2246,16 @@
     <t xml:space="preserve">3.05517339706421</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17029571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19686269760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24114036560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25885152816772</t>
+    <t xml:space="preserve">3.17029595375061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19686245918274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24114060401917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2588517665863</t>
   </si>
   <si>
     <t xml:space="preserve">3.16144037246704</t>
@@ -2267,10 +2267,10 @@
     <t xml:space="preserve">3.40054059028625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47138524055481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50680780410767</t>
+    <t xml:space="preserve">3.47138547897339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50680756568909</t>
   </si>
   <si>
     <t xml:space="preserve">3.60421919822693</t>
@@ -2294,13 +2294,13 @@
     <t xml:space="preserve">3.72270464897156</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77785587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69512867927551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70432114601135</t>
+    <t xml:space="preserve">3.77785563468933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69512891769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70432090759277</t>
   </si>
   <si>
     <t xml:space="preserve">3.78704738616943</t>
@@ -2312,7 +2312,7 @@
     <t xml:space="preserve">3.8146231174469</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76866364479065</t>
+    <t xml:space="preserve">3.76866388320923</t>
   </si>
   <si>
     <t xml:space="preserve">3.75028014183044</t>
@@ -2321,19 +2321,19 @@
     <t xml:space="preserve">3.63997769355774</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64916944503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66755342483521</t>
+    <t xml:space="preserve">3.64916968345642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66755318641663</t>
   </si>
   <si>
     <t xml:space="preserve">3.63078594207764</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62159419059753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53886699676514</t>
+    <t xml:space="preserve">3.62159395217896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53886723518372</t>
   </si>
   <si>
     <t xml:space="preserve">3.5572509765625</t>
@@ -2348,10 +2348,10 @@
     <t xml:space="preserve">3.52048349380493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4561402797699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49290776252747</t>
+    <t xml:space="preserve">3.45614051818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49290800094604</t>
   </si>
   <si>
     <t xml:space="preserve">3.56644296646118</t>
@@ -2363,19 +2363,19 @@
     <t xml:space="preserve">3.60321021080017</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51129174232483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85139060020447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84219837188721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90654182434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86058211326599</t>
+    <t xml:space="preserve">3.51129150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85139083862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84219861030579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90654158592224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86058235168457</t>
   </si>
   <si>
     <t xml:space="preserve">3.68593716621399</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">3.74108839035034</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58482670783997</t>
+    <t xml:space="preserve">3.58482646942139</t>
   </si>
   <si>
     <t xml:space="preserve">3.65836143493652</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">3.47452425956726</t>
   </si>
   <si>
-    <t xml:space="preserve">3.46533250808716</t>
+    <t xml:space="preserve">3.46533226966858</t>
   </si>
   <si>
     <t xml:space="preserve">3.50209975242615</t>
@@ -2405,7 +2405,7 @@
     <t xml:space="preserve">3.94330906867981</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9157338142395</t>
+    <t xml:space="preserve">3.91573357582092</t>
   </si>
   <si>
     <t xml:space="preserve">3.95250105857849</t>
@@ -2414,25 +2414,25 @@
     <t xml:space="preserve">3.92492532730103</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98926877975464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83300685882568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96169257164001</t>
+    <t xml:space="preserve">3.98926854133606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83300709724426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96169281005859</t>
   </si>
   <si>
     <t xml:space="preserve">3.87896609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93411755561829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97088503837585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98007678985596</t>
+    <t xml:space="preserve">3.93411731719971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97088479995728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98007655143738</t>
   </si>
   <si>
     <t xml:space="preserve">3.823814868927</t>
@@ -2441,13 +2441,13 @@
     <t xml:space="preserve">3.79623937606812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88815808296204</t>
+    <t xml:space="preserve">3.88815784454346</t>
   </si>
   <si>
     <t xml:space="preserve">3.86977458000183</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89734983444214</t>
+    <t xml:space="preserve">3.89734935760498</t>
   </si>
   <si>
     <t xml:space="preserve">4.13633823394775</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">4.20068168640137</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42128562927246</t>
+    <t xml:space="preserve">4.42128610610962</t>
   </si>
   <si>
     <t xml:space="preserve">4.66946649551392</t>
@@ -2489,13 +2489,13 @@
     <t xml:space="preserve">4.81653594970703</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9636058807373</t>
+    <t xml:space="preserve">4.96360635757446</t>
   </si>
   <si>
     <t xml:space="preserve">4.85330390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76138496398926</t>
+    <t xml:space="preserve">4.7613844871521</t>
   </si>
   <si>
     <t xml:space="preserve">4.5867395401001</t>
@@ -2519,7 +2519,7 @@
     <t xml:space="preserve">4.90845489501953</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89007091522217</t>
+    <t xml:space="preserve">4.89007139205933</t>
   </si>
   <si>
     <t xml:space="preserve">5.16600561141968</t>
@@ -25811,7 +25811,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G862" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="H862" t="s">
         <v>9</v>
@@ -25837,7 +25837,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G863" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H863" t="s">
         <v>9</v>
@@ -25863,7 +25863,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G864" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H864" t="s">
         <v>9</v>
@@ -25915,7 +25915,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G866" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H866" t="s">
         <v>9</v>
@@ -25941,7 +25941,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G867" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H867" t="s">
         <v>9</v>
@@ -25967,7 +25967,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G868" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H868" t="s">
         <v>9</v>
@@ -25993,7 +25993,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G869" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H869" t="s">
         <v>9</v>
@@ -26019,7 +26019,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G870" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H870" t="s">
         <v>9</v>
@@ -26045,7 +26045,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G871" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -26071,7 +26071,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G872" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="H872" t="s">
         <v>9</v>
@@ -26097,7 +26097,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G873" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H873" t="s">
         <v>9</v>
@@ -26123,7 +26123,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G874" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H874" t="s">
         <v>9</v>
@@ -26149,7 +26149,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G875" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H875" t="s">
         <v>9</v>
@@ -26175,7 +26175,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G876" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H876" t="s">
         <v>9</v>
@@ -26201,7 +26201,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G877" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H877" t="s">
         <v>9</v>
@@ -26227,7 +26227,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G878" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H878" t="s">
         <v>9</v>
@@ -26253,7 +26253,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G879" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="H879" t="s">
         <v>9</v>
@@ -26331,7 +26331,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G882" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H882" t="s">
         <v>9</v>
@@ -26357,7 +26357,7 @@
         <v>2.5</v>
       </c>
       <c r="G883" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H883" t="s">
         <v>9</v>
@@ -26383,7 +26383,7 @@
         <v>2.5</v>
       </c>
       <c r="G884" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H884" t="s">
         <v>9</v>
@@ -26409,7 +26409,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G885" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H885" t="s">
         <v>9</v>
@@ -26435,7 +26435,7 @@
         <v>2.5</v>
       </c>
       <c r="G886" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H886" t="s">
         <v>9</v>
@@ -26461,7 +26461,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G887" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H887" t="s">
         <v>9</v>
@@ -26487,7 +26487,7 @@
         <v>2.5</v>
       </c>
       <c r="G888" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H888" t="s">
         <v>9</v>
@@ -26513,7 +26513,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H889" t="s">
         <v>9</v>
@@ -26539,7 +26539,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G890" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H890" t="s">
         <v>9</v>
@@ -26565,7 +26565,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G891" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H891" t="s">
         <v>9</v>
@@ -26591,7 +26591,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G892" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H892" t="s">
         <v>9</v>
@@ -26617,7 +26617,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G893" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -26643,7 +26643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G894" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H894" t="s">
         <v>9</v>
@@ -26669,7 +26669,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G895" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H895" t="s">
         <v>9</v>
@@ -26695,7 +26695,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G896" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H896" t="s">
         <v>9</v>
@@ -26721,7 +26721,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G897" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H897" t="s">
         <v>9</v>
@@ -26747,7 +26747,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G898" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H898" t="s">
         <v>9</v>
@@ -26773,7 +26773,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G899" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H899" t="s">
         <v>9</v>
@@ -26799,7 +26799,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G900" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H900" t="s">
         <v>9</v>
@@ -26825,7 +26825,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G901" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H901" t="s">
         <v>9</v>
@@ -26851,7 +26851,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G902" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H902" t="s">
         <v>9</v>
@@ -26877,7 +26877,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G903" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H903" t="s">
         <v>9</v>
@@ -26903,7 +26903,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G904" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H904" t="s">
         <v>9</v>
@@ -26929,7 +26929,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G905" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H905" t="s">
         <v>9</v>
@@ -26955,7 +26955,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G906" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H906" t="s">
         <v>9</v>
@@ -26981,7 +26981,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G907" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H907" t="s">
         <v>9</v>
@@ -27007,7 +27007,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G908" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H908" t="s">
         <v>9</v>
@@ -27033,7 +27033,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G909" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H909" t="s">
         <v>9</v>
@@ -27059,7 +27059,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G910" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H910" t="s">
         <v>9</v>
@@ -27085,7 +27085,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G911" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H911" t="s">
         <v>9</v>
@@ -27111,7 +27111,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G912" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H912" t="s">
         <v>9</v>
@@ -27137,7 +27137,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G913" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H913" t="s">
         <v>9</v>
@@ -27163,7 +27163,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G914" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H914" t="s">
         <v>9</v>
@@ -27189,7 +27189,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G915" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H915" t="s">
         <v>9</v>
@@ -27215,7 +27215,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G916" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H916" t="s">
         <v>9</v>
@@ -27241,7 +27241,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G917" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H917" t="s">
         <v>9</v>
@@ -27267,7 +27267,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G918" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H918" t="s">
         <v>9</v>
@@ -27293,7 +27293,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G919" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H919" t="s">
         <v>9</v>
@@ -27319,7 +27319,7 @@
         <v>2.75</v>
       </c>
       <c r="G920" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H920" t="s">
         <v>9</v>
@@ -27345,7 +27345,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G921" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H921" t="s">
         <v>9</v>
@@ -27371,7 +27371,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G922" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H922" t="s">
         <v>9</v>
@@ -27397,7 +27397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G923" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H923" t="s">
         <v>9</v>
@@ -27423,7 +27423,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G924" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H924" t="s">
         <v>9</v>
@@ -27449,7 +27449,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G925" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H925" t="s">
         <v>9</v>
@@ -27475,7 +27475,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G926" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H926" t="s">
         <v>9</v>
@@ -27501,7 +27501,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G927" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H927" t="s">
         <v>9</v>
@@ -27527,7 +27527,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G928" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H928" t="s">
         <v>9</v>
@@ -27553,7 +27553,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G929" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H929" t="s">
         <v>9</v>
@@ -27579,7 +27579,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G930" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H930" t="s">
         <v>9</v>
@@ -27605,7 +27605,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G931" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H931" t="s">
         <v>9</v>
@@ -27631,7 +27631,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G932" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H932" t="s">
         <v>9</v>
@@ -27657,7 +27657,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G933" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H933" t="s">
         <v>9</v>
@@ -27683,7 +27683,7 @@
         <v>2.75</v>
       </c>
       <c r="G934" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H934" t="s">
         <v>9</v>
@@ -27709,7 +27709,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G935" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H935" t="s">
         <v>9</v>
@@ -27735,7 +27735,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G936" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H936" t="s">
         <v>9</v>
@@ -27761,7 +27761,7 @@
         <v>2.75</v>
       </c>
       <c r="G937" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H937" t="s">
         <v>9</v>
@@ -27787,7 +27787,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G938" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H938" t="s">
         <v>9</v>
@@ -27813,7 +27813,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G939" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H939" t="s">
         <v>9</v>
@@ -27839,7 +27839,7 @@
         <v>2.75</v>
       </c>
       <c r="G940" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H940" t="s">
         <v>9</v>
@@ -27865,7 +27865,7 @@
         <v>2.75</v>
       </c>
       <c r="G941" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H941" t="s">
         <v>9</v>
@@ -27891,7 +27891,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G942" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H942" t="s">
         <v>9</v>
@@ -27917,7 +27917,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G943" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H943" t="s">
         <v>9</v>
@@ -27943,7 +27943,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G944" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H944" t="s">
         <v>9</v>
@@ -27969,7 +27969,7 @@
         <v>2.75</v>
       </c>
       <c r="G945" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H945" t="s">
         <v>9</v>
@@ -27995,7 +27995,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G946" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H946" t="s">
         <v>9</v>
@@ -28021,7 +28021,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G947" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H947" t="s">
         <v>9</v>
@@ -28047,7 +28047,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G948" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H948" t="s">
         <v>9</v>
@@ -28073,7 +28073,7 @@
         <v>2.75</v>
       </c>
       <c r="G949" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H949" t="s">
         <v>9</v>
@@ -28099,7 +28099,7 @@
         <v>2.75</v>
       </c>
       <c r="G950" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H950" t="s">
         <v>9</v>
@@ -28125,7 +28125,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G951" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H951" t="s">
         <v>9</v>
@@ -28151,7 +28151,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G952" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H952" t="s">
         <v>9</v>
@@ -28177,7 +28177,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G953" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H953" t="s">
         <v>9</v>
@@ -28203,7 +28203,7 @@
         <v>2.75</v>
       </c>
       <c r="G954" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H954" t="s">
         <v>9</v>
@@ -28229,7 +28229,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G955" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H955" t="s">
         <v>9</v>
@@ -28255,7 +28255,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G956" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H956" t="s">
         <v>9</v>
@@ -28281,7 +28281,7 @@
         <v>2.75</v>
       </c>
       <c r="G957" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H957" t="s">
         <v>9</v>
@@ -28307,7 +28307,7 @@
         <v>2.75</v>
       </c>
       <c r="G958" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H958" t="s">
         <v>9</v>
@@ -28333,7 +28333,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G959" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H959" t="s">
         <v>9</v>
@@ -28359,7 +28359,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G960" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H960" t="s">
         <v>9</v>
@@ -28385,7 +28385,7 @@
         <v>2.75</v>
       </c>
       <c r="G961" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H961" t="s">
         <v>9</v>
@@ -28411,7 +28411,7 @@
         <v>2.75</v>
       </c>
       <c r="G962" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H962" t="s">
         <v>9</v>
@@ -28437,7 +28437,7 @@
         <v>2.75</v>
       </c>
       <c r="G963" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H963" t="s">
         <v>9</v>
@@ -28463,7 +28463,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G964" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H964" t="s">
         <v>9</v>
@@ -28489,7 +28489,7 @@
         <v>2.75</v>
       </c>
       <c r="G965" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H965" t="s">
         <v>9</v>
@@ -28515,7 +28515,7 @@
         <v>2.75</v>
       </c>
       <c r="G966" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H966" t="s">
         <v>9</v>
@@ -28541,7 +28541,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G967" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H967" t="s">
         <v>9</v>
@@ -28567,7 +28567,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G968" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H968" t="s">
         <v>9</v>
@@ -28593,7 +28593,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G969" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H969" t="s">
         <v>9</v>
@@ -28619,7 +28619,7 @@
         <v>2.75</v>
       </c>
       <c r="G970" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H970" t="s">
         <v>9</v>
@@ -28645,7 +28645,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G971" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H971" t="s">
         <v>9</v>
@@ -28671,7 +28671,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G972" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H972" t="s">
         <v>9</v>
@@ -28697,7 +28697,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G973" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H973" t="s">
         <v>9</v>
@@ -28723,7 +28723,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G974" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H974" t="s">
         <v>9</v>
@@ -28749,7 +28749,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G975" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H975" t="s">
         <v>9</v>
@@ -28775,7 +28775,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G976" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H976" t="s">
         <v>9</v>
@@ -28801,7 +28801,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G977" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H977" t="s">
         <v>9</v>
@@ -28827,7 +28827,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G978" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H978" t="s">
         <v>9</v>
@@ -28853,7 +28853,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G979" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H979" t="s">
         <v>9</v>
@@ -28879,7 +28879,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G980" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H980" t="s">
         <v>9</v>
@@ -28905,7 +28905,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G981" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H981" t="s">
         <v>9</v>
@@ -28931,7 +28931,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G982" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H982" t="s">
         <v>9</v>
@@ -28957,7 +28957,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G983" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H983" t="s">
         <v>9</v>
@@ -28983,7 +28983,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G984" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H984" t="s">
         <v>9</v>
@@ -29009,7 +29009,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G985" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H985" t="s">
         <v>9</v>
@@ -29035,7 +29035,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G986" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H986" t="s">
         <v>9</v>
@@ -29061,7 +29061,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G987" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H987" t="s">
         <v>9</v>
@@ -29087,7 +29087,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G988" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H988" t="s">
         <v>9</v>
@@ -29113,7 +29113,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G989" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H989" t="s">
         <v>9</v>
@@ -29139,7 +29139,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G990" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H990" t="s">
         <v>9</v>
@@ -29165,7 +29165,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G991" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H991" t="s">
         <v>9</v>
@@ -29191,7 +29191,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G992" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H992" t="s">
         <v>9</v>
@@ -29217,7 +29217,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G993" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H993" t="s">
         <v>9</v>
@@ -29243,7 +29243,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G994" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -29269,7 +29269,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G995" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H995" t="s">
         <v>9</v>
@@ -29295,7 +29295,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G996" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H996" t="s">
         <v>9</v>
@@ -29321,7 +29321,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G997" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H997" t="s">
         <v>9</v>
@@ -29347,7 +29347,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G998" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H998" t="s">
         <v>9</v>
@@ -29373,7 +29373,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G999" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H999" t="s">
         <v>9</v>
@@ -29399,7 +29399,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1000" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1000" t="s">
         <v>9</v>
@@ -29425,7 +29425,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1001" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1001" t="s">
         <v>9</v>
@@ -29451,7 +29451,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1002" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1002" t="s">
         <v>9</v>
@@ -29477,7 +29477,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1003" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1003" t="s">
         <v>9</v>
@@ -29503,7 +29503,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1004" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1004" t="s">
         <v>9</v>
@@ -29529,7 +29529,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1005" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -29555,7 +29555,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1006" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1006" t="s">
         <v>9</v>
@@ -29581,7 +29581,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1007" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1007" t="s">
         <v>9</v>
@@ -29607,7 +29607,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1008" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1008" t="s">
         <v>9</v>
@@ -29633,7 +29633,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1009" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -29659,7 +29659,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1010" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1010" t="s">
         <v>9</v>
@@ -29685,7 +29685,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1011" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1011" t="s">
         <v>9</v>
@@ -29711,7 +29711,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1012" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1012" t="s">
         <v>9</v>
@@ -29737,7 +29737,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1013" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1013" t="s">
         <v>9</v>
@@ -29763,7 +29763,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1014" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1014" t="s">
         <v>9</v>
@@ -29789,7 +29789,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G1015" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -29815,7 +29815,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1016" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1016" t="s">
         <v>9</v>
@@ -29841,7 +29841,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1017" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1017" t="s">
         <v>9</v>
@@ -29867,7 +29867,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1018" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1018" t="s">
         <v>9</v>
@@ -29893,7 +29893,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1019" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H1019" t="s">
         <v>9</v>
@@ -29919,7 +29919,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1020" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1020" t="s">
         <v>9</v>
@@ -29945,7 +29945,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1021" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H1021" t="s">
         <v>9</v>
@@ -29971,7 +29971,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1022" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1022" t="s">
         <v>9</v>
@@ -29997,7 +29997,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1023" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H1023" t="s">
         <v>9</v>
@@ -30023,7 +30023,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1024" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1024" t="s">
         <v>9</v>
@@ -30049,7 +30049,7 @@
         <v>3</v>
       </c>
       <c r="G1025" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1025" t="s">
         <v>9</v>
@@ -30075,7 +30075,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1026" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1026" t="s">
         <v>9</v>
@@ -30101,7 +30101,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1027" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H1027" t="s">
         <v>9</v>
@@ -30127,7 +30127,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G1028" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H1028" t="s">
         <v>9</v>
@@ -30153,7 +30153,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1029" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -30179,7 +30179,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1030" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1030" t="s">
         <v>9</v>
@@ -30205,7 +30205,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1031" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -30231,7 +30231,7 @@
         <v>3</v>
       </c>
       <c r="G1032" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1032" t="s">
         <v>9</v>
@@ -30257,7 +30257,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1033" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H1033" t="s">
         <v>9</v>
@@ -30283,7 +30283,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1034" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1034" t="s">
         <v>9</v>
@@ -30309,7 +30309,7 @@
         <v>3</v>
       </c>
       <c r="G1035" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1035" t="s">
         <v>9</v>
@@ -30335,7 +30335,7 @@
         <v>3</v>
       </c>
       <c r="G1036" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1036" t="s">
         <v>9</v>
@@ -30361,7 +30361,7 @@
         <v>3</v>
       </c>
       <c r="G1037" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1037" t="s">
         <v>9</v>
@@ -30387,7 +30387,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1038" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1038" t="s">
         <v>9</v>
@@ -30413,7 +30413,7 @@
         <v>3</v>
       </c>
       <c r="G1039" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -30439,7 +30439,7 @@
         <v>3</v>
       </c>
       <c r="G1040" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1040" t="s">
         <v>9</v>
@@ -30465,7 +30465,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1041" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H1041" t="s">
         <v>9</v>
@@ -30491,7 +30491,7 @@
         <v>3</v>
       </c>
       <c r="G1042" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1042" t="s">
         <v>9</v>
@@ -30517,7 +30517,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1043" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H1043" t="s">
         <v>9</v>
@@ -30543,7 +30543,7 @@
         <v>3</v>
       </c>
       <c r="G1044" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1044" t="s">
         <v>9</v>
@@ -30569,7 +30569,7 @@
         <v>3</v>
       </c>
       <c r="G1045" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1045" t="s">
         <v>9</v>
@@ -30595,7 +30595,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1046" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H1046" t="s">
         <v>9</v>
@@ -30621,7 +30621,7 @@
         <v>3</v>
       </c>
       <c r="G1047" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H1047" t="s">
         <v>9</v>
@@ -30647,7 +30647,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1048" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H1048" t="s">
         <v>9</v>
@@ -30673,7 +30673,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G1049" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H1049" t="s">
         <v>9</v>
@@ -30699,7 +30699,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1050" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1050" t="s">
         <v>9</v>
@@ -30725,7 +30725,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1051" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1051" t="s">
         <v>9</v>
@@ -30751,7 +30751,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1052" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H1052" t="s">
         <v>9</v>
@@ -30777,7 +30777,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1053" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H1053" t="s">
         <v>9</v>
@@ -30803,7 +30803,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G1054" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H1054" t="s">
         <v>9</v>
@@ -30829,7 +30829,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1055" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H1055" t="s">
         <v>9</v>
@@ -30855,7 +30855,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1056" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H1056" t="s">
         <v>9</v>
@@ -30881,7 +30881,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1057" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H1057" t="s">
         <v>9</v>
@@ -30907,7 +30907,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1058" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1058" t="s">
         <v>9</v>
@@ -30933,7 +30933,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1059" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H1059" t="s">
         <v>9</v>
@@ -30959,7 +30959,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1060" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H1060" t="s">
         <v>9</v>
@@ -30985,7 +30985,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1061" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1061" t="s">
         <v>9</v>
@@ -31011,7 +31011,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1062" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1062" t="s">
         <v>9</v>
@@ -31037,7 +31037,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1063" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1063" t="s">
         <v>9</v>
@@ -31063,7 +31063,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1064" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1064" t="s">
         <v>9</v>
@@ -31089,7 +31089,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1065" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H1065" t="s">
         <v>9</v>
@@ -31115,7 +31115,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1066" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H1066" t="s">
         <v>9</v>
@@ -31141,7 +31141,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1067" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1067" t="s">
         <v>9</v>
@@ -31167,7 +31167,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1068" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1068" t="s">
         <v>9</v>
@@ -31193,7 +31193,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1069" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H1069" t="s">
         <v>9</v>
@@ -31219,7 +31219,7 @@
         <v>1.99500000476837</v>
       </c>
       <c r="G1070" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H1070" t="s">
         <v>9</v>
@@ -31245,7 +31245,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1071" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H1071" t="s">
         <v>9</v>
@@ -31271,7 +31271,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1072" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H1072" t="s">
         <v>9</v>
@@ -31297,7 +31297,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1073" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1073" t="s">
         <v>9</v>
@@ -31323,7 +31323,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1074" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H1074" t="s">
         <v>9</v>
@@ -31349,7 +31349,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1075" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H1075" t="s">
         <v>9</v>
@@ -31375,7 +31375,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1076" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1076" t="s">
         <v>9</v>
@@ -31401,7 +31401,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1077" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H1077" t="s">
         <v>9</v>
@@ -31427,7 +31427,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1078" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1078" t="s">
         <v>9</v>
@@ -31453,7 +31453,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1079" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1079" t="s">
         <v>9</v>
@@ -31479,7 +31479,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1080" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1080" t="s">
         <v>9</v>
@@ -31505,7 +31505,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1081" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1081" t="s">
         <v>9</v>
@@ -31531,7 +31531,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1082" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H1082" t="s">
         <v>9</v>
@@ -31557,7 +31557,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1083" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1083" t="s">
         <v>9</v>
@@ -31583,7 +31583,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1084" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1084" t="s">
         <v>9</v>
@@ -31635,7 +31635,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1086" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1086" t="s">
         <v>9</v>
@@ -31661,7 +31661,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1087" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1087" t="s">
         <v>9</v>
@@ -31687,7 +31687,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1088" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1088" t="s">
         <v>9</v>
@@ -31713,7 +31713,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1089" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1089" t="s">
         <v>9</v>
@@ -31739,7 +31739,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1090" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1090" t="s">
         <v>9</v>
@@ -31765,7 +31765,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1091" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1091" t="s">
         <v>9</v>
@@ -31791,7 +31791,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1092" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1092" t="s">
         <v>9</v>
@@ -31817,7 +31817,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1093" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1093" t="s">
         <v>9</v>
@@ -31843,7 +31843,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1094" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1094" t="s">
         <v>9</v>
@@ -31869,7 +31869,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1095" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1095" t="s">
         <v>9</v>
@@ -31895,7 +31895,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1096" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1096" t="s">
         <v>9</v>
@@ -31921,7 +31921,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1097" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1097" t="s">
         <v>9</v>
@@ -31947,7 +31947,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1098" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H1098" t="s">
         <v>9</v>
@@ -31973,7 +31973,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1099" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1099" t="s">
         <v>9</v>
@@ -31999,7 +31999,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1100" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1100" t="s">
         <v>9</v>
@@ -32025,7 +32025,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1101" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1101" t="s">
         <v>9</v>
@@ -32051,7 +32051,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1102" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1102" t="s">
         <v>9</v>
@@ -32077,7 +32077,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1103" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1103" t="s">
         <v>9</v>
@@ -32103,7 +32103,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1104" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H1104" t="s">
         <v>9</v>
@@ -32129,7 +32129,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1105" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H1105" t="s">
         <v>9</v>
@@ -32155,7 +32155,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1106" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1106" t="s">
         <v>9</v>
@@ -32181,7 +32181,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1107" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1107" t="s">
         <v>9</v>
@@ -32207,7 +32207,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1108" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H1108" t="s">
         <v>9</v>
@@ -32233,7 +32233,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1109" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1109" t="s">
         <v>9</v>
@@ -32259,7 +32259,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1110" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H1110" t="s">
         <v>9</v>
@@ -32285,7 +32285,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1111" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H1111" t="s">
         <v>9</v>
@@ -32311,7 +32311,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1112" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1112" t="s">
         <v>9</v>
@@ -32337,7 +32337,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1113" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H1113" t="s">
         <v>9</v>
@@ -32363,7 +32363,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1114" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H1114" t="s">
         <v>9</v>
@@ -32389,7 +32389,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1115" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H1115" t="s">
         <v>9</v>
@@ -32415,7 +32415,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1116" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H1116" t="s">
         <v>9</v>
@@ -32441,7 +32441,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1117" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1117" t="s">
         <v>9</v>
@@ -32467,7 +32467,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1118" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H1118" t="s">
         <v>9</v>
@@ -32493,7 +32493,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H1119" t="s">
         <v>9</v>
@@ -32519,7 +32519,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1120" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H1120" t="s">
         <v>9</v>
@@ -32545,7 +32545,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1121" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H1121" t="s">
         <v>9</v>
@@ -32571,7 +32571,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1122" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1122" t="s">
         <v>9</v>
@@ -32649,7 +32649,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1125" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1125" t="s">
         <v>9</v>
@@ -32675,7 +32675,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1126" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1126" t="s">
         <v>9</v>
@@ -32727,7 +32727,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1128" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1128" t="s">
         <v>9</v>
@@ -32753,7 +32753,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1129" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1129" t="s">
         <v>9</v>
@@ -32779,7 +32779,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1130" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1130" t="s">
         <v>9</v>
@@ -32831,7 +32831,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1132" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1132" t="s">
         <v>9</v>
@@ -32857,7 +32857,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1133" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1133" t="s">
         <v>9</v>
@@ -32883,7 +32883,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1134" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1134" t="s">
         <v>9</v>
@@ -32909,7 +32909,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1135" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1135" t="s">
         <v>9</v>
@@ -32935,7 +32935,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1136" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="H1136" t="s">
         <v>9</v>
@@ -32961,7 +32961,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1137" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1137" t="s">
         <v>9</v>
@@ -32987,7 +32987,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1138" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1138" t="s">
         <v>9</v>
@@ -33013,7 +33013,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1139" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1139" t="s">
         <v>9</v>
@@ -33039,7 +33039,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1140" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1140" t="s">
         <v>9</v>
@@ -33065,7 +33065,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1141" t="s">
-        <v>409</v>
+        <v>381</v>
       </c>
       <c r="H1141" t="s">
         <v>9</v>
@@ -33091,7 +33091,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1142" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1142" t="s">
         <v>9</v>
@@ -33117,7 +33117,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1143" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H1143" t="s">
         <v>9</v>
@@ -33143,7 +33143,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1144" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1144" t="s">
         <v>9</v>
@@ -33169,7 +33169,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1145" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1145" t="s">
         <v>9</v>
@@ -33195,7 +33195,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1146" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1146" t="s">
         <v>9</v>
@@ -33221,7 +33221,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1147" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1147" t="s">
         <v>9</v>
@@ -33247,7 +33247,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1148" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1148" t="s">
         <v>9</v>
@@ -33273,7 +33273,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1149" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1149" t="s">
         <v>9</v>
@@ -33299,7 +33299,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1150" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1150" t="s">
         <v>9</v>
@@ -33351,7 +33351,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1152" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1152" t="s">
         <v>9</v>
@@ -33429,7 +33429,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1155" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1155" t="s">
         <v>9</v>
@@ -33481,7 +33481,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1157" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1157" t="s">
         <v>9</v>
@@ -33507,7 +33507,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1158" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1158" t="s">
         <v>9</v>
@@ -33533,7 +33533,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1159" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1159" t="s">
         <v>9</v>
@@ -33559,7 +33559,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1160" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1160" t="s">
         <v>9</v>
@@ -33585,7 +33585,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1161" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H1161" t="s">
         <v>9</v>
@@ -33611,7 +33611,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1162" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H1162" t="s">
         <v>9</v>
@@ -33637,7 +33637,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1163" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1163" t="s">
         <v>9</v>
@@ -33663,7 +33663,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1164" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1164" t="s">
         <v>9</v>
@@ -33689,7 +33689,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1165" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H1165" t="s">
         <v>9</v>
@@ -33715,7 +33715,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1166" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H1166" t="s">
         <v>9</v>
@@ -33741,7 +33741,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1167" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1167" t="s">
         <v>9</v>
@@ -33767,7 +33767,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1168" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1168" t="s">
         <v>9</v>
@@ -33793,7 +33793,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1169" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1169" t="s">
         <v>9</v>
@@ -33819,7 +33819,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1170" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H1170" t="s">
         <v>9</v>
@@ -33845,7 +33845,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1171" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1171" t="s">
         <v>9</v>
@@ -33871,7 +33871,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1172" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H1172" t="s">
         <v>9</v>
@@ -33897,7 +33897,7 @@
         <v>2.5</v>
       </c>
       <c r="G1173" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1173" t="s">
         <v>9</v>
@@ -33923,7 +33923,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1174" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1174" t="s">
         <v>9</v>
@@ -33949,7 +33949,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1175" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1175" t="s">
         <v>9</v>
@@ -33975,7 +33975,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1176" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1176" t="s">
         <v>9</v>
@@ -34001,7 +34001,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1177" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1177" t="s">
         <v>9</v>
@@ -34027,7 +34027,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1178" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1178" t="s">
         <v>9</v>
@@ -34053,7 +34053,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1179" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H1179" t="s">
         <v>9</v>
@@ -34079,7 +34079,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1180" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1180" t="s">
         <v>9</v>
@@ -34105,7 +34105,7 @@
         <v>2.5</v>
       </c>
       <c r="G1181" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1181" t="s">
         <v>9</v>
@@ -34131,7 +34131,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1182" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H1182" t="s">
         <v>9</v>
@@ -34157,7 +34157,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1183" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1183" t="s">
         <v>9</v>
@@ -34183,7 +34183,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1184" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1184" t="s">
         <v>9</v>
@@ -34209,7 +34209,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1185" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H1185" t="s">
         <v>9</v>
@@ -34261,7 +34261,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1187" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1187" t="s">
         <v>9</v>
@@ -34287,7 +34287,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1188" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H1188" t="s">
         <v>9</v>
@@ -34339,7 +34339,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G1190" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1190" t="s">
         <v>9</v>
@@ -34365,7 +34365,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1191" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H1191" t="s">
         <v>9</v>
@@ -34391,7 +34391,7 @@
         <v>2.5</v>
       </c>
       <c r="G1192" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H1192" t="s">
         <v>9</v>
@@ -34417,7 +34417,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1193" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1193" t="s">
         <v>9</v>
@@ -34443,7 +34443,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1194" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1194" t="s">
         <v>9</v>
@@ -34469,7 +34469,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1195" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H1195" t="s">
         <v>9</v>
@@ -34495,7 +34495,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1196" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H1196" t="s">
         <v>9</v>
@@ -34521,7 +34521,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1197" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H1197" t="s">
         <v>9</v>
@@ -34547,7 +34547,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1198" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H1198" t="s">
         <v>9</v>
@@ -34573,7 +34573,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1199" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H1199" t="s">
         <v>9</v>
@@ -34599,7 +34599,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1200" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1200" t="s">
         <v>9</v>
@@ -34625,7 +34625,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1201" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1201" t="s">
         <v>9</v>
@@ -34651,7 +34651,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1202" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1202" t="s">
         <v>9</v>
@@ -34677,7 +34677,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1203" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H1203" t="s">
         <v>9</v>
@@ -34703,7 +34703,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1204" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1204" t="s">
         <v>9</v>
@@ -34729,7 +34729,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1205" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1205" t="s">
         <v>9</v>
@@ -34755,7 +34755,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1206" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1206" t="s">
         <v>9</v>
@@ -34781,7 +34781,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1207" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1207" t="s">
         <v>9</v>
@@ -34807,7 +34807,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1208" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1208" t="s">
         <v>9</v>
@@ -34833,7 +34833,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1209" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H1209" t="s">
         <v>9</v>
@@ -34859,7 +34859,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1210" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1210" t="s">
         <v>9</v>
@@ -34885,7 +34885,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1211" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1211" t="s">
         <v>9</v>
@@ -34911,7 +34911,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1212" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H1212" t="s">
         <v>9</v>
@@ -34937,7 +34937,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1213" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1213" t="s">
         <v>9</v>
@@ -34963,7 +34963,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1214" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1214" t="s">
         <v>9</v>
@@ -34989,7 +34989,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1215" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1215" t="s">
         <v>9</v>
@@ -35015,7 +35015,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1216" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1216" t="s">
         <v>9</v>
@@ -35041,7 +35041,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1217" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1217" t="s">
         <v>9</v>
@@ -35067,7 +35067,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1218" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1218" t="s">
         <v>9</v>
@@ -35093,7 +35093,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1219" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H1219" t="s">
         <v>9</v>
@@ -35119,7 +35119,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1220" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1220" t="s">
         <v>9</v>
@@ -35145,7 +35145,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1221" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H1221" t="s">
         <v>9</v>
@@ -35171,7 +35171,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1222" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1222" t="s">
         <v>9</v>
@@ -35197,7 +35197,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1223" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1223" t="s">
         <v>9</v>
@@ -35223,7 +35223,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1224" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H1224" t="s">
         <v>9</v>
@@ -35249,7 +35249,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1225" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H1225" t="s">
         <v>9</v>
@@ -35275,7 +35275,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1226" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H1226" t="s">
         <v>9</v>
@@ -35301,7 +35301,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1227" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H1227" t="s">
         <v>9</v>
@@ -35327,7 +35327,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1228" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H1228" t="s">
         <v>9</v>
@@ -35353,7 +35353,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1229" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H1229" t="s">
         <v>9</v>
@@ -35379,7 +35379,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1230" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H1230" t="s">
         <v>9</v>
@@ -35405,7 +35405,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1231" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1231" t="s">
         <v>9</v>
@@ -35431,7 +35431,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1232" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H1232" t="s">
         <v>9</v>
@@ -35457,7 +35457,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1233" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1233" t="s">
         <v>9</v>
@@ -35483,7 +35483,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1234" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H1234" t="s">
         <v>9</v>
@@ -35509,7 +35509,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1235" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1235" t="s">
         <v>9</v>
@@ -35535,7 +35535,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1236" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H1236" t="s">
         <v>9</v>
@@ -35561,7 +35561,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1237" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H1237" t="s">
         <v>9</v>
@@ -35587,7 +35587,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1238" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H1238" t="s">
         <v>9</v>
@@ -35613,7 +35613,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1239" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H1239" t="s">
         <v>9</v>
@@ -35639,7 +35639,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1240" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H1240" t="s">
         <v>9</v>
@@ -35665,7 +35665,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1241" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H1241" t="s">
         <v>9</v>
@@ -35691,7 +35691,7 @@
         <v>2.5</v>
       </c>
       <c r="G1242" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H1242" t="s">
         <v>9</v>
@@ -35717,7 +35717,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1243" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1243" t="s">
         <v>9</v>
@@ -35743,7 +35743,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1244" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H1244" t="s">
         <v>9</v>
@@ -35769,7 +35769,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1245" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H1245" t="s">
         <v>9</v>
@@ -35795,7 +35795,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1246" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H1246" t="s">
         <v>9</v>
@@ -35821,7 +35821,7 @@
         <v>2.75</v>
       </c>
       <c r="G1247" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H1247" t="s">
         <v>9</v>
@@ -35847,7 +35847,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G1248" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H1248" t="s">
         <v>9</v>
@@ -35873,7 +35873,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G1249" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H1249" t="s">
         <v>9</v>
@@ -35899,7 +35899,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G1250" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H1250" t="s">
         <v>9</v>
@@ -35925,7 +35925,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1251" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H1251" t="s">
         <v>9</v>
@@ -35951,7 +35951,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1252" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1252" t="s">
         <v>9</v>
@@ -35977,7 +35977,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1253" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H1253" t="s">
         <v>9</v>
@@ -36003,7 +36003,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1254" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1254" t="s">
         <v>9</v>
@@ -36029,7 +36029,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1255" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H1255" t="s">
         <v>9</v>
@@ -36055,7 +36055,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1256" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1256" t="s">
         <v>9</v>
@@ -36081,7 +36081,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G1257" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H1257" t="s">
         <v>9</v>
@@ -36107,7 +36107,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G1258" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H1258" t="s">
         <v>9</v>
@@ -36133,7 +36133,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1259" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1259" t="s">
         <v>9</v>
@@ -36159,7 +36159,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1260" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1260" t="s">
         <v>9</v>
@@ -36185,7 +36185,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1261" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H1261" t="s">
         <v>9</v>
@@ -36211,7 +36211,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G1262" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H1262" t="s">
         <v>9</v>
@@ -36237,7 +36237,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G1263" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H1263" t="s">
         <v>9</v>
@@ -36263,7 +36263,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G1264" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H1264" t="s">
         <v>9</v>
@@ -36289,7 +36289,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1265" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H1265" t="s">
         <v>9</v>
@@ -36315,7 +36315,7 @@
         <v>3</v>
       </c>
       <c r="G1266" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H1266" t="s">
         <v>9</v>
@@ -36341,7 +36341,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1